--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E968"/>
+  <dimension ref="A1:E995"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22416,6 +22416,629 @@
         </is>
       </c>
     </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>0396aa9f-a349-49d0-a449-291447cbe024</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>2026-02-23T20:16:29.147Z</t>
+        </is>
+      </c>
+      <c r="D969" t="n">
+        <v>40</v>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>Warr</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>30fda260-c593-4a37-b326-bca4f6637545</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>2026-02-23T20:18:31.711Z</t>
+        </is>
+      </c>
+      <c r="D970" t="n">
+        <v>15</v>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>bd9020db-861a-45b8-bc2b-48f8e9062c10</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>2026-02-23T20:35:18.678Z</t>
+        </is>
+      </c>
+      <c r="D971" t="n">
+        <v>36</v>
+      </c>
+      <c r="E971" t="inlineStr"/>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>6536f4dc-7be9-46bc-aac3-336a1dd92a11</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>2026-03-03T03:23:42.276Z</t>
+        </is>
+      </c>
+      <c r="D972" t="n">
+        <v>432</v>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>01baef5b-d1b9-4a01-af54-24003eb0ed5f</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>2026-03-06T17:13:13.749Z</t>
+        </is>
+      </c>
+      <c r="D973" t="n">
+        <v>576</v>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>suspect ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2b9e0df3-000c-4b4f-9f5d-57e8d01b648e</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>2026-03-06T20:55:14.300Z</t>
+        </is>
+      </c>
+      <c r="D974" t="n">
+        <v>432</v>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>suspect ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>b2b6a04e-7c65-4b86-b91b-6dcefa2d98fd</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>2026-03-09T16:24:34.689Z</t>
+        </is>
+      </c>
+      <c r="D975" t="n">
+        <v>3</v>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>207 sus</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>a6468f2c-d570-44b4-ae96-c5daa5d8e041</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>2026-03-09T16:25:08.759Z</t>
+        </is>
+      </c>
+      <c r="D976" t="n">
+        <v>532</v>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>9cc8ba08-e3bf-4a61-9d24-ad0c64eaab77</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>2026-03-14T21:39:51.037Z</t>
+        </is>
+      </c>
+      <c r="D977" t="n">
+        <v>575</v>
+      </c>
+      <c r="E977" t="inlineStr"/>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>9be097ae-3bd6-4ebb-a23d-47a22e9f99c3</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>2026-03-18T15:54:28.964Z</t>
+        </is>
+      </c>
+      <c r="D978" t="n">
+        <v>531</v>
+      </c>
+      <c r="E978" t="inlineStr"/>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>9ebe0f3e-26c3-4d0a-8c74-d0542f0c9d1a</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>2026-03-21T03:07:13.713Z</t>
+        </is>
+      </c>
+      <c r="D979" t="n">
+        <v>3</v>
+      </c>
+      <c r="E979" t="inlineStr"/>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>9bd5dc2c-0f76-4c97-8821-fec078aae004</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>2026-03-21T03:20:45.976Z</t>
+        </is>
+      </c>
+      <c r="D980" t="n">
+        <v>575</v>
+      </c>
+      <c r="E980" t="inlineStr"/>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>733664b8-e67a-4506-b29a-51670b15e11c</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>2026-03-22T00:02:46.672Z</t>
+        </is>
+      </c>
+      <c r="D981" t="n">
+        <v>3</v>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>dv</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>d1035c96-d78e-42f9-8351-4cc93d0e8abe</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>2026-03-22T06:45:41.304Z</t>
+        </is>
+      </c>
+      <c r="D982" t="n">
+        <v>575</v>
+      </c>
+      <c r="E982" t="inlineStr"/>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>ca677a49-4288-443e-b7b0-b382d7b2c22a</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>2026-03-22T12:03:29.854Z</t>
+        </is>
+      </c>
+      <c r="D983" t="n">
+        <v>3</v>
+      </c>
+      <c r="E983" t="inlineStr"/>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>1716bbc5-4bd2-4886-bff7-04e3f06f1ef9</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>2026-03-22T18:14:29.988Z</t>
+        </is>
+      </c>
+      <c r="D984" t="n">
+        <v>3</v>
+      </c>
+      <c r="E984" t="inlineStr"/>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>c3323135-068e-48cf-91a3-df2addcd7a0c</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>2026-03-22T18:14:47.120Z</t>
+        </is>
+      </c>
+      <c r="D985" t="n">
+        <v>3</v>
+      </c>
+      <c r="E985" t="inlineStr"/>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>e4de9937-800e-4b4c-81df-2760a9c50188</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>2026-03-22T18:16:17.899Z</t>
+        </is>
+      </c>
+      <c r="D986" t="n">
+        <v>2</v>
+      </c>
+      <c r="E986" t="inlineStr"/>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>80cbf115-1489-4289-988d-ff21d0f273d3</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>2026-03-22T18:24:04.275Z</t>
+        </is>
+      </c>
+      <c r="D987" t="n">
+        <v>531</v>
+      </c>
+      <c r="E987" t="inlineStr"/>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>7795f858-7f5d-4f43-a7d8-e3f0b711d611</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>2026-03-22T18:53:40.177Z</t>
+        </is>
+      </c>
+      <c r="D988" t="n">
+        <v>531</v>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2efcde64-75e8-4038-990e-33d19917ad5e</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>2026-03-22T19:04:39.292Z</t>
+        </is>
+      </c>
+      <c r="D989" t="n">
+        <v>531</v>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>e1ecaee7-c13e-403e-96ca-414eb8fe4fb2</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>2026-03-22T21:14:22.253Z</t>
+        </is>
+      </c>
+      <c r="D990" t="n">
+        <v>531</v>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>b9e10df6-3d69-4156-aa30-31cee576d7ef</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>2026-03-22T21:41:03.079Z</t>
+        </is>
+      </c>
+      <c r="D991" t="n">
+        <v>531</v>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>Drug Investigations</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>9f9458d0-e56b-4870-807a-38d8810d878a</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>2026-03-22T23:06:44.511Z</t>
+        </is>
+      </c>
+      <c r="D992" t="n">
+        <v>3</v>
+      </c>
+      <c r="E992" t="inlineStr"/>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>1dcd11fd-ac45-47ca-85a7-18bab7bf64ba</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>2026-03-22T23:11:35.917Z</t>
+        </is>
+      </c>
+      <c r="D993" t="n">
+        <v>35</v>
+      </c>
+      <c r="E993" t="inlineStr"/>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>e7514d08-4285-4502-9a37-8ae95e856e78</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>2026-03-22T23:21:35.476Z</t>
+        </is>
+      </c>
+      <c r="D994" t="n">
+        <v>3</v>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>10851</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>5e658e79-2224-49cb-884b-1e289d78c882</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>2026-03-22T23:22:12.019Z</t>
+        </is>
+      </c>
+      <c r="D995" t="n">
+        <v>3</v>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E995"/>
+  <dimension ref="A1:E1046"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23039,6 +23039,1165 @@
         </is>
       </c>
     </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>263c5cc4-eb68-47aa-a991-f8195ea5ab88</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>2026-02-23T21:11:00.438Z</t>
+        </is>
+      </c>
+      <c r="D996" t="n">
+        <v>40</v>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>Warr</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>b44d85df-fa0b-4fe7-b7b9-8cb7f5821c55</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>2026-02-24T18:50:18.491Z</t>
+        </is>
+      </c>
+      <c r="D997" t="n">
+        <v>1</v>
+      </c>
+      <c r="E997" t="inlineStr"/>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>d4f08b8d-b067-4555-a8db-cefd673383cf</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>2026-03-10T16:10:47.132Z</t>
+        </is>
+      </c>
+      <c r="D998" t="n">
+        <v>3</v>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>82bd2958-77d8-4428-a8d4-fc2b7344926d</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>2026-03-14T02:53:49.357Z</t>
+        </is>
+      </c>
+      <c r="D999" t="n">
+        <v>3</v>
+      </c>
+      <c r="E999" t="inlineStr"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>f0af8cd0-a3cb-4df1-9535-30653ba6806d</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>2026-03-14T21:29:32.442Z</t>
+        </is>
+      </c>
+      <c r="D1000" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1000" t="inlineStr"/>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>75ca9b71-98ae-4c8d-af39-2ad7140cd2d6</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>2026-03-21T04:56:34.653Z</t>
+        </is>
+      </c>
+      <c r="D1001" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1001" t="inlineStr"/>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>bab9d086-204d-47ae-bad6-4812a2a2a3b7</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>2026-03-23T01:04:48.768Z</t>
+        </is>
+      </c>
+      <c r="D1002" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1002" t="inlineStr"/>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>3733fabe-8c96-446e-b4db-aa3a9715cf50</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>2026-03-23T04:45:15.156Z</t>
+        </is>
+      </c>
+      <c r="D1003" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>3884f823-5526-4e80-a6e4-7de5074bc9d2</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>2026-03-23T06:41:18.287Z</t>
+        </is>
+      </c>
+      <c r="D1004" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1004" t="inlineStr"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>7db6f7bd-44db-4283-bdef-a481ecabd1cc</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>2026-03-23T14:44:45.326Z</t>
+        </is>
+      </c>
+      <c r="D1005" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1005" t="inlineStr"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>560c74fb-7ae1-4b3c-b6ad-07214a6d4d97</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>2026-03-23T16:21:14.323Z</t>
+        </is>
+      </c>
+      <c r="D1006" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1006" t="inlineStr"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>027f84b5-3914-4636-b579-5f6b83777fc7</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>2026-03-23T20:11:52.030Z</t>
+        </is>
+      </c>
+      <c r="D1007" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1007" t="inlineStr"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>e30947ea-e75c-4d84-9f3d-95ccbdc7ae5e</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>2026-03-23T22:33:44.093Z</t>
+        </is>
+      </c>
+      <c r="D1008" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1008" t="inlineStr"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>47a89f63-5d9a-4490-b0e4-a2ab8fa41f5e</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>2026-03-23T23:44:10.788Z</t>
+        </is>
+      </c>
+      <c r="D1009" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1009" t="inlineStr"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2598b917-95c3-4705-9e2e-7d70a44445df</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:53:29.516Z</t>
+        </is>
+      </c>
+      <c r="D1010" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1010" t="inlineStr"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>73722c23-2750-46f4-9b46-4f79b9118550</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>2026-03-04T17:40:10.834Z</t>
+        </is>
+      </c>
+      <c r="D1011" t="n">
+        <v>471</v>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>Drug Intel</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>547e0f94-b9af-42ce-8b06-00c99cdf2ff5</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>2026-03-19T04:49:28.847Z</t>
+        </is>
+      </c>
+      <c r="D1012" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1012" t="inlineStr"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2c94c220-f32f-425a-9326-5cdc008e681f</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>2026-03-24T00:04:38.807Z</t>
+        </is>
+      </c>
+      <c r="D1013" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1013" t="inlineStr"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>4b52bc4a-920a-43ce-9c98-438714e92dde</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>2026-03-24T00:18:11.651Z</t>
+        </is>
+      </c>
+      <c r="D1014" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>SUSPECT VEHICLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>9ffd729e-1d9d-4c14-8238-7c187b9e9cce</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>2026-03-24T00:20:49.852Z</t>
+        </is>
+      </c>
+      <c r="D1015" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1015" t="inlineStr"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>a5d8bcee-7382-4841-a8b7-075778d8e40d</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>2026-03-24T00:28:02.966Z</t>
+        </is>
+      </c>
+      <c r="D1016" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>ROBBERY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>d29c2751-af5c-4ba5-8021-2b9e30104f2e</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>2026-03-24T03:43:15.423Z</t>
+        </is>
+      </c>
+      <c r="D1017" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1017" t="inlineStr"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>e51dd753-4ee9-42c7-929f-9605863a3f99</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:24:53.117Z</t>
+        </is>
+      </c>
+      <c r="D1018" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>42a4df16-d0c9-4a51-aeb9-ad6f59d14b63</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:27:39.932Z</t>
+        </is>
+      </c>
+      <c r="D1019" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1019" t="inlineStr"/>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>007a9d62-0a3b-4fbb-ac88-687cbb0c163f</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>2026-03-24T06:02:16.394Z</t>
+        </is>
+      </c>
+      <c r="D1020" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>ea7ca7e5-a594-41d9-a172-14470eafe8fc</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>2026-03-24T08:03:06.230Z</t>
+        </is>
+      </c>
+      <c r="D1021" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>243d suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>867ec029-372a-425c-8c03-9097d4a4a94b</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>2026-03-24T08:06:52.070Z</t>
+        </is>
+      </c>
+      <c r="D1022" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1022" t="inlineStr"/>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>50c9df05-053a-4d4b-923a-0327ad177168</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>2026-03-24T08:24:51.681Z</t>
+        </is>
+      </c>
+      <c r="D1023" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>981393ee-dba7-4a53-aa63-9eef0c0c8a7e</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>2026-03-24T09:32:55.286Z</t>
+        </is>
+      </c>
+      <c r="D1024" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>482acac6-c871-4aec-9e38-22853271bee2</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>2026-03-24T09:33:01.571Z</t>
+        </is>
+      </c>
+      <c r="D1025" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>243d suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>bd1ee308-8805-4e35-b0eb-be314edc882f</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>2026-03-24T14:06:59.394Z</t>
+        </is>
+      </c>
+      <c r="D1026" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>suspect ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>5a9565d6-5b85-4b6e-9106-9769e06974da</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>2026-03-24T15:07:36.378Z</t>
+        </is>
+      </c>
+      <c r="D1027" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>victim's vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>4bcccd18-4181-41c0-a09b-954af6e27916</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>2026-03-24T16:42:04.892Z</t>
+        </is>
+      </c>
+      <c r="D1028" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2a0a9354-ea42-4327-bfd7-207992943e9a</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>2026-03-24T16:53:07.822Z</t>
+        </is>
+      </c>
+      <c r="D1029" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1029" t="inlineStr"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>7516e1d1-9ea4-49f4-af5f-86c3d3c65efc</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>2026-03-24T17:05:50.612Z</t>
+        </is>
+      </c>
+      <c r="D1030" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>4c06acaa-598d-447d-ade3-0b95345ec000</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>2026-03-24T17:09:16.695Z</t>
+        </is>
+      </c>
+      <c r="D1031" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1031" t="inlineStr"/>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>4c217ec1-fd5f-45e8-8fb7-b07f125394af</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>2026-03-24T17:48:29.725Z</t>
+        </is>
+      </c>
+      <c r="D1032" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1032" t="inlineStr"/>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>67765334-5019-4d9b-a711-b7483c4df5ca</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>2026-03-24T17:50:04.945Z</t>
+        </is>
+      </c>
+      <c r="D1033" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1033" t="inlineStr"/>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>a64c55d1-431e-463e-9332-77c383c6890b</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>2026-03-24T17:52:19.770Z</t>
+        </is>
+      </c>
+      <c r="D1034" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>ATL suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>998e29ce-4498-4c14-8a54-e7afcd1dca48</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>2026-03-24T18:07:32.615Z</t>
+        </is>
+      </c>
+      <c r="D1035" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>9b4a4f39-f2c4-4efe-97ce-b2deb319842c</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>2026-03-24T18:07:35.306Z</t>
+        </is>
+      </c>
+      <c r="D1036" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1036" t="inlineStr"/>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>7d18d95a-08af-4e96-a8d0-d98140b25bb5</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>2026-03-24T18:54:29.525Z</t>
+        </is>
+      </c>
+      <c r="D1037" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1037" t="inlineStr"/>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>a43ac52a-ebf1-4977-a661-0df0154db89f</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>2026-03-24T18:58:58.122Z</t>
+        </is>
+      </c>
+      <c r="D1038" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>suspect ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>687e542f-09b7-4b56-8d85-9eaea7fdc50e</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:02:19.098Z</t>
+        </is>
+      </c>
+      <c r="D1039" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>suspect ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>8660c8e4-b132-4bae-b390-f89ab18edb46</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:36:51.120Z</t>
+        </is>
+      </c>
+      <c r="D1040" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1040" t="inlineStr"/>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>f8266f63-a658-4958-a947-e85ea96bf462</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>2026-03-24T20:02:01.686Z</t>
+        </is>
+      </c>
+      <c r="D1041" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>cb57f586-1197-48f8-90ee-96be9264b034</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>2026-03-24T20:02:55.891Z</t>
+        </is>
+      </c>
+      <c r="D1042" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1042" t="inlineStr"/>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>bd5887fd-c67c-4a4b-9b0b-25dc45eae257</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>2026-03-24T20:54:57.540Z</t>
+        </is>
+      </c>
+      <c r="D1043" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1043" t="inlineStr"/>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2c109665-a6e7-4215-8b82-5f1ddb9c1334</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>2026-03-24T21:14:57.258Z</t>
+        </is>
+      </c>
+      <c r="D1044" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1044" t="inlineStr"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>bb15af15-2e33-45cb-a70c-1a71883e9976</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>2026-03-24T22:31:20.423Z</t>
+        </is>
+      </c>
+      <c r="D1045" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>4a56ee55-d540-41b4-8994-f1438e3e44a6</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>2026-03-24T23:03:06.928Z</t>
+        </is>
+      </c>
+      <c r="D1046" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1046" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1046"/>
+  <dimension ref="A1:E1071"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24198,6 +24198,591 @@
       </c>
       <c r="E1046" t="inlineStr"/>
     </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>a9e7d67b-da04-4785-9523-566b27d2b641</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>2026-03-09T03:33:50.465Z</t>
+        </is>
+      </c>
+      <c r="D1047" t="n">
+        <v>532</v>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>5ecaf8fd-7537-40d9-ac0f-c20c6dbecf78</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>2026-03-10T23:52:01.211Z</t>
+        </is>
+      </c>
+      <c r="D1048" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>487 pc suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>20e33dc6-18a5-4b3c-bfcd-01f1c6ac14f4</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>2026-03-14T02:51:59.212Z</t>
+        </is>
+      </c>
+      <c r="D1049" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>wanted person</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>73424d8c-b8d3-4a5d-a1de-dc88514c356d</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>2026-03-19T17:30:08.949Z</t>
+        </is>
+      </c>
+      <c r="D1050" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1050" t="inlineStr"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>f95b0c73-29e2-4d57-b353-b3dea72d8e99</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>2026-03-25T00:04:03.256Z</t>
+        </is>
+      </c>
+      <c r="D1051" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>a7c9b459-8000-425c-9a7d-096dca3ed31b</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>2026-03-25T04:15:23.981Z</t>
+        </is>
+      </c>
+      <c r="D1052" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>96d0fff8-676c-4869-ac63-997f39d53c3a</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>2026-03-25T04:18:18.327Z</t>
+        </is>
+      </c>
+      <c r="D1053" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1053" t="inlineStr"/>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>ffefa729-3d01-4678-bf94-5c14a637a27c</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>2026-03-25T04:18:26.745Z</t>
+        </is>
+      </c>
+      <c r="D1054" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>e996136c-a8fd-4804-8cd1-d3839d064105</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>2026-03-25T04:41:50.514Z</t>
+        </is>
+      </c>
+      <c r="D1055" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1055" t="inlineStr"/>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>20e6799a-1eed-4177-b02b-bf01b40b806f</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>2026-03-25T05:04:42.543Z</t>
+        </is>
+      </c>
+      <c r="D1056" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>ef565e3b-fe7f-435d-8fb0-8b8c15e0b737</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>2026-03-25T06:09:33.302Z</t>
+        </is>
+      </c>
+      <c r="D1057" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>ca681421-4b69-4e5e-b8fd-aaea96eb7db6</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>2026-03-25T07:48:30.890Z</t>
+        </is>
+      </c>
+      <c r="D1058" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2f5bd676-704a-421f-9a12-2fda56062ce7</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>2026-03-25T09:01:55.055Z</t>
+        </is>
+      </c>
+      <c r="D1059" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>f0acad80-68c2-45d5-84a7-9717a4b4c01e</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>2026-03-25T14:49:58.814Z</t>
+        </is>
+      </c>
+      <c r="D1060" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1060" t="inlineStr"/>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>1b59f256-2ed5-48d3-b2e8-44ae09dba0a4</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>2026-03-25T14:56:09.299Z</t>
+        </is>
+      </c>
+      <c r="D1061" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>187 PC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>7639302c-471b-4ff7-a098-ad43a541026c</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>2026-03-25T15:00:36.980Z</t>
+        </is>
+      </c>
+      <c r="D1062" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>187 PC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>79f98f18-e4cc-4e53-9a84-cc556340e959</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>2026-03-25T15:29:57.187Z</t>
+        </is>
+      </c>
+      <c r="D1063" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1063" t="inlineStr"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>061e404a-edfb-487c-b87e-d75e3b394d00</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>2026-03-25T17:47:38.423Z</t>
+        </is>
+      </c>
+      <c r="D1064" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1064" t="inlineStr"/>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>cbf52f4b-3536-4348-a53a-154536e1d0d6</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>2026-03-25T18:13:57.860Z</t>
+        </is>
+      </c>
+      <c r="D1065" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>10851 VC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>15658532-ebe8-459e-9067-aface7c78a93</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>2026-03-25T18:26:38.800Z</t>
+        </is>
+      </c>
+      <c r="D1066" t="n">
+        <v>593</v>
+      </c>
+      <c r="E1066" t="inlineStr"/>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>d6431c87-4ecb-4b35-9c00-4192dda29cf4</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>2026-03-25T19:26:29.045Z</t>
+        </is>
+      </c>
+      <c r="D1067" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1067" t="inlineStr"/>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>8ac60a3b-69da-413d-ac1b-33f63825d2c1</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>2026-03-25T20:42:59.512Z</t>
+        </is>
+      </c>
+      <c r="D1068" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1068" t="inlineStr"/>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>281806af-56e1-4ce1-8573-b0d46b53a1e4</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>2026-03-25T22:01:05.100Z</t>
+        </is>
+      </c>
+      <c r="D1069" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2a4cc7ce-f1b8-49b4-87d3-d6fdfe679cdb</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>2026-03-25T22:10:25.417Z</t>
+        </is>
+      </c>
+      <c r="D1070" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1070" t="inlineStr"/>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>5f0773f1-41c2-499a-b769-509c62afd0ec</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>2026-03-25T23:19:57.698Z</t>
+        </is>
+      </c>
+      <c r="D1071" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1071"/>
+  <dimension ref="A1:E1091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24783,6 +24783,462 @@
         </is>
       </c>
     </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>aa0299c8-470c-4b5e-8e43-c96500016f34</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>2026-03-06T17:31:56.523Z</t>
+        </is>
+      </c>
+      <c r="D1072" t="n">
+        <v>576</v>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>suspect ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>a6cb5975-8fb7-4128-8a95-32416651ddd2</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>2026-03-19T17:23:18.631Z</t>
+        </is>
+      </c>
+      <c r="D1073" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1073" t="inlineStr"/>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>cc2cd297-d3d9-434d-87e7-e5c6130ae4d4</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>2026-03-25T23:55:23.323Z</t>
+        </is>
+      </c>
+      <c r="D1074" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>1d6f97b6-860f-4d1a-a471-8e22101e22f5</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>2026-03-26T00:06:12.370Z</t>
+        </is>
+      </c>
+      <c r="D1075" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>187 PC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>352b4833-6864-451a-877f-57a3852bb4fb</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>2026-03-26T00:13:35.294Z</t>
+        </is>
+      </c>
+      <c r="D1076" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>32d055bc-d1a6-40dc-a7ae-76b5c0e6c72d</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>2026-03-26T00:21:24.755Z</t>
+        </is>
+      </c>
+      <c r="D1077" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>ade4bdc9-bbbd-4fcf-abf5-96caaaf1d2bb</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>2026-03-26T05:48:52.078Z</t>
+        </is>
+      </c>
+      <c r="D1078" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>7d10f139-0295-425b-9341-046d68b7a94d</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>2026-03-26T05:54:12.197Z</t>
+        </is>
+      </c>
+      <c r="D1079" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1079" t="inlineStr"/>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2efb216a-f544-421d-832d-59ba740996cf</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>2026-03-26T06:03:56.125Z</t>
+        </is>
+      </c>
+      <c r="D1080" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>d9aea648-89a9-4f1b-b9f0-1502b5761405</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>2026-03-26T14:01:06.794Z</t>
+        </is>
+      </c>
+      <c r="D1081" t="n">
+        <v>891</v>
+      </c>
+      <c r="E1081" t="inlineStr"/>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>fd248853-7186-4f94-87cf-388ce0761d19</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>2026-03-26T16:22:06.340Z</t>
+        </is>
+      </c>
+      <c r="D1082" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>187 PC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>c95af929-4934-49f1-864e-4bd0919c29af</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>2026-03-26T17:42:25.036Z</t>
+        </is>
+      </c>
+      <c r="D1083" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1083" t="inlineStr"/>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>4a461c8b-0030-4d78-9d29-974c08bcba02</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>2026-03-26T18:03:11.247Z</t>
+        </is>
+      </c>
+      <c r="D1084" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1084" t="inlineStr"/>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>1853ce82-37b5-4885-99d2-b8dbb1fa34fa</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>2026-03-26T19:01:07.219Z</t>
+        </is>
+      </c>
+      <c r="D1085" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1085" t="inlineStr"/>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>f2990e3c-9b89-43aa-93b5-6bf00fad5389</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>2026-03-26T19:15:34.591Z</t>
+        </is>
+      </c>
+      <c r="D1086" t="n">
+        <v>891</v>
+      </c>
+      <c r="E1086" t="inlineStr"/>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>11918a6f-33e8-491b-b8f8-aea556e3a69a</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>2026-03-26T20:48:46.444Z</t>
+        </is>
+      </c>
+      <c r="D1087" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1087" t="inlineStr"/>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>072ae465-b6a9-4628-9ca0-21159c67d9b5</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>2026-03-26T21:15:53.060Z</t>
+        </is>
+      </c>
+      <c r="D1088" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>dadd9e38-835a-445d-8615-aa80320ff8e7</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>2026-03-26T21:34:07.806Z</t>
+        </is>
+      </c>
+      <c r="D1089" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1089" t="inlineStr"/>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>efbcbe18-9c15-4174-8659-3482b7071bf2</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>2026-03-26T22:09:24.931Z</t>
+        </is>
+      </c>
+      <c r="D1090" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1090" t="inlineStr"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>77248ce3-9469-4f81-aea5-0b8317c095aa</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>2026-03-26T23:27:29.375Z</t>
+        </is>
+      </c>
+      <c r="D1091" t="n">
+        <v>891</v>
+      </c>
+      <c r="E1091" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1091"/>
+  <dimension ref="A1:E1099"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25239,6 +25239,178 @@
       </c>
       <c r="E1091" t="inlineStr"/>
     </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>f93a0bf2-a8ad-4421-9e89-0ffac965d166</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>2026-03-17T15:32:24.440Z</t>
+        </is>
+      </c>
+      <c r="D1092" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1092" t="inlineStr"/>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>4eb15cb7-5e0e-4917-9781-b585c0a47abb</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>2026-03-27T00:00:35.563Z</t>
+        </is>
+      </c>
+      <c r="D1093" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1093" t="inlineStr"/>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>29f3d7f1-4bb3-41bc-9590-92f57b71d7d7</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>2026-03-27T06:40:00.362Z</t>
+        </is>
+      </c>
+      <c r="D1094" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1094" t="inlineStr"/>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2a5522c9-034f-4dc9-bea1-f9e9eff7b1db</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>2026-03-27T11:03:02.298Z</t>
+        </is>
+      </c>
+      <c r="D1095" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1095" t="inlineStr"/>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>0525649d-74a2-428e-a0e7-d41dcf5fac21</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>2026-03-27T13:40:55.183Z</t>
+        </is>
+      </c>
+      <c r="D1096" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>32d301a1-9c84-4376-9b36-01f8d2c6cc3b</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>2026-03-27T16:14:48.339Z</t>
+        </is>
+      </c>
+      <c r="D1097" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1097" t="inlineStr"/>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>5f19f6f1-e37d-4ec5-9f27-1f175e8c4ccb</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>2026-03-27T18:20:46.752Z</t>
+        </is>
+      </c>
+      <c r="D1098" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1098" t="inlineStr"/>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>c99e4a17-8e5d-4c31-b6ea-7e1d0b4db3f0</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>2026-03-27T19:24:10.159Z</t>
+        </is>
+      </c>
+      <c r="D1099" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1099" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1099"/>
+  <dimension ref="A1:E1113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25411,6 +25411,324 @@
       </c>
       <c r="E1099" t="inlineStr"/>
     </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>0a5d63e8-aa1d-4bea-a4c8-cebf9e70deef</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>2026-03-04T20:44:57.935Z</t>
+        </is>
+      </c>
+      <c r="D1100" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1100" t="inlineStr"/>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>ba8c5386-b7d7-4996-bef1-5c59289497af</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>2026-03-17T15:28:54.643Z</t>
+        </is>
+      </c>
+      <c r="D1101" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1101" t="inlineStr"/>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>83470cc7-95bf-41e5-9ed6-e17f9255a396</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>2026-03-18T18:36:11.895Z</t>
+        </is>
+      </c>
+      <c r="D1102" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1102" t="inlineStr"/>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>97db6142-e868-4b5a-ad4f-eb0c9d791508</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>2026-03-25T22:20:08.515Z</t>
+        </is>
+      </c>
+      <c r="D1103" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>951140d7-bdff-4ed7-9eae-70d8312e66a2</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>2026-03-28T00:03:57.317Z</t>
+        </is>
+      </c>
+      <c r="D1104" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1104" t="inlineStr"/>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>3c3b8212-932d-4ad1-8f75-e03b3f50c424</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>2026-03-28T01:21:03.581Z</t>
+        </is>
+      </c>
+      <c r="D1105" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1105" t="inlineStr"/>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>e818eb4b-e3a2-49b0-abae-655c1abb9916</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>2026-03-28T04:45:44.467Z</t>
+        </is>
+      </c>
+      <c r="D1106" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1106" t="inlineStr"/>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>c0de2522-3f8a-4f49-90f4-7f22950bdbc9</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>2026-03-28T04:46:22.237Z</t>
+        </is>
+      </c>
+      <c r="D1107" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>459.5 pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>f233361e-4832-4b3f-88af-3960b6e18eb8</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>2026-03-28T05:01:47.133Z</t>
+        </is>
+      </c>
+      <c r="D1108" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>459.5 pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>c9c128ea-c1e7-4845-95d1-7f887a4aa824</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>2026-03-28T07:11:24.488Z</t>
+        </is>
+      </c>
+      <c r="D1109" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1109" t="inlineStr"/>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>4375cf26-bf63-432a-9c8c-5729de3e6856</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>2026-03-28T21:25:29.870Z</t>
+        </is>
+      </c>
+      <c r="D1110" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>61508bf7-4272-4b5f-9cd6-15eb825fc250</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>2026-03-28T21:28:02.515Z</t>
+        </is>
+      </c>
+      <c r="D1111" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>87af3de0-3c2e-461c-98c3-f40f3534c2da</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>2026-03-28T23:45:03.479Z</t>
+        </is>
+      </c>
+      <c r="D1112" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>273apc, 273.5pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>b14be318-8433-4261-86bb-e290d63ac5e7</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>2026-03-28T23:48:16.142Z</t>
+        </is>
+      </c>
+      <c r="D1113" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1113" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1113"/>
+  <dimension ref="A1:E1120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25729,6 +25729,173 @@
       </c>
       <c r="E1113" t="inlineStr"/>
     </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>4582d4ff-5cc1-4087-9057-b9e601161962</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>2026-03-06T20:27:43.223Z</t>
+        </is>
+      </c>
+      <c r="D1114" t="n">
+        <v>432</v>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>suspect ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>f9369126-191e-4b31-9793-bb51557494ca</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>2026-03-29T00:53:21.998Z</t>
+        </is>
+      </c>
+      <c r="D1115" t="n">
+        <v>531</v>
+      </c>
+      <c r="E1115" t="inlineStr"/>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>ffa03e3c-7590-44cb-b578-e8dc18181801</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>2026-03-29T05:14:24.391Z</t>
+        </is>
+      </c>
+      <c r="D1116" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>459.5pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>36706c13-6f77-4783-a2a6-ed13eb7f7e0c</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>2026-03-29T15:28:44.848Z</t>
+        </is>
+      </c>
+      <c r="D1117" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>THEFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>d985452a-9a64-4766-8e8f-c6cc06dd9b38</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>2026-03-29T21:32:55.106Z</t>
+        </is>
+      </c>
+      <c r="D1118" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1118" t="inlineStr"/>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2de731e4-3df1-40ea-b9d9-978f2f59a641</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>2026-03-29T22:57:02.512Z</t>
+        </is>
+      </c>
+      <c r="D1119" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>wreckless</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2ebdecc1-c539-47a6-9da9-aee9e8d2b427</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>2026-03-29T22:58:50.450Z</t>
+        </is>
+      </c>
+      <c r="D1120" t="n">
+        <v>575</v>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>RECKLESS POSS DUI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1634"/>
+  <dimension ref="A1:E1653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37462,6 +37462,441 @@
       </c>
       <c r="E1634" t="inlineStr"/>
     </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>1636f44a-3f46-409c-80e8-efb2198d8ae9</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>2026-04-30T01:19:15.988Z</t>
+        </is>
+      </c>
+      <c r="D1635" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>5b4880d6-e4a8-4f67-88d3-fef9cf108f4c</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>2026-04-30T03:41:14.617Z</t>
+        </is>
+      </c>
+      <c r="D1636" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1636" t="inlineStr"/>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>e4caeb90-59c8-4078-bad8-9f4c8f15aa76</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>2026-04-30T05:30:49.539Z</t>
+        </is>
+      </c>
+      <c r="D1637" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1637" t="inlineStr">
+        <is>
+          <t>WANTED SUBJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>6bf379ff-b62f-48f0-8f99-9f90644facb8</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>2026-04-30T06:46:18.261Z</t>
+        </is>
+      </c>
+      <c r="D1638" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>aed8b72d-a3a9-4317-9fcd-7d2326686796</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>2026-04-30T12:59:28.240Z</t>
+        </is>
+      </c>
+      <c r="D1639" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1639" t="inlineStr"/>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>16f743c6-4963-4e84-86ce-3faf485994c0</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>2026-04-30T14:47:57.533Z</t>
+        </is>
+      </c>
+      <c r="D1640" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1640" t="inlineStr"/>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>7654c903-5768-402a-b228-4cbe779f59b1</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>2026-04-30T14:55:47.024Z</t>
+        </is>
+      </c>
+      <c r="D1641" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1641" t="inlineStr"/>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>041441e8-db8e-4c35-a126-1ba30aad65dc</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>2026-04-30T15:07:30.650Z</t>
+        </is>
+      </c>
+      <c r="D1642" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1642" t="inlineStr"/>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>67d50a76-5e93-488d-84b7-3cb8aab60251</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>2026-04-30T15:53:05.239Z</t>
+        </is>
+      </c>
+      <c r="D1643" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1643" t="inlineStr"/>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>d324e953-f10b-44a1-9813-1d68089ad079</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>2026-04-30T16:02:33.911Z</t>
+        </is>
+      </c>
+      <c r="D1644" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1644" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>8f6e82f0-6e9e-455a-95bc-78b825206fb4</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>2026-04-30T16:03:10.790Z</t>
+        </is>
+      </c>
+      <c r="D1645" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1645" t="inlineStr"/>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>5a055dd4-e9c5-4146-8a48-da8958539578</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>2026-04-30T16:03:20.545Z</t>
+        </is>
+      </c>
+      <c r="D1646" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1646" t="inlineStr"/>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>f9b90b02-b171-40dd-868b-68d62627f81d</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>2026-04-30T18:12:58.222Z</t>
+        </is>
+      </c>
+      <c r="D1647" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1647" t="inlineStr"/>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>6dc8729d-61db-4f51-8423-2e8d0f39a952</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>2026-04-30T18:16:57.111Z</t>
+        </is>
+      </c>
+      <c r="D1648" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1648" t="inlineStr"/>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>209d06c9-0814-4233-bd3e-ee0c2630b3e4</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>2026-04-30T18:28:27.965Z</t>
+        </is>
+      </c>
+      <c r="D1649" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1649" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>4d74fe59-187b-4050-ac73-7431797e09ad</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>2026-04-30T18:32:14.547Z</t>
+        </is>
+      </c>
+      <c r="D1650" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1650" t="inlineStr">
+        <is>
+          <t>wanted</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>7393488e-f0b9-4082-babe-32e140cc2938</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>2026-04-30T21:10:26.060Z</t>
+        </is>
+      </c>
+      <c r="D1651" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1651" t="inlineStr">
+        <is>
+          <t>SHOOTING</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>fe85277c-222e-4a34-a408-939580c73a74</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>2026-04-30T21:11:48.644Z</t>
+        </is>
+      </c>
+      <c r="D1652" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1652" t="inlineStr">
+        <is>
+          <t>suspect girlfriend</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>aaa2be68-e58b-48fa-9ee4-721203176ecd</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>2026-04-30T21:21:45.214Z</t>
+        </is>
+      </c>
+      <c r="D1653" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>Suspect gf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1653"/>
+  <dimension ref="A1:E1671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37897,6 +37897,408 @@
         </is>
       </c>
     </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>7694259d-eb20-4afa-94e9-3011e9ff58c3</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>2026-05-01T00:41:23.180Z</t>
+        </is>
+      </c>
+      <c r="D1654" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1654" t="inlineStr"/>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>ddaef4cd-5565-427a-9043-4c3895da9bba</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>2026-05-01T02:39:57.196Z</t>
+        </is>
+      </c>
+      <c r="D1655" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1655" t="inlineStr"/>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>e4477d10-4c40-47c9-b2ab-4d83f19bc087</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>2026-05-01T03:46:11.722Z</t>
+        </is>
+      </c>
+      <c r="D1656" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1656" t="inlineStr"/>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>2fbc7b0d-b978-466f-93c1-e386364282ba</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>2026-05-01T04:03:28.757Z</t>
+        </is>
+      </c>
+      <c r="D1657" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>sus id</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>0fa71aed-9d06-45ee-b46d-b08d4bdfd320</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>2026-05-01T04:10:13.616Z</t>
+        </is>
+      </c>
+      <c r="D1658" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>245 SUSPECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>5b9acb8b-a1f0-4f4a-8337-4fc3a34b2329</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>2026-05-01T04:29:24.430Z</t>
+        </is>
+      </c>
+      <c r="D1659" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>Susp veh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>f1cd11f0-68a3-44aa-b974-f346f2233f7c</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>2026-05-01T04:34:10.326Z</t>
+        </is>
+      </c>
+      <c r="D1660" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1660" t="inlineStr"/>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>e21e7dd4-5c3e-421e-8f41-404faff717b8</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>2026-05-01T05:04:10.084Z</t>
+        </is>
+      </c>
+      <c r="D1661" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>245 SUSPECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>292668a1-6cd9-4db0-9865-af457391414d</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>2026-05-01T05:59:48.624Z</t>
+        </is>
+      </c>
+      <c r="D1662" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1662" t="inlineStr"/>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>a4ffce8f-8a19-4f35-a3c8-d9b8dee9973d</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>2026-05-01T18:27:26.324Z</t>
+        </is>
+      </c>
+      <c r="D1663" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1663" t="inlineStr"/>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>268b17e2-c2f4-4211-9627-e7205f6996a3</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>2026-05-01T20:27:47.874Z</t>
+        </is>
+      </c>
+      <c r="D1664" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1664" t="inlineStr"/>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>615f9bf1-ab07-4171-bd2d-b027c571bf68</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>2026-05-01T20:28:39.450Z</t>
+        </is>
+      </c>
+      <c r="D1665" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>0b838ca4-7d18-41c6-aeba-1b641a805a99</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>2026-05-01T20:29:28.699Z</t>
+        </is>
+      </c>
+      <c r="D1666" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>64acf1a0-281e-41a0-a39a-be1908ce3ed8</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>2026-05-01T20:33:05.986Z</t>
+        </is>
+      </c>
+      <c r="D1667" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1667" t="inlineStr"/>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>a71991a0-6f4e-46d3-9a0f-804da59e96a0</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>2026-05-01T21:12:23.569Z</t>
+        </is>
+      </c>
+      <c r="D1668" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1668" t="inlineStr"/>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>8aef01ef-c638-4aca-ae1a-b8b3dc0dca3c</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>2026-05-01T22:01:21.153Z</t>
+        </is>
+      </c>
+      <c r="D1669" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1669" t="inlineStr"/>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>9d208b04-2aa6-4a21-b029-97581095ce5c</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>2026-05-01T22:50:11.349Z</t>
+        </is>
+      </c>
+      <c r="D1670" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1670" t="inlineStr"/>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>d0819716-625f-4beb-9ec3-9f7015f9bfcd</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>2026-05-01T23:13:36.854Z</t>
+        </is>
+      </c>
+      <c r="D1671" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1671" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1671"/>
+  <dimension ref="A1:E1681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38299,6 +38299,240 @@
       </c>
       <c r="E1671" t="inlineStr"/>
     </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>91402f93-ced4-4d4e-977d-cf1b72785115</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>2026-05-02T00:37:34.384Z</t>
+        </is>
+      </c>
+      <c r="D1672" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>245 SUSPECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>5fc506da-08a8-4b2a-a99a-0d6c8bcdc0d4</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>2026-05-02T00:43:48.033Z</t>
+        </is>
+      </c>
+      <c r="D1673" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>273.5 suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>7c256105-6426-44bc-91a9-285d2e77d02b</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>2026-05-02T16:59:52.707Z</t>
+        </is>
+      </c>
+      <c r="D1674" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>susp veh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>9fc90a8e-5dab-4e24-840a-2caa21d6b43c</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>2026-05-02T17:07:01.028Z</t>
+        </is>
+      </c>
+      <c r="D1675" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>susp veh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>bbab485b-5168-4e9d-a005-afdb5b8e905c</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>2026-05-02T19:10:26.394Z</t>
+        </is>
+      </c>
+      <c r="D1676" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1676" t="inlineStr"/>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>84f19636-f180-4201-b55f-d4004a34f1a9</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>2026-05-02T21:26:27.184Z</t>
+        </is>
+      </c>
+      <c r="D1677" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>3b42ceec-a604-4b4d-80c9-e60017e58e4f</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>2026-05-02T21:58:24.402Z</t>
+        </is>
+      </c>
+      <c r="D1678" t="n">
+        <v>34</v>
+      </c>
+      <c r="E1678" t="inlineStr"/>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>77bebc7e-ec9f-42a7-b8a4-ab9c3a301970</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>2026-05-02T22:02:06.554Z</t>
+        </is>
+      </c>
+      <c r="D1679" t="n">
+        <v>34</v>
+      </c>
+      <c r="E1679" t="inlineStr"/>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>84fea0ac-23fb-48ce-a914-f8f14a668dea</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>2026-05-02T22:10:59.047Z</t>
+        </is>
+      </c>
+      <c r="D1680" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>c9b8c1a6-2623-4943-a08c-7e291945a2fb</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>2026-05-02T22:25:26.291Z</t>
+        </is>
+      </c>
+      <c r="D1681" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1681" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1681"/>
+  <dimension ref="A1:E1698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38533,6 +38533,387 @@
       </c>
       <c r="E1681" t="inlineStr"/>
     </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>77e884d2-7926-48ff-b5b0-eef8e151b5bb</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>2026-05-03T00:51:39.938Z</t>
+        </is>
+      </c>
+      <c r="D1682" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1682" t="inlineStr"/>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>6cf50b4e-5fc4-4fff-bc7f-306e0a6c4dfd</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>2026-05-03T01:03:49.516Z</t>
+        </is>
+      </c>
+      <c r="D1683" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1683" t="inlineStr"/>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>3874a92d-3f69-452e-b190-d14c18490d0a</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>2026-05-03T01:10:27.908Z</t>
+        </is>
+      </c>
+      <c r="D1684" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>7827ab10-48d7-4865-bc27-cb2058a2fe43</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>2026-05-03T03:03:00.891Z</t>
+        </is>
+      </c>
+      <c r="D1685" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1685" t="inlineStr"/>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>c9767926-0419-4665-8cce-35842369acbc</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>2026-05-03T04:48:12.964Z</t>
+        </is>
+      </c>
+      <c r="D1686" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>7fbc5937-1e68-47d7-8c9c-6e655306c327</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>2026-05-03T18:00:31.785Z</t>
+        </is>
+      </c>
+      <c r="D1687" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1687" t="inlineStr"/>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>5e7ccae8-3f62-470e-9ce8-a6fc95616e24</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>2026-05-03T18:42:00.418Z</t>
+        </is>
+      </c>
+      <c r="D1688" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>wanted warrant</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>0eefe464-c849-4e6b-a1ab-3da6813f76f7</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>2026-05-03T19:02:54.906Z</t>
+        </is>
+      </c>
+      <c r="D1689" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1689" t="inlineStr"/>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>fdc896a2-a930-4a00-b9d2-15ed689036e9</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>2026-05-03T20:03:18.466Z</t>
+        </is>
+      </c>
+      <c r="D1690" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1690" t="inlineStr"/>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>b35b4d19-0e60-4288-82e4-2046ba9708fe</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>2026-05-03T20:03:34.137Z</t>
+        </is>
+      </c>
+      <c r="D1691" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1691" t="inlineStr"/>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>3f017e54-3cb0-441a-92a7-86fbe49f9b98</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>2026-05-03T20:22:27.749Z</t>
+        </is>
+      </c>
+      <c r="D1692" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1692" t="inlineStr">
+        <is>
+          <t>wanted warrant</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>d0d65476-ef14-4ff6-97ae-85a7679363ea</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>2026-05-03T20:44:17.187Z</t>
+        </is>
+      </c>
+      <c r="D1693" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1693" t="inlineStr"/>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>fa548c14-9849-40df-a92f-ca3b43e1519c</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>2026-05-03T21:00:18.936Z</t>
+        </is>
+      </c>
+      <c r="D1694" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1694" t="inlineStr"/>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>e9035a5f-13f1-4a20-86f2-13a393da6f12</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>2026-05-03T21:25:33.726Z</t>
+        </is>
+      </c>
+      <c r="D1695" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>Wire</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>c7d6f957-4f2c-4de0-a9f7-37841d03258f</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:25:17.783Z</t>
+        </is>
+      </c>
+      <c r="D1696" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1696" t="inlineStr"/>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>354d0e26-08de-4e8c-a03b-e84ac22ff2d5</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>2026-05-03T23:09:34.556Z</t>
+        </is>
+      </c>
+      <c r="D1697" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1697" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>065d5baf-ef43-4888-95d8-e7d26f89a73d</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>2026-05-03T23:53:40.902Z</t>
+        </is>
+      </c>
+      <c r="D1698" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1698" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1698"/>
+  <dimension ref="A1:E1723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38914,6 +38914,563 @@
       </c>
       <c r="E1698" t="inlineStr"/>
     </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>f31631c3-950a-4d7e-acbe-e77eafa0f95f</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>2026-05-04T00:00:37.900Z</t>
+        </is>
+      </c>
+      <c r="D1699" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1699" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>56014f2b-7a4e-4472-a247-6dd6570fbf42</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>2026-05-04T01:32:47.142Z</t>
+        </is>
+      </c>
+      <c r="D1700" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1700" t="inlineStr"/>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>b0674158-d02f-43c7-ad69-9fc09efb7761</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>2026-05-04T02:41:33.328Z</t>
+        </is>
+      </c>
+      <c r="D1701" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1701" t="inlineStr"/>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>1d0fd2b8-8916-4c81-95ea-39e1d40c91b0</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>2026-05-04T08:43:11.018Z</t>
+        </is>
+      </c>
+      <c r="D1702" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1702" t="inlineStr"/>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>be6f9af1-18a2-4549-ab01-e8aeaa50c895</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>2026-05-04T15:00:04.621Z</t>
+        </is>
+      </c>
+      <c r="D1703" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1703" t="inlineStr"/>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>c4a74999-6550-430a-82c4-3305f9803f51</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>2026-05-04T15:06:00.819Z</t>
+        </is>
+      </c>
+      <c r="D1704" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>187 PC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>911572c4-167c-4703-a397-97ac5e87775b</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>2026-05-04T15:34:20.485Z</t>
+        </is>
+      </c>
+      <c r="D1705" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1705" t="inlineStr"/>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>8d61c386-914b-4ae2-aa3a-7f26d30d9de0</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>2026-05-04T16:03:35.886Z</t>
+        </is>
+      </c>
+      <c r="D1706" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1706" t="inlineStr"/>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>0b80bb98-9de9-4002-b4e6-fb7a4091d775</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>2026-05-04T16:12:24.384Z</t>
+        </is>
+      </c>
+      <c r="D1707" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1707" t="inlineStr"/>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>a0576eef-999a-4c18-a956-bdb850c4bbaf</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>2026-05-04T16:13:22.072Z</t>
+        </is>
+      </c>
+      <c r="D1708" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>prcs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>6d7c662c-66e1-4c01-bfb2-19576e77c4ea</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>2026-05-04T16:16:06.449Z</t>
+        </is>
+      </c>
+      <c r="D1709" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>Suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>a47b8d95-5371-481d-99b3-0a3bbd5c23f0</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>2026-05-04T16:26:08.241Z</t>
+        </is>
+      </c>
+      <c r="D1710" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>wanted subject-26-1571</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>a92fa778-8163-4a6b-8016-9f9df028468e</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>2026-05-04T17:02:37.042Z</t>
+        </is>
+      </c>
+      <c r="D1711" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1711" t="inlineStr"/>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>ceac6c70-23c9-47f5-a0bf-b408887c103c</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>2026-05-04T17:12:45.171Z</t>
+        </is>
+      </c>
+      <c r="D1712" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>wanted warrant</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>16ec07e6-5d46-447a-b621-745a3a5e9cdf</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>2026-05-04T18:26:45.012Z</t>
+        </is>
+      </c>
+      <c r="D1713" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1713" t="inlineStr"/>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>6fc589cd-0dea-4195-8c8e-ee75266ad4a7</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>2026-05-04T18:29:57.082Z</t>
+        </is>
+      </c>
+      <c r="D1714" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1714" t="inlineStr"/>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>398d907e-1c10-45de-8651-d1747cdbf3bb</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>2026-05-04T19:35:47.004Z</t>
+        </is>
+      </c>
+      <c r="D1715" t="n">
+        <v>534</v>
+      </c>
+      <c r="E1715" t="inlineStr"/>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>5773abe6-b301-4b09-8442-ffd2f99a4f08</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>2026-05-04T21:09:22.331Z</t>
+        </is>
+      </c>
+      <c r="D1716" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1716" t="inlineStr"/>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>eb5e5fb1-af14-4319-83ec-469fa87bfd28</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>2026-05-04T21:12:52.515Z</t>
+        </is>
+      </c>
+      <c r="D1717" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1717" t="inlineStr"/>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>3f42aec8-3e2e-4d77-ab4f-f416e696bee2</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>2026-05-04T22:28:06.413Z</t>
+        </is>
+      </c>
+      <c r="D1718" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1718" t="inlineStr"/>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>2fe0a33e-cb3c-4cb6-ae72-ab820044d5a3</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>2026-05-04T22:28:44.656Z</t>
+        </is>
+      </c>
+      <c r="D1719" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1719" t="inlineStr"/>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>e192fe4b-d49c-4e55-93af-dbb3024b6cb3</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>2026-05-04T22:35:39.976Z</t>
+        </is>
+      </c>
+      <c r="D1720" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1720" t="inlineStr"/>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>c14e4d75-862d-43e6-b12f-71a3ab2c1e0a</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>2026-05-04T22:54:44.689Z</t>
+        </is>
+      </c>
+      <c r="D1721" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>Locate Missing Person</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>485e2896-e075-4b92-9f14-6c3abc1ec906</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>2026-05-04T23:02:09.531Z</t>
+        </is>
+      </c>
+      <c r="D1722" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1722" t="inlineStr"/>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>b4a76e77-bc76-4b45-9122-40f02179264a</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>2026-05-04T23:02:40.423Z</t>
+        </is>
+      </c>
+      <c r="D1723" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>Locate Missing Person</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1723"/>
+  <dimension ref="A1:E1770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39471,6 +39471,1037 @@
         </is>
       </c>
     </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>5ab0e392-85c6-4659-b5ea-cb652c175ae1</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>2026-05-05T00:39:05.485Z</t>
+        </is>
+      </c>
+      <c r="D1724" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1724" t="inlineStr"/>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>28a3ae19-e73c-4174-9c20-943af290a8ee</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>2026-05-05T00:40:22.971Z</t>
+        </is>
+      </c>
+      <c r="D1725" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>7beb4666-f895-4599-aa8b-e5b66b165dab</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>2026-05-05T01:03:06.840Z</t>
+        </is>
+      </c>
+      <c r="D1726" t="n">
+        <v>493</v>
+      </c>
+      <c r="E1726" t="inlineStr"/>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>4c186e8e-ffca-4d63-86e3-b8568cc579d9</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>2026-05-05T01:08:54.635Z</t>
+        </is>
+      </c>
+      <c r="D1727" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>0afb99c0-5f09-4f5e-b8a1-6fca16f02350</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>2026-05-05T02:52:21.215Z</t>
+        </is>
+      </c>
+      <c r="D1728" t="n">
+        <v>493</v>
+      </c>
+      <c r="E1728" t="inlineStr"/>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>18743baf-c5fd-4b97-844e-78afcc42a640</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>2026-05-05T04:24:07.345Z</t>
+        </is>
+      </c>
+      <c r="D1729" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>BOLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>5b2f1df9-7047-4383-963f-79e2e6d1f802</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>2026-05-05T04:31:27.421Z</t>
+        </is>
+      </c>
+      <c r="D1730" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1730" t="inlineStr"/>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>e3b26c65-7c06-4290-aa1a-58521254f0e7</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>2026-05-05T05:30:57.696Z</t>
+        </is>
+      </c>
+      <c r="D1731" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1731" t="inlineStr"/>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>4d139747-e887-4922-a487-1cffa0531207</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>2026-05-05T06:25:49.767Z</t>
+        </is>
+      </c>
+      <c r="D1732" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1732" t="inlineStr"/>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>92167134-5224-458b-b122-b6e111898da7</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>2026-05-05T07:24:11.575Z</t>
+        </is>
+      </c>
+      <c r="D1733" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1733" t="inlineStr"/>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>cdbb0725-e95f-4eb2-be17-4ef20a0046ef</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>2026-05-05T07:51:52.107Z</t>
+        </is>
+      </c>
+      <c r="D1734" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1734" t="inlineStr"/>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>1f08977f-210b-4c93-8d42-e2a2abe9c135</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>2026-05-05T07:59:05.932Z</t>
+        </is>
+      </c>
+      <c r="D1735" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>BOLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>a078c06b-8716-4f89-a082-f5018a043d56</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>2026-05-05T08:00:17.669Z</t>
+        </is>
+      </c>
+      <c r="D1736" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1736" t="inlineStr"/>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>feab3cbc-1e79-48bd-bc7a-d75f346257aa</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>2026-05-05T08:00:53.091Z</t>
+        </is>
+      </c>
+      <c r="D1737" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>BOLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>59791a0a-855c-4ca2-b100-be07917859db</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>2026-05-05T08:00:54.025Z</t>
+        </is>
+      </c>
+      <c r="D1738" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1738" t="inlineStr"/>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>55c71714-8fc7-4a4d-8008-a96ab72aab0e</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>2026-05-05T09:10:42.621Z</t>
+        </is>
+      </c>
+      <c r="D1739" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1739" t="inlineStr"/>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>7dc04f30-2bae-46f8-8985-d25776d550b5</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>2026-05-05T09:45:15.650Z</t>
+        </is>
+      </c>
+      <c r="D1740" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1740" t="inlineStr"/>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>d00a837f-8261-4877-a151-a966342f6762</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>2026-05-05T10:09:10.542Z</t>
+        </is>
+      </c>
+      <c r="D1741" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1741" t="inlineStr"/>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>f942afc9-3356-4821-9baa-075f47c82eea</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>2026-05-05T10:23:55.812Z</t>
+        </is>
+      </c>
+      <c r="D1742" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1742" t="inlineStr"/>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>12170af3-3297-4dab-8606-c525b6e5d1d3</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>2026-05-05T11:27:38.043Z</t>
+        </is>
+      </c>
+      <c r="D1743" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1743" t="inlineStr"/>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>713f3f54-8358-478e-97ca-d186045321f1</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>2026-05-05T12:23:52.649Z</t>
+        </is>
+      </c>
+      <c r="D1744" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1744" t="inlineStr"/>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>78feb735-d621-46c5-9a59-3aa17f87591f</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>2026-05-05T13:11:58.113Z</t>
+        </is>
+      </c>
+      <c r="D1745" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1745" t="inlineStr"/>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>8ffc78b4-45e6-4607-9e80-d8106e2a72aa</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>2026-05-05T14:21:02.619Z</t>
+        </is>
+      </c>
+      <c r="D1746" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1746" t="inlineStr"/>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>f03b3867-9bb7-4389-9f35-e0db2ad0f750</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>2026-05-05T14:41:25.659Z</t>
+        </is>
+      </c>
+      <c r="D1747" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1747" t="inlineStr"/>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>45f1c7cf-0dac-4d07-a75b-6c8e67a81448</t>
+        </is>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>2026-05-05T15:42:21.615Z</t>
+        </is>
+      </c>
+      <c r="D1748" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1748" t="inlineStr"/>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>c8964ddf-a0a5-4f1d-8854-cd4bd23e373b</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>2026-05-05T15:57:59.579Z</t>
+        </is>
+      </c>
+      <c r="D1749" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1749" t="inlineStr">
+        <is>
+          <t>warrant ramey-245 bat</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>f39cc7ec-f0a7-40f7-8ce8-7024ea3cb2ce</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>2026-05-05T16:22:23.370Z</t>
+        </is>
+      </c>
+      <c r="D1750" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1750" t="inlineStr"/>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>441a3aa8-bd47-4f81-8d5b-49f6be48f8ab</t>
+        </is>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>2026-05-05T16:59:07.730Z</t>
+        </is>
+      </c>
+      <c r="D1751" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1751" t="inlineStr"/>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>7adf98f0-6791-4744-924f-ea812eb5567a</t>
+        </is>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>2026-05-05T17:04:31.448Z</t>
+        </is>
+      </c>
+      <c r="D1752" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1752" t="inlineStr"/>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>0c6ee050-8058-4353-aa3d-459392d34a5a</t>
+        </is>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>2026-05-05T17:11:07.898Z</t>
+        </is>
+      </c>
+      <c r="D1753" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1753" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>46c7a8e4-240a-4a0c-a334-708a670d470b</t>
+        </is>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>2026-05-05T17:56:10.101Z</t>
+        </is>
+      </c>
+      <c r="D1754" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1754" t="inlineStr"/>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>25460517-e719-472e-9dd4-ace32b805407</t>
+        </is>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>2026-05-05T17:57:10.301Z</t>
+        </is>
+      </c>
+      <c r="D1755" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1755" t="inlineStr"/>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>b62d22fb-dcfa-4662-82f2-95fe30ea0f65</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>2026-05-05T18:00:35.333Z</t>
+        </is>
+      </c>
+      <c r="D1756" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1756" t="inlineStr"/>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>e9c75566-6587-43d2-9c62-9b1b3b2bcd57</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>2026-05-05T18:01:45.777Z</t>
+        </is>
+      </c>
+      <c r="D1757" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1757" t="inlineStr"/>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>abdeac6e-8892-46ca-b174-f094b11757ec</t>
+        </is>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>2026-05-05T18:52:10.796Z</t>
+        </is>
+      </c>
+      <c r="D1758" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1758" t="inlineStr"/>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>6789161b-c5ec-47f2-ba3c-a89a2c4e64ac</t>
+        </is>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>2026-05-05T19:25:42.750Z</t>
+        </is>
+      </c>
+      <c r="D1759" t="n">
+        <v>493</v>
+      </c>
+      <c r="E1759" t="inlineStr"/>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>652dfdd2-b48f-4e80-b6ad-8ea65c9d7040</t>
+        </is>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>2026-05-05T19:49:02.674Z</t>
+        </is>
+      </c>
+      <c r="D1760" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1760" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>a4808896-e0d6-48c4-b07e-8ac30421e880</t>
+        </is>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>2026-05-05T20:38:27.763Z</t>
+        </is>
+      </c>
+      <c r="D1761" t="n">
+        <v>493</v>
+      </c>
+      <c r="E1761" t="inlineStr"/>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>4b68eb0c-6a5e-46c0-91d6-28324247a2ba</t>
+        </is>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>2026-05-05T20:39:37.182Z</t>
+        </is>
+      </c>
+      <c r="D1762" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1762" t="inlineStr"/>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>24bbfb01-453d-4091-a031-1658f20bc619</t>
+        </is>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>2026-05-05T21:07:28.758Z</t>
+        </is>
+      </c>
+      <c r="D1763" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1763" t="inlineStr"/>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>feae5cc9-0079-499a-83c2-3c8dc6f4d020</t>
+        </is>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>2026-05-05T21:09:32.632Z</t>
+        </is>
+      </c>
+      <c r="D1764" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1764" t="inlineStr"/>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>38ac5bc8-b7d2-4b71-be03-a1365b5b52b7</t>
+        </is>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>2026-05-05T21:11:05.247Z</t>
+        </is>
+      </c>
+      <c r="D1765" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1765" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>7c10f4c3-bc2d-40b8-a1d0-0c359901aee1</t>
+        </is>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>2026-05-05T22:01:02.615Z</t>
+        </is>
+      </c>
+      <c r="D1766" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1766" t="inlineStr"/>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>1b9d7d8c-ad1a-40fc-912f-bed27aec9ed7</t>
+        </is>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>2026-05-05T22:04:09.165Z</t>
+        </is>
+      </c>
+      <c r="D1767" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1767" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>eeae9b4a-6dcd-465e-9fe8-36b1bfaeb1d2</t>
+        </is>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>2026-05-05T23:15:07.229Z</t>
+        </is>
+      </c>
+      <c r="D1768" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1768" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>3457bc82-39da-458a-a3f6-6645e484b993</t>
+        </is>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>2026-05-05T23:23:34.878Z</t>
+        </is>
+      </c>
+      <c r="D1769" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1769" t="inlineStr"/>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>542ce6c1-0524-4e58-ad29-7c37f52e292b</t>
+        </is>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>2026-05-05T23:48:22.654Z</t>
+        </is>
+      </c>
+      <c r="D1770" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1770" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1770"/>
+  <dimension ref="A1:E1804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40502,6 +40502,768 @@
       </c>
       <c r="E1770" t="inlineStr"/>
     </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>19e2cdd3-ee61-4080-886b-ed3654ea1173</t>
+        </is>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>2026-05-06T00:18:40.111Z</t>
+        </is>
+      </c>
+      <c r="D1771" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1771" t="inlineStr"/>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>17d5d56c-2e36-4577-9177-9429004af967</t>
+        </is>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>2026-05-06T00:25:31.391Z</t>
+        </is>
+      </c>
+      <c r="D1772" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1772" t="inlineStr"/>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>003ba2ec-0d15-4b52-aee6-a407afa2a8a4</t>
+        </is>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>2026-05-06T00:44:01.813Z</t>
+        </is>
+      </c>
+      <c r="D1773" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1773" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>4fea391d-d2af-41db-a7f1-0094d9101580</t>
+        </is>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>2026-05-06T01:02:13.228Z</t>
+        </is>
+      </c>
+      <c r="D1774" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1774" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>c371e252-e8f8-4565-91ac-9ef5afc2644d</t>
+        </is>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>2026-05-06T02:05:42.308Z</t>
+        </is>
+      </c>
+      <c r="D1775" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1775" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>a8bd1bbf-fb50-40ba-9aa4-1492bb37a3a9</t>
+        </is>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>2026-05-06T03:34:15.448Z</t>
+        </is>
+      </c>
+      <c r="D1776" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1776" t="inlineStr"/>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>356de267-f063-4ed6-93fc-6a9e587945eb</t>
+        </is>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>2026-05-06T03:43:47.775Z</t>
+        </is>
+      </c>
+      <c r="D1777" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1777" t="inlineStr"/>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>41d7ed8b-4c67-4e99-b5c3-616b22739916</t>
+        </is>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>2026-05-06T04:21:38.254Z</t>
+        </is>
+      </c>
+      <c r="D1778" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1778" t="inlineStr"/>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>ef532c3d-1785-4cb9-9593-b18ab1ee5bff</t>
+        </is>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>2026-05-06T04:32:30.347Z</t>
+        </is>
+      </c>
+      <c r="D1779" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1779" t="inlineStr">
+        <is>
+          <t>273a(b)PC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>a5c4159f-86e9-4040-bc46-e66dc7e8354d</t>
+        </is>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>2026-05-06T04:44:30.311Z</t>
+        </is>
+      </c>
+      <c r="D1780" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1780" t="inlineStr">
+        <is>
+          <t>BOLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>4e548e3c-0bed-45d7-a640-d399fe0c3050</t>
+        </is>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>2026-05-06T04:46:38.279Z</t>
+        </is>
+      </c>
+      <c r="D1781" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1781" t="inlineStr">
+        <is>
+          <t>BOLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>1bcb5b03-0b87-478c-baf9-076654d761bd</t>
+        </is>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>2026-05-06T04:49:14.425Z</t>
+        </is>
+      </c>
+      <c r="D1782" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1782" t="inlineStr">
+        <is>
+          <t>domestic violence susp</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>b98a1185-4af1-4bb5-9d6e-4356e7723138</t>
+        </is>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>2026-05-06T05:01:30.951Z</t>
+        </is>
+      </c>
+      <c r="D1783" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1783" t="inlineStr">
+        <is>
+          <t>domestic violence susp</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>905abd92-b433-443d-945c-3fe7d7fe6dd9</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>2026-05-06T09:10:28.010Z</t>
+        </is>
+      </c>
+      <c r="D1784" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1784" t="inlineStr"/>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>a55c9a86-f4e6-4151-bc67-4242932f0d41</t>
+        </is>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>2026-05-06T10:30:50.073Z</t>
+        </is>
+      </c>
+      <c r="D1785" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1785" t="inlineStr"/>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>e2c23722-081d-4f4b-abe4-f17c2e360fc9</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>2026-05-06T13:45:57.887Z</t>
+        </is>
+      </c>
+      <c r="D1786" t="n">
+        <v>493</v>
+      </c>
+      <c r="E1786" t="inlineStr"/>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>ba5e57bc-32d8-448f-9964-c57f95c33f68</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>2026-05-06T14:57:32.762Z</t>
+        </is>
+      </c>
+      <c r="D1787" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1787" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>a3b3439e-dd6e-4f77-81fa-8200c8d9ff21</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>2026-05-06T15:22:50.278Z</t>
+        </is>
+      </c>
+      <c r="D1788" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1788" t="inlineStr"/>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>b0eb6d53-7997-45b4-b1f2-0982c000124d</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>2026-05-06T15:51:41.107Z</t>
+        </is>
+      </c>
+      <c r="D1789" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1789" t="inlineStr"/>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>61fc7184-2c58-4bcf-888d-d21d11ff04be</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>2026-05-06T16:18:06.906Z</t>
+        </is>
+      </c>
+      <c r="D1790" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1790" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>a93de6b7-69e0-4b23-928f-a8847a623900</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>2026-05-06T16:19:18.981Z</t>
+        </is>
+      </c>
+      <c r="D1791" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1791" t="inlineStr"/>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>f30ba2b6-e846-4ace-bcc2-b7d84c0aae36</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>2026-05-06T16:39:17.270Z</t>
+        </is>
+      </c>
+      <c r="D1792" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1792" t="inlineStr"/>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>2bdeec4d-aa47-4bfd-a90a-20e165585ab3</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>2026-05-06T17:14:33.975Z</t>
+        </is>
+      </c>
+      <c r="D1793" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1793" t="inlineStr"/>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>836b58fa-3c3c-4450-9a81-c7aaf5530ef7</t>
+        </is>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>2026-05-06T17:18:02.998Z</t>
+        </is>
+      </c>
+      <c r="D1794" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1794" t="inlineStr"/>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>07c49b23-3299-4eca-86a1-fd9eea8daa3d</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>2026-05-06T17:24:50.816Z</t>
+        </is>
+      </c>
+      <c r="D1795" t="n">
+        <v>493</v>
+      </c>
+      <c r="E1795" t="inlineStr"/>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>74542c05-d906-4447-91cf-4a0d448af607</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>2026-05-06T18:01:41.189Z</t>
+        </is>
+      </c>
+      <c r="D1796" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1796" t="inlineStr"/>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>62a16dca-1f6f-49b9-b8b1-744e5952fd8e</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>2026-05-06T18:20:14.068Z</t>
+        </is>
+      </c>
+      <c r="D1797" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1797" t="inlineStr"/>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>8e28abe7-f0ec-4f90-bfed-c3485e226f91</t>
+        </is>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>2026-05-06T18:21:02.486Z</t>
+        </is>
+      </c>
+      <c r="D1798" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1798" t="inlineStr"/>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>b7912ab8-d15e-4451-b990-a0c54e90b342</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>2026-05-06T18:29:44.790Z</t>
+        </is>
+      </c>
+      <c r="D1799" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1799" t="inlineStr"/>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>86433db1-c9d6-4876-983e-00c50a4f38c6</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>2026-05-06T18:35:16.081Z</t>
+        </is>
+      </c>
+      <c r="D1800" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1800" t="inlineStr">
+        <is>
+          <t>RECKLESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>03be638f-4921-4a64-90f9-1b7655e339e2</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>2026-05-06T19:56:20.466Z</t>
+        </is>
+      </c>
+      <c r="D1801" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1801" t="inlineStr">
+        <is>
+          <t>243d suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>64af5e9c-a57c-4837-b885-6b2057a6c8a7</t>
+        </is>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>2026-05-06T20:05:26.652Z</t>
+        </is>
+      </c>
+      <c r="D1802" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1802" t="inlineStr"/>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>dead0904-2c4d-4ef0-85db-3b75864a89c2</t>
+        </is>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>2026-05-06T21:11:20.741Z</t>
+        </is>
+      </c>
+      <c r="D1803" t="n">
+        <v>493</v>
+      </c>
+      <c r="E1803" t="inlineStr"/>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>8d06d023-f41c-4cf6-863e-10795bf04c1c</t>
+        </is>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>2026-05-06T21:44:17.774Z</t>
+        </is>
+      </c>
+      <c r="D1804" t="n">
+        <v>534</v>
+      </c>
+      <c r="E1804" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1804"/>
+  <dimension ref="A1:E1820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41264,6 +41264,378 @@
       </c>
       <c r="E1804" t="inlineStr"/>
     </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>865ff351-0922-4907-b46e-addbedab3dae</t>
+        </is>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>2026-05-07T02:18:28.637Z</t>
+        </is>
+      </c>
+      <c r="D1805" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1805" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>1e43a5ab-e571-4e20-b1c8-a75e1d64ca17</t>
+        </is>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>2026-05-07T03:57:28.052Z</t>
+        </is>
+      </c>
+      <c r="D1806" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1806" t="inlineStr">
+        <is>
+          <t>7vnh893</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>e3f98439-bf00-4039-94a2-ff99cf7bc0e0</t>
+        </is>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>2026-05-07T04:11:05.588Z</t>
+        </is>
+      </c>
+      <c r="D1807" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1807" t="inlineStr">
+        <is>
+          <t>273.5 pc suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr">
+        <is>
+          <t>5395d1f9-f6e4-402e-a232-07f6030a978d</t>
+        </is>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>2026-05-07T05:02:34.178Z</t>
+        </is>
+      </c>
+      <c r="D1808" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1808" t="inlineStr">
+        <is>
+          <t>BOLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>ac75668f-e2ba-44f0-9b85-85674f5873fc</t>
+        </is>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>2026-05-07T15:32:27.404Z</t>
+        </is>
+      </c>
+      <c r="D1809" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1809" t="inlineStr"/>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>68c3c80e-fb37-48b9-88d6-02b2d27482ad</t>
+        </is>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>2026-05-07T16:14:18.125Z</t>
+        </is>
+      </c>
+      <c r="D1810" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1810" t="inlineStr"/>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>b66b2d09-6c4d-4178-bdba-e0c44e906a54</t>
+        </is>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>2026-05-07T17:29:59.106Z</t>
+        </is>
+      </c>
+      <c r="D1811" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1811" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>c3f2b1a0-a160-4533-afb9-9e0d8537aaf4</t>
+        </is>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>2026-05-07T18:26:02.266Z</t>
+        </is>
+      </c>
+      <c r="D1812" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1812" t="inlineStr">
+        <is>
+          <t>Druginvestigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>e92b7619-0590-489e-bdff-472ddad78219</t>
+        </is>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>2026-05-07T20:53:27.443Z</t>
+        </is>
+      </c>
+      <c r="D1813" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1813" t="inlineStr">
+        <is>
+          <t>SUTTER CO SUSPECT IN AREA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>d0530bc2-b024-45e9-96b5-ed08d4fe1a23</t>
+        </is>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>2026-05-07T20:53:48.663Z</t>
+        </is>
+      </c>
+      <c r="D1814" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1814" t="inlineStr"/>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>c887f4e4-f60f-4132-8731-bf80a8cd3906</t>
+        </is>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>2026-05-07T20:55:17.494Z</t>
+        </is>
+      </c>
+      <c r="D1815" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1815" t="inlineStr"/>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>11947232-0781-4b88-89d4-0669a98cd2a9</t>
+        </is>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>2026-05-07T20:55:48.497Z</t>
+        </is>
+      </c>
+      <c r="D1816" t="n">
+        <v>569</v>
+      </c>
+      <c r="E1816" t="inlineStr">
+        <is>
+          <t>SUTTER CO RAMEY WARRANT IN AREA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>0c5b8904-fe10-4998-b479-33e3b863f0e3</t>
+        </is>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>2026-05-07T21:45:01.326Z</t>
+        </is>
+      </c>
+      <c r="D1817" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1817" t="inlineStr"/>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>3d635db9-e42e-43c4-8103-ef1598678aa5</t>
+        </is>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>2026-05-07T22:14:14.517Z</t>
+        </is>
+      </c>
+      <c r="D1818" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1818" t="inlineStr"/>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>2a0723a9-65b8-4425-9640-29747664b7f4</t>
+        </is>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>2026-05-07T22:16:53.851Z</t>
+        </is>
+      </c>
+      <c r="D1819" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1819" t="inlineStr">
+        <is>
+          <t>Warrant service</t>
+        </is>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>f8345135-9554-4597-9ac9-42b88076bce6</t>
+        </is>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>2026-05-07T22:17:17.618Z</t>
+        </is>
+      </c>
+      <c r="D1820" t="n">
+        <v>526</v>
+      </c>
+      <c r="E1820" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1820"/>
+  <dimension ref="A1:E1841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41636,6 +41636,499 @@
       </c>
       <c r="E1820" t="inlineStr"/>
     </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>28c75e2c-53b1-4de0-ae65-279b533a8c0d</t>
+        </is>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>2026-05-08T01:01:54.933Z</t>
+        </is>
+      </c>
+      <c r="D1821" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1821" t="inlineStr">
+        <is>
+          <t>594PC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>73ad0d44-d0d7-4ae8-976a-6c5e97d652a1</t>
+        </is>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>2026-05-08T02:18:05.755Z</t>
+        </is>
+      </c>
+      <c r="D1822" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1822" t="inlineStr">
+        <is>
+          <t>594 SUSPECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>765363ae-a855-49db-9d33-62419dc05d8d</t>
+        </is>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>2026-05-08T03:05:44.731Z</t>
+        </is>
+      </c>
+      <c r="D1823" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1823" t="inlineStr">
+        <is>
+          <t>594 SUSPECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>4530d32c-1d6d-4b20-b9a4-a293c8e1f3fc</t>
+        </is>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>2026-05-08T03:09:34.136Z</t>
+        </is>
+      </c>
+      <c r="D1824" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1824" t="inlineStr"/>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>263e85d7-9309-4917-a1b7-a7aa3ab63193</t>
+        </is>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>2026-05-08T03:31:06.801Z</t>
+        </is>
+      </c>
+      <c r="D1825" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1825" t="inlineStr">
+        <is>
+          <t>wanted person</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>9593be95-879d-4bf5-afbe-fe6bc8ecb8bd</t>
+        </is>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>2026-05-08T04:04:41.935Z</t>
+        </is>
+      </c>
+      <c r="D1826" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1826" t="inlineStr">
+        <is>
+          <t>WANTED SUBJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr">
+        <is>
+          <t>5b207aef-b4ce-4675-9903-3a4b3ce00df8</t>
+        </is>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>2026-05-08T05:52:05.681Z</t>
+        </is>
+      </c>
+      <c r="D1827" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1827" t="inlineStr"/>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>e60023d9-8a3b-44f3-9ed2-cc3b3a1fe829</t>
+        </is>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>2026-05-08T06:02:41.165Z</t>
+        </is>
+      </c>
+      <c r="D1828" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1828" t="inlineStr">
+        <is>
+          <t>wanted person</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>d248c7fd-513b-481b-85aa-c1fdd6fb5e27</t>
+        </is>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>2026-05-08T06:19:30.425Z</t>
+        </is>
+      </c>
+      <c r="D1829" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1829" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>e1c5bfc8-bdc3-48d2-bf1f-d8358a8b68a0</t>
+        </is>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>2026-05-08T07:14:53.026Z</t>
+        </is>
+      </c>
+      <c r="D1830" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1830" t="inlineStr">
+        <is>
+          <t>594 SUSPECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>4abfae8a-6740-42c3-86a3-b6b93448419b</t>
+        </is>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>2026-05-08T16:01:54.371Z</t>
+        </is>
+      </c>
+      <c r="D1831" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1831" t="inlineStr"/>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>0a658f26-bbd4-4ed9-a9f7-5af4f4590957</t>
+        </is>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>2026-05-08T16:24:09.672Z</t>
+        </is>
+      </c>
+      <c r="D1832" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1832" t="inlineStr"/>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>d9da8e6b-601c-47cb-9af2-c49bdba35363</t>
+        </is>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>2026-05-08T16:35:10.860Z</t>
+        </is>
+      </c>
+      <c r="D1833" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1833" t="inlineStr"/>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>d1ac4ae8-de94-4a37-a908-50e87a9375df</t>
+        </is>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>2026-05-08T16:57:47.163Z</t>
+        </is>
+      </c>
+      <c r="D1834" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1834" t="inlineStr">
+        <is>
+          <t>BURG SUSPECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>1c4d6303-d76e-4257-9d04-776788f79e57</t>
+        </is>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>2026-05-08T21:09:01.107Z</t>
+        </is>
+      </c>
+      <c r="D1835" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1835" t="inlineStr">
+        <is>
+          <t>Drug</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>794c0a5f-e8dc-47d4-8715-beeb840e24fc</t>
+        </is>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t>2026-05-08T21:24:11.605Z</t>
+        </is>
+      </c>
+      <c r="D1836" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1836" t="inlineStr"/>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>f861e09b-1c5b-46a6-bc9f-72c879e8da61</t>
+        </is>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:50:56.994Z</t>
+        </is>
+      </c>
+      <c r="D1837" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1837" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>8f22bcae-a5f1-4e62-af86-c7db1ea14aa2</t>
+        </is>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:51:26.997Z</t>
+        </is>
+      </c>
+      <c r="D1838" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1838" t="inlineStr"/>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>0b904600-c49d-4a92-a014-8cea426d9dc2</t>
+        </is>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:51:36.978Z</t>
+        </is>
+      </c>
+      <c r="D1839" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1839" t="inlineStr"/>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>af8eec3f-95f2-4d8e-89df-9446b256f774</t>
+        </is>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:51:43.346Z</t>
+        </is>
+      </c>
+      <c r="D1840" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1840" t="inlineStr">
+        <is>
+          <t>sus id</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>67f7dcf6-3fda-45d5-90d8-02ecb19766b7</t>
+        </is>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>2026-05-08T23:26:26.260Z</t>
+        </is>
+      </c>
+      <c r="D1841" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1841" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1841"/>
+  <dimension ref="A1:E1845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42129,6 +42129,98 @@
         </is>
       </c>
     </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>ff77baa9-4b66-4e02-a633-5e824482bc85</t>
+        </is>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>2026-05-09T19:19:42.378Z</t>
+        </is>
+      </c>
+      <c r="D1842" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1842" t="inlineStr"/>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>5fdc53e2-c108-4690-ae0b-b2ac02abeba9</t>
+        </is>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>2026-05-09T21:21:10.152Z</t>
+        </is>
+      </c>
+      <c r="D1843" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1843" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>1e5d8573-36ba-4ec4-bf86-132ec01d861f</t>
+        </is>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>2026-05-09T21:53:49.664Z</t>
+        </is>
+      </c>
+      <c r="D1844" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1844" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>7f3cfd6f-ea60-4511-8ab0-790791fb644d</t>
+        </is>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>2026-05-09T22:12:19.775Z</t>
+        </is>
+      </c>
+      <c r="D1845" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1845" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1845"/>
+  <dimension ref="A1:E1852"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42221,6 +42221,165 @@
       </c>
       <c r="E1845" t="inlineStr"/>
     </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>5222167e-8ff0-4b3d-b3ce-bd74122f43b0</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>2026-05-10T03:11:11.589Z</t>
+        </is>
+      </c>
+      <c r="D1846" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1846" t="inlineStr"/>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>b0454fe2-23eb-4481-9a0d-11405ccf5c5d</t>
+        </is>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>2026-05-10T05:27:48.716Z</t>
+        </is>
+      </c>
+      <c r="D1847" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1847" t="inlineStr">
+        <is>
+          <t>unknown reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>181dd89e-46b6-49d0-a585-3276e65be37e</t>
+        </is>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>2026-05-10T18:25:31.463Z</t>
+        </is>
+      </c>
+      <c r="D1848" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1848" t="inlineStr"/>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>6c823e48-f3d0-42de-ae69-4f49576dd6f5</t>
+        </is>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>2026-05-10T18:37:19.668Z</t>
+        </is>
+      </c>
+      <c r="D1849" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1849" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>ad8cdbcf-0d41-468c-8c69-b7d360b371dd</t>
+        </is>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>2026-05-10T18:40:55.579Z</t>
+        </is>
+      </c>
+      <c r="D1850" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1850" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>0d3cb786-05bd-4781-989f-e18175ea465c</t>
+        </is>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>2026-05-10T20:54:08.104Z</t>
+        </is>
+      </c>
+      <c r="D1851" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1851" t="inlineStr"/>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>64a984b3-17be-4c2f-9acd-632e354d1842</t>
+        </is>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>2026-05-10T21:01:30.293Z</t>
+        </is>
+      </c>
+      <c r="D1852" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1852" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1852"/>
+  <dimension ref="A1:E1864"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42380,6 +42380,274 @@
       </c>
       <c r="E1852" t="inlineStr"/>
     </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>41bdbe4d-9142-4d6f-bcd1-478ac48e8084</t>
+        </is>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>2026-05-11T00:23:28.420Z</t>
+        </is>
+      </c>
+      <c r="D1853" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1853" t="inlineStr"/>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>8f25665e-0729-4c81-b4cc-874c7b3e0ac4</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>2026-05-11T08:24:18.871Z</t>
+        </is>
+      </c>
+      <c r="D1854" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1854" t="inlineStr"/>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>725112d0-9128-4a7d-96de-8569292e7ace</t>
+        </is>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>2026-05-11T08:25:16.926Z</t>
+        </is>
+      </c>
+      <c r="D1855" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1855" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>6d7c7216-fd62-4987-a40a-097fe051cb52</t>
+        </is>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>2026-05-11T11:42:50.097Z</t>
+        </is>
+      </c>
+      <c r="D1856" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1856" t="inlineStr">
+        <is>
+          <t>suspect id</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>9fdc949b-897b-4e55-ba0e-5fdab6f81206</t>
+        </is>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>2026-05-11T16:42:03.070Z</t>
+        </is>
+      </c>
+      <c r="D1857" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1857" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>80230dc5-e88f-4889-8170-03e9878c09ef</t>
+        </is>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>2026-05-11T18:26:53.629Z</t>
+        </is>
+      </c>
+      <c r="D1858" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1858" t="inlineStr"/>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>fba8bb62-ede5-4a23-ad8b-bc80c49abec1</t>
+        </is>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>2026-05-11T19:25:25.049Z</t>
+        </is>
+      </c>
+      <c r="D1859" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1859" t="inlineStr"/>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>c48db57d-2f9c-443d-9f16-dde47cbde301</t>
+        </is>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>2026-05-11T19:57:16.124Z</t>
+        </is>
+      </c>
+      <c r="D1860" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1860" t="inlineStr"/>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>d21ec3d2-c5a0-423d-be4d-cfaddaaf2b9c</t>
+        </is>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>2026-05-11T20:04:29.076Z</t>
+        </is>
+      </c>
+      <c r="D1861" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1861" t="inlineStr"/>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>1384c3c8-7aea-414d-b677-518bfd44acc3</t>
+        </is>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>2026-05-11T20:15:46.509Z</t>
+        </is>
+      </c>
+      <c r="D1862" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1862" t="inlineStr"/>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>323a7e84-8b1d-4715-b938-702dad56fa29</t>
+        </is>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>2026-05-11T22:19:01.616Z</t>
+        </is>
+      </c>
+      <c r="D1863" t="n">
+        <v>534</v>
+      </c>
+      <c r="E1863" t="inlineStr"/>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>c03e21c5-2088-40d9-b5f5-d3780e705d9e</t>
+        </is>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>2026-05-11T23:47:29.367Z</t>
+        </is>
+      </c>
+      <c r="D1864" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1864" t="inlineStr">
+        <is>
+          <t>susp vehicle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1864"/>
+  <dimension ref="A1:E1882"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42648,6 +42648,436 @@
         </is>
       </c>
     </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>50ee9e10-5384-4f02-8b9b-ba9a6eadd5e3</t>
+        </is>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>2026-05-12T00:02:46.892Z</t>
+        </is>
+      </c>
+      <c r="D1865" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1865" t="inlineStr">
+        <is>
+          <t>susp vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>2543017b-2cda-4aa7-a925-ffa214cb9f62</t>
+        </is>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>2026-05-12T00:58:45.350Z</t>
+        </is>
+      </c>
+      <c r="D1866" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1866" t="inlineStr">
+        <is>
+          <t>warrant-associated vehicle drive all time</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>9ff9818a-a2d1-4ce3-93ad-42b1e2db8a61</t>
+        </is>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>2026-05-12T02:48:05.459Z</t>
+        </is>
+      </c>
+      <c r="D1867" t="n">
+        <v>493</v>
+      </c>
+      <c r="E1867" t="inlineStr"/>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>de043f04-077b-45c8-9b9f-253e64c6e0fc</t>
+        </is>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>2026-05-12T06:06:35.556Z</t>
+        </is>
+      </c>
+      <c r="D1868" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1868" t="inlineStr">
+        <is>
+          <t>166(a)(4)PC suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>f407607c-3d19-45b8-9dc7-ee9117d0ec54</t>
+        </is>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>2026-05-12T10:46:25.509Z</t>
+        </is>
+      </c>
+      <c r="D1869" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1869" t="inlineStr"/>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>6f0cd025-2cf8-429f-9407-bd23d67395f6</t>
+        </is>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>2026-05-12T12:33:11.196Z</t>
+        </is>
+      </c>
+      <c r="D1870" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1870" t="inlineStr"/>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>11973c7c-84bd-4eca-a318-cefbdfe615fd</t>
+        </is>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>2026-05-12T14:49:38.931Z</t>
+        </is>
+      </c>
+      <c r="D1871" t="n">
+        <v>534</v>
+      </c>
+      <c r="E1871" t="inlineStr"/>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>0116dd6f-6eef-4ee9-8f7f-6dbb67d7f85d</t>
+        </is>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>2026-05-12T18:07:00.730Z</t>
+        </is>
+      </c>
+      <c r="D1872" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1872" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>f25538f0-28c5-44cb-bfdf-9870bfeb3d7b</t>
+        </is>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>2026-05-12T19:05:35.836Z</t>
+        </is>
+      </c>
+      <c r="D1873" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1873" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>6ee93118-c39a-445f-95d5-299c4e7876af</t>
+        </is>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>2026-05-12T19:25:32.476Z</t>
+        </is>
+      </c>
+      <c r="D1874" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1874" t="inlineStr">
+        <is>
+          <t>245 PC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>7d08c80d-4ddd-448a-b5c9-d6f591de2249</t>
+        </is>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>2026-05-12T20:29:23.430Z</t>
+        </is>
+      </c>
+      <c r="D1875" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1875" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>e52ed9d6-41e8-4268-9f03-33470263f31d</t>
+        </is>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>2026-05-12T20:29:59.330Z</t>
+        </is>
+      </c>
+      <c r="D1876" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1876" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>6084edc8-8fbd-4266-9dd4-65ab06653426</t>
+        </is>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>2026-05-12T21:34:35.588Z</t>
+        </is>
+      </c>
+      <c r="D1877" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1877" t="inlineStr">
+        <is>
+          <t>warrant suspect daily use veh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>f4bd99c5-4c56-415b-a3c9-eba4c4539bea</t>
+        </is>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>2026-05-12T21:36:27.493Z</t>
+        </is>
+      </c>
+      <c r="D1878" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1878" t="inlineStr">
+        <is>
+          <t>STOLEN VEHICLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>6eb42081-eff4-4a80-8b94-a9addbd6cdef</t>
+        </is>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>2026-05-12T22:51:58.473Z</t>
+        </is>
+      </c>
+      <c r="D1879" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1879" t="inlineStr"/>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>426b2c87-157e-49b2-a2a7-9d81de15e6c3</t>
+        </is>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>2026-05-12T23:40:07.937Z</t>
+        </is>
+      </c>
+      <c r="D1880" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1880" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>cd760a5e-0338-436c-a3c5-e172d1af70f3</t>
+        </is>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>2026-05-12T23:43:54.665Z</t>
+        </is>
+      </c>
+      <c r="D1881" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1881" t="inlineStr">
+        <is>
+          <t>veh associated to res for warrant suspect-rocole</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>f55c3eb9-4fe9-4b4c-8998-d60d335431d1</t>
+        </is>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>2026-05-12T23:51:17.155Z</t>
+        </is>
+      </c>
+      <c r="D1882" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1882" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1882"/>
+  <dimension ref="A1:E1894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43078,6 +43078,278 @@
         </is>
       </c>
     </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>8712bbe5-4c45-4b38-9f21-de01eb855fc6</t>
+        </is>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>2026-05-13T03:38:02.002Z</t>
+        </is>
+      </c>
+      <c r="D1883" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1883" t="inlineStr"/>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>109a2b21-f9a3-4687-81f0-56e91f666740</t>
+        </is>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>2026-05-13T04:01:26.146Z</t>
+        </is>
+      </c>
+      <c r="D1884" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1884" t="inlineStr"/>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>5275d740-4e6c-4fed-bb67-2f7304ad78c3</t>
+        </is>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>2026-05-13T08:39:04.816Z</t>
+        </is>
+      </c>
+      <c r="D1885" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1885" t="inlineStr"/>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>c8e8cf27-a826-4699-9c8b-0f3e4a593955</t>
+        </is>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>2026-05-13T14:48:45.289Z</t>
+        </is>
+      </c>
+      <c r="D1886" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1886" t="inlineStr"/>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>1c399ccd-bbe8-41f6-b759-e575e10f3319</t>
+        </is>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>2026-05-13T15:05:45.338Z</t>
+        </is>
+      </c>
+      <c r="D1887" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1887" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>73db1b34-f811-4309-972b-919528b50bcd</t>
+        </is>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>2026-05-13T15:11:16.543Z</t>
+        </is>
+      </c>
+      <c r="D1888" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1888" t="inlineStr"/>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>c8d2457d-8cf7-46d6-ae17-350a7449205a</t>
+        </is>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>2026-05-13T16:18:05.923Z</t>
+        </is>
+      </c>
+      <c r="D1889" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1889" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>871d27e3-2bcf-4d79-a095-5bb86fe53544</t>
+        </is>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>2026-05-13T16:36:52.864Z</t>
+        </is>
+      </c>
+      <c r="D1890" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1890" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>7f9c6833-91f3-4af2-9d6b-b61814f078ad</t>
+        </is>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>2026-05-13T17:00:39.704Z</t>
+        </is>
+      </c>
+      <c r="D1891" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1891" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>0251d794-6e32-43c9-ad4f-83d2f7b0b9ba</t>
+        </is>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>2026-05-13T17:08:42.874Z</t>
+        </is>
+      </c>
+      <c r="D1892" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1892" t="inlineStr">
+        <is>
+          <t>sus id</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>6d7438fa-1d52-4e68-92af-4450478b1279</t>
+        </is>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>2026-05-13T17:23:10.373Z</t>
+        </is>
+      </c>
+      <c r="D1893" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1893" t="inlineStr"/>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>10a6f8da-ab14-40d5-b5c7-aacea0d605ef</t>
+        </is>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>2026-05-13T19:03:00.114Z</t>
+        </is>
+      </c>
+      <c r="D1894" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1894" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1894"/>
+  <dimension ref="A1:E1900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43350,6 +43350,144 @@
       </c>
       <c r="E1894" t="inlineStr"/>
     </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>0e5beb4b-4c9e-4268-8f51-88a1f1a5b3ca</t>
+        </is>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>2026-05-14T18:29:59.228Z</t>
+        </is>
+      </c>
+      <c r="D1895" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1895" t="inlineStr"/>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>ce8d7de5-0dbb-4b8f-8bc3-622c1b5e409f</t>
+        </is>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>2026-05-14T18:48:36.456Z</t>
+        </is>
+      </c>
+      <c r="D1896" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1896" t="inlineStr"/>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>e16a73aa-f5ad-4c26-9627-a0d7a935e23e</t>
+        </is>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>2026-05-14T18:54:31.699Z</t>
+        </is>
+      </c>
+      <c r="D1897" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1897" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>631eb5f6-2533-4b43-b307-248069c4f9ce</t>
+        </is>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>2026-05-14T19:09:39.768Z</t>
+        </is>
+      </c>
+      <c r="D1898" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1898" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>a1f7070b-c184-49bd-8db9-2fdc4d369d0c</t>
+        </is>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>2026-05-14T20:08:50.965Z</t>
+        </is>
+      </c>
+      <c r="D1899" t="n">
+        <v>783</v>
+      </c>
+      <c r="E1899" t="inlineStr"/>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>70af97a7-2433-401e-a1fa-35248d847ebd</t>
+        </is>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>2026-05-14T21:17:03.032Z</t>
+        </is>
+      </c>
+      <c r="D1900" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1900" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1900"/>
+  <dimension ref="A1:E1909"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43488,6 +43488,219 @@
         </is>
       </c>
     </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>1eea6294-37c4-4f9c-bd84-5d8ba105bd5d</t>
+        </is>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>2026-05-15T02:58:32.186Z</t>
+        </is>
+      </c>
+      <c r="D1901" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1901" t="inlineStr">
+        <is>
+          <t>Hit and Run with injury, Ramey</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>dfd51eff-8452-4506-91a7-9d9dbd37f3a8</t>
+        </is>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>2026-05-15T03:03:58.569Z</t>
+        </is>
+      </c>
+      <c r="D1902" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1902" t="inlineStr"/>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>114bf0e6-64dc-4267-9e41-b73dd5897895</t>
+        </is>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t>2026-05-15T03:48:44.091Z</t>
+        </is>
+      </c>
+      <c r="D1903" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1903" t="inlineStr">
+        <is>
+          <t>Sus loc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>2dbf89c1-0574-4aab-bd86-44c1490c5e99</t>
+        </is>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>2026-05-15T04:04:08.784Z</t>
+        </is>
+      </c>
+      <c r="D1904" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1904" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>873f048c-8dc5-46b7-a499-7757efbb4a87</t>
+        </is>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>2026-05-15T15:20:42.322Z</t>
+        </is>
+      </c>
+      <c r="D1905" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1905" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>3d258da0-1a71-485f-9655-cfa3e94fe4bb</t>
+        </is>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>2026-05-15T15:37:52.943Z</t>
+        </is>
+      </c>
+      <c r="D1906" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1906" t="inlineStr">
+        <is>
+          <t>person of interest</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>847b4389-b9a4-46ff-b42f-567967637f60</t>
+        </is>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>2026-05-15T16:52:43.271Z</t>
+        </is>
+      </c>
+      <c r="D1907" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1907" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>792220d8-b614-4bb9-bfa8-57264c9c8697</t>
+        </is>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>2026-05-15T22:03:57.656Z</t>
+        </is>
+      </c>
+      <c r="D1908" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1908" t="inlineStr"/>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>bfe429ba-0d65-4a9a-b6f0-00f61126dde0</t>
+        </is>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>2026-05-15T23:14:24.109Z</t>
+        </is>
+      </c>
+      <c r="D1909" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1909" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1909"/>
+  <dimension ref="A1:E1922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43701,6 +43701,315 @@
       </c>
       <c r="E1909" t="inlineStr"/>
     </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>726df8c2-d606-4cfd-ac24-c9324eeb8894</t>
+        </is>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>2026-05-16T05:58:48.835Z</t>
+        </is>
+      </c>
+      <c r="D1910" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1910" t="inlineStr"/>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>014a21d1-0336-48aa-a912-5470cc1e2b9e</t>
+        </is>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>2026-05-16T06:00:42.886Z</t>
+        </is>
+      </c>
+      <c r="D1911" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1911" t="inlineStr"/>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>5bf3a94d-e6c2-4d8a-82f2-e06dbb594f92</t>
+        </is>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t>2026-05-16T06:03:41.293Z</t>
+        </is>
+      </c>
+      <c r="D1912" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1912" t="inlineStr">
+        <is>
+          <t>sus</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>052500e2-e9d8-4a1b-a004-0e6fa3f1ef7d</t>
+        </is>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>2026-05-16T06:04:12.382Z</t>
+        </is>
+      </c>
+      <c r="D1913" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1913" t="inlineStr">
+        <is>
+          <t>dvsuspec</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>6bee6a9e-64e0-4dcb-8803-b353b38670cb</t>
+        </is>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>2026-05-16T06:06:36.755Z</t>
+        </is>
+      </c>
+      <c r="D1914" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1914" t="inlineStr">
+        <is>
+          <t>susp</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>3974d695-e66e-45d1-a30b-a0ef6c55ee5b</t>
+        </is>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>2026-05-16T06:15:38.317Z</t>
+        </is>
+      </c>
+      <c r="D1915" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1915" t="inlineStr">
+        <is>
+          <t>Sus Loc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>0e4451dc-4807-4b6f-bcec-dcb6000fcd4f</t>
+        </is>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t>2026-05-16T06:18:37.256Z</t>
+        </is>
+      </c>
+      <c r="D1916" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1916" t="inlineStr"/>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>f6ccfd61-9483-4b6f-b264-b1eef3a59a1d</t>
+        </is>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t>2026-05-16T07:33:17.461Z</t>
+        </is>
+      </c>
+      <c r="D1917" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1917" t="inlineStr">
+        <is>
+          <t>dvsuspec</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>93e17d96-fa82-49d3-8699-decd746a1d18</t>
+        </is>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t>2026-05-16T07:33:50.155Z</t>
+        </is>
+      </c>
+      <c r="D1918" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1918" t="inlineStr">
+        <is>
+          <t>CRIMINAL INVEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>5033a0b2-dce3-4201-a4af-5b889cda6a29</t>
+        </is>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>2026-05-16T07:35:51.617Z</t>
+        </is>
+      </c>
+      <c r="D1919" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1919" t="inlineStr"/>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>8aebced5-8974-47b1-aab8-6e78661910f0</t>
+        </is>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>2026-05-16T07:36:07.833Z</t>
+        </is>
+      </c>
+      <c r="D1920" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1920" t="inlineStr">
+        <is>
+          <t>Sus Loc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>343bacf2-9c14-4945-87d9-6775f5c752b4</t>
+        </is>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>2026-05-16T10:00:38.953Z</t>
+        </is>
+      </c>
+      <c r="D1921" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1921" t="inlineStr">
+        <is>
+          <t>Sus Loc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>a0970a25-d756-43eb-a41f-2e5f206b127e</t>
+        </is>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>2026-05-16T13:32:45.775Z</t>
+        </is>
+      </c>
+      <c r="D1922" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1922" t="inlineStr">
+        <is>
+          <t>Sus Loc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1922"/>
+  <dimension ref="A1:E1929"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44010,6 +44010,161 @@
         </is>
       </c>
     </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>e7ac8d02-043a-4531-b22c-eb613736c63d</t>
+        </is>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t>2026-05-17T03:16:40.984Z</t>
+        </is>
+      </c>
+      <c r="D1923" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1923" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>aa7d15fb-cbfd-4eea-9ff2-6773c365d018</t>
+        </is>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>2026-05-17T03:59:45.919Z</t>
+        </is>
+      </c>
+      <c r="D1924" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1924" t="inlineStr"/>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>00c1c237-1ea0-4f83-9ae1-2fb3b6d893c0</t>
+        </is>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>2026-05-17T04:01:47.456Z</t>
+        </is>
+      </c>
+      <c r="D1925" t="n">
+        <v>527</v>
+      </c>
+      <c r="E1925" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>03e4c2eb-6b81-463d-87d9-437de04ae76b</t>
+        </is>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t>2026-05-17T04:04:17.510Z</t>
+        </is>
+      </c>
+      <c r="D1926" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1926" t="inlineStr"/>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>d1c68551-8cdc-4dbf-907d-5103ca38b1c2</t>
+        </is>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>2026-05-17T08:52:15.898Z</t>
+        </is>
+      </c>
+      <c r="D1927" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1927" t="inlineStr"/>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>d8cdc5ba-bacb-4b78-ab74-66d8f8c29b7c</t>
+        </is>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>2026-05-17T13:44:44.832Z</t>
+        </is>
+      </c>
+      <c r="D1928" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1928" t="inlineStr"/>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>d7e186cf-5b96-4040-94e0-a83a7d9ffabf</t>
+        </is>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>2026-05-17T21:17:59.728Z</t>
+        </is>
+      </c>
+      <c r="D1929" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1929" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1929"/>
+  <dimension ref="A1:E1942"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44165,6 +44165,295 @@
       </c>
       <c r="E1929" t="inlineStr"/>
     </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>fbd3a757-501b-429d-8ae9-d95791614097</t>
+        </is>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>2026-05-18T00:34:30.524Z</t>
+        </is>
+      </c>
+      <c r="D1930" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1930" t="inlineStr"/>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>b554c49c-2a18-43fb-b64c-baf3b40ae92f</t>
+        </is>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t>2026-05-18T00:53:18.205Z</t>
+        </is>
+      </c>
+      <c r="D1931" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1931" t="inlineStr"/>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>cf5803fa-f50b-479d-a38f-310661b15e8c</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>2026-05-18T04:06:16.132Z</t>
+        </is>
+      </c>
+      <c r="D1932" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1932" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>8fe4885e-af5e-4e14-85dc-e920be2f4061</t>
+        </is>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>2026-05-18T10:36:15.663Z</t>
+        </is>
+      </c>
+      <c r="D1933" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1933" t="inlineStr"/>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>b9cc4dd5-6df9-451d-80ec-997796355531</t>
+        </is>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>2026-05-18T10:37:04.921Z</t>
+        </is>
+      </c>
+      <c r="D1934" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1934" t="inlineStr">
+        <is>
+          <t>Sus id</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>3dca0935-8076-4f02-9279-1ff945fd7372</t>
+        </is>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>2026-05-18T15:07:56.882Z</t>
+        </is>
+      </c>
+      <c r="D1935" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1935" t="inlineStr"/>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>fc376f8f-bfbc-431e-b7c1-1180fdd8c8c8</t>
+        </is>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>2026-05-18T16:05:51.093Z</t>
+        </is>
+      </c>
+      <c r="D1936" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1936" t="inlineStr"/>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>09343d92-3a5d-40d7-9f19-ac162c58235c</t>
+        </is>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>2026-05-18T16:06:15.883Z</t>
+        </is>
+      </c>
+      <c r="D1937" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1937" t="inlineStr">
+        <is>
+          <t>STOLEN VEHICLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>9e876c16-6524-4a82-ba36-3addeb08cd31</t>
+        </is>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>2026-05-18T16:12:20.184Z</t>
+        </is>
+      </c>
+      <c r="D1938" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1938" t="inlineStr"/>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>0fb8a458-ad35-4bed-b787-0d7fa7693e11</t>
+        </is>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1939" t="inlineStr">
+        <is>
+          <t>2026-05-18T18:02:32.674Z</t>
+        </is>
+      </c>
+      <c r="D1939" t="n">
+        <v>493</v>
+      </c>
+      <c r="E1939" t="inlineStr"/>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>d744c955-9b96-41eb-8842-dc7446256ca6</t>
+        </is>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1940" t="inlineStr">
+        <is>
+          <t>2026-05-18T20:39:46.316Z</t>
+        </is>
+      </c>
+      <c r="D1940" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1940" t="inlineStr"/>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>5adaaf0d-ba37-4af2-930d-acd029b8a2cb</t>
+        </is>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1941" t="inlineStr">
+        <is>
+          <t>2026-05-18T21:04:37.014Z</t>
+        </is>
+      </c>
+      <c r="D1941" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1941" t="inlineStr">
+        <is>
+          <t>theft</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>754706dd-87aa-4ec7-9ccd-81a86c486866</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C1942" t="inlineStr">
+        <is>
+          <t>2026-05-18T21:39:56.529Z</t>
+        </is>
+      </c>
+      <c r="D1942" t="n">
+        <v>570</v>
+      </c>
+      <c r="E1942" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2065"/>
+  <dimension ref="A1:E2076"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47209,6 +47209,237 @@
       </c>
       <c r="E2065" t="inlineStr"/>
     </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>23c93c1c-c23e-4ea2-8c86-807239d027be</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2066" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:09:09.601Z</t>
+        </is>
+      </c>
+      <c r="D2066" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2066" t="inlineStr"/>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>d9ab4673-c952-45c7-89db-0cf074e59ba4</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2067" t="inlineStr">
+        <is>
+          <t>2026-06-01T02:53:26.448Z</t>
+        </is>
+      </c>
+      <c r="D2067" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2067" t="inlineStr"/>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>1edbda86-32bd-4e8e-b28d-e89bc036a60d</t>
+        </is>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2068" t="inlineStr">
+        <is>
+          <t>2026-06-01T04:43:31.076Z</t>
+        </is>
+      </c>
+      <c r="D2068" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2068" t="inlineStr"/>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>e03be57a-fe8e-4e8f-9fad-6b08d01eb580</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2069" t="inlineStr">
+        <is>
+          <t>2026-06-01T05:05:38.564Z</t>
+        </is>
+      </c>
+      <c r="D2069" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2069" t="inlineStr"/>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>db781ce6-ecac-4fd8-9e0e-391faa1f0a30</t>
+        </is>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2070" t="inlineStr">
+        <is>
+          <t>2026-06-01T06:27:13.352Z</t>
+        </is>
+      </c>
+      <c r="D2070" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2070" t="inlineStr"/>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>92e1998c-70d1-4f24-81db-6ac3e9257dcf</t>
+        </is>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2071" t="inlineStr">
+        <is>
+          <t>2026-06-01T07:24:32.815Z</t>
+        </is>
+      </c>
+      <c r="D2071" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2071" t="inlineStr"/>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
+        <is>
+          <t>c1fde341-0220-4e33-bd3f-3aec60e1c2ba</t>
+        </is>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2072" t="inlineStr">
+        <is>
+          <t>2026-06-01T08:54:28.335Z</t>
+        </is>
+      </c>
+      <c r="D2072" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2072" t="inlineStr"/>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>ef73247f-311c-4bf4-b278-887aa572b5ed</t>
+        </is>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2073" t="inlineStr">
+        <is>
+          <t>2026-06-01T09:01:17.202Z</t>
+        </is>
+      </c>
+      <c r="D2073" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2073" t="inlineStr"/>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>808390bb-d989-4f42-a518-08f80fbac008</t>
+        </is>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2074" t="inlineStr">
+        <is>
+          <t>2026-06-01T11:25:31.422Z</t>
+        </is>
+      </c>
+      <c r="D2074" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2074" t="inlineStr"/>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>a362df71-2370-4af8-9207-aa16d623ec0c</t>
+        </is>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2075" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:49:32.002Z</t>
+        </is>
+      </c>
+      <c r="D2075" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2075" t="inlineStr"/>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>670ae3f4-f212-4703-a2fd-cf820360dd8d</t>
+        </is>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2076" t="inlineStr">
+        <is>
+          <t>2026-06-01T19:11:34.451Z</t>
+        </is>
+      </c>
+      <c r="D2076" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2076" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2076"/>
+  <dimension ref="A1:E2090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47440,6 +47440,312 @@
       </c>
       <c r="E2076" t="inlineStr"/>
     </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>15fe1eeb-5693-4091-9021-5badd56d6dd3</t>
+        </is>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2077" t="inlineStr">
+        <is>
+          <t>2026-06-02T05:49:52.184Z</t>
+        </is>
+      </c>
+      <c r="D2077" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2077" t="inlineStr"/>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
+        <is>
+          <t>af4941c4-5fdd-4177-b267-67d09057bd17</t>
+        </is>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2078" t="inlineStr">
+        <is>
+          <t>2026-06-02T06:19:25.404Z</t>
+        </is>
+      </c>
+      <c r="D2078" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2078" t="inlineStr"/>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>52cd081a-cfe5-40d4-a840-836c77e2bb43</t>
+        </is>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2079" t="inlineStr">
+        <is>
+          <t>2026-06-02T08:00:23.651Z</t>
+        </is>
+      </c>
+      <c r="D2079" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2079" t="inlineStr"/>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
+        <is>
+          <t>7fc54db3-0514-4406-bf4b-f685346bb05c</t>
+        </is>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2080" t="inlineStr">
+        <is>
+          <t>2026-06-02T08:26:14.540Z</t>
+        </is>
+      </c>
+      <c r="D2080" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2080" t="inlineStr"/>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>761ba7ae-3eff-47fb-a711-8d8ae7283c42</t>
+        </is>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2081" t="inlineStr">
+        <is>
+          <t>2026-06-02T09:19:26.903Z</t>
+        </is>
+      </c>
+      <c r="D2081" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2081" t="inlineStr"/>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
+        <is>
+          <t>1a9dba91-a169-4dd1-b81b-e930df50e2e8</t>
+        </is>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2082" t="inlineStr">
+        <is>
+          <t>2026-06-02T10:04:42.176Z</t>
+        </is>
+      </c>
+      <c r="D2082" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2082" t="inlineStr"/>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>f3327cce-cf6b-4e01-87e0-1f259728d00a</t>
+        </is>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2083" t="inlineStr">
+        <is>
+          <t>2026-06-02T11:00:33.531Z</t>
+        </is>
+      </c>
+      <c r="D2083" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2083" t="inlineStr"/>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
+        <is>
+          <t>fbda700a-a200-4336-8116-fe129e184e92</t>
+        </is>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2084" t="inlineStr">
+        <is>
+          <t>2026-06-02T11:36:02.076Z</t>
+        </is>
+      </c>
+      <c r="D2084" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2084" t="inlineStr"/>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>bd92dfef-89ef-4b94-8b63-bc8caee0c3f6</t>
+        </is>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2085" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:02:34.273Z</t>
+        </is>
+      </c>
+      <c r="D2085" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2085" t="inlineStr"/>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
+        <is>
+          <t>7a65df06-4b86-4013-b505-208e236fd2e4</t>
+        </is>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2086" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:54:12.692Z</t>
+        </is>
+      </c>
+      <c r="D2086" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2086" t="inlineStr"/>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>000a7f04-0af5-4dbb-87ff-4cabb9f6b2a4</t>
+        </is>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2087" t="inlineStr">
+        <is>
+          <t>2026-06-02T20:40:23.019Z</t>
+        </is>
+      </c>
+      <c r="D2087" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
+        <is>
+          <t>8e574847-58c9-4c5b-a902-21b2ab4389a0</t>
+        </is>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2088" t="inlineStr">
+        <is>
+          <t>2026-06-02T20:49:14.947Z</t>
+        </is>
+      </c>
+      <c r="D2088" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2088" t="inlineStr"/>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>0007d8e6-c93c-4f9c-86f2-6b17b1b3402d</t>
+        </is>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2089" t="inlineStr">
+        <is>
+          <t>2026-06-02T21:32:24.095Z</t>
+        </is>
+      </c>
+      <c r="D2089" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
+        <is>
+          <t>f47ab26a-c583-4733-9371-4bf6ec351401</t>
+        </is>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2090" t="inlineStr">
+        <is>
+          <t>2026-06-02T23:34:28.026Z</t>
+        </is>
+      </c>
+      <c r="D2090" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2090"/>
+  <dimension ref="A1:E2106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47746,6 +47746,370 @@
         </is>
       </c>
     </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>cd96099d-a520-4841-9547-135ce9045d24</t>
+        </is>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2091" t="inlineStr">
+        <is>
+          <t>2026-06-03T00:33:24.406Z</t>
+        </is>
+      </c>
+      <c r="D2091" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
+        <is>
+          <t>4694dbff-cf9f-4899-9edb-9813a2409b34</t>
+        </is>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2092" t="inlineStr">
+        <is>
+          <t>2026-06-03T00:35:34.986Z</t>
+        </is>
+      </c>
+      <c r="D2092" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>search warrant</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>4ece91b1-4d0b-4dd3-8eae-e03d34f7cdd9</t>
+        </is>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2093" t="inlineStr">
+        <is>
+          <t>2026-06-03T01:14:18.933Z</t>
+        </is>
+      </c>
+      <c r="D2093" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2093" t="inlineStr"/>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
+        <is>
+          <t>9ffe97fa-907d-468c-982f-55eaad147bc2</t>
+        </is>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2094" t="inlineStr">
+        <is>
+          <t>2026-06-03T04:41:20.936Z</t>
+        </is>
+      </c>
+      <c r="D2094" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2094" t="inlineStr"/>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>8637a408-689b-4785-8abf-3cbc660c6d53</t>
+        </is>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2095" t="inlineStr">
+        <is>
+          <t>2026-06-03T05:36:03.266Z</t>
+        </is>
+      </c>
+      <c r="D2095" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2095" t="inlineStr"/>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>43d91e6c-e5f7-4e75-a219-bf07809b205b</t>
+        </is>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2096" t="inlineStr">
+        <is>
+          <t>2026-06-03T07:06:11.138Z</t>
+        </is>
+      </c>
+      <c r="D2096" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2096" t="inlineStr"/>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>5e655bc9-14d7-452e-9a0a-a2b5fd45f137</t>
+        </is>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2097" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:30:55.114Z</t>
+        </is>
+      </c>
+      <c r="D2097" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2097" t="inlineStr"/>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
+        <is>
+          <t>5d5f37c6-63cd-4d8a-8a72-2f5f44243f62</t>
+        </is>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2098" t="inlineStr">
+        <is>
+          <t>2026-06-03T11:06:59.982Z</t>
+        </is>
+      </c>
+      <c r="D2098" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2098" t="inlineStr"/>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>8b93cb98-e04d-4612-9ddd-940fb15044ab</t>
+        </is>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2099" t="inlineStr">
+        <is>
+          <t>2026-06-03T16:23:12.549Z</t>
+        </is>
+      </c>
+      <c r="D2099" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2099" t="inlineStr"/>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>e64bb5a6-07b0-4657-9d38-8c4945fba278</t>
+        </is>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2100" t="inlineStr">
+        <is>
+          <t>2026-06-03T21:17:06.265Z</t>
+        </is>
+      </c>
+      <c r="D2100" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2100" t="inlineStr"/>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>5e308ca8-acf9-4bca-930d-e562f067e460</t>
+        </is>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2101" t="inlineStr">
+        <is>
+          <t>2026-06-03T21:26:33.449Z</t>
+        </is>
+      </c>
+      <c r="D2101" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>53fffce5-4fda-4a46-971d-6b8b3f26cabf</t>
+        </is>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2102" t="inlineStr">
+        <is>
+          <t>2026-06-03T22:13:12.772Z</t>
+        </is>
+      </c>
+      <c r="D2102" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>69c06401-17e5-4feb-9b2c-e49355b670ad</t>
+        </is>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2103" t="inlineStr">
+        <is>
+          <t>2026-06-03T22:16:11.214Z</t>
+        </is>
+      </c>
+      <c r="D2103" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2103" t="inlineStr"/>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>dbb3f256-2835-4bab-a510-dbd30cad0e98</t>
+        </is>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2104" t="inlineStr">
+        <is>
+          <t>2026-06-03T22:20:56.722Z</t>
+        </is>
+      </c>
+      <c r="D2104" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>5126ce41-6e5a-41b5-92ac-316c75dbae92</t>
+        </is>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2105" t="inlineStr">
+        <is>
+          <t>2026-06-03T23:37:23.885Z</t>
+        </is>
+      </c>
+      <c r="D2105" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>locate possible suspect routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>ee04dfd7-6304-42c8-a712-7e05aad9915b</t>
+        </is>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2106" t="inlineStr">
+        <is>
+          <t>2026-06-03T23:52:14.312Z</t>
+        </is>
+      </c>
+      <c r="D2106" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2106"/>
+  <dimension ref="A1:E2122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48110,6 +48110,378 @@
         </is>
       </c>
     </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>22c5a11b-1bc6-4090-aa3e-d8311a6faef7</t>
+        </is>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2107" t="inlineStr">
+        <is>
+          <t>2026-06-04T00:48:44.510Z</t>
+        </is>
+      </c>
+      <c r="D2107" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2107" t="inlineStr"/>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>a5552174-9154-4bac-b953-d448f9fb207e</t>
+        </is>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2108" t="inlineStr">
+        <is>
+          <t>2026-06-04T00:49:42.933Z</t>
+        </is>
+      </c>
+      <c r="D2108" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>86b3ae85-0600-4d2a-a464-85fad3c763b6</t>
+        </is>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2109" t="inlineStr">
+        <is>
+          <t>2026-06-04T01:24:05.500Z</t>
+        </is>
+      </c>
+      <c r="D2109" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2109" t="inlineStr"/>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>7c71d59a-8c1f-4463-8094-b69db1b7c4a6</t>
+        </is>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2110" t="inlineStr">
+        <is>
+          <t>2026-06-04T01:41:52.447Z</t>
+        </is>
+      </c>
+      <c r="D2110" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>0e3dccf1-4c17-4591-ba14-5c710f7d5e2a</t>
+        </is>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2111" t="inlineStr">
+        <is>
+          <t>2026-06-04T01:53:24.495Z</t>
+        </is>
+      </c>
+      <c r="D2111" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>fc9c7e25-ade6-474d-b56b-99425518d6e2</t>
+        </is>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2112" t="inlineStr">
+        <is>
+          <t>2026-06-04T02:06:15.932Z</t>
+        </is>
+      </c>
+      <c r="D2112" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2112" t="inlineStr"/>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>00efb5d7-c64d-409c-8fcb-c8b9c95616c2</t>
+        </is>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2113" t="inlineStr">
+        <is>
+          <t>2026-06-04T02:09:51.240Z</t>
+        </is>
+      </c>
+      <c r="D2113" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>1efbe249-8030-467a-9edc-3ae3dcbabed4</t>
+        </is>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2114" t="inlineStr">
+        <is>
+          <t>2026-06-04T08:50:11.071Z</t>
+        </is>
+      </c>
+      <c r="D2114" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2114" t="inlineStr"/>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>d9cc3268-709e-48d3-a254-26ea0c9754ec</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2115" t="inlineStr">
+        <is>
+          <t>2026-06-04T10:21:44.376Z</t>
+        </is>
+      </c>
+      <c r="D2115" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2115" t="inlineStr"/>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>14eb7a51-9a86-472b-bfef-9aced19bfdfd</t>
+        </is>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2116" t="inlineStr">
+        <is>
+          <t>2026-06-04T10:22:11.284Z</t>
+        </is>
+      </c>
+      <c r="D2116" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>BOLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>2699cbdf-b8e0-4340-a9d3-e8a31270ba21</t>
+        </is>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2117" t="inlineStr">
+        <is>
+          <t>2026-06-04T16:02:16.677Z</t>
+        </is>
+      </c>
+      <c r="D2117" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>possible suspect vehicle identification</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>8994fc01-0f51-49f0-a51e-fd223a32f7ca</t>
+        </is>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2118" t="inlineStr">
+        <is>
+          <t>2026-06-04T17:24:08.733Z</t>
+        </is>
+      </c>
+      <c r="D2118" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>bcf5ceaf-27a5-4c0f-a64f-382d77a8712a</t>
+        </is>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2119" t="inlineStr">
+        <is>
+          <t>2026-06-04T17:32:47.472Z</t>
+        </is>
+      </c>
+      <c r="D2119" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2119" t="inlineStr"/>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>9ac724b1-dae7-42fa-87bc-f0050ce04f55</t>
+        </is>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2120" t="inlineStr">
+        <is>
+          <t>2026-06-04T18:06:17.571Z</t>
+        </is>
+      </c>
+      <c r="D2120" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>33e426b4-c1c2-4a2d-92f6-0d3ff6365e8b</t>
+        </is>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2121" t="inlineStr">
+        <is>
+          <t>2026-06-04T18:41:54.651Z</t>
+        </is>
+      </c>
+      <c r="D2121" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2121" t="inlineStr"/>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>1ef88ff7-22d3-4f16-b33b-136260a20a5e</t>
+        </is>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2122" t="inlineStr">
+        <is>
+          <t>2026-06-04T20:19:56.547Z</t>
+        </is>
+      </c>
+      <c r="D2122" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2122"/>
+  <dimension ref="A1:E2138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48482,6 +48482,378 @@
         </is>
       </c>
     </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>871a2089-a335-47bd-bb79-03ae42d11068</t>
+        </is>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2123" t="inlineStr">
+        <is>
+          <t>2026-06-05T08:55:01.999Z</t>
+        </is>
+      </c>
+      <c r="D2123" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2123" t="inlineStr"/>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>0cc35d3e-c08f-4ec9-ba25-e0f7917a7172</t>
+        </is>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2124" t="inlineStr">
+        <is>
+          <t>2026-06-05T16:16:01.587Z</t>
+        </is>
+      </c>
+      <c r="D2124" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>01595589-529a-47e1-a5ef-707f06169c60</t>
+        </is>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2125" t="inlineStr">
+        <is>
+          <t>2026-06-05T16:39:55.436Z</t>
+        </is>
+      </c>
+      <c r="D2125" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>possible suspect vehicle identification</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>c182dff6-0a7f-4e0d-8ec4-a05d302b6e1f</t>
+        </is>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2126" t="inlineStr">
+        <is>
+          <t>2026-06-05T16:41:49.720Z</t>
+        </is>
+      </c>
+      <c r="D2126" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>poss sus vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>00feaddf-e49f-48b9-aa17-9745bd12fc1b</t>
+        </is>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2127" t="inlineStr">
+        <is>
+          <t>2026-06-05T16:59:42.667Z</t>
+        </is>
+      </c>
+      <c r="D2127" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2127" t="inlineStr"/>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>8b16fddd-a225-44d1-9d5d-f0ca31103741</t>
+        </is>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2128" t="inlineStr">
+        <is>
+          <t>2026-06-05T17:45:05.349Z</t>
+        </is>
+      </c>
+      <c r="D2128" t="n">
+        <v>492</v>
+      </c>
+      <c r="E2128" t="inlineStr"/>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>6fffed2f-b945-4cf2-be2d-ce51fbfef9af</t>
+        </is>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2129" t="inlineStr">
+        <is>
+          <t>2026-06-05T17:49:24.166Z</t>
+        </is>
+      </c>
+      <c r="D2129" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>a9a9b87f-86db-4982-afb2-1e02610ebde7</t>
+        </is>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2130" t="inlineStr">
+        <is>
+          <t>2026-06-05T18:11:27.515Z</t>
+        </is>
+      </c>
+      <c r="D2130" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2130" t="inlineStr"/>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>b353ab49-10f8-4a76-9af8-3ab542a6888c</t>
+        </is>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2131" t="inlineStr">
+        <is>
+          <t>2026-06-05T18:28:52.390Z</t>
+        </is>
+      </c>
+      <c r="D2131" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>02df5d31-9380-441e-8cd1-85d5264c44f7</t>
+        </is>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2132" t="inlineStr">
+        <is>
+          <t>2026-06-05T19:02:12.213Z</t>
+        </is>
+      </c>
+      <c r="D2132" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>2c0f7517-bfd0-4fe9-b4e2-e0ac51a30212</t>
+        </is>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2133" t="inlineStr">
+        <is>
+          <t>2026-06-05T19:24:47.912Z</t>
+        </is>
+      </c>
+      <c r="D2133" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2133" t="inlineStr"/>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>247250a0-97ca-407b-921d-bcf675108d17</t>
+        </is>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2134" t="inlineStr">
+        <is>
+          <t>2026-06-05T19:26:30.763Z</t>
+        </is>
+      </c>
+      <c r="D2134" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>4e710c35-559d-4138-879e-be63892a825b</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2135" t="inlineStr">
+        <is>
+          <t>2026-06-05T19:27:39.152Z</t>
+        </is>
+      </c>
+      <c r="D2135" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2135" t="inlineStr"/>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>644d7859-28f0-4393-ba51-d5664cba9410</t>
+        </is>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2136" t="inlineStr">
+        <is>
+          <t>2026-06-05T21:31:51.105Z</t>
+        </is>
+      </c>
+      <c r="D2136" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2136" t="inlineStr"/>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>bdb013e3-972a-4d46-8639-0b397d984a18</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>2026-06-05T21:44:55.249Z</t>
+        </is>
+      </c>
+      <c r="D2137" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>70f65379-235e-4b6a-ae73-ca04b431e054</t>
+        </is>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2138" t="inlineStr">
+        <is>
+          <t>2026-06-05T22:49:39.818Z</t>
+        </is>
+      </c>
+      <c r="D2138" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2138"/>
+  <dimension ref="A1:E2155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48854,6 +48854,407 @@
         </is>
       </c>
     </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>85319609-d347-4445-812d-751e6ec2d887</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2139" t="inlineStr">
+        <is>
+          <t>2026-06-06T00:53:07.997Z</t>
+        </is>
+      </c>
+      <c r="D2139" t="n">
+        <v>533</v>
+      </c>
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>1dd36ca0-59f9-4a34-89f5-6dae94ae3538</t>
+        </is>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2140" t="inlineStr">
+        <is>
+          <t>2026-06-06T04:27:01.268Z</t>
+        </is>
+      </c>
+      <c r="D2140" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2140" t="inlineStr"/>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>f180f5f5-4aaa-4c91-8ca5-705c4b3ad288</t>
+        </is>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2141" t="inlineStr">
+        <is>
+          <t>2026-06-06T04:35:37.174Z</t>
+        </is>
+      </c>
+      <c r="D2141" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>wanted person</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>760b0ddd-8505-435f-9c8f-587aa7464518</t>
+        </is>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2142" t="inlineStr">
+        <is>
+          <t>2026-06-06T04:36:38.121Z</t>
+        </is>
+      </c>
+      <c r="D2142" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2142" t="inlineStr"/>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>01e79185-4f89-4b10-8d14-aa8f614bfc6a</t>
+        </is>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2143" t="inlineStr">
+        <is>
+          <t>2026-06-06T05:00:26.198Z</t>
+        </is>
+      </c>
+      <c r="D2143" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>wanted person</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>b04b251a-4342-4e55-8382-49dd0d063da4</t>
+        </is>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2144" t="inlineStr">
+        <is>
+          <t>2026-06-06T05:02:24.434Z</t>
+        </is>
+      </c>
+      <c r="D2144" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2144" t="inlineStr"/>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>eb3d0ec2-0a1e-44ba-ac7c-153c37b805fb</t>
+        </is>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2145" t="inlineStr">
+        <is>
+          <t>2026-06-06T05:15:17.061Z</t>
+        </is>
+      </c>
+      <c r="D2145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2145" t="inlineStr"/>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>10648259-2c62-493d-b6d7-42c641170fcc</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2146" t="inlineStr">
+        <is>
+          <t>2026-06-06T16:09:33.786Z</t>
+        </is>
+      </c>
+      <c r="D2146" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>82d23800-4b7a-4a54-b419-bb2335539149</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>2026-06-06T17:03:30.750Z</t>
+        </is>
+      </c>
+      <c r="D2147" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>a54366ad-4982-444b-9c8a-54628a9f95a2</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2148" t="inlineStr">
+        <is>
+          <t>2026-06-06T17:40:47.751Z</t>
+        </is>
+      </c>
+      <c r="D2148" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>013ddaa4-a826-43f9-b54e-5d4989db30fd</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2149" t="inlineStr">
+        <is>
+          <t>2026-06-06T17:49:17.379Z</t>
+        </is>
+      </c>
+      <c r="D2149" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2149" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>8d8de854-703c-4842-a0c5-d30f4f406a18</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2150" t="inlineStr">
+        <is>
+          <t>2026-06-06T18:10:35.419Z</t>
+        </is>
+      </c>
+      <c r="D2150" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2150" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>6d5a37f8-e146-47b3-8f41-de28ace0f006</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2151" t="inlineStr">
+        <is>
+          <t>2026-06-06T18:31:52.074Z</t>
+        </is>
+      </c>
+      <c r="D2151" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2151" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>1987469c-af1c-494a-b4fe-dfba4f47316b</t>
+        </is>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2152" t="inlineStr">
+        <is>
+          <t>2026-06-06T21:47:17.287Z</t>
+        </is>
+      </c>
+      <c r="D2152" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2152" t="inlineStr"/>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>e968c51a-1f02-4c68-b6a7-ecc1a8abf8fb</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2153" t="inlineStr">
+        <is>
+          <t>2026-06-06T22:24:46.301Z</t>
+        </is>
+      </c>
+      <c r="D2153" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2153" t="inlineStr"/>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>bb49f91f-f3f3-4b7f-be80-accbb397130d</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2154" t="inlineStr">
+        <is>
+          <t>2026-06-06T22:25:44.820Z</t>
+        </is>
+      </c>
+      <c r="D2154" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2154" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>9b771160-e490-4c45-bf8b-43cbe72f7822</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2155" t="inlineStr">
+        <is>
+          <t>2026-06-06T23:27:34.018Z</t>
+        </is>
+      </c>
+      <c r="D2155" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2155" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2155"/>
+  <dimension ref="A1:E2166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49255,6 +49255,269 @@
         </is>
       </c>
     </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>a47781d5-a33e-492e-94a5-9f918d56416c</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2156" t="inlineStr">
+        <is>
+          <t>2026-06-07T03:15:47.299Z</t>
+        </is>
+      </c>
+      <c r="D2156" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2156" t="inlineStr">
+        <is>
+          <t>Sus loc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>8722c6ab-3a50-451a-9802-e4011b4bdb7b</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2157" t="inlineStr">
+        <is>
+          <t>2026-06-07T03:17:56.790Z</t>
+        </is>
+      </c>
+      <c r="D2157" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2157" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>51d862a4-f680-4a00-93ff-8a055b861a52</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>2026-06-07T04:33:38.480Z</t>
+        </is>
+      </c>
+      <c r="D2158" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2158" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>d962cc94-ac38-46cb-9e38-8a9e4ee6967e</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>2026-06-07T04:54:58.143Z</t>
+        </is>
+      </c>
+      <c r="D2159" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2159" t="inlineStr">
+        <is>
+          <t>Sus loc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>0bc603f8-4ddc-41f4-9f82-501e5648aac7</t>
+        </is>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>2026-06-07T14:38:22.306Z</t>
+        </is>
+      </c>
+      <c r="D2160" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2160" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>156a309b-3046-4977-b64b-4912ff55bbeb</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>2026-06-07T15:56:48.481Z</t>
+        </is>
+      </c>
+      <c r="D2161" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2161" t="inlineStr"/>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>1ae39142-20b6-4b97-979a-3f3436a60284</t>
+        </is>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>2026-06-07T16:15:40.572Z</t>
+        </is>
+      </c>
+      <c r="D2162" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2162" t="inlineStr">
+        <is>
+          <t>sus id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>9cbd8f00-5ebb-4dc2-8013-d91bb8247fe9</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>2026-06-07T19:46:47.445Z</t>
+        </is>
+      </c>
+      <c r="D2163" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2163" t="inlineStr"/>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>785a1790-b216-4878-9989-80ea83bfa188</t>
+        </is>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>2026-06-07T20:38:36.139Z</t>
+        </is>
+      </c>
+      <c r="D2164" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2164" t="inlineStr">
+        <is>
+          <t>sus id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>f6697ae5-0224-4c73-a295-cdcc588d93d2</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>2026-06-07T23:03:36.758Z</t>
+        </is>
+      </c>
+      <c r="D2165" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2165" t="inlineStr"/>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>5768ad55-2d76-49a2-b963-f53ef22a6748</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2166" t="inlineStr">
+        <is>
+          <t>2026-06-07T23:41:41.866Z</t>
+        </is>
+      </c>
+      <c r="D2166" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2166" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2166"/>
+  <dimension ref="A1:E2200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49518,6 +49518,736 @@
         </is>
       </c>
     </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>bd765db1-f642-4c1b-ab4f-dc12a99f6fd0</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2167" t="inlineStr">
+        <is>
+          <t>2026-06-08T04:02:41.030Z</t>
+        </is>
+      </c>
+      <c r="D2167" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2167" t="inlineStr"/>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>fa88e400-5843-4f48-bfcf-0ca07ad621a8</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2168" t="inlineStr">
+        <is>
+          <t>2026-06-08T04:09:07.885Z</t>
+        </is>
+      </c>
+      <c r="D2168" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2168" t="inlineStr"/>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>6c595de2-6d65-4b33-b7a3-113ca1cf8deb</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2169" t="inlineStr">
+        <is>
+          <t>2026-06-08T05:27:10.482Z</t>
+        </is>
+      </c>
+      <c r="D2169" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2169" t="inlineStr"/>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>8606cf8a-bdac-4e98-b6f0-74de8f243fad</t>
+        </is>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2170" t="inlineStr">
+        <is>
+          <t>2026-06-08T05:30:22.072Z</t>
+        </is>
+      </c>
+      <c r="D2170" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2170" t="inlineStr"/>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>46ce672e-50fc-477f-b47e-b9f72426c05f</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2171" t="inlineStr">
+        <is>
+          <t>2026-06-08T06:00:14.770Z</t>
+        </is>
+      </c>
+      <c r="D2171" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2171" t="inlineStr"/>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>4e4b024a-ae2f-43d0-a09d-903775fe9609</t>
+        </is>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2172" t="inlineStr">
+        <is>
+          <t>2026-06-08T06:02:04.102Z</t>
+        </is>
+      </c>
+      <c r="D2172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2172" t="inlineStr"/>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>a5aafcf1-2440-4937-8207-099b1a04bf26</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>2026-06-08T07:25:12.216Z</t>
+        </is>
+      </c>
+      <c r="D2173" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2173" t="inlineStr"/>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>d32bd807-8199-432c-8e36-349be47cb594</t>
+        </is>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>2026-06-08T07:38:41.391Z</t>
+        </is>
+      </c>
+      <c r="D2174" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2174" t="inlineStr"/>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>08ef3b5d-9123-4748-a6e0-2e6fb9c8529c</t>
+        </is>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>2026-06-08T07:46:55.428Z</t>
+        </is>
+      </c>
+      <c r="D2175" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2175" t="inlineStr"/>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>18c353ce-7d83-4242-a48f-647143d0579d</t>
+        </is>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>2026-06-08T08:00:12.319Z</t>
+        </is>
+      </c>
+      <c r="D2176" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2176" t="inlineStr"/>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>2f846d96-0f03-47db-a0b5-507f3a3917c5</t>
+        </is>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>2026-06-08T08:01:32.304Z</t>
+        </is>
+      </c>
+      <c r="D2177" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2177" t="inlineStr"/>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>fa8f281f-f28e-4544-b1f6-5a9118909aa5</t>
+        </is>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t>2026-06-08T08:14:04.872Z</t>
+        </is>
+      </c>
+      <c r="D2178" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2178" t="inlineStr"/>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>fd6b99cf-2ae5-4c36-8b6e-218d22244415</t>
+        </is>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>2026-06-08T09:14:33.501Z</t>
+        </is>
+      </c>
+      <c r="D2179" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2179" t="inlineStr"/>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>4cfcf7e7-cffe-409c-a35a-fd52c7706162</t>
+        </is>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>2026-06-08T09:30:50.925Z</t>
+        </is>
+      </c>
+      <c r="D2180" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2180" t="inlineStr"/>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>82e90d36-b699-4f97-acaf-dc85b8a733be</t>
+        </is>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>2026-06-08T10:04:49.528Z</t>
+        </is>
+      </c>
+      <c r="D2181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2181" t="inlineStr"/>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>da8cdabd-768e-45f4-8d24-4bc9d88bc224</t>
+        </is>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2182" t="inlineStr">
+        <is>
+          <t>2026-06-08T11:00:32.084Z</t>
+        </is>
+      </c>
+      <c r="D2182" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2182" t="inlineStr"/>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>7ac46a83-3bc3-401d-ad58-0f43f5942c31</t>
+        </is>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2183" t="inlineStr">
+        <is>
+          <t>2026-06-08T11:02:52.218Z</t>
+        </is>
+      </c>
+      <c r="D2183" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2183" t="inlineStr"/>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>9d13b554-df71-4846-85ca-9ad91bd67bef</t>
+        </is>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2184" t="inlineStr">
+        <is>
+          <t>2026-06-08T11:14:11.259Z</t>
+        </is>
+      </c>
+      <c r="D2184" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2184" t="inlineStr"/>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>2033a15c-ec39-427a-bc84-43092c87f4c4</t>
+        </is>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2185" t="inlineStr">
+        <is>
+          <t>2026-06-08T12:02:53.105Z</t>
+        </is>
+      </c>
+      <c r="D2185" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2185" t="inlineStr"/>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>27015c95-0179-4049-8c6d-c24a99bbd21c</t>
+        </is>
+      </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2186" t="inlineStr">
+        <is>
+          <t>2026-06-08T12:30:26.275Z</t>
+        </is>
+      </c>
+      <c r="D2186" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2186" t="inlineStr"/>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>a0030b8a-dd05-4f68-87c5-9a9789b146e8</t>
+        </is>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2187" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:09:21.112Z</t>
+        </is>
+      </c>
+      <c r="D2187" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2187" t="inlineStr"/>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>87aea9f8-bac1-4deb-9737-bc0ca983044d</t>
+        </is>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2188" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:43:24.532Z</t>
+        </is>
+      </c>
+      <c r="D2188" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2188" t="inlineStr"/>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>11c4344e-13e5-4f58-8a26-278ca71951e2</t>
+        </is>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2189" t="inlineStr">
+        <is>
+          <t>2026-06-08T14:01:38.706Z</t>
+        </is>
+      </c>
+      <c r="D2189" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2189" t="inlineStr"/>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>04175077-510e-4c00-95b6-6106ef57ae92</t>
+        </is>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2190" t="inlineStr">
+        <is>
+          <t>2026-06-08T16:38:15.913Z</t>
+        </is>
+      </c>
+      <c r="D2190" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2190" t="inlineStr">
+        <is>
+          <t>sus id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>9d0b19ba-a765-4c15-9a49-63c08d30b944</t>
+        </is>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2191" t="inlineStr">
+        <is>
+          <t>2026-06-08T17:13:47.260Z</t>
+        </is>
+      </c>
+      <c r="D2191" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2191" t="inlineStr"/>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>2be5fe6a-bf3e-4a5f-8e17-24ade25fe484</t>
+        </is>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2192" t="inlineStr">
+        <is>
+          <t>2026-06-08T18:17:07.557Z</t>
+        </is>
+      </c>
+      <c r="D2192" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2192" t="inlineStr">
+        <is>
+          <t>ID subject</t>
+        </is>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>19d7026b-4294-47d8-bda5-8e76777cff86</t>
+        </is>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2193" t="inlineStr">
+        <is>
+          <t>2026-06-08T18:35:56.822Z</t>
+        </is>
+      </c>
+      <c r="D2193" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2193" t="inlineStr"/>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>c51f39b5-7d42-4542-9318-57cba2633c54</t>
+        </is>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2194" t="inlineStr">
+        <is>
+          <t>2026-06-08T18:55:08.328Z</t>
+        </is>
+      </c>
+      <c r="D2194" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2194" t="inlineStr"/>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>83125338-4b44-47d1-926c-14834d1d9761</t>
+        </is>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2195" t="inlineStr">
+        <is>
+          <t>2026-06-08T19:38:05.384Z</t>
+        </is>
+      </c>
+      <c r="D2195" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2195" t="inlineStr">
+        <is>
+          <t>236pc and 243e1pc out of Davis PD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>a1261972-f3d1-4537-ac68-d3dd1dafd536</t>
+        </is>
+      </c>
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2196" t="inlineStr">
+        <is>
+          <t>2026-06-08T19:39:17.422Z</t>
+        </is>
+      </c>
+      <c r="D2196" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2196" t="inlineStr"/>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>525f7040-1bf9-4164-8010-dff768016a74</t>
+        </is>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2197" t="inlineStr">
+        <is>
+          <t>2026-06-08T20:00:12.481Z</t>
+        </is>
+      </c>
+      <c r="D2197" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2197" t="inlineStr"/>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>4bdd2caf-0217-48b4-a346-b7e51365ff1c</t>
+        </is>
+      </c>
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2198" t="inlineStr">
+        <is>
+          <t>2026-06-08T20:17:29.544Z</t>
+        </is>
+      </c>
+      <c r="D2198" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2198" t="inlineStr">
+        <is>
+          <t>Sus id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>c6c23ad4-29c6-4612-a8f9-9053872d6e45</t>
+        </is>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2199" t="inlineStr">
+        <is>
+          <t>2026-06-08T20:25:06.583Z</t>
+        </is>
+      </c>
+      <c r="D2199" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2199" t="inlineStr"/>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>44b7900a-2dd9-4a03-9e6f-58f957d54ba0</t>
+        </is>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2200" t="inlineStr">
+        <is>
+          <t>2026-06-08T21:01:54.367Z</t>
+        </is>
+      </c>
+      <c r="D2200" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2200" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2200"/>
+  <dimension ref="A1:E2240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50248,6 +50248,902 @@
       </c>
       <c r="E2200" t="inlineStr"/>
     </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>e0fb2902-3def-4dd9-94a6-9831666286e0</t>
+        </is>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2201" t="inlineStr">
+        <is>
+          <t>2026-06-09T00:23:22.199Z</t>
+        </is>
+      </c>
+      <c r="D2201" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2201" t="inlineStr"/>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>7c8ac530-c614-4185-8153-2653577769e2</t>
+        </is>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2202" t="inlineStr">
+        <is>
+          <t>2026-06-09T00:36:08.840Z</t>
+        </is>
+      </c>
+      <c r="D2202" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2202" t="inlineStr">
+        <is>
+          <t>Drug Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>09fa8bb2-dd15-44a4-bc4a-df02bad33cd6</t>
+        </is>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2203" t="inlineStr">
+        <is>
+          <t>2026-06-09T00:53:40.924Z</t>
+        </is>
+      </c>
+      <c r="D2203" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2203" t="inlineStr">
+        <is>
+          <t>Drug investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>4d73a485-15e8-4f39-9c5c-f060184a8fcc</t>
+        </is>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2204" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:14:01.106Z</t>
+        </is>
+      </c>
+      <c r="D2204" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2204" t="inlineStr">
+        <is>
+          <t>wanted</t>
+        </is>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>5c5f2fe0-b5a6-4d1e-9b1e-4b50ad0b7f87</t>
+        </is>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2205" t="inlineStr">
+        <is>
+          <t>2026-06-09T03:14:14.080Z</t>
+        </is>
+      </c>
+      <c r="D2205" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2205" t="inlineStr"/>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>90296452-8847-42b8-bc79-8019b9d4f37e</t>
+        </is>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2206" t="inlineStr">
+        <is>
+          <t>2026-06-09T03:23:07.124Z</t>
+        </is>
+      </c>
+      <c r="D2206" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2206" t="inlineStr"/>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>47866896-35f8-4581-a0f2-78aaae574df5</t>
+        </is>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2207" t="inlineStr">
+        <is>
+          <t>2026-06-09T03:34:23.072Z</t>
+        </is>
+      </c>
+      <c r="D2207" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2207" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>feb134d4-e926-4632-9c3c-415a2a4c963b</t>
+        </is>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2208" t="inlineStr">
+        <is>
+          <t>2026-06-09T04:00:53.125Z</t>
+        </is>
+      </c>
+      <c r="D2208" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2208" t="inlineStr"/>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>b713cb97-0392-4d1e-927a-c635d30b514d</t>
+        </is>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2209" t="inlineStr">
+        <is>
+          <t>2026-06-09T05:42:48.495Z</t>
+        </is>
+      </c>
+      <c r="D2209" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2209" t="inlineStr"/>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>f4da6262-fe6c-481b-83bd-489607ee9a10</t>
+        </is>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2210" t="inlineStr">
+        <is>
+          <t>2026-06-09T05:46:01.186Z</t>
+        </is>
+      </c>
+      <c r="D2210" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2210" t="inlineStr"/>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>e440f23c-1303-4d61-ac48-9f7d7a3066ea</t>
+        </is>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2211" t="inlineStr">
+        <is>
+          <t>2026-06-09T05:53:08.110Z</t>
+        </is>
+      </c>
+      <c r="D2211" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2211" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>d97e4d86-f55c-431e-80ce-a453a0ba9e1b</t>
+        </is>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2212" t="inlineStr">
+        <is>
+          <t>2026-06-09T06:02:17.703Z</t>
+        </is>
+      </c>
+      <c r="D2212" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2212" t="inlineStr"/>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>46da3f00-ed72-4a7e-b0b4-cc8182bf799e</t>
+        </is>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2213" t="inlineStr">
+        <is>
+          <t>2026-06-09T06:14:30.324Z</t>
+        </is>
+      </c>
+      <c r="D2213" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2213" t="inlineStr"/>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>18dff8cb-6a17-4e75-acaf-77f4137a6c16</t>
+        </is>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2214" t="inlineStr">
+        <is>
+          <t>2026-06-09T07:04:16.907Z</t>
+        </is>
+      </c>
+      <c r="D2214" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2214" t="inlineStr"/>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>05887fe8-3547-4759-993f-37761fa1577c</t>
+        </is>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2215" t="inlineStr">
+        <is>
+          <t>2026-06-09T07:11:12.207Z</t>
+        </is>
+      </c>
+      <c r="D2215" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2215" t="inlineStr"/>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>9a3d2b4a-6235-4be1-b050-075eb96d0cb6</t>
+        </is>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2216" t="inlineStr">
+        <is>
+          <t>2026-06-09T07:51:31.880Z</t>
+        </is>
+      </c>
+      <c r="D2216" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2216" t="inlineStr"/>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>f4490c17-355c-48e5-8609-a97cf71b39cc</t>
+        </is>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2217" t="inlineStr">
+        <is>
+          <t>2026-06-09T08:42:36.391Z</t>
+        </is>
+      </c>
+      <c r="D2217" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2217" t="inlineStr"/>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>37ec8820-4f58-4694-9313-5d405c31a6c9</t>
+        </is>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2218" t="inlineStr">
+        <is>
+          <t>2026-06-09T09:25:25.518Z</t>
+        </is>
+      </c>
+      <c r="D2218" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2218" t="inlineStr"/>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>0ac7dff6-3d66-4155-8fef-f18a07e4fa55</t>
+        </is>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>2026-06-09T09:45:41.428Z</t>
+        </is>
+      </c>
+      <c r="D2219" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2219" t="inlineStr"/>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>6613428e-2810-4ff4-af12-cb76e460de70</t>
+        </is>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>2026-06-09T10:37:31.086Z</t>
+        </is>
+      </c>
+      <c r="D2220" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2220" t="inlineStr"/>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>0f963277-ab64-4d6f-8fbb-10bca0548856</t>
+        </is>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2221" t="inlineStr">
+        <is>
+          <t>2026-06-09T11:00:50.614Z</t>
+        </is>
+      </c>
+      <c r="D2221" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2221" t="inlineStr"/>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>c710bdd6-31b9-410a-ac4d-f9bbc3cc462b</t>
+        </is>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2222" t="inlineStr">
+        <is>
+          <t>2026-06-09T11:19:56.180Z</t>
+        </is>
+      </c>
+      <c r="D2222" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2222" t="inlineStr"/>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>836dfee6-22db-4f59-96c7-dba6c64eff02</t>
+        </is>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2223" t="inlineStr">
+        <is>
+          <t>2026-06-09T11:27:28.639Z</t>
+        </is>
+      </c>
+      <c r="D2223" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2223" t="inlineStr"/>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>5e3e5759-f789-4ae4-a5c0-61e693d5afe3</t>
+        </is>
+      </c>
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2224" t="inlineStr">
+        <is>
+          <t>2026-06-09T12:34:15.843Z</t>
+        </is>
+      </c>
+      <c r="D2224" t="n">
+        <v>491</v>
+      </c>
+      <c r="E2224" t="inlineStr"/>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>ffe7def0-b2d5-4da3-9a3e-fc22e541bbb9</t>
+        </is>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2225" t="inlineStr">
+        <is>
+          <t>2026-06-09T13:28:36.315Z</t>
+        </is>
+      </c>
+      <c r="D2225" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2225" t="inlineStr"/>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>79424176-fa07-4e2d-bce5-ce6608808c4f</t>
+        </is>
+      </c>
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2226" t="inlineStr">
+        <is>
+          <t>2026-06-09T15:19:51.881Z</t>
+        </is>
+      </c>
+      <c r="D2226" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2226" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>9b8a1359-50ee-4fde-a46d-a765924e243c</t>
+        </is>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2227" t="inlineStr">
+        <is>
+          <t>2026-06-09T15:45:40.382Z</t>
+        </is>
+      </c>
+      <c r="D2227" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2227" t="inlineStr">
+        <is>
+          <t>ID subject</t>
+        </is>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>d57f7ef9-3bb0-42ed-85bc-c476fca2d375</t>
+        </is>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2228" t="inlineStr">
+        <is>
+          <t>2026-06-09T16:34:45.809Z</t>
+        </is>
+      </c>
+      <c r="D2228" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2228" t="inlineStr">
+        <is>
+          <t>245 PC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>a85cb5dc-42ad-4f64-82ff-537ecfc431ba</t>
+        </is>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2229" t="inlineStr">
+        <is>
+          <t>2026-06-09T19:18:47.594Z</t>
+        </is>
+      </c>
+      <c r="D2229" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2229" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>b704f166-86f8-43ca-aa0c-06e52474a046</t>
+        </is>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2230" t="inlineStr">
+        <is>
+          <t>2026-06-09T19:44:49.554Z</t>
+        </is>
+      </c>
+      <c r="D2230" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2230" t="inlineStr"/>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>a701a3d1-26b7-49a2-9e60-fb2e1e1288d7</t>
+        </is>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2231" t="inlineStr">
+        <is>
+          <t>2026-06-09T19:52:46.640Z</t>
+        </is>
+      </c>
+      <c r="D2231" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2231" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>199c3c87-3d37-4e18-a000-554cea1e5a01</t>
+        </is>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2232" t="inlineStr">
+        <is>
+          <t>2026-06-09T20:02:39.762Z</t>
+        </is>
+      </c>
+      <c r="D2232" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2232" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>fefab440-bbee-43c7-9a17-e0eff3425050</t>
+        </is>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2233" t="inlineStr">
+        <is>
+          <t>2026-06-09T20:03:18.121Z</t>
+        </is>
+      </c>
+      <c r="D2233" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2233" t="inlineStr"/>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>e9f721b8-b895-4497-b7d5-c773a5e1a7a5</t>
+        </is>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2234" t="inlineStr">
+        <is>
+          <t>2026-06-09T21:33:24.562Z</t>
+        </is>
+      </c>
+      <c r="D2234" t="n">
+        <v>490</v>
+      </c>
+      <c r="E2234" t="inlineStr"/>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>eb2632c3-ad2e-405b-9731-bc9b4f5923cf</t>
+        </is>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2235" t="inlineStr">
+        <is>
+          <t>2026-06-09T21:51:45.335Z</t>
+        </is>
+      </c>
+      <c r="D2235" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2235" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>1f53bc15-8cc5-4605-8e7d-c1ba29ef2826</t>
+        </is>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2236" t="inlineStr">
+        <is>
+          <t>2026-06-09T22:09:03.969Z</t>
+        </is>
+      </c>
+      <c r="D2236" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2236" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>990043eb-567d-48c0-9bfd-6ea9ccee06b1</t>
+        </is>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2237" t="inlineStr">
+        <is>
+          <t>2026-06-09T22:19:50.469Z</t>
+        </is>
+      </c>
+      <c r="D2237" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2237" t="inlineStr"/>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>b84a27ce-2393-4e00-be0e-e11e7cb2a342</t>
+        </is>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2238" t="inlineStr">
+        <is>
+          <t>2026-06-09T22:20:19.420Z</t>
+        </is>
+      </c>
+      <c r="D2238" t="n">
+        <v>490</v>
+      </c>
+      <c r="E2238" t="inlineStr"/>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>86025d48-637a-4a9c-b8ae-290064785bb2</t>
+        </is>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2239" t="inlineStr">
+        <is>
+          <t>2026-06-09T23:03:40.862Z</t>
+        </is>
+      </c>
+      <c r="D2239" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2239" t="inlineStr"/>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>e2c7ac69-0711-4240-9e82-44a58fc87210</t>
+        </is>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2240" t="inlineStr">
+        <is>
+          <t>2026-06-09T23:03:56.324Z</t>
+        </is>
+      </c>
+      <c r="D2240" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2240" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2240"/>
+  <dimension ref="A1:E2253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51144,6 +51144,291 @@
         </is>
       </c>
     </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>0deaaddc-483a-4d57-87fc-e8df5d6cbced</t>
+        </is>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2241" t="inlineStr">
+        <is>
+          <t>2026-06-10T00:12:37.853Z</t>
+        </is>
+      </c>
+      <c r="D2241" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2241" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>38bb3b83-f975-4bcf-b0b3-58fb07c0e176</t>
+        </is>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2242" t="inlineStr">
+        <is>
+          <t>2026-06-10T04:16:26.516Z</t>
+        </is>
+      </c>
+      <c r="D2242" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2242" t="inlineStr"/>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>f31dace7-10c6-4d9c-b22f-b987f70ecceb</t>
+        </is>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2243" t="inlineStr">
+        <is>
+          <t>2026-06-10T04:31:40.706Z</t>
+        </is>
+      </c>
+      <c r="D2243" t="n">
+        <v>490</v>
+      </c>
+      <c r="E2243" t="inlineStr"/>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>977051dd-9b3a-4b77-ae45-700d15982589</t>
+        </is>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2244" t="inlineStr">
+        <is>
+          <t>2026-06-10T06:17:47.067Z</t>
+        </is>
+      </c>
+      <c r="D2244" t="n">
+        <v>490</v>
+      </c>
+      <c r="E2244" t="inlineStr"/>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>071019cb-2967-4bd3-884d-cd23aca45090</t>
+        </is>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2245" t="inlineStr">
+        <is>
+          <t>2026-06-10T10:08:34.984Z</t>
+        </is>
+      </c>
+      <c r="D2245" t="n">
+        <v>490</v>
+      </c>
+      <c r="E2245" t="inlineStr"/>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>eaee7323-fe43-4426-82cf-b60044c0e422</t>
+        </is>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2246" t="inlineStr">
+        <is>
+          <t>2026-06-10T11:09:26.598Z</t>
+        </is>
+      </c>
+      <c r="D2246" t="n">
+        <v>490</v>
+      </c>
+      <c r="E2246" t="inlineStr"/>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>e70514b7-8814-4441-bd62-a89f7385d63b</t>
+        </is>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2247" t="inlineStr">
+        <is>
+          <t>2026-06-10T13:07:48.435Z</t>
+        </is>
+      </c>
+      <c r="D2247" t="n">
+        <v>531</v>
+      </c>
+      <c r="E2247" t="inlineStr"/>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>a43a9146-648b-4efe-8325-49f88cd76398</t>
+        </is>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2248" t="inlineStr">
+        <is>
+          <t>2026-06-10T14:58:24.694Z</t>
+        </is>
+      </c>
+      <c r="D2248" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2248" t="inlineStr"/>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>9587da66-0aba-4a73-93aa-09b772a69c1c</t>
+        </is>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2249" t="inlineStr">
+        <is>
+          <t>2026-06-10T16:49:24.867Z</t>
+        </is>
+      </c>
+      <c r="D2249" t="n">
+        <v>490</v>
+      </c>
+      <c r="E2249" t="inlineStr"/>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>182a0d18-b599-4d24-ae46-6783c1c4452f</t>
+        </is>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2250" t="inlineStr">
+        <is>
+          <t>2026-06-10T16:59:18.300Z</t>
+        </is>
+      </c>
+      <c r="D2250" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2250" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>9013e5b5-58ee-47b7-9cb5-ed19cf5ee401</t>
+        </is>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2251" t="inlineStr">
+        <is>
+          <t>2026-06-10T17:09:50.647Z</t>
+        </is>
+      </c>
+      <c r="D2251" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2251" t="inlineStr"/>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
+        <is>
+          <t>6b2a1bd2-d3f5-4f74-b726-1da674cbf1ac</t>
+        </is>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2252" t="inlineStr">
+        <is>
+          <t>2026-06-10T17:19:17.645Z</t>
+        </is>
+      </c>
+      <c r="D2252" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2252" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>69fda0ae-7445-4fdd-8b27-30fa94f9aae4</t>
+        </is>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2253" t="inlineStr">
+        <is>
+          <t>2026-06-10T18:32:50.900Z</t>
+        </is>
+      </c>
+      <c r="D2253" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2253" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2253"/>
+  <dimension ref="A1:E2265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51429,6 +51429,258 @@
       </c>
       <c r="E2253" t="inlineStr"/>
     </row>
+    <row r="2254">
+      <c r="A2254" t="inlineStr">
+        <is>
+          <t>f1d77cc9-c3c7-429a-9690-055d073d90b9</t>
+        </is>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2254" t="inlineStr">
+        <is>
+          <t>2026-06-11T03:43:21.165Z</t>
+        </is>
+      </c>
+      <c r="D2254" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2254" t="inlineStr"/>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>883e1b5b-5070-4541-8733-002cd1cadd87</t>
+        </is>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2255" t="inlineStr">
+        <is>
+          <t>2026-06-11T16:56:05.019Z</t>
+        </is>
+      </c>
+      <c r="D2255" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2255" t="inlineStr"/>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="inlineStr">
+        <is>
+          <t>982d217e-274c-415d-b063-c25865d1c65e</t>
+        </is>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2256" t="inlineStr">
+        <is>
+          <t>2026-06-11T18:15:06.031Z</t>
+        </is>
+      </c>
+      <c r="D2256" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2256" t="inlineStr"/>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>999d64b2-a6ed-4818-90a5-9ccbc105e2bf</t>
+        </is>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2257" t="inlineStr">
+        <is>
+          <t>2026-06-11T18:30:57.309Z</t>
+        </is>
+      </c>
+      <c r="D2257" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2257" t="inlineStr"/>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="inlineStr">
+        <is>
+          <t>fb41b382-6457-4f5a-9c74-84a93902c443</t>
+        </is>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2258" t="inlineStr">
+        <is>
+          <t>2026-06-11T19:04:32.437Z</t>
+        </is>
+      </c>
+      <c r="D2258" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2258" t="inlineStr"/>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>8e9c6902-1d85-4507-abaa-25b8a88be408</t>
+        </is>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2259" t="inlineStr">
+        <is>
+          <t>2026-06-11T20:16:53.366Z</t>
+        </is>
+      </c>
+      <c r="D2259" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2259" t="inlineStr"/>
+    </row>
+    <row r="2260">
+      <c r="A2260" t="inlineStr">
+        <is>
+          <t>bfbefc2c-50dc-4f13-968c-b53cf877aac9</t>
+        </is>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2260" t="inlineStr">
+        <is>
+          <t>2026-06-11T20:56:30.938Z</t>
+        </is>
+      </c>
+      <c r="D2260" t="n">
+        <v>490</v>
+      </c>
+      <c r="E2260" t="inlineStr"/>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>f842aad5-4769-4809-87ec-dd071dc368be</t>
+        </is>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2261" t="inlineStr">
+        <is>
+          <t>2026-06-11T21:05:33.554Z</t>
+        </is>
+      </c>
+      <c r="D2261" t="n">
+        <v>490</v>
+      </c>
+      <c r="E2261" t="inlineStr"/>
+    </row>
+    <row r="2262">
+      <c r="A2262" t="inlineStr">
+        <is>
+          <t>4bf9cd26-b2e9-4361-ba74-98af96065628</t>
+        </is>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2262" t="inlineStr">
+        <is>
+          <t>2026-06-11T21:08:38.403Z</t>
+        </is>
+      </c>
+      <c r="D2262" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2262" t="inlineStr"/>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>e62b2c16-b375-4d79-bf4c-3fe936aa4811</t>
+        </is>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2263" t="inlineStr">
+        <is>
+          <t>2026-06-11T21:29:43.427Z</t>
+        </is>
+      </c>
+      <c r="D2263" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2263" t="inlineStr"/>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>a07f835e-6a1d-4c0d-8817-83cf9e087adf</t>
+        </is>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2264" t="inlineStr">
+        <is>
+          <t>2026-06-11T22:11:52.052Z</t>
+        </is>
+      </c>
+      <c r="D2264" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2264" t="inlineStr"/>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>9a09c566-4de2-4e49-be17-eacae94fd369</t>
+        </is>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2265" t="inlineStr">
+        <is>
+          <t>2026-06-11T23:27:14.587Z</t>
+        </is>
+      </c>
+      <c r="D2265" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2265" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2265"/>
+  <dimension ref="A1:E2280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51681,6 +51681,341 @@
       </c>
       <c r="E2265" t="inlineStr"/>
     </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>5df70a35-d6a2-4856-b473-666a29ad4a0e</t>
+        </is>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2266" t="inlineStr">
+        <is>
+          <t>2026-06-12T01:06:20.690Z</t>
+        </is>
+      </c>
+      <c r="D2266" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2266" t="inlineStr"/>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>a3a5bfac-bfc6-4dbb-8470-4c7cfb36d20c</t>
+        </is>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2267" t="inlineStr">
+        <is>
+          <t>2026-06-12T04:10:40.138Z</t>
+        </is>
+      </c>
+      <c r="D2267" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2267" t="inlineStr">
+        <is>
+          <t>Sus Loc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>12a1bc1d-124f-40a1-9b7e-4f58168c3bb8</t>
+        </is>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2268" t="inlineStr">
+        <is>
+          <t>2026-06-12T04:17:30.718Z</t>
+        </is>
+      </c>
+      <c r="D2268" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2268" t="inlineStr"/>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>2ee0dcee-5144-4adf-8cfc-f2e4ace515d0</t>
+        </is>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2269" t="inlineStr">
+        <is>
+          <t>2026-06-12T05:04:12.118Z</t>
+        </is>
+      </c>
+      <c r="D2269" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2269" t="inlineStr"/>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>ee896cfd-7bb0-412f-9033-f15e6fdd6799</t>
+        </is>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2270" t="inlineStr">
+        <is>
+          <t>2026-06-12T16:17:32.053Z</t>
+        </is>
+      </c>
+      <c r="D2270" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2270" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>886e8317-c08b-40a1-925a-ebb767388a33</t>
+        </is>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2271" t="inlineStr">
+        <is>
+          <t>2026-06-12T16:49:14.902Z</t>
+        </is>
+      </c>
+      <c r="D2271" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2271" t="inlineStr"/>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>06857176-d50c-4cc6-8ad6-542e7769f418</t>
+        </is>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2272" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:17:49.869Z</t>
+        </is>
+      </c>
+      <c r="D2272" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2272" t="inlineStr"/>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>475857ce-b742-48da-897a-f888298941ac</t>
+        </is>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2273" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:32:04.007Z</t>
+        </is>
+      </c>
+      <c r="D2273" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2273" t="inlineStr"/>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>1582fbb4-7f21-4efa-ba1f-e03338a7e3a8</t>
+        </is>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2274" t="inlineStr">
+        <is>
+          <t>2026-06-12T18:11:30.490Z</t>
+        </is>
+      </c>
+      <c r="D2274" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2274" t="inlineStr"/>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>8e229f4c-8a4d-406f-87e1-6d61d286deae</t>
+        </is>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2275" t="inlineStr">
+        <is>
+          <t>2026-06-12T19:29:25.082Z</t>
+        </is>
+      </c>
+      <c r="D2275" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2275" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>bcd22947-c926-4697-bcf5-ff557d09c31d</t>
+        </is>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2276" t="inlineStr">
+        <is>
+          <t>2026-06-12T19:54:22.763Z</t>
+        </is>
+      </c>
+      <c r="D2276" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2276" t="inlineStr"/>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>a8d48bc7-3451-4ffa-9fb3-66a090a7e6f5</t>
+        </is>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2277" t="inlineStr">
+        <is>
+          <t>2026-06-12T20:12:59.071Z</t>
+        </is>
+      </c>
+      <c r="D2277" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2277" t="inlineStr"/>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>ebfe00a9-fb65-46d3-9545-2de99e69e3ac</t>
+        </is>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2278" t="inlineStr">
+        <is>
+          <t>2026-06-12T21:22:29.801Z</t>
+        </is>
+      </c>
+      <c r="D2278" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2278" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>a8268b48-2dae-42c8-92bd-3edf74055aae</t>
+        </is>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2279" t="inlineStr">
+        <is>
+          <t>2026-06-12T21:48:33.660Z</t>
+        </is>
+      </c>
+      <c r="D2279" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2279" t="inlineStr">
+        <is>
+          <t>locate suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>75930674-c1df-475d-991a-500e52831303</t>
+        </is>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2280" t="inlineStr">
+        <is>
+          <t>2026-06-12T23:46:54.304Z</t>
+        </is>
+      </c>
+      <c r="D2280" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2280" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2280"/>
+  <dimension ref="A1:E2294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52016,6 +52016,328 @@
       </c>
       <c r="E2280" t="inlineStr"/>
     </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>cef68400-6252-4c4f-a3f0-eed571754ff6</t>
+        </is>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2281" t="inlineStr">
+        <is>
+          <t>2026-06-13T00:44:29.482Z</t>
+        </is>
+      </c>
+      <c r="D2281" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2281" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>c0865f80-3042-40d2-9f7f-9addb9726571</t>
+        </is>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>2026-06-13T00:51:43.204Z</t>
+        </is>
+      </c>
+      <c r="D2282" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2282" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>0b9b0ecd-bb53-4436-bd33-430aa99e903e</t>
+        </is>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2283" t="inlineStr">
+        <is>
+          <t>2026-06-13T01:06:17.449Z</t>
+        </is>
+      </c>
+      <c r="D2283" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2283" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>420fc30d-043f-4b9c-b623-2cf597cf8a21</t>
+        </is>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>2026-06-13T01:28:36.415Z</t>
+        </is>
+      </c>
+      <c r="D2284" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2284" t="inlineStr">
+        <is>
+          <t>theft suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>95988174-ae0d-49fd-9aba-f7f50e240fcb</t>
+        </is>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2285" t="inlineStr">
+        <is>
+          <t>2026-06-13T02:08:21.734Z</t>
+        </is>
+      </c>
+      <c r="D2285" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2285" t="inlineStr">
+        <is>
+          <t>theft suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>3271ccfc-56f3-4c87-bbd8-fcf0ce779912</t>
+        </is>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>2026-06-13T02:10:23.975Z</t>
+        </is>
+      </c>
+      <c r="D2286" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2286" t="inlineStr"/>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>16a6e0ce-f285-47eb-a934-f366b6e5fddc</t>
+        </is>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2287" t="inlineStr">
+        <is>
+          <t>2026-06-13T02:10:33.569Z</t>
+        </is>
+      </c>
+      <c r="D2287" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2287" t="inlineStr"/>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>c1ad815c-373e-4902-831c-c03a1b2ff60a</t>
+        </is>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t>2026-06-13T02:47:02.587Z</t>
+        </is>
+      </c>
+      <c r="D2288" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2288" t="inlineStr">
+        <is>
+          <t>pursuit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>c008d474-9237-48a1-afb9-dca1a014d487</t>
+        </is>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2289" t="inlineStr">
+        <is>
+          <t>2026-06-13T16:03:41.264Z</t>
+        </is>
+      </c>
+      <c r="D2289" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2289" t="inlineStr"/>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>9543df3a-403b-4395-a418-8faa37994057</t>
+        </is>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2290" t="inlineStr">
+        <is>
+          <t>2026-06-13T19:11:07.198Z</t>
+        </is>
+      </c>
+      <c r="D2290" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2290" t="inlineStr"/>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>3da3ef67-a154-4daf-9f77-3d5f84e88d67</t>
+        </is>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2291" t="inlineStr">
+        <is>
+          <t>2026-06-13T19:18:46.990Z</t>
+        </is>
+      </c>
+      <c r="D2291" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2291" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>21f8e0e4-7ee5-4cd6-a2a5-77c2fe1b96da</t>
+        </is>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2292" t="inlineStr">
+        <is>
+          <t>2026-06-13T19:49:41.181Z</t>
+        </is>
+      </c>
+      <c r="D2292" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2292" t="inlineStr"/>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>0353ab34-db80-496d-bc61-5d48c41a05a6</t>
+        </is>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2293" t="inlineStr">
+        <is>
+          <t>2026-06-13T20:35:27.081Z</t>
+        </is>
+      </c>
+      <c r="D2293" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2293" t="inlineStr"/>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>eb32e9ce-43f4-410a-a5a0-787112ccdf08</t>
+        </is>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2294" t="inlineStr">
+        <is>
+          <t>2026-06-13T21:25:20.431Z</t>
+        </is>
+      </c>
+      <c r="D2294" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2294" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2294"/>
+  <dimension ref="A1:E2305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52338,6 +52338,237 @@
       </c>
       <c r="E2294" t="inlineStr"/>
     </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>b94ab663-7959-4c67-8377-07fbb80424d2</t>
+        </is>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2295" t="inlineStr">
+        <is>
+          <t>2026-06-14T00:53:22.282Z</t>
+        </is>
+      </c>
+      <c r="D2295" t="n">
+        <v>490</v>
+      </c>
+      <c r="E2295" t="inlineStr"/>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="inlineStr">
+        <is>
+          <t>ec2f1528-9607-44be-b229-63a4e76377f4</t>
+        </is>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2296" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:04:14.329Z</t>
+        </is>
+      </c>
+      <c r="D2296" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2296" t="inlineStr"/>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>5715bba5-2d0b-4b0a-8de4-4e0b98706103</t>
+        </is>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2297" t="inlineStr">
+        <is>
+          <t>2026-06-14T03:50:22.312Z</t>
+        </is>
+      </c>
+      <c r="D2297" t="n">
+        <v>490</v>
+      </c>
+      <c r="E2297" t="inlineStr"/>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>a0b4e1bf-cab0-4cbf-9a71-2bb6a92bf30d</t>
+        </is>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2298" t="inlineStr">
+        <is>
+          <t>2026-06-14T05:00:01.609Z</t>
+        </is>
+      </c>
+      <c r="D2298" t="n">
+        <v>490</v>
+      </c>
+      <c r="E2298" t="inlineStr"/>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>26831c56-e1a6-4a60-b7dd-00e87d918d7b</t>
+        </is>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>2026-06-14T05:03:00.728Z</t>
+        </is>
+      </c>
+      <c r="D2299" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2299" t="inlineStr"/>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>b0a94fe5-91e2-457e-a315-339abc597f6b</t>
+        </is>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>2026-06-14T06:55:39.027Z</t>
+        </is>
+      </c>
+      <c r="D2300" t="n">
+        <v>490</v>
+      </c>
+      <c r="E2300" t="inlineStr"/>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>1d388a45-9918-417b-b9b8-0bc8b3aae6fd</t>
+        </is>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>2026-06-14T12:59:02.860Z</t>
+        </is>
+      </c>
+      <c r="D2301" t="n">
+        <v>800</v>
+      </c>
+      <c r="E2301" t="inlineStr"/>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>7a2937ca-ecdd-436a-b726-ae5fb185800b</t>
+        </is>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>2026-06-14T13:02:00.051Z</t>
+        </is>
+      </c>
+      <c r="D2302" t="n">
+        <v>800</v>
+      </c>
+      <c r="E2302" t="inlineStr"/>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>f563fbe7-4969-4ce2-aa4a-093949e0957a</t>
+        </is>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t>2026-06-14T21:20:16.945Z</t>
+        </is>
+      </c>
+      <c r="D2303" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2303" t="inlineStr"/>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>e65577f4-e9f4-4571-a967-fff73eb356dd</t>
+        </is>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>2026-06-14T21:22:39.579Z</t>
+        </is>
+      </c>
+      <c r="D2304" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2304" t="inlineStr"/>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>5e145b77-8902-4771-b3e2-4f133edb24cb</t>
+        </is>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>2026-06-14T21:46:53.528Z</t>
+        </is>
+      </c>
+      <c r="D2305" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2305" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2305"/>
+  <dimension ref="A1:E2309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52569,6 +52569,94 @@
       </c>
       <c r="E2305" t="inlineStr"/>
     </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>b768c11e-5f9b-459b-9df6-1eda7293b37b</t>
+        </is>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t>2026-06-15T11:31:49.116Z</t>
+        </is>
+      </c>
+      <c r="D2306" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2306" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>15ecc4b3-ff89-4bab-901c-ceb4ab171414</t>
+        </is>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>2026-06-15T20:21:18.381Z</t>
+        </is>
+      </c>
+      <c r="D2307" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2307" t="inlineStr"/>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>5e3fab46-83b3-48d6-9cb4-29d602a1ab79</t>
+        </is>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>2026-06-15T20:23:37.693Z</t>
+        </is>
+      </c>
+      <c r="D2308" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2308" t="inlineStr"/>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>1dd4ec9f-2003-49c6-9df2-f169866a9537</t>
+        </is>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>2026-06-15T23:15:10.281Z</t>
+        </is>
+      </c>
+      <c r="D2309" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2309" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2309"/>
+  <dimension ref="A1:E2321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52657,6 +52657,262 @@
       </c>
       <c r="E2309" t="inlineStr"/>
     </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>b6215867-5f59-4478-9c57-1af87d90c145</t>
+        </is>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2310" t="inlineStr">
+        <is>
+          <t>2026-06-16T03:18:25.619Z</t>
+        </is>
+      </c>
+      <c r="D2310" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2310" t="inlineStr"/>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>43807710-cdbd-4045-9734-018bcf102078</t>
+        </is>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2311" t="inlineStr">
+        <is>
+          <t>2026-06-16T07:19:44.598Z</t>
+        </is>
+      </c>
+      <c r="D2311" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2311" t="inlineStr"/>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>b2019117-2c93-4e8f-831e-9db631032ded</t>
+        </is>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2312" t="inlineStr">
+        <is>
+          <t>2026-06-16T15:37:00.536Z</t>
+        </is>
+      </c>
+      <c r="D2312" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2312" t="inlineStr"/>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>3732e90c-4181-4dcf-9d95-6f7f1280236b</t>
+        </is>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2313" t="inlineStr">
+        <is>
+          <t>2026-06-16T15:50:43.492Z</t>
+        </is>
+      </c>
+      <c r="D2313" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2313" t="inlineStr">
+        <is>
+          <t>MOD BOLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="inlineStr">
+        <is>
+          <t>ed2e5c03-9054-457d-b0a1-1d1d6027b0ec</t>
+        </is>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2314" t="inlineStr">
+        <is>
+          <t>2026-06-16T16:14:46.928Z</t>
+        </is>
+      </c>
+      <c r="D2314" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2314" t="inlineStr"/>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="inlineStr">
+        <is>
+          <t>02a7a10e-665f-456e-b530-06de9095e794</t>
+        </is>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2315" t="inlineStr">
+        <is>
+          <t>2026-06-16T17:05:51.449Z</t>
+        </is>
+      </c>
+      <c r="D2315" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2315" t="inlineStr"/>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="inlineStr">
+        <is>
+          <t>bd0f54bf-a417-45b4-b4d1-e081f5e75278</t>
+        </is>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2316" t="inlineStr">
+        <is>
+          <t>2026-06-16T18:22:07.443Z</t>
+        </is>
+      </c>
+      <c r="D2316" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2316" t="inlineStr"/>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="inlineStr">
+        <is>
+          <t>678c3874-378a-47a4-aff1-20be5429751d</t>
+        </is>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2317" t="inlineStr">
+        <is>
+          <t>2026-06-16T19:22:14.738Z</t>
+        </is>
+      </c>
+      <c r="D2317" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2317" t="inlineStr"/>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="inlineStr">
+        <is>
+          <t>00189af1-04cd-4e48-8048-55663eca20fe</t>
+        </is>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2318" t="inlineStr">
+        <is>
+          <t>2026-06-16T20:24:37.250Z</t>
+        </is>
+      </c>
+      <c r="D2318" t="n">
+        <v>568</v>
+      </c>
+      <c r="E2318" t="inlineStr"/>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="inlineStr">
+        <is>
+          <t>351cd366-3ad7-417e-91cb-43d4c9b7c55d</t>
+        </is>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2319" t="inlineStr">
+        <is>
+          <t>2026-06-16T22:49:19.638Z</t>
+        </is>
+      </c>
+      <c r="D2319" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2319" t="inlineStr"/>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="inlineStr">
+        <is>
+          <t>1f435fd3-794b-4354-b652-0a39e185abe5</t>
+        </is>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2320" t="inlineStr">
+        <is>
+          <t>2026-06-16T23:00:07.104Z</t>
+        </is>
+      </c>
+      <c r="D2320" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2320" t="inlineStr"/>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>70ce6ccb-622c-408c-9835-9bccf4b0a993</t>
+        </is>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2321" t="inlineStr">
+        <is>
+          <t>2026-06-16T23:30:18.432Z</t>
+        </is>
+      </c>
+      <c r="D2321" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2321" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2321"/>
+  <dimension ref="A1:E2341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52913,6 +52913,458 @@
       </c>
       <c r="E2321" t="inlineStr"/>
     </row>
+    <row r="2322">
+      <c r="A2322" t="inlineStr">
+        <is>
+          <t>7a86109b-17b6-4b62-946d-7de0d1c04168</t>
+        </is>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2322" t="inlineStr">
+        <is>
+          <t>2026-06-17T00:10:10.803Z</t>
+        </is>
+      </c>
+      <c r="D2322" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2322" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="inlineStr">
+        <is>
+          <t>060c2cc1-df87-4a66-b805-234a7f38ebf6</t>
+        </is>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2323" t="inlineStr">
+        <is>
+          <t>2026-06-17T00:26:37.407Z</t>
+        </is>
+      </c>
+      <c r="D2323" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2323" t="inlineStr"/>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="inlineStr">
+        <is>
+          <t>4c791fc8-8df0-46d8-ae65-1cfbc36a9642</t>
+        </is>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2324" t="inlineStr">
+        <is>
+          <t>2026-06-17T00:46:05.470Z</t>
+        </is>
+      </c>
+      <c r="D2324" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2324" t="inlineStr"/>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="inlineStr">
+        <is>
+          <t>e5da918d-c109-4fc1-adcb-18102706fe60</t>
+        </is>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2325" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:02:34.109Z</t>
+        </is>
+      </c>
+      <c r="D2325" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2325" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="inlineStr">
+        <is>
+          <t>79727198-24db-4260-9263-1ba9c366c5d8</t>
+        </is>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2326" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:57:14.105Z</t>
+        </is>
+      </c>
+      <c r="D2326" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2326" t="inlineStr"/>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="inlineStr">
+        <is>
+          <t>ff8764b7-e7c3-44f2-85cd-213f9cc2c2af</t>
+        </is>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2327" t="inlineStr">
+        <is>
+          <t>2026-06-17T02:43:19.589Z</t>
+        </is>
+      </c>
+      <c r="D2327" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2327" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="inlineStr">
+        <is>
+          <t>6c671cab-e7e0-4b7f-bdab-e285d3a9ba16</t>
+        </is>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2328" t="inlineStr">
+        <is>
+          <t>2026-06-17T03:22:56.298Z</t>
+        </is>
+      </c>
+      <c r="D2328" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2328" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="inlineStr">
+        <is>
+          <t>75f5560d-49e8-4761-8801-6db7f105ea26</t>
+        </is>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2329" t="inlineStr">
+        <is>
+          <t>2026-06-17T04:01:10.462Z</t>
+        </is>
+      </c>
+      <c r="D2329" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2329" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="inlineStr">
+        <is>
+          <t>c3474ebe-f028-4a45-b387-2239ee62f371</t>
+        </is>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2330" t="inlineStr">
+        <is>
+          <t>2026-06-17T04:23:26.452Z</t>
+        </is>
+      </c>
+      <c r="D2330" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2330" t="inlineStr"/>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="inlineStr">
+        <is>
+          <t>dae5e161-09a9-43ba-83a8-40db4c817fee</t>
+        </is>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2331" t="inlineStr">
+        <is>
+          <t>2026-06-17T05:50:05.663Z</t>
+        </is>
+      </c>
+      <c r="D2331" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2331" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" t="inlineStr">
+        <is>
+          <t>3ab20040-3544-4332-997c-8d77a8ea694c</t>
+        </is>
+      </c>
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2332" t="inlineStr">
+        <is>
+          <t>2026-06-17T08:22:49.281Z</t>
+        </is>
+      </c>
+      <c r="D2332" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2332" t="inlineStr"/>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="inlineStr">
+        <is>
+          <t>afd1889d-d2bf-444d-8520-5bb9c9cef35e</t>
+        </is>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2333" t="inlineStr">
+        <is>
+          <t>2026-06-17T08:41:08.787Z</t>
+        </is>
+      </c>
+      <c r="D2333" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2333" t="inlineStr"/>
+    </row>
+    <row r="2334">
+      <c r="A2334" t="inlineStr">
+        <is>
+          <t>e0684209-85be-4955-b4a5-a0fee9416edf</t>
+        </is>
+      </c>
+      <c r="B2334" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2334" t="inlineStr">
+        <is>
+          <t>2026-06-17T08:48:28.208Z</t>
+        </is>
+      </c>
+      <c r="D2334" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2334" t="inlineStr">
+        <is>
+          <t>ATL missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" t="inlineStr">
+        <is>
+          <t>9ac8bdd6-c6ca-4e5c-893b-ddb2bd2b9ff3</t>
+        </is>
+      </c>
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2335" t="inlineStr">
+        <is>
+          <t>2026-06-17T08:56:57.605Z</t>
+        </is>
+      </c>
+      <c r="D2335" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2335" t="inlineStr"/>
+    </row>
+    <row r="2336">
+      <c r="A2336" t="inlineStr">
+        <is>
+          <t>f233e778-fe11-414b-998a-446d9e6d2811</t>
+        </is>
+      </c>
+      <c r="B2336" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2336" t="inlineStr">
+        <is>
+          <t>2026-06-17T10:44:52.703Z</t>
+        </is>
+      </c>
+      <c r="D2336" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2336" t="inlineStr">
+        <is>
+          <t>BOLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" t="inlineStr">
+        <is>
+          <t>31672d35-e455-4e1b-bc68-277783b68ed1</t>
+        </is>
+      </c>
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2337" t="inlineStr">
+        <is>
+          <t>2026-06-17T10:47:49.608Z</t>
+        </is>
+      </c>
+      <c r="D2337" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2337" t="inlineStr"/>
+    </row>
+    <row r="2338">
+      <c r="A2338" t="inlineStr">
+        <is>
+          <t>204be28d-d865-41da-b557-349c3e230ddf</t>
+        </is>
+      </c>
+      <c r="B2338" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2338" t="inlineStr">
+        <is>
+          <t>2026-06-17T11:16:21.421Z</t>
+        </is>
+      </c>
+      <c r="D2338" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2338" t="inlineStr"/>
+    </row>
+    <row r="2339">
+      <c r="A2339" t="inlineStr">
+        <is>
+          <t>cbe89056-86bb-4e62-9875-d130c965b0ab</t>
+        </is>
+      </c>
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2339" t="inlineStr">
+        <is>
+          <t>2026-06-17T13:00:09.944Z</t>
+        </is>
+      </c>
+      <c r="D2339" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2339" t="inlineStr"/>
+    </row>
+    <row r="2340">
+      <c r="A2340" t="inlineStr">
+        <is>
+          <t>b2130674-fe8d-4714-b21b-884dc33bb18c</t>
+        </is>
+      </c>
+      <c r="B2340" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2340" t="inlineStr">
+        <is>
+          <t>2026-06-17T15:21:56.569Z</t>
+        </is>
+      </c>
+      <c r="D2340" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2340" t="inlineStr"/>
+    </row>
+    <row r="2341">
+      <c r="A2341" t="inlineStr">
+        <is>
+          <t>567e451f-97a2-41f6-968f-e3e8c88fe267</t>
+        </is>
+      </c>
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2341" t="inlineStr">
+        <is>
+          <t>2026-06-17T16:03:37.602Z</t>
+        </is>
+      </c>
+      <c r="D2341" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2341" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2341"/>
+  <dimension ref="A1:E2354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53365,6 +53365,311 @@
       </c>
       <c r="E2341" t="inlineStr"/>
     </row>
+    <row r="2342">
+      <c r="A2342" t="inlineStr">
+        <is>
+          <t>3d4fe1d7-5691-4ffe-acb0-b5f96ef0c0aa</t>
+        </is>
+      </c>
+      <c r="B2342" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2342" t="inlineStr">
+        <is>
+          <t>2026-06-18T00:09:59.521Z</t>
+        </is>
+      </c>
+      <c r="D2342" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2342" t="inlineStr">
+        <is>
+          <t>welfare check</t>
+        </is>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="inlineStr">
+        <is>
+          <t>a882778c-4df1-47fe-b387-c69b04d2a7e5</t>
+        </is>
+      </c>
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2343" t="inlineStr">
+        <is>
+          <t>2026-06-18T00:28:31.146Z</t>
+        </is>
+      </c>
+      <c r="D2343" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2343" t="inlineStr"/>
+    </row>
+    <row r="2344">
+      <c r="A2344" t="inlineStr">
+        <is>
+          <t>e7c3c0d6-43f9-4852-981a-e976b9c6b1d9</t>
+        </is>
+      </c>
+      <c r="B2344" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2344" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:12:11.248Z</t>
+        </is>
+      </c>
+      <c r="D2344" t="n">
+        <v>530</v>
+      </c>
+      <c r="E2344" t="inlineStr"/>
+    </row>
+    <row r="2345">
+      <c r="A2345" t="inlineStr">
+        <is>
+          <t>40417229-c670-485f-9510-1e62f876037b</t>
+        </is>
+      </c>
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2345" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:42:43.537Z</t>
+        </is>
+      </c>
+      <c r="D2345" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2345" t="inlineStr"/>
+    </row>
+    <row r="2346">
+      <c r="A2346" t="inlineStr">
+        <is>
+          <t>28d80f44-36ec-48e4-99de-1bb8fada6c41</t>
+        </is>
+      </c>
+      <c r="B2346" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2346" t="inlineStr">
+        <is>
+          <t>2026-06-18T10:17:40.073Z</t>
+        </is>
+      </c>
+      <c r="D2346" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2346" t="inlineStr"/>
+    </row>
+    <row r="2347">
+      <c r="A2347" t="inlineStr">
+        <is>
+          <t>bf90c3fa-a90e-4337-bb6b-dddcc592baca</t>
+        </is>
+      </c>
+      <c r="B2347" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2347" t="inlineStr">
+        <is>
+          <t>2026-06-18T17:08:33.915Z</t>
+        </is>
+      </c>
+      <c r="D2347" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2347" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" t="inlineStr">
+        <is>
+          <t>af98b8cf-c211-4b65-a408-2797cb76ed52</t>
+        </is>
+      </c>
+      <c r="B2348" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2348" t="inlineStr">
+        <is>
+          <t>2026-06-18T18:07:35.627Z</t>
+        </is>
+      </c>
+      <c r="D2348" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2348" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="inlineStr">
+        <is>
+          <t>af3e234a-2e9a-40b6-b30b-5867b5f6c8df</t>
+        </is>
+      </c>
+      <c r="B2349" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2349" t="inlineStr">
+        <is>
+          <t>2026-06-18T20:24:24.910Z</t>
+        </is>
+      </c>
+      <c r="D2349" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2349" t="inlineStr"/>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="inlineStr">
+        <is>
+          <t>529ea2af-c1e7-40fc-877b-7f92b7201337</t>
+        </is>
+      </c>
+      <c r="B2350" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2350" t="inlineStr">
+        <is>
+          <t>2026-06-18T20:33:44.099Z</t>
+        </is>
+      </c>
+      <c r="D2350" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2350" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="inlineStr">
+        <is>
+          <t>ef415a9b-cc99-455d-817a-b9b0d32eb017</t>
+        </is>
+      </c>
+      <c r="B2351" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2351" t="inlineStr">
+        <is>
+          <t>2026-06-18T21:08:39.010Z</t>
+        </is>
+      </c>
+      <c r="D2351" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2351" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="inlineStr">
+        <is>
+          <t>227a781d-3bf4-4f43-b7bd-3d4fdd24102a</t>
+        </is>
+      </c>
+      <c r="B2352" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2352" t="inlineStr">
+        <is>
+          <t>2026-06-18T21:24:56.113Z</t>
+        </is>
+      </c>
+      <c r="D2352" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2352" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" t="inlineStr">
+        <is>
+          <t>9cdc165d-2190-4363-a64a-e5649a0b8385</t>
+        </is>
+      </c>
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2353" t="inlineStr">
+        <is>
+          <t>2026-06-18T22:02:30.159Z</t>
+        </is>
+      </c>
+      <c r="D2353" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2353" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="inlineStr">
+        <is>
+          <t>db8598c4-f16b-4fec-99c4-b86e8ff71558</t>
+        </is>
+      </c>
+      <c r="B2354" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2354" t="inlineStr">
+        <is>
+          <t>2026-06-18T23:19:28.715Z</t>
+        </is>
+      </c>
+      <c r="D2354" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2354" t="inlineStr">
+        <is>
+          <t>investigation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2354"/>
+  <dimension ref="A1:E2364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53670,6 +53670,228 @@
         </is>
       </c>
     </row>
+    <row r="2355">
+      <c r="A2355" t="inlineStr">
+        <is>
+          <t>e7253ba1-9a38-4740-a14a-6f55b0128b8a</t>
+        </is>
+      </c>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2355" t="inlineStr">
+        <is>
+          <t>2026-06-19T00:07:27.976Z</t>
+        </is>
+      </c>
+      <c r="D2355" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2355" t="inlineStr"/>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="inlineStr">
+        <is>
+          <t>a4c7fb4e-3ef8-493d-b06d-43f0bc261629</t>
+        </is>
+      </c>
+      <c r="B2356" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2356" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:16:49.727Z</t>
+        </is>
+      </c>
+      <c r="D2356" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2356" t="inlineStr"/>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="inlineStr">
+        <is>
+          <t>ef2da5f7-2ce5-41c0-a21d-33e51145bd48</t>
+        </is>
+      </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2357" t="inlineStr">
+        <is>
+          <t>2026-06-19T08:20:50.435Z</t>
+        </is>
+      </c>
+      <c r="D2357" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2357" t="inlineStr"/>
+    </row>
+    <row r="2358">
+      <c r="A2358" t="inlineStr">
+        <is>
+          <t>2dedfe64-38e3-4c45-b988-4dbdf722eaac</t>
+        </is>
+      </c>
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2358" t="inlineStr">
+        <is>
+          <t>2026-06-19T18:37:41.816Z</t>
+        </is>
+      </c>
+      <c r="D2358" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2358" t="inlineStr"/>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="inlineStr">
+        <is>
+          <t>31efb101-e94a-463b-9b8e-589004ee95f8</t>
+        </is>
+      </c>
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2359" t="inlineStr">
+        <is>
+          <t>2026-06-19T18:41:21.968Z</t>
+        </is>
+      </c>
+      <c r="D2359" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2359" t="inlineStr"/>
+    </row>
+    <row r="2360">
+      <c r="A2360" t="inlineStr">
+        <is>
+          <t>2a7f4093-7112-4b09-911a-6d54afc34697</t>
+        </is>
+      </c>
+      <c r="B2360" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2360" t="inlineStr">
+        <is>
+          <t>2026-06-19T18:41:23.255Z</t>
+        </is>
+      </c>
+      <c r="D2360" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2360" t="inlineStr">
+        <is>
+          <t>OAA BOLO IN OUR COUNTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" t="inlineStr">
+        <is>
+          <t>fe0c7595-9d07-4911-b032-4acfd5401d5a</t>
+        </is>
+      </c>
+      <c r="B2361" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2361" t="inlineStr">
+        <is>
+          <t>2026-06-19T18:43:06.613Z</t>
+        </is>
+      </c>
+      <c r="D2361" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2361" t="inlineStr">
+        <is>
+          <t>ycpd bolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" t="inlineStr">
+        <is>
+          <t>24ee1aec-edbc-4379-a483-d0e35aa8b850</t>
+        </is>
+      </c>
+      <c r="B2362" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2362" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:16:19.178Z</t>
+        </is>
+      </c>
+      <c r="D2362" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2362" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" t="inlineStr">
+        <is>
+          <t>dfec12f3-360b-4474-b4d5-9da58541418f</t>
+        </is>
+      </c>
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2363" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:17:53.735Z</t>
+        </is>
+      </c>
+      <c r="D2363" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2363" t="inlineStr"/>
+    </row>
+    <row r="2364">
+      <c r="A2364" t="inlineStr">
+        <is>
+          <t>4b8a2471-6299-4adf-946a-69b9c289601d</t>
+        </is>
+      </c>
+      <c r="B2364" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2364" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:11:51.817Z</t>
+        </is>
+      </c>
+      <c r="D2364" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2364" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2364"/>
+  <dimension ref="A1:E2367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53892,6 +53892,77 @@
       </c>
       <c r="E2364" t="inlineStr"/>
     </row>
+    <row r="2365">
+      <c r="A2365" t="inlineStr">
+        <is>
+          <t>79a8fd71-6e69-4c1c-b76e-3f39328f6271</t>
+        </is>
+      </c>
+      <c r="B2365" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2365" t="inlineStr">
+        <is>
+          <t>2026-06-20T03:40:01.043Z</t>
+        </is>
+      </c>
+      <c r="D2365" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2365" t="inlineStr"/>
+    </row>
+    <row r="2366">
+      <c r="A2366" t="inlineStr">
+        <is>
+          <t>c7bc0b0b-245e-41c7-88fc-9b7a8d961b77</t>
+        </is>
+      </c>
+      <c r="B2366" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2366" t="inlineStr">
+        <is>
+          <t>2026-06-20T04:56:05.171Z</t>
+        </is>
+      </c>
+      <c r="D2366" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2366" t="inlineStr">
+        <is>
+          <t>273.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" t="inlineStr">
+        <is>
+          <t>2dd47a38-8c48-416b-b741-945f2920774f</t>
+        </is>
+      </c>
+      <c r="B2367" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2367" t="inlineStr">
+        <is>
+          <t>2026-06-20T13:18:03.873Z</t>
+        </is>
+      </c>
+      <c r="D2367" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2367" t="inlineStr">
+        <is>
+          <t>10851</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2367"/>
+  <dimension ref="A1:E2380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53963,6 +53963,291 @@
         </is>
       </c>
     </row>
+    <row r="2368">
+      <c r="A2368" t="inlineStr">
+        <is>
+          <t>96d1820f-50dc-4c00-ba39-9c283c68a826</t>
+        </is>
+      </c>
+      <c r="B2368" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2368" t="inlineStr">
+        <is>
+          <t>2026-06-22T03:13:43.306Z</t>
+        </is>
+      </c>
+      <c r="D2368" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2368" t="inlineStr">
+        <is>
+          <t>Poss suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" t="inlineStr">
+        <is>
+          <t>72bb7b2c-1864-4e03-a005-e29957f0c762</t>
+        </is>
+      </c>
+      <c r="B2369" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2369" t="inlineStr">
+        <is>
+          <t>2026-06-22T04:21:01.911Z</t>
+        </is>
+      </c>
+      <c r="D2369" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2369" t="inlineStr"/>
+    </row>
+    <row r="2370">
+      <c r="A2370" t="inlineStr">
+        <is>
+          <t>4349a222-c5d8-48fc-9be0-9c8c4aa65c2d</t>
+        </is>
+      </c>
+      <c r="B2370" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2370" t="inlineStr">
+        <is>
+          <t>2026-06-22T05:53:51.082Z</t>
+        </is>
+      </c>
+      <c r="D2370" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2370" t="inlineStr"/>
+    </row>
+    <row r="2371">
+      <c r="A2371" t="inlineStr">
+        <is>
+          <t>0b3d5d3c-8b31-4ce1-848d-ac9b75fb52aa</t>
+        </is>
+      </c>
+      <c r="B2371" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2371" t="inlineStr">
+        <is>
+          <t>2026-06-22T06:01:46.054Z</t>
+        </is>
+      </c>
+      <c r="D2371" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2371" t="inlineStr"/>
+    </row>
+    <row r="2372">
+      <c r="A2372" t="inlineStr">
+        <is>
+          <t>6f290e82-ef6c-433e-8496-cf71e5a77dca</t>
+        </is>
+      </c>
+      <c r="B2372" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2372" t="inlineStr">
+        <is>
+          <t>2026-06-22T08:46:49.264Z</t>
+        </is>
+      </c>
+      <c r="D2372" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2372" t="inlineStr"/>
+    </row>
+    <row r="2373">
+      <c r="A2373" t="inlineStr">
+        <is>
+          <t>9590c239-7e48-44ca-9a44-c51e580aa67d</t>
+        </is>
+      </c>
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2373" t="inlineStr">
+        <is>
+          <t>2026-06-22T09:27:57.320Z</t>
+        </is>
+      </c>
+      <c r="D2373" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2373" t="inlineStr"/>
+    </row>
+    <row r="2374">
+      <c r="A2374" t="inlineStr">
+        <is>
+          <t>3c1d719f-3982-4c54-8208-0d68f91a09fc</t>
+        </is>
+      </c>
+      <c r="B2374" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2374" t="inlineStr">
+        <is>
+          <t>2026-06-22T10:08:31.085Z</t>
+        </is>
+      </c>
+      <c r="D2374" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2374" t="inlineStr"/>
+    </row>
+    <row r="2375">
+      <c r="A2375" t="inlineStr">
+        <is>
+          <t>68b0b351-327e-4ba9-8848-965ff0249442</t>
+        </is>
+      </c>
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2375" t="inlineStr">
+        <is>
+          <t>2026-06-22T11:05:48.071Z</t>
+        </is>
+      </c>
+      <c r="D2375" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2375" t="inlineStr"/>
+    </row>
+    <row r="2376">
+      <c r="A2376" t="inlineStr">
+        <is>
+          <t>66e1298d-9765-4c46-9384-221022c3f8a7</t>
+        </is>
+      </c>
+      <c r="B2376" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2376" t="inlineStr">
+        <is>
+          <t>2026-06-22T12:11:57.481Z</t>
+        </is>
+      </c>
+      <c r="D2376" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2376" t="inlineStr"/>
+    </row>
+    <row r="2377">
+      <c r="A2377" t="inlineStr">
+        <is>
+          <t>3a9aac8d-324b-4e20-b67e-c5d035bf0015</t>
+        </is>
+      </c>
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2377" t="inlineStr">
+        <is>
+          <t>2026-06-22T13:28:38.316Z</t>
+        </is>
+      </c>
+      <c r="D2377" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2377" t="inlineStr">
+        <is>
+          <t>Poss suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" t="inlineStr">
+        <is>
+          <t>d44ac27e-5743-421d-a719-24fa61fbeec2</t>
+        </is>
+      </c>
+      <c r="B2378" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2378" t="inlineStr">
+        <is>
+          <t>2026-06-22T15:54:12.862Z</t>
+        </is>
+      </c>
+      <c r="D2378" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2378" t="inlineStr"/>
+    </row>
+    <row r="2379">
+      <c r="A2379" t="inlineStr">
+        <is>
+          <t>bfba084e-7c47-4838-9456-f5043af93ec3</t>
+        </is>
+      </c>
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2379" t="inlineStr">
+        <is>
+          <t>2026-06-22T16:03:51.039Z</t>
+        </is>
+      </c>
+      <c r="D2379" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2379" t="inlineStr"/>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>9d572265-1c2d-4bf7-b1d2-d98dfaec8c75</t>
+        </is>
+      </c>
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2380" t="inlineStr">
+        <is>
+          <t>2026-06-22T22:35:49.985Z</t>
+        </is>
+      </c>
+      <c r="D2380" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2380" t="inlineStr">
+        <is>
+          <t>FTA warrants</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2380"/>
+  <dimension ref="A1:E2406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54248,6 +54248,596 @@
         </is>
       </c>
     </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>722b5af5-96ec-4333-9e01-997d8be61e82</t>
+        </is>
+      </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2381" t="inlineStr">
+        <is>
+          <t>2026-06-23T00:16:28.106Z</t>
+        </is>
+      </c>
+      <c r="D2381" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2381" t="inlineStr"/>
+    </row>
+    <row r="2382">
+      <c r="A2382" t="inlineStr">
+        <is>
+          <t>9857cb17-6575-454f-aed6-3865276b2b58</t>
+        </is>
+      </c>
+      <c r="B2382" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2382" t="inlineStr">
+        <is>
+          <t>2026-06-23T00:25:59.772Z</t>
+        </is>
+      </c>
+      <c r="D2382" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2382" t="inlineStr"/>
+    </row>
+    <row r="2383">
+      <c r="A2383" t="inlineStr">
+        <is>
+          <t>abcb5dd4-9b8a-46cf-8235-91e514391813</t>
+        </is>
+      </c>
+      <c r="B2383" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2383" t="inlineStr">
+        <is>
+          <t>2026-06-23T00:37:12.798Z</t>
+        </is>
+      </c>
+      <c r="D2383" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2383" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" t="inlineStr">
+        <is>
+          <t>00adf1e0-ea8f-4fcc-9b8f-d4d34d9972d4</t>
+        </is>
+      </c>
+      <c r="B2384" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2384" t="inlineStr">
+        <is>
+          <t>2026-06-23T01:00:05.605Z</t>
+        </is>
+      </c>
+      <c r="D2384" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2384" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="A2385" t="inlineStr">
+        <is>
+          <t>9f81c104-73b4-4ff6-a3ba-5e6314a9f44c</t>
+        </is>
+      </c>
+      <c r="B2385" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2385" t="inlineStr">
+        <is>
+          <t>2026-06-23T01:04:57.703Z</t>
+        </is>
+      </c>
+      <c r="D2385" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2385" t="inlineStr"/>
+    </row>
+    <row r="2386">
+      <c r="A2386" t="inlineStr">
+        <is>
+          <t>d6a0c7ee-93d3-43f0-bbfd-0cfe4bd02b9b</t>
+        </is>
+      </c>
+      <c r="B2386" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2386" t="inlineStr">
+        <is>
+          <t>2026-06-23T03:35:30.147Z</t>
+        </is>
+      </c>
+      <c r="D2386" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2386" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" t="inlineStr">
+        <is>
+          <t>409178c4-86f0-4a46-bed1-18dbfe7cc6b8</t>
+        </is>
+      </c>
+      <c r="B2387" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2387" t="inlineStr">
+        <is>
+          <t>2026-06-23T03:44:46.477Z</t>
+        </is>
+      </c>
+      <c r="D2387" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2387" t="inlineStr"/>
+    </row>
+    <row r="2388">
+      <c r="A2388" t="inlineStr">
+        <is>
+          <t>c416dc51-3262-4d43-80f3-af84baf165bc</t>
+        </is>
+      </c>
+      <c r="B2388" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2388" t="inlineStr">
+        <is>
+          <t>2026-06-23T07:46:21.522Z</t>
+        </is>
+      </c>
+      <c r="D2388" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2388" t="inlineStr"/>
+    </row>
+    <row r="2389">
+      <c r="A2389" t="inlineStr">
+        <is>
+          <t>7b222e50-5a62-4f90-b118-d1bdd203dc7c</t>
+        </is>
+      </c>
+      <c r="B2389" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2389" t="inlineStr">
+        <is>
+          <t>2026-06-23T08:00:35.596Z</t>
+        </is>
+      </c>
+      <c r="D2389" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2389" t="inlineStr"/>
+    </row>
+    <row r="2390">
+      <c r="A2390" t="inlineStr">
+        <is>
+          <t>73dc6c98-2b2a-4ad4-bd5a-32950146f2f4</t>
+        </is>
+      </c>
+      <c r="B2390" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2390" t="inlineStr">
+        <is>
+          <t>2026-06-23T08:15:34.607Z</t>
+        </is>
+      </c>
+      <c r="D2390" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2390" t="inlineStr"/>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="inlineStr">
+        <is>
+          <t>f8a37baa-82be-402d-ab0f-8c188ff5f2b4</t>
+        </is>
+      </c>
+      <c r="B2391" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2391" t="inlineStr">
+        <is>
+          <t>2026-06-23T08:57:06.931Z</t>
+        </is>
+      </c>
+      <c r="D2391" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2391" t="inlineStr">
+        <is>
+          <t>Poss suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" t="inlineStr">
+        <is>
+          <t>7b967ead-5913-4a0e-991a-a3ac3be67676</t>
+        </is>
+      </c>
+      <c r="B2392" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2392" t="inlineStr">
+        <is>
+          <t>2026-06-23T09:09:47.302Z</t>
+        </is>
+      </c>
+      <c r="D2392" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2392" t="inlineStr">
+        <is>
+          <t>Poss suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>a7e23e0c-0c2b-4035-b6e9-584d0a30158f</t>
+        </is>
+      </c>
+      <c r="B2393" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2393" t="inlineStr">
+        <is>
+          <t>2026-06-23T09:45:29.432Z</t>
+        </is>
+      </c>
+      <c r="D2393" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2393" t="inlineStr"/>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>b20a9b30-a188-4da7-a9df-4c493476b607</t>
+        </is>
+      </c>
+      <c r="B2394" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2394" t="inlineStr">
+        <is>
+          <t>2026-06-23T10:25:22.324Z</t>
+        </is>
+      </c>
+      <c r="D2394" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2394" t="inlineStr"/>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
+        <is>
+          <t>3aba5eb8-f9f1-425e-a705-a70979850fd8</t>
+        </is>
+      </c>
+      <c r="B2395" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2395" t="inlineStr">
+        <is>
+          <t>2026-06-23T11:03:22.838Z</t>
+        </is>
+      </c>
+      <c r="D2395" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2395" t="inlineStr"/>
+    </row>
+    <row r="2396">
+      <c r="A2396" t="inlineStr">
+        <is>
+          <t>d4fbcf5d-2d98-4e9c-b06a-1b75ed1d2bfa</t>
+        </is>
+      </c>
+      <c r="B2396" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2396" t="inlineStr">
+        <is>
+          <t>2026-06-23T11:20:53.029Z</t>
+        </is>
+      </c>
+      <c r="D2396" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2396" t="inlineStr"/>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
+        <is>
+          <t>e577bedd-e252-4898-b094-8551968950c2</t>
+        </is>
+      </c>
+      <c r="B2397" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2397" t="inlineStr">
+        <is>
+          <t>2026-06-23T12:40:41.387Z</t>
+        </is>
+      </c>
+      <c r="D2397" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2397" t="inlineStr"/>
+    </row>
+    <row r="2398">
+      <c r="A2398" t="inlineStr">
+        <is>
+          <t>f0d60817-af96-444a-b8f8-9c1deb5d951b</t>
+        </is>
+      </c>
+      <c r="B2398" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2398" t="inlineStr">
+        <is>
+          <t>2026-06-23T13:52:35.355Z</t>
+        </is>
+      </c>
+      <c r="D2398" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2398" t="inlineStr"/>
+    </row>
+    <row r="2399">
+      <c r="A2399" t="inlineStr">
+        <is>
+          <t>f8fba4b8-a0b2-4552-99a9-f3365be2365f</t>
+        </is>
+      </c>
+      <c r="B2399" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2399" t="inlineStr">
+        <is>
+          <t>2026-06-23T15:59:04.111Z</t>
+        </is>
+      </c>
+      <c r="D2399" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2399" t="inlineStr"/>
+    </row>
+    <row r="2400">
+      <c r="A2400" t="inlineStr">
+        <is>
+          <t>52293def-8bc7-4451-b262-6988b3257707</t>
+        </is>
+      </c>
+      <c r="B2400" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2400" t="inlineStr">
+        <is>
+          <t>2026-06-23T16:14:27.273Z</t>
+        </is>
+      </c>
+      <c r="D2400" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2400" t="inlineStr"/>
+    </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>298a3af6-8369-4cac-aba2-58adbb962907</t>
+        </is>
+      </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2401" t="inlineStr">
+        <is>
+          <t>2026-06-23T17:31:26.214Z</t>
+        </is>
+      </c>
+      <c r="D2401" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2401" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" t="inlineStr">
+        <is>
+          <t>ace9e2b7-3e81-4111-a482-420235f766d5</t>
+        </is>
+      </c>
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2402" t="inlineStr">
+        <is>
+          <t>2026-06-23T18:26:19.439Z</t>
+        </is>
+      </c>
+      <c r="D2402" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2402" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="inlineStr">
+        <is>
+          <t>746419e9-d8ce-4fec-bc30-e5f61efba0e2</t>
+        </is>
+      </c>
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2403" t="inlineStr">
+        <is>
+          <t>2026-06-23T18:30:41.337Z</t>
+        </is>
+      </c>
+      <c r="D2403" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2403" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" t="inlineStr">
+        <is>
+          <t>bb328020-6e51-4630-876c-66605eb8338f</t>
+        </is>
+      </c>
+      <c r="B2404" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2404" t="inlineStr">
+        <is>
+          <t>2026-06-23T20:33:25.246Z</t>
+        </is>
+      </c>
+      <c r="D2404" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2404" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" t="inlineStr">
+        <is>
+          <t>34b9eb62-7e12-482d-9661-8b354593f3f4</t>
+        </is>
+      </c>
+      <c r="B2405" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2405" t="inlineStr">
+        <is>
+          <t>2026-06-23T21:58:52.677Z</t>
+        </is>
+      </c>
+      <c r="D2405" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2405" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" t="inlineStr">
+        <is>
+          <t>266b1417-2df3-48b3-8df7-d9069470c2a2</t>
+        </is>
+      </c>
+      <c r="B2406" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2406" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:14:45.400Z</t>
+        </is>
+      </c>
+      <c r="D2406" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2406" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2406"/>
+  <dimension ref="A1:E2433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54838,6 +54838,601 @@
         </is>
       </c>
     </row>
+    <row r="2407">
+      <c r="A2407" t="inlineStr">
+        <is>
+          <t>1a5624a2-3dc6-4219-9ccb-ac92863d5142</t>
+        </is>
+      </c>
+      <c r="B2407" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2407" t="inlineStr">
+        <is>
+          <t>2026-06-24T02:59:10.126Z</t>
+        </is>
+      </c>
+      <c r="D2407" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2407" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" t="inlineStr">
+        <is>
+          <t>21754643-91b8-42ea-a655-af93a22247a5</t>
+        </is>
+      </c>
+      <c r="B2408" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2408" t="inlineStr">
+        <is>
+          <t>2026-06-24T03:01:42.862Z</t>
+        </is>
+      </c>
+      <c r="D2408" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2408" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" t="inlineStr">
+        <is>
+          <t>9b3403a5-2049-426a-b844-9564fa60947a</t>
+        </is>
+      </c>
+      <c r="B2409" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2409" t="inlineStr">
+        <is>
+          <t>2026-06-24T04:10:00.926Z</t>
+        </is>
+      </c>
+      <c r="D2409" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2409" t="inlineStr"/>
+    </row>
+    <row r="2410">
+      <c r="A2410" t="inlineStr">
+        <is>
+          <t>067304e0-1985-4776-9618-b716010af360</t>
+        </is>
+      </c>
+      <c r="B2410" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2410" t="inlineStr">
+        <is>
+          <t>2026-06-24T04:22:38.540Z</t>
+        </is>
+      </c>
+      <c r="D2410" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2410" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" t="inlineStr">
+        <is>
+          <t>648261e9-473a-4b4e-9651-3ad66066c2b1</t>
+        </is>
+      </c>
+      <c r="B2411" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2411" t="inlineStr">
+        <is>
+          <t>2026-06-24T04:49:36.719Z</t>
+        </is>
+      </c>
+      <c r="D2411" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2411" t="inlineStr"/>
+    </row>
+    <row r="2412">
+      <c r="A2412" t="inlineStr">
+        <is>
+          <t>99707622-0332-449a-9323-96984567c1b0</t>
+        </is>
+      </c>
+      <c r="B2412" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2412" t="inlineStr">
+        <is>
+          <t>2026-06-24T05:22:23.695Z</t>
+        </is>
+      </c>
+      <c r="D2412" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2412" t="inlineStr"/>
+    </row>
+    <row r="2413">
+      <c r="A2413" t="inlineStr">
+        <is>
+          <t>b1f9c660-6b84-442e-a01c-5abd2798e090</t>
+        </is>
+      </c>
+      <c r="B2413" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2413" t="inlineStr">
+        <is>
+          <t>2026-06-24T06:01:13.659Z</t>
+        </is>
+      </c>
+      <c r="D2413" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2413" t="inlineStr"/>
+    </row>
+    <row r="2414">
+      <c r="A2414" t="inlineStr">
+        <is>
+          <t>587e2b63-cf58-440a-9719-f3db27e127a0</t>
+        </is>
+      </c>
+      <c r="B2414" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2414" t="inlineStr">
+        <is>
+          <t>2026-06-24T07:26:20.488Z</t>
+        </is>
+      </c>
+      <c r="D2414" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2414" t="inlineStr"/>
+    </row>
+    <row r="2415">
+      <c r="A2415" t="inlineStr">
+        <is>
+          <t>d5fd9afb-9143-4f3a-bb23-0ca0841aac30</t>
+        </is>
+      </c>
+      <c r="B2415" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2415" t="inlineStr">
+        <is>
+          <t>2026-06-24T08:29:05.921Z</t>
+        </is>
+      </c>
+      <c r="D2415" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2415" t="inlineStr"/>
+    </row>
+    <row r="2416">
+      <c r="A2416" t="inlineStr">
+        <is>
+          <t>d91b9192-6589-4fee-9d18-17e308f2b49f</t>
+        </is>
+      </c>
+      <c r="B2416" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2416" t="inlineStr">
+        <is>
+          <t>2026-06-24T09:21:08.260Z</t>
+        </is>
+      </c>
+      <c r="D2416" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2416" t="inlineStr"/>
+    </row>
+    <row r="2417">
+      <c r="A2417" t="inlineStr">
+        <is>
+          <t>5891a1f8-2026-40f7-9a2d-7ce79be1a583</t>
+        </is>
+      </c>
+      <c r="B2417" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2417" t="inlineStr">
+        <is>
+          <t>2026-06-24T10:20:57.874Z</t>
+        </is>
+      </c>
+      <c r="D2417" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2417" t="inlineStr"/>
+    </row>
+    <row r="2418">
+      <c r="A2418" t="inlineStr">
+        <is>
+          <t>13755ca2-a5f6-4cb0-bbd8-d0cabb319252</t>
+        </is>
+      </c>
+      <c r="B2418" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2418" t="inlineStr">
+        <is>
+          <t>2026-06-24T11:37:27.486Z</t>
+        </is>
+      </c>
+      <c r="D2418" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2418" t="inlineStr"/>
+    </row>
+    <row r="2419">
+      <c r="A2419" t="inlineStr">
+        <is>
+          <t>ca878638-991d-42c3-8efa-2350e4b56558</t>
+        </is>
+      </c>
+      <c r="B2419" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2419" t="inlineStr">
+        <is>
+          <t>2026-06-24T12:06:40.477Z</t>
+        </is>
+      </c>
+      <c r="D2419" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2419" t="inlineStr"/>
+    </row>
+    <row r="2420">
+      <c r="A2420" t="inlineStr">
+        <is>
+          <t>1ff76b1c-6be4-4472-bc8f-d2cafd7c9a73</t>
+        </is>
+      </c>
+      <c r="B2420" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2420" t="inlineStr">
+        <is>
+          <t>2026-06-24T15:44:51.521Z</t>
+        </is>
+      </c>
+      <c r="D2420" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2420" t="inlineStr"/>
+    </row>
+    <row r="2421">
+      <c r="A2421" t="inlineStr">
+        <is>
+          <t>b902d318-de45-48e5-836a-809c78063136</t>
+        </is>
+      </c>
+      <c r="B2421" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2421" t="inlineStr">
+        <is>
+          <t>2026-06-24T16:30:54.211Z</t>
+        </is>
+      </c>
+      <c r="D2421" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2421" t="inlineStr"/>
+    </row>
+    <row r="2422">
+      <c r="A2422" t="inlineStr">
+        <is>
+          <t>9f6a7585-f8ba-4abb-8e22-dbae89e6bd05</t>
+        </is>
+      </c>
+      <c r="B2422" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2422" t="inlineStr">
+        <is>
+          <t>2026-06-24T16:33:05.023Z</t>
+        </is>
+      </c>
+      <c r="D2422" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2422" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="inlineStr">
+        <is>
+          <t>166f5c1b-f8bc-4c40-a341-b007c7d9adf7</t>
+        </is>
+      </c>
+      <c r="B2423" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2423" t="inlineStr">
+        <is>
+          <t>2026-06-24T16:33:50.525Z</t>
+        </is>
+      </c>
+      <c r="D2423" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2423" t="inlineStr"/>
+    </row>
+    <row r="2424">
+      <c r="A2424" t="inlineStr">
+        <is>
+          <t>ba5e2823-9f8b-46af-a3fb-270fd87e4163</t>
+        </is>
+      </c>
+      <c r="B2424" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2424" t="inlineStr">
+        <is>
+          <t>2026-06-24T17:32:41.619Z</t>
+        </is>
+      </c>
+      <c r="D2424" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2424" t="inlineStr"/>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="inlineStr">
+        <is>
+          <t>6e957f14-130d-4cf2-8ff5-f25f7764fcbd</t>
+        </is>
+      </c>
+      <c r="B2425" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2425" t="inlineStr">
+        <is>
+          <t>2026-06-24T17:37:24.176Z</t>
+        </is>
+      </c>
+      <c r="D2425" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2425" t="inlineStr"/>
+    </row>
+    <row r="2426">
+      <c r="A2426" t="inlineStr">
+        <is>
+          <t>eddc0ba2-5f16-44ef-abd7-57d644f2c371</t>
+        </is>
+      </c>
+      <c r="B2426" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2426" t="inlineStr">
+        <is>
+          <t>2026-06-24T17:58:23.304Z</t>
+        </is>
+      </c>
+      <c r="D2426" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2426" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" t="inlineStr">
+        <is>
+          <t>6e344e0a-a984-421b-9927-437f48fd0014</t>
+        </is>
+      </c>
+      <c r="B2427" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2427" t="inlineStr">
+        <is>
+          <t>2026-06-24T18:00:09.466Z</t>
+        </is>
+      </c>
+      <c r="D2427" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2427" t="inlineStr"/>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="inlineStr">
+        <is>
+          <t>3b0131bd-2a4e-408b-b90f-a155f4872d1d</t>
+        </is>
+      </c>
+      <c r="B2428" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2428" t="inlineStr">
+        <is>
+          <t>2026-06-24T18:00:13.568Z</t>
+        </is>
+      </c>
+      <c r="D2428" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2428" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" t="inlineStr">
+        <is>
+          <t>1be6f75b-0ed8-4d9f-aed3-f6fe0e32d573</t>
+        </is>
+      </c>
+      <c r="B2429" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2429" t="inlineStr">
+        <is>
+          <t>2026-06-24T18:35:14.978Z</t>
+        </is>
+      </c>
+      <c r="D2429" t="n">
+        <v>530</v>
+      </c>
+      <c r="E2429" t="inlineStr"/>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="inlineStr">
+        <is>
+          <t>6bac9279-fdac-474d-a065-1ffbcdbdf567</t>
+        </is>
+      </c>
+      <c r="B2430" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2430" t="inlineStr">
+        <is>
+          <t>2026-06-24T20:19:09.514Z</t>
+        </is>
+      </c>
+      <c r="D2430" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2430" t="inlineStr"/>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="inlineStr">
+        <is>
+          <t>19e5420a-66f9-4629-86f5-63a2e04eed64</t>
+        </is>
+      </c>
+      <c r="B2431" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2431" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:03:18.915Z</t>
+        </is>
+      </c>
+      <c r="D2431" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2431" t="inlineStr"/>
+    </row>
+    <row r="2432">
+      <c r="A2432" t="inlineStr">
+        <is>
+          <t>29640dba-ef7a-4169-ad85-0c0a17075628</t>
+        </is>
+      </c>
+      <c r="B2432" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2432" t="inlineStr">
+        <is>
+          <t>2026-06-24T23:04:03.798Z</t>
+        </is>
+      </c>
+      <c r="D2432" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2432" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="inlineStr">
+        <is>
+          <t>5343642d-d0c5-4f28-a62f-c37ad21b50f3</t>
+        </is>
+      </c>
+      <c r="B2433" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2433" t="inlineStr">
+        <is>
+          <t>2026-06-24T23:37:15.328Z</t>
+        </is>
+      </c>
+      <c r="D2433" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2433" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2433"/>
+  <dimension ref="A1:E2444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55433,6 +55433,261 @@
       </c>
       <c r="E2433" t="inlineStr"/>
     </row>
+    <row r="2434">
+      <c r="A2434" t="inlineStr">
+        <is>
+          <t>08e609d8-21e9-427c-a683-dcd5d392ca68</t>
+        </is>
+      </c>
+      <c r="B2434" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2434" t="inlineStr">
+        <is>
+          <t>2026-06-25T00:15:15.638Z</t>
+        </is>
+      </c>
+      <c r="D2434" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2434" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" t="inlineStr">
+        <is>
+          <t>d36e5e17-ea83-47f5-b9e9-51d2687b5b94</t>
+        </is>
+      </c>
+      <c r="B2435" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2435" t="inlineStr">
+        <is>
+          <t>2026-06-25T00:24:38.986Z</t>
+        </is>
+      </c>
+      <c r="D2435" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2435" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" t="inlineStr">
+        <is>
+          <t>7dfd8bdc-1fbb-4e86-8a5c-c34c1060dbf3</t>
+        </is>
+      </c>
+      <c r="B2436" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2436" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:23:13.201Z</t>
+        </is>
+      </c>
+      <c r="D2436" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2436" t="inlineStr"/>
+    </row>
+    <row r="2437">
+      <c r="A2437" t="inlineStr">
+        <is>
+          <t>600a34a9-123d-4480-ab84-0555799952a0</t>
+        </is>
+      </c>
+      <c r="B2437" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2437" t="inlineStr">
+        <is>
+          <t>2026-06-25T02:46:12.812Z</t>
+        </is>
+      </c>
+      <c r="D2437" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2437" t="inlineStr">
+        <is>
+          <t>CRIMINAL INVEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" t="inlineStr">
+        <is>
+          <t>05eecdb5-930b-4087-a275-7bcc5216e202</t>
+        </is>
+      </c>
+      <c r="B2438" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2438" t="inlineStr">
+        <is>
+          <t>2026-06-25T02:46:39.502Z</t>
+        </is>
+      </c>
+      <c r="D2438" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2438" t="inlineStr">
+        <is>
+          <t>CRIMINAL INVESTIGATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" t="inlineStr">
+        <is>
+          <t>651cd75e-dd43-4d45-95e8-2fbd5a3b2417</t>
+        </is>
+      </c>
+      <c r="B2439" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2439" t="inlineStr">
+        <is>
+          <t>2026-06-25T02:52:05.025Z</t>
+        </is>
+      </c>
+      <c r="D2439" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2439" t="inlineStr"/>
+    </row>
+    <row r="2440">
+      <c r="A2440" t="inlineStr">
+        <is>
+          <t>45a789dc-53af-4156-a371-b020b95316ee</t>
+        </is>
+      </c>
+      <c r="B2440" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2440" t="inlineStr">
+        <is>
+          <t>2026-06-25T03:02:04.668Z</t>
+        </is>
+      </c>
+      <c r="D2440" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2440" t="inlineStr"/>
+    </row>
+    <row r="2441">
+      <c r="A2441" t="inlineStr">
+        <is>
+          <t>1c4a23e2-fd54-4560-b34c-9240bee43955</t>
+        </is>
+      </c>
+      <c r="B2441" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2441" t="inlineStr">
+        <is>
+          <t>2026-06-25T03:09:28.126Z</t>
+        </is>
+      </c>
+      <c r="D2441" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2441" t="inlineStr">
+        <is>
+          <t>273.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" t="inlineStr">
+        <is>
+          <t>d29bab6b-2daf-4d06-868b-d44f10d1e2f7</t>
+        </is>
+      </c>
+      <c r="B2442" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2442" t="inlineStr">
+        <is>
+          <t>2026-06-25T03:10:19.216Z</t>
+        </is>
+      </c>
+      <c r="D2442" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2442" t="inlineStr">
+        <is>
+          <t>7A88379</t>
+        </is>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="inlineStr">
+        <is>
+          <t>7063deeb-674c-4445-9468-f77a1b72aef7</t>
+        </is>
+      </c>
+      <c r="B2443" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2443" t="inlineStr">
+        <is>
+          <t>2026-06-25T16:40:34.162Z</t>
+        </is>
+      </c>
+      <c r="D2443" t="n">
+        <v>488</v>
+      </c>
+      <c r="E2443" t="inlineStr"/>
+    </row>
+    <row r="2444">
+      <c r="A2444" t="inlineStr">
+        <is>
+          <t>e42efca9-b550-4ebe-bac2-75bfab1fc47a</t>
+        </is>
+      </c>
+      <c r="B2444" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2444" t="inlineStr">
+        <is>
+          <t>2026-06-25T18:00:19.496Z</t>
+        </is>
+      </c>
+      <c r="D2444" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2444" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2444"/>
+  <dimension ref="A1:E2471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55688,6 +55688,609 @@
       </c>
       <c r="E2444" t="inlineStr"/>
     </row>
+    <row r="2445">
+      <c r="A2445" t="inlineStr">
+        <is>
+          <t>78ba3d99-6950-4918-ba9a-f86ce54ddb49</t>
+        </is>
+      </c>
+      <c r="B2445" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2445" t="inlineStr">
+        <is>
+          <t>2026-06-26T00:41:07.638Z</t>
+        </is>
+      </c>
+      <c r="D2445" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2445" t="inlineStr"/>
+    </row>
+    <row r="2446">
+      <c r="A2446" t="inlineStr">
+        <is>
+          <t>05765b93-9864-4527-a514-b41049a7d630</t>
+        </is>
+      </c>
+      <c r="B2446" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2446" t="inlineStr">
+        <is>
+          <t>2026-06-26T00:44:59.455Z</t>
+        </is>
+      </c>
+      <c r="D2446" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2446" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" t="inlineStr">
+        <is>
+          <t>075e276a-0559-47cf-8793-9430cf258bf7</t>
+        </is>
+      </c>
+      <c r="B2447" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2447" t="inlineStr">
+        <is>
+          <t>2026-06-26T01:07:27.186Z</t>
+        </is>
+      </c>
+      <c r="D2447" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2447" t="inlineStr"/>
+    </row>
+    <row r="2448">
+      <c r="A2448" t="inlineStr">
+        <is>
+          <t>d5c8fc49-8477-4a74-823e-b2b64c916207</t>
+        </is>
+      </c>
+      <c r="B2448" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2448" t="inlineStr">
+        <is>
+          <t>2026-06-26T02:22:28.916Z</t>
+        </is>
+      </c>
+      <c r="D2448" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2448" t="inlineStr"/>
+    </row>
+    <row r="2449">
+      <c r="A2449" t="inlineStr">
+        <is>
+          <t>a51c855c-93a6-4cea-b03d-9f3773bae013</t>
+        </is>
+      </c>
+      <c r="B2449" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2449" t="inlineStr">
+        <is>
+          <t>2026-06-26T05:10:52.107Z</t>
+        </is>
+      </c>
+      <c r="D2449" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2449" t="inlineStr"/>
+    </row>
+    <row r="2450">
+      <c r="A2450" t="inlineStr">
+        <is>
+          <t>d27ad1c7-91ba-43e3-aafa-0eaaa6e1b9a7</t>
+        </is>
+      </c>
+      <c r="B2450" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2450" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:15:21.342Z</t>
+        </is>
+      </c>
+      <c r="D2450" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2450" t="inlineStr">
+        <is>
+          <t>CRIMINAL INVESTIGATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" t="inlineStr">
+        <is>
+          <t>9d89aef3-0a13-43ca-85e3-05ef9152e6bf</t>
+        </is>
+      </c>
+      <c r="B2451" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2451" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:16:44.151Z</t>
+        </is>
+      </c>
+      <c r="D2451" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2451" t="inlineStr"/>
+    </row>
+    <row r="2452">
+      <c r="A2452" t="inlineStr">
+        <is>
+          <t>02981106-b2fc-4c8c-966b-0bfcfd5728a0</t>
+        </is>
+      </c>
+      <c r="B2452" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2452" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:17:37.164Z</t>
+        </is>
+      </c>
+      <c r="D2452" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2452" t="inlineStr">
+        <is>
+          <t>10851</t>
+        </is>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" t="inlineStr">
+        <is>
+          <t>976e67f8-68e1-4aa6-8e68-87430fe4ff91</t>
+        </is>
+      </c>
+      <c r="B2453" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2453" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:17:37.640Z</t>
+        </is>
+      </c>
+      <c r="D2453" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2453" t="inlineStr">
+        <is>
+          <t>10851</t>
+        </is>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" t="inlineStr">
+        <is>
+          <t>0f318f8e-302d-4754-85c1-26f6f1f6b807</t>
+        </is>
+      </c>
+      <c r="B2454" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2454" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:18:09.679Z</t>
+        </is>
+      </c>
+      <c r="D2454" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2454" t="inlineStr"/>
+    </row>
+    <row r="2455">
+      <c r="A2455" t="inlineStr">
+        <is>
+          <t>0eb7db0e-f4df-41ba-9525-4429c9f6d31d</t>
+        </is>
+      </c>
+      <c r="B2455" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2455" t="inlineStr">
+        <is>
+          <t>2026-06-26T14:08:08.171Z</t>
+        </is>
+      </c>
+      <c r="D2455" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2455" t="inlineStr">
+        <is>
+          <t>10851</t>
+        </is>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" t="inlineStr">
+        <is>
+          <t>a1e36cd4-152a-4736-b167-f5fdbc60297b</t>
+        </is>
+      </c>
+      <c r="B2456" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2456" t="inlineStr">
+        <is>
+          <t>2026-06-26T14:15:39.281Z</t>
+        </is>
+      </c>
+      <c r="D2456" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2456" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" t="inlineStr">
+        <is>
+          <t>115dde10-aad8-444c-89d6-a61a2ea6639e</t>
+        </is>
+      </c>
+      <c r="B2457" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2457" t="inlineStr">
+        <is>
+          <t>2026-06-26T15:53:14.263Z</t>
+        </is>
+      </c>
+      <c r="D2457" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2457" t="inlineStr"/>
+    </row>
+    <row r="2458">
+      <c r="A2458" t="inlineStr">
+        <is>
+          <t>10f51853-0769-4903-8888-ef49b117888f</t>
+        </is>
+      </c>
+      <c r="B2458" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2458" t="inlineStr">
+        <is>
+          <t>2026-06-26T18:05:39.410Z</t>
+        </is>
+      </c>
+      <c r="D2458" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2458" t="inlineStr"/>
+    </row>
+    <row r="2459">
+      <c r="A2459" t="inlineStr">
+        <is>
+          <t>ff46ead9-e8b6-457a-bf8b-f92617b2c84b</t>
+        </is>
+      </c>
+      <c r="B2459" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2459" t="inlineStr">
+        <is>
+          <t>2026-06-26T18:20:39.506Z</t>
+        </is>
+      </c>
+      <c r="D2459" t="n">
+        <v>567</v>
+      </c>
+      <c r="E2459" t="inlineStr"/>
+    </row>
+    <row r="2460">
+      <c r="A2460" t="inlineStr">
+        <is>
+          <t>992919ee-5a3f-4f23-8804-a49df40bdc60</t>
+        </is>
+      </c>
+      <c r="B2460" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2460" t="inlineStr">
+        <is>
+          <t>2026-06-26T18:33:12.746Z</t>
+        </is>
+      </c>
+      <c r="D2460" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2460" t="inlineStr"/>
+    </row>
+    <row r="2461">
+      <c r="A2461" t="inlineStr">
+        <is>
+          <t>becf0002-3b4a-4461-a04d-ad6f4d2d190a</t>
+        </is>
+      </c>
+      <c r="B2461" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2461" t="inlineStr">
+        <is>
+          <t>2026-06-26T20:10:43.942Z</t>
+        </is>
+      </c>
+      <c r="D2461" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2461" t="inlineStr"/>
+    </row>
+    <row r="2462">
+      <c r="A2462" t="inlineStr">
+        <is>
+          <t>377de13b-de46-45f0-8158-bf0ef21ded1e</t>
+        </is>
+      </c>
+      <c r="B2462" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2462" t="inlineStr">
+        <is>
+          <t>2026-06-26T20:28:45.577Z</t>
+        </is>
+      </c>
+      <c r="D2462" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2462" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" t="inlineStr">
+        <is>
+          <t>5935a6dd-feec-4bb0-8225-dbb74598456f</t>
+        </is>
+      </c>
+      <c r="B2463" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2463" t="inlineStr">
+        <is>
+          <t>2026-06-26T20:31:18.864Z</t>
+        </is>
+      </c>
+      <c r="D2463" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2463" t="inlineStr"/>
+    </row>
+    <row r="2464">
+      <c r="A2464" t="inlineStr">
+        <is>
+          <t>c27e9c69-9060-4803-a367-77df68ee57dc</t>
+        </is>
+      </c>
+      <c r="B2464" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2464" t="inlineStr">
+        <is>
+          <t>2026-06-26T21:03:41.123Z</t>
+        </is>
+      </c>
+      <c r="D2464" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2464" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" t="inlineStr">
+        <is>
+          <t>6c9dfb06-7409-45b9-8fca-ff41bc33adc3</t>
+        </is>
+      </c>
+      <c r="B2465" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2465" t="inlineStr">
+        <is>
+          <t>2026-06-26T21:08:18.695Z</t>
+        </is>
+      </c>
+      <c r="D2465" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2465" t="inlineStr"/>
+    </row>
+    <row r="2466">
+      <c r="A2466" t="inlineStr">
+        <is>
+          <t>6bc44637-5b04-4223-9faa-6a5f4103ff0b</t>
+        </is>
+      </c>
+      <c r="B2466" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2466" t="inlineStr">
+        <is>
+          <t>2026-06-26T21:20:14.082Z</t>
+        </is>
+      </c>
+      <c r="D2466" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2466" t="inlineStr">
+        <is>
+          <t>theft investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" t="inlineStr">
+        <is>
+          <t>9388dc42-6ff3-4f3d-8f78-faf2ba6a0631</t>
+        </is>
+      </c>
+      <c r="B2467" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2467" t="inlineStr">
+        <is>
+          <t>2026-06-26T21:25:41.287Z</t>
+        </is>
+      </c>
+      <c r="D2467" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2467" t="inlineStr"/>
+    </row>
+    <row r="2468">
+      <c r="A2468" t="inlineStr">
+        <is>
+          <t>a38ad4bc-ed8a-4787-8b7c-876cfe2de3a2</t>
+        </is>
+      </c>
+      <c r="B2468" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2468" t="inlineStr">
+        <is>
+          <t>2026-06-26T21:59:50.130Z</t>
+        </is>
+      </c>
+      <c r="D2468" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2468" t="inlineStr"/>
+    </row>
+    <row r="2469">
+      <c r="A2469" t="inlineStr">
+        <is>
+          <t>90265084-8878-4376-a712-bd76041835c7</t>
+        </is>
+      </c>
+      <c r="B2469" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2469" t="inlineStr">
+        <is>
+          <t>2026-06-26T22:00:09.611Z</t>
+        </is>
+      </c>
+      <c r="D2469" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2469" t="inlineStr"/>
+    </row>
+    <row r="2470">
+      <c r="A2470" t="inlineStr">
+        <is>
+          <t>ecbe4ba5-33f7-40cf-b6dc-4ea985bfa133</t>
+        </is>
+      </c>
+      <c r="B2470" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2470" t="inlineStr">
+        <is>
+          <t>2026-06-26T22:06:14.480Z</t>
+        </is>
+      </c>
+      <c r="D2470" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2470" t="inlineStr"/>
+    </row>
+    <row r="2471">
+      <c r="A2471" t="inlineStr">
+        <is>
+          <t>a666bc63-44dc-48b8-ab1f-89ce17ae471f</t>
+        </is>
+      </c>
+      <c r="B2471" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2471" t="inlineStr">
+        <is>
+          <t>2026-06-26T22:21:24.194Z</t>
+        </is>
+      </c>
+      <c r="D2471" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2471" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2471"/>
+  <dimension ref="A1:E2478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56291,6 +56291,165 @@
       </c>
       <c r="E2471" t="inlineStr"/>
     </row>
+    <row r="2472">
+      <c r="A2472" t="inlineStr">
+        <is>
+          <t>183f3767-39fc-4906-ba7c-d5f4064742ab</t>
+        </is>
+      </c>
+      <c r="B2472" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2472" t="inlineStr">
+        <is>
+          <t>2026-06-27T05:31:19.875Z</t>
+        </is>
+      </c>
+      <c r="D2472" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2472" t="inlineStr"/>
+    </row>
+    <row r="2473">
+      <c r="A2473" t="inlineStr">
+        <is>
+          <t>d2c27c4a-f83f-4bba-92d8-2a3cfdce13a7</t>
+        </is>
+      </c>
+      <c r="B2473" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2473" t="inlineStr">
+        <is>
+          <t>2026-06-27T05:56:58.129Z</t>
+        </is>
+      </c>
+      <c r="D2473" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2473" t="inlineStr">
+        <is>
+          <t>CRIMINAL INVESTIGATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" t="inlineStr">
+        <is>
+          <t>33f93d78-48fb-4654-b83a-8d26906ebdec</t>
+        </is>
+      </c>
+      <c r="B2474" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2474" t="inlineStr">
+        <is>
+          <t>2026-06-27T06:02:40.547Z</t>
+        </is>
+      </c>
+      <c r="D2474" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2474" t="inlineStr">
+        <is>
+          <t>10851</t>
+        </is>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" t="inlineStr">
+        <is>
+          <t>70f76bb4-98f8-49a4-90d7-81c411d08f52</t>
+        </is>
+      </c>
+      <c r="B2475" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2475" t="inlineStr">
+        <is>
+          <t>2026-06-27T06:03:25.061Z</t>
+        </is>
+      </c>
+      <c r="D2475" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2475" t="inlineStr"/>
+    </row>
+    <row r="2476">
+      <c r="A2476" t="inlineStr">
+        <is>
+          <t>54aad469-9bba-46f6-8117-147647bec23f</t>
+        </is>
+      </c>
+      <c r="B2476" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2476" t="inlineStr">
+        <is>
+          <t>2026-06-27T07:07:05.714Z</t>
+        </is>
+      </c>
+      <c r="D2476" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2476" t="inlineStr">
+        <is>
+          <t>CRIMINAL INVESTIGATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" t="inlineStr">
+        <is>
+          <t>92a250bd-0920-46a5-94a9-fabb8784d448</t>
+        </is>
+      </c>
+      <c r="B2477" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2477" t="inlineStr">
+        <is>
+          <t>2026-06-27T17:16:36.499Z</t>
+        </is>
+      </c>
+      <c r="D2477" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2477" t="inlineStr"/>
+    </row>
+    <row r="2478">
+      <c r="A2478" t="inlineStr">
+        <is>
+          <t>f7ff36c0-4262-4607-bb61-e5f8f77fba2a</t>
+        </is>
+      </c>
+      <c r="B2478" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2478" t="inlineStr">
+        <is>
+          <t>2026-06-27T23:09:29.378Z</t>
+        </is>
+      </c>
+      <c r="D2478" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2478" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2478"/>
+  <dimension ref="A1:E2480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56450,6 +56450,52 @@
       </c>
       <c r="E2478" t="inlineStr"/>
     </row>
+    <row r="2479">
+      <c r="A2479" t="inlineStr">
+        <is>
+          <t>cbf92ab9-a1aa-48a5-8cb1-17c660272762</t>
+        </is>
+      </c>
+      <c r="B2479" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2479" t="inlineStr">
+        <is>
+          <t>2026-06-28T23:21:06.489Z</t>
+        </is>
+      </c>
+      <c r="D2479" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2479" t="inlineStr"/>
+    </row>
+    <row r="2480">
+      <c r="A2480" t="inlineStr">
+        <is>
+          <t>ea75d056-e123-416a-a6dc-df638f7e3dbf</t>
+        </is>
+      </c>
+      <c r="B2480" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2480" t="inlineStr">
+        <is>
+          <t>2026-06-28T23:59:47.939Z</t>
+        </is>
+      </c>
+      <c r="D2480" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2480" t="inlineStr">
+        <is>
+          <t>victim's vehicle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2480"/>
+  <dimension ref="A1:E2508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56496,6 +56496,642 @@
         </is>
       </c>
     </row>
+    <row r="2481">
+      <c r="A2481" t="inlineStr">
+        <is>
+          <t>c1431525-92e8-4dc1-81b5-e184f51cfdca</t>
+        </is>
+      </c>
+      <c r="B2481" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2481" t="inlineStr">
+        <is>
+          <t>2026-06-29T00:00:22.128Z</t>
+        </is>
+      </c>
+      <c r="D2481" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2481" t="inlineStr">
+        <is>
+          <t>victim's vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" t="inlineStr">
+        <is>
+          <t>6511bd12-fed5-426d-881a-925d8973de67</t>
+        </is>
+      </c>
+      <c r="B2482" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2482" t="inlineStr">
+        <is>
+          <t>2026-06-29T01:50:55.366Z</t>
+        </is>
+      </c>
+      <c r="D2482" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2482" t="inlineStr">
+        <is>
+          <t>victim's vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" t="inlineStr">
+        <is>
+          <t>451d7314-1c5f-488f-8833-bfa2dd82805d</t>
+        </is>
+      </c>
+      <c r="B2483" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2483" t="inlineStr">
+        <is>
+          <t>2026-06-29T02:28:03.186Z</t>
+        </is>
+      </c>
+      <c r="D2483" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2483" t="inlineStr">
+        <is>
+          <t>victim's vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" t="inlineStr">
+        <is>
+          <t>408c62d1-4980-41c4-a1a9-b7149fe93bfe</t>
+        </is>
+      </c>
+      <c r="B2484" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2484" t="inlineStr">
+        <is>
+          <t>2026-06-29T05:03:05.761Z</t>
+        </is>
+      </c>
+      <c r="D2484" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2484" t="inlineStr"/>
+    </row>
+    <row r="2485">
+      <c r="A2485" t="inlineStr">
+        <is>
+          <t>357e1996-35fe-4404-a7ba-86d76408cc71</t>
+        </is>
+      </c>
+      <c r="B2485" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2485" t="inlineStr">
+        <is>
+          <t>2026-06-29T06:35:25.304Z</t>
+        </is>
+      </c>
+      <c r="D2485" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2485" t="inlineStr"/>
+    </row>
+    <row r="2486">
+      <c r="A2486" t="inlineStr">
+        <is>
+          <t>4a984262-6d76-4017-a1be-11a94842cf48</t>
+        </is>
+      </c>
+      <c r="B2486" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2486" t="inlineStr">
+        <is>
+          <t>2026-06-29T07:26:16.188Z</t>
+        </is>
+      </c>
+      <c r="D2486" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2486" t="inlineStr">
+        <is>
+          <t>Poss suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" t="inlineStr">
+        <is>
+          <t>e51e5740-cc0f-4951-be69-2c6472280987</t>
+        </is>
+      </c>
+      <c r="B2487" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2487" t="inlineStr">
+        <is>
+          <t>2026-06-29T07:26:16.779Z</t>
+        </is>
+      </c>
+      <c r="D2487" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2487" t="inlineStr"/>
+    </row>
+    <row r="2488">
+      <c r="A2488" t="inlineStr">
+        <is>
+          <t>1fba3e41-2663-4789-b72a-f3659ce7b85e</t>
+        </is>
+      </c>
+      <c r="B2488" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2488" t="inlineStr">
+        <is>
+          <t>2026-06-29T09:20:38.457Z</t>
+        </is>
+      </c>
+      <c r="D2488" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2488" t="inlineStr"/>
+    </row>
+    <row r="2489">
+      <c r="A2489" t="inlineStr">
+        <is>
+          <t>a2eb38c3-951a-47a7-88aa-ec3f717878b4</t>
+        </is>
+      </c>
+      <c r="B2489" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2489" t="inlineStr">
+        <is>
+          <t>2026-06-29T09:25:14.922Z</t>
+        </is>
+      </c>
+      <c r="D2489" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2489" t="inlineStr">
+        <is>
+          <t>Poss suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" t="inlineStr">
+        <is>
+          <t>e2adf5fc-330c-414d-8e29-cb33eabf284a</t>
+        </is>
+      </c>
+      <c r="B2490" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2490" t="inlineStr">
+        <is>
+          <t>2026-06-29T10:02:38.780Z</t>
+        </is>
+      </c>
+      <c r="D2490" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2490" t="inlineStr"/>
+    </row>
+    <row r="2491">
+      <c r="A2491" t="inlineStr">
+        <is>
+          <t>4a58db55-c47c-4d8f-b7b2-7d9661a8d652</t>
+        </is>
+      </c>
+      <c r="B2491" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2491" t="inlineStr">
+        <is>
+          <t>2026-06-29T10:36:10.602Z</t>
+        </is>
+      </c>
+      <c r="D2491" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2491" t="inlineStr">
+        <is>
+          <t>Poss suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" t="inlineStr">
+        <is>
+          <t>68d153e5-5e41-4e89-bf12-2a46973d1069</t>
+        </is>
+      </c>
+      <c r="B2492" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2492" t="inlineStr">
+        <is>
+          <t>2026-06-29T11:06:13.447Z</t>
+        </is>
+      </c>
+      <c r="D2492" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2492" t="inlineStr"/>
+    </row>
+    <row r="2493">
+      <c r="A2493" t="inlineStr">
+        <is>
+          <t>50088a30-53be-4d70-9069-023da8f59064</t>
+        </is>
+      </c>
+      <c r="B2493" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2493" t="inlineStr">
+        <is>
+          <t>2026-06-29T12:12:38.347Z</t>
+        </is>
+      </c>
+      <c r="D2493" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2493" t="inlineStr"/>
+    </row>
+    <row r="2494">
+      <c r="A2494" t="inlineStr">
+        <is>
+          <t>04bf3d52-dd84-4acb-8efc-936de24c2d79</t>
+        </is>
+      </c>
+      <c r="B2494" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2494" t="inlineStr">
+        <is>
+          <t>2026-06-29T15:12:22.420Z</t>
+        </is>
+      </c>
+      <c r="D2494" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2494" t="inlineStr">
+        <is>
+          <t>245 pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" t="inlineStr">
+        <is>
+          <t>1121d5be-1596-48c4-8154-453aa5cef575</t>
+        </is>
+      </c>
+      <c r="B2495" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2495" t="inlineStr">
+        <is>
+          <t>2026-06-29T15:52:09.576Z</t>
+        </is>
+      </c>
+      <c r="D2495" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2495" t="inlineStr"/>
+    </row>
+    <row r="2496">
+      <c r="A2496" t="inlineStr">
+        <is>
+          <t>db63f79c-d897-4f82-8d8f-3c6441ae9251</t>
+        </is>
+      </c>
+      <c r="B2496" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2496" t="inlineStr">
+        <is>
+          <t>2026-06-29T16:06:05.165Z</t>
+        </is>
+      </c>
+      <c r="D2496" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2496" t="inlineStr"/>
+    </row>
+    <row r="2497">
+      <c r="A2497" t="inlineStr">
+        <is>
+          <t>73081cd6-c54b-4d74-b721-765ed91e57e1</t>
+        </is>
+      </c>
+      <c r="B2497" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2497" t="inlineStr">
+        <is>
+          <t>2026-06-29T17:27:22.969Z</t>
+        </is>
+      </c>
+      <c r="D2497" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2497" t="inlineStr">
+        <is>
+          <t>Suspect vehicle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" t="inlineStr">
+        <is>
+          <t>b682127c-764f-4512-aa42-8cfe120f96ef</t>
+        </is>
+      </c>
+      <c r="B2498" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2498" t="inlineStr">
+        <is>
+          <t>2026-06-29T17:38:56.533Z</t>
+        </is>
+      </c>
+      <c r="D2498" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2498" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" t="inlineStr">
+        <is>
+          <t>0fc32abc-60a9-4828-8097-d2707a49df08</t>
+        </is>
+      </c>
+      <c r="B2499" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2499" t="inlineStr">
+        <is>
+          <t>2026-06-29T18:22:15.888Z</t>
+        </is>
+      </c>
+      <c r="D2499" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2499" t="inlineStr"/>
+    </row>
+    <row r="2500">
+      <c r="A2500" t="inlineStr">
+        <is>
+          <t>5ad47a36-ed5c-417a-a206-11671dc460ea</t>
+        </is>
+      </c>
+      <c r="B2500" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2500" t="inlineStr">
+        <is>
+          <t>2026-06-29T19:03:33.792Z</t>
+        </is>
+      </c>
+      <c r="D2500" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2500" t="inlineStr"/>
+    </row>
+    <row r="2501">
+      <c r="A2501" t="inlineStr">
+        <is>
+          <t>51f39d69-8c15-42b6-8a2c-bee4f4853781</t>
+        </is>
+      </c>
+      <c r="B2501" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2501" t="inlineStr">
+        <is>
+          <t>2026-06-29T19:29:08.551Z</t>
+        </is>
+      </c>
+      <c r="D2501" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2501" t="inlineStr"/>
+    </row>
+    <row r="2502">
+      <c r="A2502" t="inlineStr">
+        <is>
+          <t>b235c580-2f84-41ec-aebf-0285a2b8859e</t>
+        </is>
+      </c>
+      <c r="B2502" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2502" t="inlineStr">
+        <is>
+          <t>2026-06-29T19:38:54.490Z</t>
+        </is>
+      </c>
+      <c r="D2502" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2502" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" t="inlineStr">
+        <is>
+          <t>c8be9e81-6fac-4a28-a16e-e9ab58ffa7ec</t>
+        </is>
+      </c>
+      <c r="B2503" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2503" t="inlineStr">
+        <is>
+          <t>2026-06-29T20:00:41.001Z</t>
+        </is>
+      </c>
+      <c r="D2503" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2503" t="inlineStr"/>
+    </row>
+    <row r="2504">
+      <c r="A2504" t="inlineStr">
+        <is>
+          <t>790090d7-a539-45ff-87e4-e697246101f7</t>
+        </is>
+      </c>
+      <c r="B2504" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2504" t="inlineStr">
+        <is>
+          <t>2026-06-29T20:02:45.618Z</t>
+        </is>
+      </c>
+      <c r="D2504" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2504" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" t="inlineStr">
+        <is>
+          <t>cd153e3d-f7bd-4916-be27-1189d2ce526f</t>
+        </is>
+      </c>
+      <c r="B2505" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2505" t="inlineStr">
+        <is>
+          <t>2026-06-29T20:05:10.973Z</t>
+        </is>
+      </c>
+      <c r="D2505" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2505" t="inlineStr"/>
+    </row>
+    <row r="2506">
+      <c r="A2506" t="inlineStr">
+        <is>
+          <t>3f0b306c-d4ec-4bc0-9e90-3dfea1e6d7b5</t>
+        </is>
+      </c>
+      <c r="B2506" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2506" t="inlineStr">
+        <is>
+          <t>2026-06-29T21:05:20.096Z</t>
+        </is>
+      </c>
+      <c r="D2506" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2506" t="inlineStr"/>
+    </row>
+    <row r="2507">
+      <c r="A2507" t="inlineStr">
+        <is>
+          <t>e465629e-61aa-4cf8-befc-b84317d067c3</t>
+        </is>
+      </c>
+      <c r="B2507" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2507" t="inlineStr">
+        <is>
+          <t>2026-06-29T21:31:48.112Z</t>
+        </is>
+      </c>
+      <c r="D2507" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2507" t="inlineStr"/>
+    </row>
+    <row r="2508">
+      <c r="A2508" t="inlineStr">
+        <is>
+          <t>1812452a-d159-48fd-94c7-cb3799cbedfb</t>
+        </is>
+      </c>
+      <c r="B2508" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2508" t="inlineStr">
+        <is>
+          <t>2026-06-29T23:49:06.076Z</t>
+        </is>
+      </c>
+      <c r="D2508" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2508" t="inlineStr">
+        <is>
+          <t>suspect in wire theft</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2508"/>
+  <dimension ref="A1:E2540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57132,6 +57132,702 @@
         </is>
       </c>
     </row>
+    <row r="2509">
+      <c r="A2509" t="inlineStr">
+        <is>
+          <t>d43fc340-e1a0-4585-a72b-30667a460d9e</t>
+        </is>
+      </c>
+      <c r="B2509" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2509" t="inlineStr">
+        <is>
+          <t>2026-06-30T01:59:58.234Z</t>
+        </is>
+      </c>
+      <c r="D2509" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2509" t="inlineStr"/>
+    </row>
+    <row r="2510">
+      <c r="A2510" t="inlineStr">
+        <is>
+          <t>40f47b6d-e467-44d4-9e90-826e8c57cb76</t>
+        </is>
+      </c>
+      <c r="B2510" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2510" t="inlineStr">
+        <is>
+          <t>2026-06-30T02:16:52.088Z</t>
+        </is>
+      </c>
+      <c r="D2510" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2510" t="inlineStr"/>
+    </row>
+    <row r="2511">
+      <c r="A2511" t="inlineStr">
+        <is>
+          <t>9b5c2285-4576-4bca-a3bf-f92d7b39252b</t>
+        </is>
+      </c>
+      <c r="B2511" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2511" t="inlineStr">
+        <is>
+          <t>2026-06-30T02:53:25.049Z</t>
+        </is>
+      </c>
+      <c r="D2511" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2511" t="inlineStr"/>
+    </row>
+    <row r="2512">
+      <c r="A2512" t="inlineStr">
+        <is>
+          <t>bd4ee4d1-a700-4e19-ad4d-5433b14a7ae4</t>
+        </is>
+      </c>
+      <c r="B2512" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2512" t="inlineStr">
+        <is>
+          <t>2026-06-30T03:15:02.999Z</t>
+        </is>
+      </c>
+      <c r="D2512" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2512" t="inlineStr"/>
+    </row>
+    <row r="2513">
+      <c r="A2513" t="inlineStr">
+        <is>
+          <t>efac3ee2-5990-4cce-95da-9f1b0c91e7b7</t>
+        </is>
+      </c>
+      <c r="B2513" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2513" t="inlineStr">
+        <is>
+          <t>2026-06-30T04:45:16.921Z</t>
+        </is>
+      </c>
+      <c r="D2513" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2513" t="inlineStr"/>
+    </row>
+    <row r="2514">
+      <c r="A2514" t="inlineStr">
+        <is>
+          <t>f5096372-c4bc-43e9-af4f-88b371523002</t>
+        </is>
+      </c>
+      <c r="B2514" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2514" t="inlineStr">
+        <is>
+          <t>2026-06-30T04:50:05.800Z</t>
+        </is>
+      </c>
+      <c r="D2514" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2514" t="inlineStr"/>
+    </row>
+    <row r="2515">
+      <c r="A2515" t="inlineStr">
+        <is>
+          <t>fd7faa82-9ed2-42ee-a80a-fc72c7c5249f</t>
+        </is>
+      </c>
+      <c r="B2515" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2515" t="inlineStr">
+        <is>
+          <t>2026-06-30T05:04:38.127Z</t>
+        </is>
+      </c>
+      <c r="D2515" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2515" t="inlineStr"/>
+    </row>
+    <row r="2516">
+      <c r="A2516" t="inlineStr">
+        <is>
+          <t>7a132843-df45-4451-b867-8b18010435df</t>
+        </is>
+      </c>
+      <c r="B2516" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2516" t="inlineStr">
+        <is>
+          <t>2026-06-30T05:08:47.845Z</t>
+        </is>
+      </c>
+      <c r="D2516" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2516" t="inlineStr"/>
+    </row>
+    <row r="2517">
+      <c r="A2517" t="inlineStr">
+        <is>
+          <t>e269f118-c272-4e61-8158-81282154e1a3</t>
+        </is>
+      </c>
+      <c r="B2517" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2517" t="inlineStr">
+        <is>
+          <t>2026-06-30T05:35:33.874Z</t>
+        </is>
+      </c>
+      <c r="D2517" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2517" t="inlineStr">
+        <is>
+          <t>Locate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" t="inlineStr">
+        <is>
+          <t>4696af89-dba5-43b6-9c52-67a07e371009</t>
+        </is>
+      </c>
+      <c r="B2518" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2518" t="inlineStr">
+        <is>
+          <t>2026-06-30T06:02:23.931Z</t>
+        </is>
+      </c>
+      <c r="D2518" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2518" t="inlineStr"/>
+    </row>
+    <row r="2519">
+      <c r="A2519" t="inlineStr">
+        <is>
+          <t>d5255f74-f147-4a87-9fab-10c65e11d19a</t>
+        </is>
+      </c>
+      <c r="B2519" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2519" t="inlineStr">
+        <is>
+          <t>2026-06-30T06:03:53.231Z</t>
+        </is>
+      </c>
+      <c r="D2519" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2519" t="inlineStr"/>
+    </row>
+    <row r="2520">
+      <c r="A2520" t="inlineStr">
+        <is>
+          <t>ec050331-e814-41e2-a137-b332723f317b</t>
+        </is>
+      </c>
+      <c r="B2520" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2520" t="inlineStr">
+        <is>
+          <t>2026-06-30T06:11:00.549Z</t>
+        </is>
+      </c>
+      <c r="D2520" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2520" t="inlineStr"/>
+    </row>
+    <row r="2521">
+      <c r="A2521" t="inlineStr">
+        <is>
+          <t>4c8a4aa0-09b3-4d37-b1c5-e183fd400d33</t>
+        </is>
+      </c>
+      <c r="B2521" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2521" t="inlineStr">
+        <is>
+          <t>2026-06-30T06:25:17.821Z</t>
+        </is>
+      </c>
+      <c r="D2521" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2521" t="inlineStr">
+        <is>
+          <t>Locate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" t="inlineStr">
+        <is>
+          <t>a7f846d0-b3be-4478-b0b5-2b5a88f31587</t>
+        </is>
+      </c>
+      <c r="B2522" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2522" t="inlineStr">
+        <is>
+          <t>2026-06-30T07:00:41.140Z</t>
+        </is>
+      </c>
+      <c r="D2522" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2522" t="inlineStr"/>
+    </row>
+    <row r="2523">
+      <c r="A2523" t="inlineStr">
+        <is>
+          <t>8f6ce5f8-0aef-4776-b83f-f40ba0c12540</t>
+        </is>
+      </c>
+      <c r="B2523" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2523" t="inlineStr">
+        <is>
+          <t>2026-06-30T07:05:51.746Z</t>
+        </is>
+      </c>
+      <c r="D2523" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2523" t="inlineStr"/>
+    </row>
+    <row r="2524">
+      <c r="A2524" t="inlineStr">
+        <is>
+          <t>cf7d4308-5cba-4b3e-8f12-433abb6abd69</t>
+        </is>
+      </c>
+      <c r="B2524" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2524" t="inlineStr">
+        <is>
+          <t>2026-06-30T07:25:05.007Z</t>
+        </is>
+      </c>
+      <c r="D2524" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2524" t="inlineStr"/>
+    </row>
+    <row r="2525">
+      <c r="A2525" t="inlineStr">
+        <is>
+          <t>0ea39710-dbe6-4499-b537-888f3e31b7c3</t>
+        </is>
+      </c>
+      <c r="B2525" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2525" t="inlineStr">
+        <is>
+          <t>2026-06-30T07:27:58.112Z</t>
+        </is>
+      </c>
+      <c r="D2525" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2525" t="inlineStr">
+        <is>
+          <t>Locate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" t="inlineStr">
+        <is>
+          <t>90432d4f-9787-4c6a-84c2-5fb9e0604e2c</t>
+        </is>
+      </c>
+      <c r="B2526" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2526" t="inlineStr">
+        <is>
+          <t>2026-06-30T08:56:48.243Z</t>
+        </is>
+      </c>
+      <c r="D2526" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2526" t="inlineStr">
+        <is>
+          <t>Locate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" t="inlineStr">
+        <is>
+          <t>c0f586e8-794c-4c74-8cd3-cc88175ea8ca</t>
+        </is>
+      </c>
+      <c r="B2527" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2527" t="inlineStr">
+        <is>
+          <t>2026-06-30T08:59:08.715Z</t>
+        </is>
+      </c>
+      <c r="D2527" t="n">
+        <v>566</v>
+      </c>
+      <c r="E2527" t="inlineStr"/>
+    </row>
+    <row r="2528">
+      <c r="A2528" t="inlineStr">
+        <is>
+          <t>2224481e-37d3-4d3f-9ef7-2ae4c0afe6b0</t>
+        </is>
+      </c>
+      <c r="B2528" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2528" t="inlineStr">
+        <is>
+          <t>2026-06-30T09:00:37.252Z</t>
+        </is>
+      </c>
+      <c r="D2528" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2528" t="inlineStr">
+        <is>
+          <t>Locate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" t="inlineStr">
+        <is>
+          <t>ca44bbdf-b518-4577-bed3-8b0971fd5ac6</t>
+        </is>
+      </c>
+      <c r="B2529" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2529" t="inlineStr">
+        <is>
+          <t>2026-06-30T09:09:31.661Z</t>
+        </is>
+      </c>
+      <c r="D2529" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2529" t="inlineStr"/>
+    </row>
+    <row r="2530">
+      <c r="A2530" t="inlineStr">
+        <is>
+          <t>d14c6815-6a90-4b09-9801-046510351ced</t>
+        </is>
+      </c>
+      <c r="B2530" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2530" t="inlineStr">
+        <is>
+          <t>2026-06-30T09:37:43.196Z</t>
+        </is>
+      </c>
+      <c r="D2530" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2530" t="inlineStr"/>
+    </row>
+    <row r="2531">
+      <c r="A2531" t="inlineStr">
+        <is>
+          <t>5e103acc-1d64-412d-ba48-cd8b90488224</t>
+        </is>
+      </c>
+      <c r="B2531" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2531" t="inlineStr">
+        <is>
+          <t>2026-06-30T10:45:38.224Z</t>
+        </is>
+      </c>
+      <c r="D2531" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2531" t="inlineStr"/>
+    </row>
+    <row r="2532">
+      <c r="A2532" t="inlineStr">
+        <is>
+          <t>e1b56b30-c326-416c-b494-17f5315d5d9d</t>
+        </is>
+      </c>
+      <c r="B2532" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2532" t="inlineStr">
+        <is>
+          <t>2026-06-30T11:07:38.742Z</t>
+        </is>
+      </c>
+      <c r="D2532" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2532" t="inlineStr"/>
+    </row>
+    <row r="2533">
+      <c r="A2533" t="inlineStr">
+        <is>
+          <t>fe15f74c-b0a1-4a6f-9edb-584cc6647cea</t>
+        </is>
+      </c>
+      <c r="B2533" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2533" t="inlineStr">
+        <is>
+          <t>2026-06-30T12:26:47.372Z</t>
+        </is>
+      </c>
+      <c r="D2533" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2533" t="inlineStr"/>
+    </row>
+    <row r="2534">
+      <c r="A2534" t="inlineStr">
+        <is>
+          <t>fd337192-21d1-49c7-812b-ca13d2ca1f3d</t>
+        </is>
+      </c>
+      <c r="B2534" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2534" t="inlineStr">
+        <is>
+          <t>2026-06-30T14:51:50.187Z</t>
+        </is>
+      </c>
+      <c r="D2534" t="n">
+        <v>522</v>
+      </c>
+      <c r="E2534" t="inlineStr"/>
+    </row>
+    <row r="2535">
+      <c r="A2535" t="inlineStr">
+        <is>
+          <t>1308ee92-c1e4-41d7-a3b2-b6c1c031798a</t>
+        </is>
+      </c>
+      <c r="B2535" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2535" t="inlineStr">
+        <is>
+          <t>2026-06-30T20:18:30.485Z</t>
+        </is>
+      </c>
+      <c r="D2535" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2535" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" t="inlineStr">
+        <is>
+          <t>67d85f0d-213e-4b49-a7ca-71f7c3d2256f</t>
+        </is>
+      </c>
+      <c r="B2536" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2536" t="inlineStr">
+        <is>
+          <t>2026-06-30T20:20:09.148Z</t>
+        </is>
+      </c>
+      <c r="D2536" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2536" t="inlineStr"/>
+    </row>
+    <row r="2537">
+      <c r="A2537" t="inlineStr">
+        <is>
+          <t>907c6b1f-6dfe-4320-aa92-5122f0c1354a</t>
+        </is>
+      </c>
+      <c r="B2537" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2537" t="inlineStr">
+        <is>
+          <t>2026-06-30T20:25:54.640Z</t>
+        </is>
+      </c>
+      <c r="D2537" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2537" t="inlineStr"/>
+    </row>
+    <row r="2538">
+      <c r="A2538" t="inlineStr">
+        <is>
+          <t>bd8e83e5-a362-4d01-b979-8497db53678f</t>
+        </is>
+      </c>
+      <c r="B2538" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2538" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:54:08.884Z</t>
+        </is>
+      </c>
+      <c r="D2538" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2538" t="inlineStr"/>
+    </row>
+    <row r="2539">
+      <c r="A2539" t="inlineStr">
+        <is>
+          <t>18beaa0b-8dda-4a08-98f6-82a607c42036</t>
+        </is>
+      </c>
+      <c r="B2539" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2539" t="inlineStr">
+        <is>
+          <t>2026-06-30T23:46:39.026Z</t>
+        </is>
+      </c>
+      <c r="D2539" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2539" t="inlineStr"/>
+    </row>
+    <row r="2540">
+      <c r="A2540" t="inlineStr">
+        <is>
+          <t>b6f36fa1-d51f-4a91-8911-89905fcbd761</t>
+        </is>
+      </c>
+      <c r="B2540" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2540" t="inlineStr">
+        <is>
+          <t>2026-06-30T23:50:59.046Z</t>
+        </is>
+      </c>
+      <c r="D2540" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2540" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2540"/>
+  <dimension ref="A1:E2568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57828,6 +57828,618 @@
       </c>
       <c r="E2540" t="inlineStr"/>
     </row>
+    <row r="2541">
+      <c r="A2541" t="inlineStr">
+        <is>
+          <t>7ed4c396-2cf9-450d-aa33-67eb31e21469</t>
+        </is>
+      </c>
+      <c r="B2541" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2541" t="inlineStr">
+        <is>
+          <t>2026-07-01T00:38:01.470Z</t>
+        </is>
+      </c>
+      <c r="D2541" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2541" t="inlineStr"/>
+    </row>
+    <row r="2542">
+      <c r="A2542" t="inlineStr">
+        <is>
+          <t>79c8e5f1-f7d2-47f5-ac11-4d686e470519</t>
+        </is>
+      </c>
+      <c r="B2542" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2542" t="inlineStr">
+        <is>
+          <t>2026-07-01T01:09:58.758Z</t>
+        </is>
+      </c>
+      <c r="D2542" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2542" t="inlineStr"/>
+    </row>
+    <row r="2543">
+      <c r="A2543" t="inlineStr">
+        <is>
+          <t>99b795b3-8a8a-415a-8323-a53e31a5b65e</t>
+        </is>
+      </c>
+      <c r="B2543" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2543" t="inlineStr">
+        <is>
+          <t>2026-07-01T02:20:20.432Z</t>
+        </is>
+      </c>
+      <c r="D2543" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2543" t="inlineStr"/>
+    </row>
+    <row r="2544">
+      <c r="A2544" t="inlineStr">
+        <is>
+          <t>281f559c-0767-4879-967b-d547d3ab5403</t>
+        </is>
+      </c>
+      <c r="B2544" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2544" t="inlineStr">
+        <is>
+          <t>2026-07-01T02:23:51.924Z</t>
+        </is>
+      </c>
+      <c r="D2544" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2544" t="inlineStr"/>
+    </row>
+    <row r="2545">
+      <c r="A2545" t="inlineStr">
+        <is>
+          <t>6f985e8e-61c5-40d8-88b8-ca6dcc192287</t>
+        </is>
+      </c>
+      <c r="B2545" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2545" t="inlineStr">
+        <is>
+          <t>2026-07-01T02:48:22.576Z</t>
+        </is>
+      </c>
+      <c r="D2545" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2545" t="inlineStr"/>
+    </row>
+    <row r="2546">
+      <c r="A2546" t="inlineStr">
+        <is>
+          <t>acedbe16-fc50-4574-8299-d3dfe5265d67</t>
+        </is>
+      </c>
+      <c r="B2546" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2546" t="inlineStr">
+        <is>
+          <t>2026-07-01T04:19:43.972Z</t>
+        </is>
+      </c>
+      <c r="D2546" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2546" t="inlineStr"/>
+    </row>
+    <row r="2547">
+      <c r="A2547" t="inlineStr">
+        <is>
+          <t>539104d6-8fbd-4981-ad55-6e80abbf8553</t>
+        </is>
+      </c>
+      <c r="B2547" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2547" t="inlineStr">
+        <is>
+          <t>2026-07-01T04:23:46.852Z</t>
+        </is>
+      </c>
+      <c r="D2547" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2547" t="inlineStr"/>
+    </row>
+    <row r="2548">
+      <c r="A2548" t="inlineStr">
+        <is>
+          <t>bb69eea8-7398-4f7e-91d5-a9a7859f81ff</t>
+        </is>
+      </c>
+      <c r="B2548" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2548" t="inlineStr">
+        <is>
+          <t>2026-07-01T04:29:42.652Z</t>
+        </is>
+      </c>
+      <c r="D2548" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2548" t="inlineStr">
+        <is>
+          <t>suspect/victim vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2549">
+      <c r="A2549" t="inlineStr">
+        <is>
+          <t>fe98c977-2af4-4c3a-b0c2-151c09785204</t>
+        </is>
+      </c>
+      <c r="B2549" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2549" t="inlineStr">
+        <is>
+          <t>2026-07-01T05:00:00.679Z</t>
+        </is>
+      </c>
+      <c r="D2549" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2549" t="inlineStr">
+        <is>
+          <t>suspect/victim vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" t="inlineStr">
+        <is>
+          <t>43560bdf-4c7c-409d-8e3c-e44052033706</t>
+        </is>
+      </c>
+      <c r="B2550" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2550" t="inlineStr">
+        <is>
+          <t>2026-07-01T05:20:18.194Z</t>
+        </is>
+      </c>
+      <c r="D2550" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2550" t="inlineStr"/>
+    </row>
+    <row r="2551">
+      <c r="A2551" t="inlineStr">
+        <is>
+          <t>2e937d81-464d-46a4-88f3-f9584be1e76e</t>
+        </is>
+      </c>
+      <c r="B2551" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2551" t="inlineStr">
+        <is>
+          <t>2026-07-01T05:34:51.399Z</t>
+        </is>
+      </c>
+      <c r="D2551" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2551" t="inlineStr"/>
+    </row>
+    <row r="2552">
+      <c r="A2552" t="inlineStr">
+        <is>
+          <t>17ea75a2-d2cf-4335-86b4-ec7118686eef</t>
+        </is>
+      </c>
+      <c r="B2552" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2552" t="inlineStr">
+        <is>
+          <t>2026-07-01T06:04:19.380Z</t>
+        </is>
+      </c>
+      <c r="D2552" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2552" t="inlineStr"/>
+    </row>
+    <row r="2553">
+      <c r="A2553" t="inlineStr">
+        <is>
+          <t>83cbf786-9506-4724-b276-fba4c8ed39c8</t>
+        </is>
+      </c>
+      <c r="B2553" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2553" t="inlineStr">
+        <is>
+          <t>2026-07-01T07:05:52.390Z</t>
+        </is>
+      </c>
+      <c r="D2553" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2553" t="inlineStr"/>
+    </row>
+    <row r="2554">
+      <c r="A2554" t="inlineStr">
+        <is>
+          <t>0064cf49-9b0f-44f5-930c-4d71eeb7a37a</t>
+        </is>
+      </c>
+      <c r="B2554" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2554" t="inlineStr">
+        <is>
+          <t>2026-07-01T10:03:19.387Z</t>
+        </is>
+      </c>
+      <c r="D2554" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2554" t="inlineStr"/>
+    </row>
+    <row r="2555">
+      <c r="A2555" t="inlineStr">
+        <is>
+          <t>39f5455a-c63d-44f9-871b-53115697ba40</t>
+        </is>
+      </c>
+      <c r="B2555" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2555" t="inlineStr">
+        <is>
+          <t>2026-07-01T11:05:17.801Z</t>
+        </is>
+      </c>
+      <c r="D2555" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2555" t="inlineStr"/>
+    </row>
+    <row r="2556">
+      <c r="A2556" t="inlineStr">
+        <is>
+          <t>a255a5bb-a136-4e01-b727-d49a802dc8b0</t>
+        </is>
+      </c>
+      <c r="B2556" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2556" t="inlineStr">
+        <is>
+          <t>2026-07-01T12:43:22.778Z</t>
+        </is>
+      </c>
+      <c r="D2556" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2556" t="inlineStr"/>
+    </row>
+    <row r="2557">
+      <c r="A2557" t="inlineStr">
+        <is>
+          <t>268d654d-a0dd-4143-a5fa-af56885638b5</t>
+        </is>
+      </c>
+      <c r="B2557" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2557" t="inlineStr">
+        <is>
+          <t>2026-07-01T13:02:02.508Z</t>
+        </is>
+      </c>
+      <c r="D2557" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2557" t="inlineStr"/>
+    </row>
+    <row r="2558">
+      <c r="A2558" t="inlineStr">
+        <is>
+          <t>67518f32-65c3-4f3f-8111-7d3f126f61b0</t>
+        </is>
+      </c>
+      <c r="B2558" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2558" t="inlineStr">
+        <is>
+          <t>2026-07-01T15:15:42.009Z</t>
+        </is>
+      </c>
+      <c r="D2558" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2558" t="inlineStr"/>
+    </row>
+    <row r="2559">
+      <c r="A2559" t="inlineStr">
+        <is>
+          <t>df5e11ba-70e1-4be0-817b-c2d0b7eb2438</t>
+        </is>
+      </c>
+      <c r="B2559" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2559" t="inlineStr">
+        <is>
+          <t>2026-07-01T15:25:58.582Z</t>
+        </is>
+      </c>
+      <c r="D2559" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2559" t="inlineStr">
+        <is>
+          <t>Poss sus</t>
+        </is>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" t="inlineStr">
+        <is>
+          <t>d5d4435f-ec76-4d9b-8ddb-32f0283b8b02</t>
+        </is>
+      </c>
+      <c r="B2560" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2560" t="inlineStr">
+        <is>
+          <t>2026-07-01T17:26:06.320Z</t>
+        </is>
+      </c>
+      <c r="D2560" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2560" t="inlineStr"/>
+    </row>
+    <row r="2561">
+      <c r="A2561" t="inlineStr">
+        <is>
+          <t>83f15c64-dbc8-4e20-87ec-7433208c5fc8</t>
+        </is>
+      </c>
+      <c r="B2561" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2561" t="inlineStr">
+        <is>
+          <t>2026-07-01T17:42:37.839Z</t>
+        </is>
+      </c>
+      <c r="D2561" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2561" t="inlineStr">
+        <is>
+          <t>follow up poss connection to wire thefts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" t="inlineStr">
+        <is>
+          <t>cedf4137-6147-4e34-85f8-f13f7f173d20</t>
+        </is>
+      </c>
+      <c r="B2562" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2562" t="inlineStr">
+        <is>
+          <t>2026-07-01T20:00:03.990Z</t>
+        </is>
+      </c>
+      <c r="D2562" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2562" t="inlineStr"/>
+    </row>
+    <row r="2563">
+      <c r="A2563" t="inlineStr">
+        <is>
+          <t>6995f33d-1de7-4c7f-9cbf-ebfb5fae2bb4</t>
+        </is>
+      </c>
+      <c r="B2563" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2563" t="inlineStr">
+        <is>
+          <t>2026-07-01T20:39:11.306Z</t>
+        </is>
+      </c>
+      <c r="D2563" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2563" t="inlineStr"/>
+    </row>
+    <row r="2564">
+      <c r="A2564" t="inlineStr">
+        <is>
+          <t>1b3e7a38-32f3-48f9-aa3e-5abe4fbff03e</t>
+        </is>
+      </c>
+      <c r="B2564" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2564" t="inlineStr">
+        <is>
+          <t>2026-07-01T21:14:43.882Z</t>
+        </is>
+      </c>
+      <c r="D2564" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2564" t="inlineStr"/>
+    </row>
+    <row r="2565">
+      <c r="A2565" t="inlineStr">
+        <is>
+          <t>4f6e5345-8c87-422e-9418-63da4c89d725</t>
+        </is>
+      </c>
+      <c r="B2565" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2565" t="inlineStr">
+        <is>
+          <t>2026-07-01T21:49:47.867Z</t>
+        </is>
+      </c>
+      <c r="D2565" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2565" t="inlineStr"/>
+    </row>
+    <row r="2566">
+      <c r="A2566" t="inlineStr">
+        <is>
+          <t>32475401-3fb6-4326-a049-59b234dae0ea</t>
+        </is>
+      </c>
+      <c r="B2566" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2566" t="inlineStr">
+        <is>
+          <t>2026-07-01T22:30:32.477Z</t>
+        </is>
+      </c>
+      <c r="D2566" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2566" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" t="inlineStr">
+        <is>
+          <t>5444acb8-5a1a-4203-b443-bceb3020a149</t>
+        </is>
+      </c>
+      <c r="B2567" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2567" t="inlineStr">
+        <is>
+          <t>2026-07-01T22:34:03.030Z</t>
+        </is>
+      </c>
+      <c r="D2567" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2567" t="inlineStr"/>
+    </row>
+    <row r="2568">
+      <c r="A2568" t="inlineStr">
+        <is>
+          <t>b837e4db-8b39-40c1-b11e-1de21276e8dc</t>
+        </is>
+      </c>
+      <c r="B2568" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2568" t="inlineStr">
+        <is>
+          <t>2026-07-01T23:08:44.489Z</t>
+        </is>
+      </c>
+      <c r="D2568" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2568" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2568"/>
+  <dimension ref="A1:E2596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58440,6 +58440,618 @@
         </is>
       </c>
     </row>
+    <row r="2569">
+      <c r="A2569" t="inlineStr">
+        <is>
+          <t>05f1b306-6aba-416e-9766-de395e6831ec</t>
+        </is>
+      </c>
+      <c r="B2569" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2569" t="inlineStr">
+        <is>
+          <t>2026-07-02T00:26:25.883Z</t>
+        </is>
+      </c>
+      <c r="D2569" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2569" t="inlineStr"/>
+    </row>
+    <row r="2570">
+      <c r="A2570" t="inlineStr">
+        <is>
+          <t>4688f633-f3fe-42c9-aa9b-842f4be223da</t>
+        </is>
+      </c>
+      <c r="B2570" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2570" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:02:26.522Z</t>
+        </is>
+      </c>
+      <c r="D2570" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2570" t="inlineStr"/>
+    </row>
+    <row r="2571">
+      <c r="A2571" t="inlineStr">
+        <is>
+          <t>95391516-f47a-4e70-b4ea-560531e62211</t>
+        </is>
+      </c>
+      <c r="B2571" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2571" t="inlineStr">
+        <is>
+          <t>2026-07-02T03:07:12.994Z</t>
+        </is>
+      </c>
+      <c r="D2571" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2571" t="inlineStr"/>
+    </row>
+    <row r="2572">
+      <c r="A2572" t="inlineStr">
+        <is>
+          <t>51452c32-50c5-43ab-95ce-6470636b0240</t>
+        </is>
+      </c>
+      <c r="B2572" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2572" t="inlineStr">
+        <is>
+          <t>2026-07-02T04:31:13.862Z</t>
+        </is>
+      </c>
+      <c r="D2572" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2572" t="inlineStr"/>
+    </row>
+    <row r="2573">
+      <c r="A2573" t="inlineStr">
+        <is>
+          <t>0e8d19dc-a4e7-46ec-bbbf-2d25f4a034ba</t>
+        </is>
+      </c>
+      <c r="B2573" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2573" t="inlineStr">
+        <is>
+          <t>2026-07-02T05:15:14.280Z</t>
+        </is>
+      </c>
+      <c r="D2573" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2573" t="inlineStr"/>
+    </row>
+    <row r="2574">
+      <c r="A2574" t="inlineStr">
+        <is>
+          <t>c4395574-9443-4ead-9d26-e1a593d102d7</t>
+        </is>
+      </c>
+      <c r="B2574" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2574" t="inlineStr">
+        <is>
+          <t>2026-07-02T06:07:47.149Z</t>
+        </is>
+      </c>
+      <c r="D2574" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2574" t="inlineStr"/>
+    </row>
+    <row r="2575">
+      <c r="A2575" t="inlineStr">
+        <is>
+          <t>cfd1c5a8-ee0f-408c-9101-a837766a6c6c</t>
+        </is>
+      </c>
+      <c r="B2575" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2575" t="inlineStr">
+        <is>
+          <t>2026-07-02T07:17:24.171Z</t>
+        </is>
+      </c>
+      <c r="D2575" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2575" t="inlineStr"/>
+    </row>
+    <row r="2576">
+      <c r="A2576" t="inlineStr">
+        <is>
+          <t>d335e3ec-2fa6-45d0-8a88-61b9f9652dfb</t>
+        </is>
+      </c>
+      <c r="B2576" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2576" t="inlineStr">
+        <is>
+          <t>2026-07-02T07:24:26.652Z</t>
+        </is>
+      </c>
+      <c r="D2576" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2576" t="inlineStr">
+        <is>
+          <t>273.5 sus</t>
+        </is>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" t="inlineStr">
+        <is>
+          <t>18405886-396f-473d-b063-8c3bc9dc6b1f</t>
+        </is>
+      </c>
+      <c r="B2577" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2577" t="inlineStr">
+        <is>
+          <t>2026-07-02T07:47:24.452Z</t>
+        </is>
+      </c>
+      <c r="D2577" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2577" t="inlineStr"/>
+    </row>
+    <row r="2578">
+      <c r="A2578" t="inlineStr">
+        <is>
+          <t>a2803ce4-75b4-4dea-9184-d07a6f8e5984</t>
+        </is>
+      </c>
+      <c r="B2578" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2578" t="inlineStr">
+        <is>
+          <t>2026-07-02T08:04:55.911Z</t>
+        </is>
+      </c>
+      <c r="D2578" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2578" t="inlineStr"/>
+    </row>
+    <row r="2579">
+      <c r="A2579" t="inlineStr">
+        <is>
+          <t>326f55e6-7736-4410-a852-0cea3071cf4a</t>
+        </is>
+      </c>
+      <c r="B2579" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2579" t="inlineStr">
+        <is>
+          <t>2026-07-02T09:37:42.951Z</t>
+        </is>
+      </c>
+      <c r="D2579" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2579" t="inlineStr"/>
+    </row>
+    <row r="2580">
+      <c r="A2580" t="inlineStr">
+        <is>
+          <t>e80a2d7b-6b29-436f-9c2b-b2aefd70fdce</t>
+        </is>
+      </c>
+      <c r="B2580" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2580" t="inlineStr">
+        <is>
+          <t>2026-07-02T09:49:24.096Z</t>
+        </is>
+      </c>
+      <c r="D2580" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2580" t="inlineStr"/>
+    </row>
+    <row r="2581">
+      <c r="A2581" t="inlineStr">
+        <is>
+          <t>725941e6-9e59-485b-aa5e-c16360fc476e</t>
+        </is>
+      </c>
+      <c r="B2581" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2581" t="inlineStr">
+        <is>
+          <t>2026-07-02T10:13:36.536Z</t>
+        </is>
+      </c>
+      <c r="D2581" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2581" t="inlineStr"/>
+    </row>
+    <row r="2582">
+      <c r="A2582" t="inlineStr">
+        <is>
+          <t>90cb2a06-13c9-41a7-9ba2-073b640dabf3</t>
+        </is>
+      </c>
+      <c r="B2582" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2582" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:08:31.827Z</t>
+        </is>
+      </c>
+      <c r="D2582" t="n">
+        <v>529</v>
+      </c>
+      <c r="E2582" t="inlineStr">
+        <is>
+          <t>Carjacking suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2583">
+      <c r="A2583" t="inlineStr">
+        <is>
+          <t>85633e99-16f4-4a3e-9510-d445c20f7e78</t>
+        </is>
+      </c>
+      <c r="B2583" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2583" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:49:37.146Z</t>
+        </is>
+      </c>
+      <c r="D2583" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2583" t="inlineStr"/>
+    </row>
+    <row r="2584">
+      <c r="A2584" t="inlineStr">
+        <is>
+          <t>cd8c4fde-871f-4baa-afe6-ab1b082b56cc</t>
+        </is>
+      </c>
+      <c r="B2584" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2584" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:54:58.466Z</t>
+        </is>
+      </c>
+      <c r="D2584" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2584" t="inlineStr"/>
+    </row>
+    <row r="2585">
+      <c r="A2585" t="inlineStr">
+        <is>
+          <t>2d0c0da9-e41f-4b98-9376-793388e4cdb7</t>
+        </is>
+      </c>
+      <c r="B2585" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2585" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:43:54.984Z</t>
+        </is>
+      </c>
+      <c r="D2585" t="n">
+        <v>529</v>
+      </c>
+      <c r="E2585" t="inlineStr">
+        <is>
+          <t>Carjacking suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2586">
+      <c r="A2586" t="inlineStr">
+        <is>
+          <t>3398d9ce-177c-43dc-b060-51fdfb2852a0</t>
+        </is>
+      </c>
+      <c r="B2586" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2586" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:46:53.138Z</t>
+        </is>
+      </c>
+      <c r="D2586" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2586" t="inlineStr"/>
+    </row>
+    <row r="2587">
+      <c r="A2587" t="inlineStr">
+        <is>
+          <t>b06f9575-f674-4c3e-9f1e-d788f746d23c</t>
+        </is>
+      </c>
+      <c r="B2587" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2587" t="inlineStr">
+        <is>
+          <t>2026-07-02T19:28:17.969Z</t>
+        </is>
+      </c>
+      <c r="D2587" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2587" t="inlineStr"/>
+    </row>
+    <row r="2588">
+      <c r="A2588" t="inlineStr">
+        <is>
+          <t>8a25cb21-dc4a-4ce7-b200-e9157b98b8a2</t>
+        </is>
+      </c>
+      <c r="B2588" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2588" t="inlineStr">
+        <is>
+          <t>2026-07-02T19:44:17.585Z</t>
+        </is>
+      </c>
+      <c r="D2588" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2588" t="inlineStr"/>
+    </row>
+    <row r="2589">
+      <c r="A2589" t="inlineStr">
+        <is>
+          <t>e3592c02-3aed-4a45-b056-542588458460</t>
+        </is>
+      </c>
+      <c r="B2589" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2589" t="inlineStr">
+        <is>
+          <t>2026-07-02T20:00:09.321Z</t>
+        </is>
+      </c>
+      <c r="D2589" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2589" t="inlineStr"/>
+    </row>
+    <row r="2590">
+      <c r="A2590" t="inlineStr">
+        <is>
+          <t>f9f60d61-7cbb-4225-87c2-845d7b1858a3</t>
+        </is>
+      </c>
+      <c r="B2590" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2590" t="inlineStr">
+        <is>
+          <t>2026-07-02T21:05:53.183Z</t>
+        </is>
+      </c>
+      <c r="D2590" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2590" t="inlineStr"/>
+    </row>
+    <row r="2591">
+      <c r="A2591" t="inlineStr">
+        <is>
+          <t>f2ff2ece-bdc7-4e17-a83d-55e41492065e</t>
+        </is>
+      </c>
+      <c r="B2591" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2591" t="inlineStr">
+        <is>
+          <t>2026-07-02T21:55:55.502Z</t>
+        </is>
+      </c>
+      <c r="D2591" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2591" t="inlineStr">
+        <is>
+          <t>poss susp wire theft</t>
+        </is>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" t="inlineStr">
+        <is>
+          <t>84401f82-8b23-4752-a248-829ee2ce573c</t>
+        </is>
+      </c>
+      <c r="B2592" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2592" t="inlineStr">
+        <is>
+          <t>2026-07-02T21:56:14.467Z</t>
+        </is>
+      </c>
+      <c r="D2592" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2592" t="inlineStr"/>
+    </row>
+    <row r="2593">
+      <c r="A2593" t="inlineStr">
+        <is>
+          <t>b1f1ec2c-68f9-4d26-8673-48631ea01d9e</t>
+        </is>
+      </c>
+      <c r="B2593" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2593" t="inlineStr">
+        <is>
+          <t>2026-07-02T22:00:13.725Z</t>
+        </is>
+      </c>
+      <c r="D2593" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2593" t="inlineStr"/>
+    </row>
+    <row r="2594">
+      <c r="A2594" t="inlineStr">
+        <is>
+          <t>7eee3830-0615-43c2-a4c2-d8fa7a097f15</t>
+        </is>
+      </c>
+      <c r="B2594" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2594" t="inlineStr">
+        <is>
+          <t>2026-07-02T22:06:47.572Z</t>
+        </is>
+      </c>
+      <c r="D2594" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2594" t="inlineStr">
+        <is>
+          <t>Car jacking</t>
+        </is>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" t="inlineStr">
+        <is>
+          <t>64fd3025-3499-44fa-bbca-4f9980ec2b70</t>
+        </is>
+      </c>
+      <c r="B2595" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2595" t="inlineStr">
+        <is>
+          <t>2026-07-02T22:13:02.738Z</t>
+        </is>
+      </c>
+      <c r="D2595" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2595" t="inlineStr">
+        <is>
+          <t>poss susp wire theft</t>
+        </is>
+      </c>
+    </row>
+    <row r="2596">
+      <c r="A2596" t="inlineStr">
+        <is>
+          <t>aef8ff8e-0475-4971-af13-2fa5a8e89fb8</t>
+        </is>
+      </c>
+      <c r="B2596" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2596" t="inlineStr">
+        <is>
+          <t>2026-07-02T22:43:20.077Z</t>
+        </is>
+      </c>
+      <c r="D2596" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2596" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2596"/>
+  <dimension ref="A1:E2605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59052,6 +59052,203 @@
       </c>
       <c r="E2596" t="inlineStr"/>
     </row>
+    <row r="2597">
+      <c r="A2597" t="inlineStr">
+        <is>
+          <t>b1d1a7f3-5ed8-4694-88a9-b97110223dab</t>
+        </is>
+      </c>
+      <c r="B2597" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2597" t="inlineStr">
+        <is>
+          <t>2026-07-03T00:16:14.861Z</t>
+        </is>
+      </c>
+      <c r="D2597" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2597" t="inlineStr">
+        <is>
+          <t>identify vehicle poss involved in theft</t>
+        </is>
+      </c>
+    </row>
+    <row r="2598">
+      <c r="A2598" t="inlineStr">
+        <is>
+          <t>de294969-cb32-44d0-a9cc-28f46a251474</t>
+        </is>
+      </c>
+      <c r="B2598" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2598" t="inlineStr">
+        <is>
+          <t>2026-07-03T01:12:33.333Z</t>
+        </is>
+      </c>
+      <c r="D2598" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2598" t="inlineStr"/>
+    </row>
+    <row r="2599">
+      <c r="A2599" t="inlineStr">
+        <is>
+          <t>bd690679-85c7-40e4-8be4-23e525cda73b</t>
+        </is>
+      </c>
+      <c r="B2599" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2599" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:32:17.088Z</t>
+        </is>
+      </c>
+      <c r="D2599" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2599" t="inlineStr"/>
+    </row>
+    <row r="2600">
+      <c r="A2600" t="inlineStr">
+        <is>
+          <t>56402231-a443-4575-bf61-3737f10c5110</t>
+        </is>
+      </c>
+      <c r="B2600" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2600" t="inlineStr">
+        <is>
+          <t>2026-07-03T05:46:34.544Z</t>
+        </is>
+      </c>
+      <c r="D2600" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2600" t="inlineStr"/>
+    </row>
+    <row r="2601">
+      <c r="A2601" t="inlineStr">
+        <is>
+          <t>13449127-c427-4c34-97eb-443352e4fd4c</t>
+        </is>
+      </c>
+      <c r="B2601" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2601" t="inlineStr">
+        <is>
+          <t>2026-07-03T05:48:54.504Z</t>
+        </is>
+      </c>
+      <c r="D2601" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2601" t="inlineStr">
+        <is>
+          <t>law enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2602">
+      <c r="A2602" t="inlineStr">
+        <is>
+          <t>6b8a695d-c193-4b48-bae1-4e292b955c1c</t>
+        </is>
+      </c>
+      <c r="B2602" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2602" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:15:06.266Z</t>
+        </is>
+      </c>
+      <c r="D2602" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2602" t="inlineStr"/>
+    </row>
+    <row r="2603">
+      <c r="A2603" t="inlineStr">
+        <is>
+          <t>b49b352f-c119-47f1-ad71-e70ac406fc77</t>
+        </is>
+      </c>
+      <c r="B2603" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2603" t="inlineStr">
+        <is>
+          <t>2026-07-03T16:16:23.098Z</t>
+        </is>
+      </c>
+      <c r="D2603" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2603" t="inlineStr"/>
+    </row>
+    <row r="2604">
+      <c r="A2604" t="inlineStr">
+        <is>
+          <t>6da219d9-e018-408d-afb5-c21d602347ec</t>
+        </is>
+      </c>
+      <c r="B2604" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2604" t="inlineStr">
+        <is>
+          <t>2026-07-03T22:01:26.663Z</t>
+        </is>
+      </c>
+      <c r="D2604" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2604" t="inlineStr"/>
+    </row>
+    <row r="2605">
+      <c r="A2605" t="inlineStr">
+        <is>
+          <t>b65d8617-1953-4d1d-9726-bf1bfd94ce3b</t>
+        </is>
+      </c>
+      <c r="B2605" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2605" t="inlineStr">
+        <is>
+          <t>2026-07-03T23:07:46.525Z</t>
+        </is>
+      </c>
+      <c r="D2605" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2605" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2605"/>
+  <dimension ref="A1:E2617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59249,6 +59249,274 @@
       </c>
       <c r="E2605" t="inlineStr"/>
     </row>
+    <row r="2606">
+      <c r="A2606" t="inlineStr">
+        <is>
+          <t>4feb8f1c-270a-4c45-a4a2-56ab6e116fc8</t>
+        </is>
+      </c>
+      <c r="B2606" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2606" t="inlineStr">
+        <is>
+          <t>2026-07-04T01:13:20.512Z</t>
+        </is>
+      </c>
+      <c r="D2606" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2606" t="inlineStr"/>
+    </row>
+    <row r="2607">
+      <c r="A2607" t="inlineStr">
+        <is>
+          <t>df9acd1e-a51c-49bc-a7cc-9f18cc4a9348</t>
+        </is>
+      </c>
+      <c r="B2607" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2607" t="inlineStr">
+        <is>
+          <t>2026-07-04T02:08:52.935Z</t>
+        </is>
+      </c>
+      <c r="D2607" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2607" t="inlineStr"/>
+    </row>
+    <row r="2608">
+      <c r="A2608" t="inlineStr">
+        <is>
+          <t>ed5d15c8-ab3a-4d60-9255-38b820119298</t>
+        </is>
+      </c>
+      <c r="B2608" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2608" t="inlineStr">
+        <is>
+          <t>2026-07-04T03:34:11.046Z</t>
+        </is>
+      </c>
+      <c r="D2608" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2608" t="inlineStr"/>
+    </row>
+    <row r="2609">
+      <c r="A2609" t="inlineStr">
+        <is>
+          <t>568158d3-d071-4d36-97fb-f996d0993d38</t>
+        </is>
+      </c>
+      <c r="B2609" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2609" t="inlineStr">
+        <is>
+          <t>2026-07-04T04:46:58.581Z</t>
+        </is>
+      </c>
+      <c r="D2609" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2609" t="inlineStr"/>
+    </row>
+    <row r="2610">
+      <c r="A2610" t="inlineStr">
+        <is>
+          <t>9662fbd9-7070-4491-82b1-536b52bdbbdd</t>
+        </is>
+      </c>
+      <c r="B2610" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2610" t="inlineStr">
+        <is>
+          <t>2026-07-04T04:49:39.089Z</t>
+        </is>
+      </c>
+      <c r="D2610" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2610" t="inlineStr"/>
+    </row>
+    <row r="2611">
+      <c r="A2611" t="inlineStr">
+        <is>
+          <t>9bec01d6-9c20-4fed-a7cc-c15cc6677488</t>
+        </is>
+      </c>
+      <c r="B2611" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2611" t="inlineStr">
+        <is>
+          <t>2026-07-04T04:59:32.113Z</t>
+        </is>
+      </c>
+      <c r="D2611" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2611" t="inlineStr">
+        <is>
+          <t>Sus Loc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2612">
+      <c r="A2612" t="inlineStr">
+        <is>
+          <t>48463093-eafb-44fb-97ce-5a04e5766bfb</t>
+        </is>
+      </c>
+      <c r="B2612" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2612" t="inlineStr">
+        <is>
+          <t>2026-07-04T05:00:33.661Z</t>
+        </is>
+      </c>
+      <c r="D2612" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2612" t="inlineStr">
+        <is>
+          <t>Sus Loc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2613">
+      <c r="A2613" t="inlineStr">
+        <is>
+          <t>6e8e05d6-ada0-4abe-9bf5-8b29ee925008</t>
+        </is>
+      </c>
+      <c r="B2613" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2613" t="inlineStr">
+        <is>
+          <t>2026-07-04T05:06:26.622Z</t>
+        </is>
+      </c>
+      <c r="D2613" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2613" t="inlineStr"/>
+    </row>
+    <row r="2614">
+      <c r="A2614" t="inlineStr">
+        <is>
+          <t>d077c9b5-7b05-4fb1-bb38-23fb00c1884c</t>
+        </is>
+      </c>
+      <c r="B2614" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2614" t="inlineStr">
+        <is>
+          <t>2026-07-04T05:46:36.553Z</t>
+        </is>
+      </c>
+      <c r="D2614" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2614" t="inlineStr"/>
+    </row>
+    <row r="2615">
+      <c r="A2615" t="inlineStr">
+        <is>
+          <t>939d837f-e322-4d17-86c0-b2b7419c688d</t>
+        </is>
+      </c>
+      <c r="B2615" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2615" t="inlineStr">
+        <is>
+          <t>2026-07-04T05:58:26.534Z</t>
+        </is>
+      </c>
+      <c r="D2615" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2615" t="inlineStr">
+        <is>
+          <t>Sus loc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2616">
+      <c r="A2616" t="inlineStr">
+        <is>
+          <t>08cdc9ef-7752-46ac-b5f8-121ed624fd63</t>
+        </is>
+      </c>
+      <c r="B2616" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2616" t="inlineStr">
+        <is>
+          <t>2026-07-04T06:01:44.273Z</t>
+        </is>
+      </c>
+      <c r="D2616" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2616" t="inlineStr">
+        <is>
+          <t>Sus Loc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2617">
+      <c r="A2617" t="inlineStr">
+        <is>
+          <t>26274522-b4c7-4468-9b27-020a3b438356</t>
+        </is>
+      </c>
+      <c r="B2617" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2617" t="inlineStr">
+        <is>
+          <t>2026-07-04T06:38:50.347Z</t>
+        </is>
+      </c>
+      <c r="D2617" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2617" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2617"/>
+  <dimension ref="A1:E2621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59517,6 +59517,98 @@
       </c>
       <c r="E2617" t="inlineStr"/>
     </row>
+    <row r="2618">
+      <c r="A2618" t="inlineStr">
+        <is>
+          <t>cbafb89c-6c81-4d44-aecc-e8d56e22275c</t>
+        </is>
+      </c>
+      <c r="B2618" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2618" t="inlineStr">
+        <is>
+          <t>2026-07-05T09:26:16.446Z</t>
+        </is>
+      </c>
+      <c r="D2618" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2618" t="inlineStr"/>
+    </row>
+    <row r="2619">
+      <c r="A2619" t="inlineStr">
+        <is>
+          <t>43a9b4f5-7993-4596-b4a3-6ec7079658cf</t>
+        </is>
+      </c>
+      <c r="B2619" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2619" t="inlineStr">
+        <is>
+          <t>2026-07-05T19:21:31.235Z</t>
+        </is>
+      </c>
+      <c r="D2619" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2619" t="inlineStr"/>
+    </row>
+    <row r="2620">
+      <c r="A2620" t="inlineStr">
+        <is>
+          <t>2d4c5d67-79d5-4bb7-b4c7-73db6e97c0ef</t>
+        </is>
+      </c>
+      <c r="B2620" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2620" t="inlineStr">
+        <is>
+          <t>2026-07-05T22:41:50.228Z</t>
+        </is>
+      </c>
+      <c r="D2620" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2620" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2621">
+      <c r="A2621" t="inlineStr">
+        <is>
+          <t>aaaf7159-8055-4a9a-8a53-1fb5c34ba0e0</t>
+        </is>
+      </c>
+      <c r="B2621" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2621" t="inlineStr">
+        <is>
+          <t>2026-07-05T23:02:25.966Z</t>
+        </is>
+      </c>
+      <c r="D2621" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2621" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2621"/>
+  <dimension ref="A1:E2633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59609,6 +59609,274 @@
         </is>
       </c>
     </row>
+    <row r="2622">
+      <c r="A2622" t="inlineStr">
+        <is>
+          <t>c5f1134e-ae2b-4a12-8cdf-82263f47f4eb</t>
+        </is>
+      </c>
+      <c r="B2622" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2622" t="inlineStr">
+        <is>
+          <t>2026-07-06T05:33:34.136Z</t>
+        </is>
+      </c>
+      <c r="D2622" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2622" t="inlineStr"/>
+    </row>
+    <row r="2623">
+      <c r="A2623" t="inlineStr">
+        <is>
+          <t>7a7eb909-e38d-412c-9f91-a833db19ba11</t>
+        </is>
+      </c>
+      <c r="B2623" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2623" t="inlineStr">
+        <is>
+          <t>2026-07-06T06:11:45.535Z</t>
+        </is>
+      </c>
+      <c r="D2623" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2623" t="inlineStr"/>
+    </row>
+    <row r="2624">
+      <c r="A2624" t="inlineStr">
+        <is>
+          <t>a9b77636-6169-4cfa-b68d-b2f4ca9df082</t>
+        </is>
+      </c>
+      <c r="B2624" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2624" t="inlineStr">
+        <is>
+          <t>2026-07-06T07:26:20.334Z</t>
+        </is>
+      </c>
+      <c r="D2624" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2624" t="inlineStr"/>
+    </row>
+    <row r="2625">
+      <c r="A2625" t="inlineStr">
+        <is>
+          <t>1283816a-b89e-44d3-aa36-818c1de44431</t>
+        </is>
+      </c>
+      <c r="B2625" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2625" t="inlineStr">
+        <is>
+          <t>2026-07-06T08:54:18.570Z</t>
+        </is>
+      </c>
+      <c r="D2625" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2625" t="inlineStr"/>
+    </row>
+    <row r="2626">
+      <c r="A2626" t="inlineStr">
+        <is>
+          <t>a44797e4-aa00-443b-b83d-bd361674c475</t>
+        </is>
+      </c>
+      <c r="B2626" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2626" t="inlineStr">
+        <is>
+          <t>2026-07-06T09:05:42.628Z</t>
+        </is>
+      </c>
+      <c r="D2626" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2626" t="inlineStr"/>
+    </row>
+    <row r="2627">
+      <c r="A2627" t="inlineStr">
+        <is>
+          <t>8980877e-0ec8-49c5-994f-9fce13bbdfc1</t>
+        </is>
+      </c>
+      <c r="B2627" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2627" t="inlineStr">
+        <is>
+          <t>2026-07-06T10:11:06.348Z</t>
+        </is>
+      </c>
+      <c r="D2627" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2627" t="inlineStr"/>
+    </row>
+    <row r="2628">
+      <c r="A2628" t="inlineStr">
+        <is>
+          <t>4e817be8-c436-45cd-be02-8fe636b796c7</t>
+        </is>
+      </c>
+      <c r="B2628" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2628" t="inlineStr">
+        <is>
+          <t>2026-07-06T10:13:35.096Z</t>
+        </is>
+      </c>
+      <c r="D2628" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2628" t="inlineStr"/>
+    </row>
+    <row r="2629">
+      <c r="A2629" t="inlineStr">
+        <is>
+          <t>a2594e94-d37c-4bd3-aefd-a2cc2fd14706</t>
+        </is>
+      </c>
+      <c r="B2629" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2629" t="inlineStr">
+        <is>
+          <t>2026-07-06T17:25:49.043Z</t>
+        </is>
+      </c>
+      <c r="D2629" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2629" t="inlineStr">
+        <is>
+          <t>suspec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2630">
+      <c r="A2630" t="inlineStr">
+        <is>
+          <t>5e9bce77-79c1-4949-930d-d1aa0e03fc4d</t>
+        </is>
+      </c>
+      <c r="B2630" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2630" t="inlineStr">
+        <is>
+          <t>2026-07-06T18:24:12.485Z</t>
+        </is>
+      </c>
+      <c r="D2630" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2630" t="inlineStr">
+        <is>
+          <t>suspec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2631">
+      <c r="A2631" t="inlineStr">
+        <is>
+          <t>d86b56eb-b15a-4d8a-a910-15220e9f9c47</t>
+        </is>
+      </c>
+      <c r="B2631" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2631" t="inlineStr">
+        <is>
+          <t>2026-07-06T20:53:59.032Z</t>
+        </is>
+      </c>
+      <c r="D2631" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2631" t="inlineStr">
+        <is>
+          <t>suspec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2632">
+      <c r="A2632" t="inlineStr">
+        <is>
+          <t>fb186700-dcec-4683-be04-85695a51fbb6</t>
+        </is>
+      </c>
+      <c r="B2632" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2632" t="inlineStr">
+        <is>
+          <t>2026-07-06T21:09:03.978Z</t>
+        </is>
+      </c>
+      <c r="D2632" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2632" t="inlineStr"/>
+    </row>
+    <row r="2633">
+      <c r="A2633" t="inlineStr">
+        <is>
+          <t>d701a6df-80aa-442e-b35b-7e7be6f5830b</t>
+        </is>
+      </c>
+      <c r="B2633" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2633" t="inlineStr">
+        <is>
+          <t>2026-07-06T21:27:42.060Z</t>
+        </is>
+      </c>
+      <c r="D2633" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2633" t="inlineStr">
+        <is>
+          <t>suspec</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2633"/>
+  <dimension ref="A1:E2649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59877,6 +59877,366 @@
         </is>
       </c>
     </row>
+    <row r="2634">
+      <c r="A2634" t="inlineStr">
+        <is>
+          <t>fd717dcf-f20b-4b2a-a06a-02dda6026f1d</t>
+        </is>
+      </c>
+      <c r="B2634" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2634" t="inlineStr">
+        <is>
+          <t>2026-07-07T00:12:54.076Z</t>
+        </is>
+      </c>
+      <c r="D2634" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2634" t="inlineStr">
+        <is>
+          <t>suspec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2635">
+      <c r="A2635" t="inlineStr">
+        <is>
+          <t>0d0feb43-0452-4827-8f98-cd88a655cace</t>
+        </is>
+      </c>
+      <c r="B2635" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2635" t="inlineStr">
+        <is>
+          <t>2026-07-07T03:03:28.106Z</t>
+        </is>
+      </c>
+      <c r="D2635" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2635" t="inlineStr"/>
+    </row>
+    <row r="2636">
+      <c r="A2636" t="inlineStr">
+        <is>
+          <t>c6f36365-560d-4379-a3d4-9a55c80ada51</t>
+        </is>
+      </c>
+      <c r="B2636" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2636" t="inlineStr">
+        <is>
+          <t>2026-07-07T04:38:23.864Z</t>
+        </is>
+      </c>
+      <c r="D2636" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2636" t="inlineStr"/>
+    </row>
+    <row r="2637">
+      <c r="A2637" t="inlineStr">
+        <is>
+          <t>0decdaa1-31a2-40e9-bd88-c32bcb655513</t>
+        </is>
+      </c>
+      <c r="B2637" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2637" t="inlineStr">
+        <is>
+          <t>2026-07-07T07:54:27.162Z</t>
+        </is>
+      </c>
+      <c r="D2637" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2637" t="inlineStr"/>
+    </row>
+    <row r="2638">
+      <c r="A2638" t="inlineStr">
+        <is>
+          <t>14c8f31c-57bc-44d2-90bc-3d72a7b31d3b</t>
+        </is>
+      </c>
+      <c r="B2638" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2638" t="inlineStr">
+        <is>
+          <t>2026-07-07T08:27:06.044Z</t>
+        </is>
+      </c>
+      <c r="D2638" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2638" t="inlineStr"/>
+    </row>
+    <row r="2639">
+      <c r="A2639" t="inlineStr">
+        <is>
+          <t>e065c783-21e5-4f91-8081-41021427bd36</t>
+        </is>
+      </c>
+      <c r="B2639" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2639" t="inlineStr">
+        <is>
+          <t>2026-07-07T09:33:46.828Z</t>
+        </is>
+      </c>
+      <c r="D2639" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2639" t="inlineStr"/>
+    </row>
+    <row r="2640">
+      <c r="A2640" t="inlineStr">
+        <is>
+          <t>f83df01b-f8af-457f-b9a1-fd4df0b65b23</t>
+        </is>
+      </c>
+      <c r="B2640" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2640" t="inlineStr">
+        <is>
+          <t>2026-07-07T10:26:14.319Z</t>
+        </is>
+      </c>
+      <c r="D2640" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2640" t="inlineStr"/>
+    </row>
+    <row r="2641">
+      <c r="A2641" t="inlineStr">
+        <is>
+          <t>5f3ef9d1-ca72-46e4-bc83-0dc22dd46999</t>
+        </is>
+      </c>
+      <c r="B2641" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2641" t="inlineStr">
+        <is>
+          <t>2026-07-07T10:46:28.587Z</t>
+        </is>
+      </c>
+      <c r="D2641" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2641" t="inlineStr"/>
+    </row>
+    <row r="2642">
+      <c r="A2642" t="inlineStr">
+        <is>
+          <t>76bfb37b-cb01-4805-8128-ccd4a587843a</t>
+        </is>
+      </c>
+      <c r="B2642" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2642" t="inlineStr">
+        <is>
+          <t>2026-07-07T12:38:34.056Z</t>
+        </is>
+      </c>
+      <c r="D2642" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2642" t="inlineStr"/>
+    </row>
+    <row r="2643">
+      <c r="A2643" t="inlineStr">
+        <is>
+          <t>689e4a55-f12b-4502-97b9-8fe558610e70</t>
+        </is>
+      </c>
+      <c r="B2643" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2643" t="inlineStr">
+        <is>
+          <t>2026-07-07T15:51:52.191Z</t>
+        </is>
+      </c>
+      <c r="D2643" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2643" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2644">
+      <c r="A2644" t="inlineStr">
+        <is>
+          <t>89b2c408-0864-4e3c-9587-092888ee518e</t>
+        </is>
+      </c>
+      <c r="B2644" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2644" t="inlineStr">
+        <is>
+          <t>2026-07-07T16:12:48.241Z</t>
+        </is>
+      </c>
+      <c r="D2644" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2644" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2645">
+      <c r="A2645" t="inlineStr">
+        <is>
+          <t>3a671feb-1e44-4b53-805d-9526b97e6344</t>
+        </is>
+      </c>
+      <c r="B2645" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2645" t="inlineStr">
+        <is>
+          <t>2026-07-07T17:10:09.635Z</t>
+        </is>
+      </c>
+      <c r="D2645" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2645" t="inlineStr">
+        <is>
+          <t>possible theft</t>
+        </is>
+      </c>
+    </row>
+    <row r="2646">
+      <c r="A2646" t="inlineStr">
+        <is>
+          <t>89abee76-46b4-4872-bb81-c1131f0f08dc</t>
+        </is>
+      </c>
+      <c r="B2646" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2646" t="inlineStr">
+        <is>
+          <t>2026-07-07T17:19:01.271Z</t>
+        </is>
+      </c>
+      <c r="D2646" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2646" t="inlineStr"/>
+    </row>
+    <row r="2647">
+      <c r="A2647" t="inlineStr">
+        <is>
+          <t>519245b9-e769-4874-904b-f76ee6db4f2c</t>
+        </is>
+      </c>
+      <c r="B2647" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2647" t="inlineStr">
+        <is>
+          <t>2026-07-07T20:01:46.780Z</t>
+        </is>
+      </c>
+      <c r="D2647" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2647" t="inlineStr"/>
+    </row>
+    <row r="2648">
+      <c r="A2648" t="inlineStr">
+        <is>
+          <t>e66cd209-20b2-4933-b90a-ccc76e63c229</t>
+        </is>
+      </c>
+      <c r="B2648" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2648" t="inlineStr">
+        <is>
+          <t>2026-07-07T20:12:32.396Z</t>
+        </is>
+      </c>
+      <c r="D2648" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2648" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2649">
+      <c r="A2649" t="inlineStr">
+        <is>
+          <t>b37b9cbe-1e19-4c00-bf21-effe9e8f71a3</t>
+        </is>
+      </c>
+      <c r="B2649" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2649" t="inlineStr">
+        <is>
+          <t>2026-07-07T20:43:09.147Z</t>
+        </is>
+      </c>
+      <c r="D2649" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2649" t="inlineStr">
+        <is>
+          <t>possible theft</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2649"/>
+  <dimension ref="A1:E2658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60237,6 +60237,207 @@
         </is>
       </c>
     </row>
+    <row r="2650">
+      <c r="A2650" t="inlineStr">
+        <is>
+          <t>fe50b43b-097e-4a45-854c-b150aa096591</t>
+        </is>
+      </c>
+      <c r="B2650" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2650" t="inlineStr">
+        <is>
+          <t>2026-07-08T04:30:45.209Z</t>
+        </is>
+      </c>
+      <c r="D2650" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2650" t="inlineStr"/>
+    </row>
+    <row r="2651">
+      <c r="A2651" t="inlineStr">
+        <is>
+          <t>6469a24d-e96d-485b-974e-ff8c3ddd8698</t>
+        </is>
+      </c>
+      <c r="B2651" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2651" t="inlineStr">
+        <is>
+          <t>2026-07-08T05:24:06.050Z</t>
+        </is>
+      </c>
+      <c r="D2651" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2651" t="inlineStr"/>
+    </row>
+    <row r="2652">
+      <c r="A2652" t="inlineStr">
+        <is>
+          <t>e0f5bd96-396b-41b8-9ce4-3a25f7960928</t>
+        </is>
+      </c>
+      <c r="B2652" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2652" t="inlineStr">
+        <is>
+          <t>2026-07-08T05:32:44.354Z</t>
+        </is>
+      </c>
+      <c r="D2652" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2652" t="inlineStr"/>
+    </row>
+    <row r="2653">
+      <c r="A2653" t="inlineStr">
+        <is>
+          <t>102eadca-f338-4031-b1a2-9ea2b0ac77cc</t>
+        </is>
+      </c>
+      <c r="B2653" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2653" t="inlineStr">
+        <is>
+          <t>2026-07-08T06:00:12.550Z</t>
+        </is>
+      </c>
+      <c r="D2653" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2653" t="inlineStr"/>
+    </row>
+    <row r="2654">
+      <c r="A2654" t="inlineStr">
+        <is>
+          <t>f04b63d8-b482-4bfe-bf8e-5d66cb309f88</t>
+        </is>
+      </c>
+      <c r="B2654" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2654" t="inlineStr">
+        <is>
+          <t>2026-07-08T06:48:27.053Z</t>
+        </is>
+      </c>
+      <c r="D2654" t="n">
+        <v>521</v>
+      </c>
+      <c r="E2654" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2655">
+      <c r="A2655" t="inlineStr">
+        <is>
+          <t>b6bb648d-77b5-4960-b54e-96f5ef81bcbf</t>
+        </is>
+      </c>
+      <c r="B2655" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2655" t="inlineStr">
+        <is>
+          <t>2026-07-08T08:10:32.976Z</t>
+        </is>
+      </c>
+      <c r="D2655" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2655" t="inlineStr"/>
+    </row>
+    <row r="2656">
+      <c r="A2656" t="inlineStr">
+        <is>
+          <t>9d6372cc-fbae-4a9c-8a67-f6af8504c81e</t>
+        </is>
+      </c>
+      <c r="B2656" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2656" t="inlineStr">
+        <is>
+          <t>2026-07-08T18:08:15.020Z</t>
+        </is>
+      </c>
+      <c r="D2656" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2656" t="inlineStr">
+        <is>
+          <t>probation 487</t>
+        </is>
+      </c>
+    </row>
+    <row r="2657">
+      <c r="A2657" t="inlineStr">
+        <is>
+          <t>ca5f98ec-3348-4c0c-8bfe-a1ee48930275</t>
+        </is>
+      </c>
+      <c r="B2657" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2657" t="inlineStr">
+        <is>
+          <t>2026-07-08T23:37:34.282Z</t>
+        </is>
+      </c>
+      <c r="D2657" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2657" t="inlineStr">
+        <is>
+          <t>Suspect ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2658">
+      <c r="A2658" t="inlineStr">
+        <is>
+          <t>f40bd43a-3b38-4174-9acd-1996d544bd16</t>
+        </is>
+      </c>
+      <c r="B2658" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2658" t="inlineStr">
+        <is>
+          <t>2026-07-08T23:58:48.880Z</t>
+        </is>
+      </c>
+      <c r="D2658" t="n">
+        <v>529</v>
+      </c>
+      <c r="E2658" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2658"/>
+  <dimension ref="A1:E2664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60438,6 +60438,148 @@
       </c>
       <c r="E2658" t="inlineStr"/>
     </row>
+    <row r="2659">
+      <c r="A2659" t="inlineStr">
+        <is>
+          <t>a643e394-43cd-4236-81b6-10563fbd8a2e</t>
+        </is>
+      </c>
+      <c r="B2659" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2659" t="inlineStr">
+        <is>
+          <t>2026-07-09T00:00:12.259Z</t>
+        </is>
+      </c>
+      <c r="D2659" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2659" t="inlineStr"/>
+    </row>
+    <row r="2660">
+      <c r="A2660" t="inlineStr">
+        <is>
+          <t>04a962a1-3af1-4e56-bd5a-3208315b07d2</t>
+        </is>
+      </c>
+      <c r="B2660" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2660" t="inlineStr">
+        <is>
+          <t>2026-07-09T02:22:08.763Z</t>
+        </is>
+      </c>
+      <c r="D2660" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2660" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2661">
+      <c r="A2661" t="inlineStr">
+        <is>
+          <t>b304cae7-7d8b-4109-913a-26e786e73ca0</t>
+        </is>
+      </c>
+      <c r="B2661" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2661" t="inlineStr">
+        <is>
+          <t>2026-07-09T03:09:37.286Z</t>
+        </is>
+      </c>
+      <c r="D2661" t="n">
+        <v>565</v>
+      </c>
+      <c r="E2661" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2662">
+      <c r="A2662" t="inlineStr">
+        <is>
+          <t>255c02e1-80a1-4ad5-bf6c-1b6de1f7abc4</t>
+        </is>
+      </c>
+      <c r="B2662" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2662" t="inlineStr">
+        <is>
+          <t>2026-07-09T07:04:26.439Z</t>
+        </is>
+      </c>
+      <c r="D2662" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2662" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2663">
+      <c r="A2663" t="inlineStr">
+        <is>
+          <t>bb41433e-14a3-4b02-b32f-78ffa3c8c7c8</t>
+        </is>
+      </c>
+      <c r="B2663" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2663" t="inlineStr">
+        <is>
+          <t>2026-07-09T17:03:34.622Z</t>
+        </is>
+      </c>
+      <c r="D2663" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2663" t="inlineStr"/>
+    </row>
+    <row r="2664">
+      <c r="A2664" t="inlineStr">
+        <is>
+          <t>ba976626-e19d-4f38-bc46-b46b5f70ca7c</t>
+        </is>
+      </c>
+      <c r="B2664" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2664" t="inlineStr">
+        <is>
+          <t>2026-07-09T20:54:28.499Z</t>
+        </is>
+      </c>
+      <c r="D2664" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2664" t="inlineStr">
+        <is>
+          <t>Stolen Vehicle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2664"/>
+  <dimension ref="A1:E2677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60580,6 +60580,291 @@
         </is>
       </c>
     </row>
+    <row r="2665">
+      <c r="A2665" t="inlineStr">
+        <is>
+          <t>21e6692e-7c05-45b8-9228-c737d2fdcaba</t>
+        </is>
+      </c>
+      <c r="B2665" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2665" t="inlineStr">
+        <is>
+          <t>2026-07-10T05:31:24.830Z</t>
+        </is>
+      </c>
+      <c r="D2665" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2665" t="inlineStr"/>
+    </row>
+    <row r="2666">
+      <c r="A2666" t="inlineStr">
+        <is>
+          <t>1890bd86-33a2-4c32-aca5-ca4ee63f6f9e</t>
+        </is>
+      </c>
+      <c r="B2666" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2666" t="inlineStr">
+        <is>
+          <t>2026-07-10T06:00:25.691Z</t>
+        </is>
+      </c>
+      <c r="D2666" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2666" t="inlineStr"/>
+    </row>
+    <row r="2667">
+      <c r="A2667" t="inlineStr">
+        <is>
+          <t>84b4f504-65be-4202-8337-0200cee19bf2</t>
+        </is>
+      </c>
+      <c r="B2667" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2667" t="inlineStr">
+        <is>
+          <t>2026-07-10T12:59:11.327Z</t>
+        </is>
+      </c>
+      <c r="D2667" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2667" t="inlineStr"/>
+    </row>
+    <row r="2668">
+      <c r="A2668" t="inlineStr">
+        <is>
+          <t>977a8a29-6f0a-40da-b324-c2b00a1be5ff</t>
+        </is>
+      </c>
+      <c r="B2668" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2668" t="inlineStr">
+        <is>
+          <t>2026-07-10T13:01:27.253Z</t>
+        </is>
+      </c>
+      <c r="D2668" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2668" t="inlineStr"/>
+    </row>
+    <row r="2669">
+      <c r="A2669" t="inlineStr">
+        <is>
+          <t>e653929b-cd89-4753-8a5d-01a5a4bb713f</t>
+        </is>
+      </c>
+      <c r="B2669" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2669" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:08:30.238Z</t>
+        </is>
+      </c>
+      <c r="D2669" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2669" t="inlineStr"/>
+    </row>
+    <row r="2670">
+      <c r="A2670" t="inlineStr">
+        <is>
+          <t>7e71be15-4aca-4c1a-be38-d192cf4b3885</t>
+        </is>
+      </c>
+      <c r="B2670" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2670" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:25:37.538Z</t>
+        </is>
+      </c>
+      <c r="D2670" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2670" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2671">
+      <c r="A2671" t="inlineStr">
+        <is>
+          <t>72fd86ba-0b41-404f-9474-51d3eb1f6e07</t>
+        </is>
+      </c>
+      <c r="B2671" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2671" t="inlineStr">
+        <is>
+          <t>2026-07-10T15:57:40.901Z</t>
+        </is>
+      </c>
+      <c r="D2671" t="n">
+        <v>782</v>
+      </c>
+      <c r="E2671" t="inlineStr">
+        <is>
+          <t>ASSIST HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2672">
+      <c r="A2672" t="inlineStr">
+        <is>
+          <t>5321c01c-73a5-41e2-8732-7be5c0f6b4d4</t>
+        </is>
+      </c>
+      <c r="B2672" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2672" t="inlineStr">
+        <is>
+          <t>2026-07-10T16:33:07.601Z</t>
+        </is>
+      </c>
+      <c r="D2672" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2672" t="inlineStr"/>
+    </row>
+    <row r="2673">
+      <c r="A2673" t="inlineStr">
+        <is>
+          <t>0495792c-1b57-46fc-b171-a1b890541eed</t>
+        </is>
+      </c>
+      <c r="B2673" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2673" t="inlineStr">
+        <is>
+          <t>2026-07-10T19:06:15.231Z</t>
+        </is>
+      </c>
+      <c r="D2673" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2673" t="inlineStr">
+        <is>
+          <t>associated to wire theft case</t>
+        </is>
+      </c>
+    </row>
+    <row r="2674">
+      <c r="A2674" t="inlineStr">
+        <is>
+          <t>f44dc8ef-7174-459e-b9c7-5134fa3bce1c</t>
+        </is>
+      </c>
+      <c r="B2674" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2674" t="inlineStr">
+        <is>
+          <t>2026-07-10T20:07:13.641Z</t>
+        </is>
+      </c>
+      <c r="D2674" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2674" t="inlineStr"/>
+    </row>
+    <row r="2675">
+      <c r="A2675" t="inlineStr">
+        <is>
+          <t>17b6e44e-d87a-4d19-9592-5262bfdbda9d</t>
+        </is>
+      </c>
+      <c r="B2675" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2675" t="inlineStr">
+        <is>
+          <t>2026-07-10T20:10:09.549Z</t>
+        </is>
+      </c>
+      <c r="D2675" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2675" t="inlineStr"/>
+    </row>
+    <row r="2676">
+      <c r="A2676" t="inlineStr">
+        <is>
+          <t>b273cf43-aca3-4611-9dfb-01f57addca56</t>
+        </is>
+      </c>
+      <c r="B2676" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2676" t="inlineStr">
+        <is>
+          <t>2026-07-10T21:18:37.923Z</t>
+        </is>
+      </c>
+      <c r="D2676" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2676" t="inlineStr"/>
+    </row>
+    <row r="2677">
+      <c r="A2677" t="inlineStr">
+        <is>
+          <t>1e1b104d-fe27-44d2-a3b0-072166475318</t>
+        </is>
+      </c>
+      <c r="B2677" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2677" t="inlineStr">
+        <is>
+          <t>2026-07-10T21:38:17.978Z</t>
+        </is>
+      </c>
+      <c r="D2677" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2677" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2677"/>
+  <dimension ref="A1:E2696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60865,6 +60865,461 @@
       </c>
       <c r="E2677" t="inlineStr"/>
     </row>
+    <row r="2678">
+      <c r="A2678" t="inlineStr">
+        <is>
+          <t>88e7ff43-1ebf-4589-a6fa-62e8fc82c746</t>
+        </is>
+      </c>
+      <c r="B2678" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2678" t="inlineStr">
+        <is>
+          <t>2026-07-11T00:30:38.107Z</t>
+        </is>
+      </c>
+      <c r="D2678" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2678" t="inlineStr"/>
+    </row>
+    <row r="2679">
+      <c r="A2679" t="inlineStr">
+        <is>
+          <t>e3635935-9754-48f2-826e-33e6daa7ab84</t>
+        </is>
+      </c>
+      <c r="B2679" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2679" t="inlineStr">
+        <is>
+          <t>2026-07-11T01:42:57.899Z</t>
+        </is>
+      </c>
+      <c r="D2679" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2679" t="inlineStr">
+        <is>
+          <t>wanted person</t>
+        </is>
+      </c>
+    </row>
+    <row r="2680">
+      <c r="A2680" t="inlineStr">
+        <is>
+          <t>39430cb2-29d4-4450-84a0-376bf20430c0</t>
+        </is>
+      </c>
+      <c r="B2680" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2680" t="inlineStr">
+        <is>
+          <t>2026-07-11T01:58:09.295Z</t>
+        </is>
+      </c>
+      <c r="D2680" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2680" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="2681">
+      <c r="A2681" t="inlineStr">
+        <is>
+          <t>5526320c-30af-4e96-a269-5d27c5908b14</t>
+        </is>
+      </c>
+      <c r="B2681" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2681" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:00:18.765Z</t>
+        </is>
+      </c>
+      <c r="D2681" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2681" t="inlineStr">
+        <is>
+          <t>wanted person</t>
+        </is>
+      </c>
+    </row>
+    <row r="2682">
+      <c r="A2682" t="inlineStr">
+        <is>
+          <t>f11f1e6d-91e5-4e86-9741-99225a6a58fc</t>
+        </is>
+      </c>
+      <c r="B2682" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2682" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:02:33.002Z</t>
+        </is>
+      </c>
+      <c r="D2682" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2682" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="2683">
+      <c r="A2683" t="inlineStr">
+        <is>
+          <t>9b8899a5-0236-4204-a08c-9b8d60be14f3</t>
+        </is>
+      </c>
+      <c r="B2683" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2683" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:07:43.536Z</t>
+        </is>
+      </c>
+      <c r="D2683" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2683" t="inlineStr">
+        <is>
+          <t>law enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2684">
+      <c r="A2684" t="inlineStr">
+        <is>
+          <t>cf2e9c36-8e48-4dfd-91aa-f1c8dc29a3b8</t>
+        </is>
+      </c>
+      <c r="B2684" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2684" t="inlineStr">
+        <is>
+          <t>2026-07-11T03:03:25.167Z</t>
+        </is>
+      </c>
+      <c r="D2684" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2684" t="inlineStr">
+        <is>
+          <t>law enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2685">
+      <c r="A2685" t="inlineStr">
+        <is>
+          <t>4ded00c3-79a2-424d-9884-a7f2556479cd</t>
+        </is>
+      </c>
+      <c r="B2685" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2685" t="inlineStr">
+        <is>
+          <t>2026-07-11T03:19:14.929Z</t>
+        </is>
+      </c>
+      <c r="D2685" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2685" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="2686">
+      <c r="A2686" t="inlineStr">
+        <is>
+          <t>0437c97b-5505-49dc-8356-de965edd2e4d</t>
+        </is>
+      </c>
+      <c r="B2686" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2686" t="inlineStr">
+        <is>
+          <t>2026-07-11T04:08:22.369Z</t>
+        </is>
+      </c>
+      <c r="D2686" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2686" t="inlineStr">
+        <is>
+          <t>law enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2687">
+      <c r="A2687" t="inlineStr">
+        <is>
+          <t>869b5330-7950-42aa-8cc5-b6fc69bc15d2</t>
+        </is>
+      </c>
+      <c r="B2687" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2687" t="inlineStr">
+        <is>
+          <t>2026-07-11T05:08:44.553Z</t>
+        </is>
+      </c>
+      <c r="D2687" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2687" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="2688">
+      <c r="A2688" t="inlineStr">
+        <is>
+          <t>c31e5c79-4be3-4a8a-b5dd-828b5ea9e291</t>
+        </is>
+      </c>
+      <c r="B2688" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2688" t="inlineStr">
+        <is>
+          <t>2026-07-11T05:39:10.880Z</t>
+        </is>
+      </c>
+      <c r="D2688" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2688" t="inlineStr">
+        <is>
+          <t>law enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2689">
+      <c r="A2689" t="inlineStr">
+        <is>
+          <t>6eb45347-57dd-4ff9-bc8e-57d605f55ed9</t>
+        </is>
+      </c>
+      <c r="B2689" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2689" t="inlineStr">
+        <is>
+          <t>2026-07-11T06:03:27.527Z</t>
+        </is>
+      </c>
+      <c r="D2689" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2689" t="inlineStr"/>
+    </row>
+    <row r="2690">
+      <c r="A2690" t="inlineStr">
+        <is>
+          <t>f8ce8b18-14f7-45f8-86ce-fa72d1dc5f7a</t>
+        </is>
+      </c>
+      <c r="B2690" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2690" t="inlineStr">
+        <is>
+          <t>2026-07-11T06:30:53.576Z</t>
+        </is>
+      </c>
+      <c r="D2690" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2690" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="2691">
+      <c r="A2691" t="inlineStr">
+        <is>
+          <t>3e045462-9e86-494a-aaee-b7e15b40921e</t>
+        </is>
+      </c>
+      <c r="B2691" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2691" t="inlineStr">
+        <is>
+          <t>2026-07-11T07:14:11.880Z</t>
+        </is>
+      </c>
+      <c r="D2691" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2691" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" t="inlineStr">
+        <is>
+          <t>fa5bd0d8-88bd-4f9f-a713-447bc50bb3f8</t>
+        </is>
+      </c>
+      <c r="B2692" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2692" t="inlineStr">
+        <is>
+          <t>2026-07-11T19:05:43.487Z</t>
+        </is>
+      </c>
+      <c r="D2692" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2692" t="inlineStr"/>
+    </row>
+    <row r="2693">
+      <c r="A2693" t="inlineStr">
+        <is>
+          <t>321340d2-20ba-4a96-9c64-4fd8d5e6198e</t>
+        </is>
+      </c>
+      <c r="B2693" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2693" t="inlineStr">
+        <is>
+          <t>2026-07-11T21:46:09.742Z</t>
+        </is>
+      </c>
+      <c r="D2693" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2693" t="inlineStr">
+        <is>
+          <t>THEFT OF PLASMA CUTTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2694">
+      <c r="A2694" t="inlineStr">
+        <is>
+          <t>d2a40789-b994-443c-8ce2-2de82cf1b724</t>
+        </is>
+      </c>
+      <c r="B2694" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2694" t="inlineStr">
+        <is>
+          <t>2026-07-11T21:49:03.088Z</t>
+        </is>
+      </c>
+      <c r="D2694" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2694" t="inlineStr"/>
+    </row>
+    <row r="2695">
+      <c r="A2695" t="inlineStr">
+        <is>
+          <t>483d52f7-ffae-4038-9aee-fa8ccbfdc78a</t>
+        </is>
+      </c>
+      <c r="B2695" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2695" t="inlineStr">
+        <is>
+          <t>2026-07-11T21:56:33.524Z</t>
+        </is>
+      </c>
+      <c r="D2695" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2695" t="inlineStr">
+        <is>
+          <t>theft get away vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2696">
+      <c r="A2696" t="inlineStr">
+        <is>
+          <t>6d7802f7-97ec-4839-822f-de7378c169d6</t>
+        </is>
+      </c>
+      <c r="B2696" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2696" t="inlineStr">
+        <is>
+          <t>2026-07-11T22:24:15.114Z</t>
+        </is>
+      </c>
+      <c r="D2696" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2696" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2696"/>
+  <dimension ref="A1:E2697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61320,6 +61320,27 @@
       </c>
       <c r="E2696" t="inlineStr"/>
     </row>
+    <row r="2697">
+      <c r="A2697" t="inlineStr">
+        <is>
+          <t>c5e05769-9083-4c3f-b00a-77ce15e2d5ca</t>
+        </is>
+      </c>
+      <c r="B2697" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2697" t="inlineStr">
+        <is>
+          <t>2026-07-12T03:06:26.606Z</t>
+        </is>
+      </c>
+      <c r="D2697" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2697" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2697"/>
+  <dimension ref="A1:E2719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61341,6 +61341,496 @@
       </c>
       <c r="E2697" t="inlineStr"/>
     </row>
+    <row r="2698">
+      <c r="A2698" t="inlineStr">
+        <is>
+          <t>aa83948d-d1b6-4e9c-abf3-344cd2ba1e73</t>
+        </is>
+      </c>
+      <c r="B2698" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2698" t="inlineStr">
+        <is>
+          <t>2026-07-13T01:21:30.105Z</t>
+        </is>
+      </c>
+      <c r="D2698" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2698" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="2699">
+      <c r="A2699" t="inlineStr">
+        <is>
+          <t>b3c9c619-efdf-48db-8961-11e07cbecd9c</t>
+        </is>
+      </c>
+      <c r="B2699" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2699" t="inlineStr">
+        <is>
+          <t>2026-07-13T03:40:54.135Z</t>
+        </is>
+      </c>
+      <c r="D2699" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2699" t="inlineStr"/>
+    </row>
+    <row r="2700">
+      <c r="A2700" t="inlineStr">
+        <is>
+          <t>721ae5f5-9897-4152-8dff-46775efdd3b1</t>
+        </is>
+      </c>
+      <c r="B2700" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2700" t="inlineStr">
+        <is>
+          <t>2026-07-13T05:46:27.690Z</t>
+        </is>
+      </c>
+      <c r="D2700" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2700" t="inlineStr"/>
+    </row>
+    <row r="2701">
+      <c r="A2701" t="inlineStr">
+        <is>
+          <t>dd8417b4-fd9b-4096-8595-2b5cacba913e</t>
+        </is>
+      </c>
+      <c r="B2701" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2701" t="inlineStr">
+        <is>
+          <t>2026-07-13T06:20:18.548Z</t>
+        </is>
+      </c>
+      <c r="D2701" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2701" t="inlineStr"/>
+    </row>
+    <row r="2702">
+      <c r="A2702" t="inlineStr">
+        <is>
+          <t>394824e6-d7b6-4ac2-95cb-e1cbcdb79b0d</t>
+        </is>
+      </c>
+      <c r="B2702" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2702" t="inlineStr">
+        <is>
+          <t>2026-07-13T07:16:57.318Z</t>
+        </is>
+      </c>
+      <c r="D2702" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2702" t="inlineStr"/>
+    </row>
+    <row r="2703">
+      <c r="A2703" t="inlineStr">
+        <is>
+          <t>b81ddde7-4f3c-4d13-a441-f08a2c62427f</t>
+        </is>
+      </c>
+      <c r="B2703" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2703" t="inlineStr">
+        <is>
+          <t>2026-07-13T07:29:47.523Z</t>
+        </is>
+      </c>
+      <c r="D2703" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2703" t="inlineStr">
+        <is>
+          <t>sus veh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2704">
+      <c r="A2704" t="inlineStr">
+        <is>
+          <t>bd7ecf84-6ced-4dee-b208-3d909e29f894</t>
+        </is>
+      </c>
+      <c r="B2704" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2704" t="inlineStr">
+        <is>
+          <t>2026-07-13T07:35:28.326Z</t>
+        </is>
+      </c>
+      <c r="D2704" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2704" t="inlineStr">
+        <is>
+          <t>Sus veh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2705">
+      <c r="A2705" t="inlineStr">
+        <is>
+          <t>6571a49d-68b9-4c17-b2df-9cf0606ab2fc</t>
+        </is>
+      </c>
+      <c r="B2705" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2705" t="inlineStr">
+        <is>
+          <t>2026-07-13T07:53:41.298Z</t>
+        </is>
+      </c>
+      <c r="D2705" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2705" t="inlineStr"/>
+    </row>
+    <row r="2706">
+      <c r="A2706" t="inlineStr">
+        <is>
+          <t>899ceb67-c22e-4fa1-b9ba-8e4e83f25ad7</t>
+        </is>
+      </c>
+      <c r="B2706" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2706" t="inlineStr">
+        <is>
+          <t>2026-07-13T08:01:22.120Z</t>
+        </is>
+      </c>
+      <c r="D2706" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2706" t="inlineStr">
+        <is>
+          <t>Suspect wire theft vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2707">
+      <c r="A2707" t="inlineStr">
+        <is>
+          <t>7d2e06f3-bddd-433c-ac1c-88dcb2ad00b7</t>
+        </is>
+      </c>
+      <c r="B2707" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2707" t="inlineStr">
+        <is>
+          <t>2026-07-13T08:05:18.805Z</t>
+        </is>
+      </c>
+      <c r="D2707" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2707" t="inlineStr">
+        <is>
+          <t>Wire theft. Veh associate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2708">
+      <c r="A2708" t="inlineStr">
+        <is>
+          <t>27bad246-24ef-4589-b6a3-eef8f0c9839a</t>
+        </is>
+      </c>
+      <c r="B2708" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2708" t="inlineStr">
+        <is>
+          <t>2026-07-13T08:19:15.604Z</t>
+        </is>
+      </c>
+      <c r="D2708" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2708" t="inlineStr"/>
+    </row>
+    <row r="2709">
+      <c r="A2709" t="inlineStr">
+        <is>
+          <t>1c7b44f7-5746-4f05-aa5d-2b3b8f9755db</t>
+        </is>
+      </c>
+      <c r="B2709" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2709" t="inlineStr">
+        <is>
+          <t>2026-07-13T09:15:35.952Z</t>
+        </is>
+      </c>
+      <c r="D2709" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2709" t="inlineStr"/>
+    </row>
+    <row r="2710">
+      <c r="A2710" t="inlineStr">
+        <is>
+          <t>eb9639ae-7ec5-4e10-bbe7-673db68af62a</t>
+        </is>
+      </c>
+      <c r="B2710" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2710" t="inlineStr">
+        <is>
+          <t>2026-07-13T10:16:56.001Z</t>
+        </is>
+      </c>
+      <c r="D2710" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2710" t="inlineStr"/>
+    </row>
+    <row r="2711">
+      <c r="A2711" t="inlineStr">
+        <is>
+          <t>c9f974b7-c77e-4625-8015-8a3cb5d10557</t>
+        </is>
+      </c>
+      <c r="B2711" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2711" t="inlineStr">
+        <is>
+          <t>2026-07-13T11:22:12.594Z</t>
+        </is>
+      </c>
+      <c r="D2711" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2711" t="inlineStr"/>
+    </row>
+    <row r="2712">
+      <c r="A2712" t="inlineStr">
+        <is>
+          <t>bb86eaae-bb49-43ac-bf62-3b8e7fdde191</t>
+        </is>
+      </c>
+      <c r="B2712" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2712" t="inlineStr">
+        <is>
+          <t>2026-07-13T14:19:27.641Z</t>
+        </is>
+      </c>
+      <c r="D2712" t="n">
+        <v>528</v>
+      </c>
+      <c r="E2712" t="inlineStr">
+        <is>
+          <t>wanted suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2713">
+      <c r="A2713" t="inlineStr">
+        <is>
+          <t>3c988c64-1fab-45e7-bcdc-00216ae2bd40</t>
+        </is>
+      </c>
+      <c r="B2713" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2713" t="inlineStr">
+        <is>
+          <t>2026-07-13T16:16:33.892Z</t>
+        </is>
+      </c>
+      <c r="D2713" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2713" t="inlineStr"/>
+    </row>
+    <row r="2714">
+      <c r="A2714" t="inlineStr">
+        <is>
+          <t>410ab809-6794-4395-bca3-1accf04845c3</t>
+        </is>
+      </c>
+      <c r="B2714" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2714" t="inlineStr">
+        <is>
+          <t>2026-07-13T17:06:19.428Z</t>
+        </is>
+      </c>
+      <c r="D2714" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2714" t="inlineStr"/>
+    </row>
+    <row r="2715">
+      <c r="A2715" t="inlineStr">
+        <is>
+          <t>cfc958eb-2ecb-467f-b2d7-866a7f12ab09</t>
+        </is>
+      </c>
+      <c r="B2715" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2715" t="inlineStr">
+        <is>
+          <t>2026-07-13T18:27:54.542Z</t>
+        </is>
+      </c>
+      <c r="D2715" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2715" t="inlineStr"/>
+    </row>
+    <row r="2716">
+      <c r="A2716" t="inlineStr">
+        <is>
+          <t>f7346910-386a-4248-a5c1-38d64f458b63</t>
+        </is>
+      </c>
+      <c r="B2716" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2716" t="inlineStr">
+        <is>
+          <t>2026-07-13T19:06:44.941Z</t>
+        </is>
+      </c>
+      <c r="D2716" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2716" t="inlineStr"/>
+    </row>
+    <row r="2717">
+      <c r="A2717" t="inlineStr">
+        <is>
+          <t>1e0b4736-c177-48bd-a3ee-a0bbc9357974</t>
+        </is>
+      </c>
+      <c r="B2717" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2717" t="inlineStr">
+        <is>
+          <t>2026-07-13T19:30:12.152Z</t>
+        </is>
+      </c>
+      <c r="D2717" t="n">
+        <v>528</v>
+      </c>
+      <c r="E2717" t="inlineStr">
+        <is>
+          <t>wanted suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2718">
+      <c r="A2718" t="inlineStr">
+        <is>
+          <t>b9e9a8c4-e92e-4918-9cee-fbd0a1b63b52</t>
+        </is>
+      </c>
+      <c r="B2718" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2718" t="inlineStr">
+        <is>
+          <t>2026-07-13T20:15:44.276Z</t>
+        </is>
+      </c>
+      <c r="D2718" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2718" t="inlineStr"/>
+    </row>
+    <row r="2719">
+      <c r="A2719" t="inlineStr">
+        <is>
+          <t>6feb799e-8fc6-4f8a-bd0b-26f3dd85e1f0</t>
+        </is>
+      </c>
+      <c r="B2719" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2719" t="inlineStr">
+        <is>
+          <t>2026-07-13T21:28:16.650Z</t>
+        </is>
+      </c>
+      <c r="D2719" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2719" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2719"/>
+  <dimension ref="A1:E2749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61831,6 +61831,716 @@
       </c>
       <c r="E2719" t="inlineStr"/>
     </row>
+    <row r="2720">
+      <c r="A2720" t="inlineStr">
+        <is>
+          <t>3b92650a-7063-4623-8f5f-14cae28d878c</t>
+        </is>
+      </c>
+      <c r="B2720" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2720" t="inlineStr">
+        <is>
+          <t>2026-07-14T01:14:24.445Z</t>
+        </is>
+      </c>
+      <c r="D2720" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2720" t="inlineStr">
+        <is>
+          <t>suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" t="inlineStr">
+        <is>
+          <t>eb5f2a7c-6573-44c7-9995-c0c8d34140e2</t>
+        </is>
+      </c>
+      <c r="B2721" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2721" t="inlineStr">
+        <is>
+          <t>2026-07-14T03:10:58.335Z</t>
+        </is>
+      </c>
+      <c r="D2721" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2721" t="inlineStr"/>
+    </row>
+    <row r="2722">
+      <c r="A2722" t="inlineStr">
+        <is>
+          <t>008ca165-d1c9-4145-b8d7-f2a0c13315c3</t>
+        </is>
+      </c>
+      <c r="B2722" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2722" t="inlineStr">
+        <is>
+          <t>2026-07-14T06:26:33.131Z</t>
+        </is>
+      </c>
+      <c r="D2722" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2722" t="inlineStr"/>
+    </row>
+    <row r="2723">
+      <c r="A2723" t="inlineStr">
+        <is>
+          <t>d1c92942-91e6-40f3-a4d1-18cc72ddb8e2</t>
+        </is>
+      </c>
+      <c r="B2723" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2723" t="inlineStr">
+        <is>
+          <t>2026-07-14T07:36:49.228Z</t>
+        </is>
+      </c>
+      <c r="D2723" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2723" t="inlineStr"/>
+    </row>
+    <row r="2724">
+      <c r="A2724" t="inlineStr">
+        <is>
+          <t>e0b13ae7-d4e5-46ad-b040-4fdc4ebf5fe0</t>
+        </is>
+      </c>
+      <c r="B2724" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2724" t="inlineStr">
+        <is>
+          <t>2026-07-14T11:00:28.446Z</t>
+        </is>
+      </c>
+      <c r="D2724" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2724" t="inlineStr"/>
+    </row>
+    <row r="2725">
+      <c r="A2725" t="inlineStr">
+        <is>
+          <t>267dd31f-39f1-4f35-8343-d87d54b012cd</t>
+        </is>
+      </c>
+      <c r="B2725" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2725" t="inlineStr">
+        <is>
+          <t>2026-07-14T11:12:55.684Z</t>
+        </is>
+      </c>
+      <c r="D2725" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2725" t="inlineStr"/>
+    </row>
+    <row r="2726">
+      <c r="A2726" t="inlineStr">
+        <is>
+          <t>f9baad0a-e8d0-4e2a-86da-1c84800707f8</t>
+        </is>
+      </c>
+      <c r="B2726" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2726" t="inlineStr">
+        <is>
+          <t>2026-07-14T11:20:07.020Z</t>
+        </is>
+      </c>
+      <c r="D2726" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2726" t="inlineStr">
+        <is>
+          <t>theft suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" t="inlineStr">
+        <is>
+          <t>73bd4753-d45d-4f97-a6c0-77283e2d8274</t>
+        </is>
+      </c>
+      <c r="B2727" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2727" t="inlineStr">
+        <is>
+          <t>2026-07-14T11:32:58.930Z</t>
+        </is>
+      </c>
+      <c r="D2727" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2727" t="inlineStr"/>
+    </row>
+    <row r="2728">
+      <c r="A2728" t="inlineStr">
+        <is>
+          <t>be0b84cc-c365-4165-87fb-7c43f4dd06ea</t>
+        </is>
+      </c>
+      <c r="B2728" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2728" t="inlineStr">
+        <is>
+          <t>2026-07-14T15:16:12.664Z</t>
+        </is>
+      </c>
+      <c r="D2728" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2728" t="inlineStr"/>
+    </row>
+    <row r="2729">
+      <c r="A2729" t="inlineStr">
+        <is>
+          <t>b87d8106-008a-4a56-aed6-92e55b59ba60</t>
+        </is>
+      </c>
+      <c r="B2729" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2729" t="inlineStr">
+        <is>
+          <t>2026-07-14T16:37:40.937Z</t>
+        </is>
+      </c>
+      <c r="D2729" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2729" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="A2730" t="inlineStr">
+        <is>
+          <t>8c52be42-37b7-43bc-8ac8-9f32c65d608c</t>
+        </is>
+      </c>
+      <c r="B2730" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2730" t="inlineStr">
+        <is>
+          <t>2026-07-14T17:16:40.835Z</t>
+        </is>
+      </c>
+      <c r="D2730" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2730" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2731">
+      <c r="A2731" t="inlineStr">
+        <is>
+          <t>37dfb77d-94ad-4dc5-8d52-0be5a5c51bec</t>
+        </is>
+      </c>
+      <c r="B2731" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2731" t="inlineStr">
+        <is>
+          <t>2026-07-14T17:57:11.892Z</t>
+        </is>
+      </c>
+      <c r="D2731" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2731" t="inlineStr">
+        <is>
+          <t>Sus id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" t="inlineStr">
+        <is>
+          <t>9624a20a-c0f4-4915-a0b3-9eeb0d250fd1</t>
+        </is>
+      </c>
+      <c r="B2732" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2732" t="inlineStr">
+        <is>
+          <t>2026-07-14T17:57:57.810Z</t>
+        </is>
+      </c>
+      <c r="D2732" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2732" t="inlineStr">
+        <is>
+          <t>suspec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2733">
+      <c r="A2733" t="inlineStr">
+        <is>
+          <t>d33070bc-b7c6-4ea7-925c-190d2d5bb86d</t>
+        </is>
+      </c>
+      <c r="B2733" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2733" t="inlineStr">
+        <is>
+          <t>2026-07-14T18:20:07.563Z</t>
+        </is>
+      </c>
+      <c r="D2733" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2733" t="inlineStr">
+        <is>
+          <t>suspec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2734">
+      <c r="A2734" t="inlineStr">
+        <is>
+          <t>5b017b58-73c2-46c7-99af-c7728c95c6db</t>
+        </is>
+      </c>
+      <c r="B2734" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2734" t="inlineStr">
+        <is>
+          <t>2026-07-14T18:46:54.744Z</t>
+        </is>
+      </c>
+      <c r="D2734" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2734" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2735">
+      <c r="A2735" t="inlineStr">
+        <is>
+          <t>0c1032e2-b3d2-40f1-a2a1-e73879cd6968</t>
+        </is>
+      </c>
+      <c r="B2735" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2735" t="inlineStr">
+        <is>
+          <t>2026-07-14T19:20:12.594Z</t>
+        </is>
+      </c>
+      <c r="D2735" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2735" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" t="inlineStr">
+        <is>
+          <t>1de4594a-79e6-4657-ab16-0413dd331969</t>
+        </is>
+      </c>
+      <c r="B2736" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2736" t="inlineStr">
+        <is>
+          <t>2026-07-14T20:23:18.533Z</t>
+        </is>
+      </c>
+      <c r="D2736" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2736" t="inlineStr">
+        <is>
+          <t>warrant subject</t>
+        </is>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" t="inlineStr">
+        <is>
+          <t>8790379d-8b99-429e-849e-ece721fa16ae</t>
+        </is>
+      </c>
+      <c r="B2737" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2737" t="inlineStr">
+        <is>
+          <t>2026-07-14T20:25:51.078Z</t>
+        </is>
+      </c>
+      <c r="D2737" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2737" t="inlineStr">
+        <is>
+          <t>wire theft investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" t="inlineStr">
+        <is>
+          <t>6326dfa1-f95d-4533-8688-569ff2e4a527</t>
+        </is>
+      </c>
+      <c r="B2738" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2738" t="inlineStr">
+        <is>
+          <t>2026-07-14T20:28:47.370Z</t>
+        </is>
+      </c>
+      <c r="D2738" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2738" t="inlineStr">
+        <is>
+          <t>theft investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" t="inlineStr">
+        <is>
+          <t>2590fbb5-74be-4ac0-af1a-9e56ca7a009f</t>
+        </is>
+      </c>
+      <c r="B2739" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2739" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:05:59.148Z</t>
+        </is>
+      </c>
+      <c r="D2739" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2739" t="inlineStr">
+        <is>
+          <t>theft suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2740">
+      <c r="A2740" t="inlineStr">
+        <is>
+          <t>1e1851f1-a8ce-42a4-9628-dfb0512c3c98</t>
+        </is>
+      </c>
+      <c r="B2740" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2740" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:17:22.041Z</t>
+        </is>
+      </c>
+      <c r="D2740" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2740" t="inlineStr"/>
+    </row>
+    <row r="2741">
+      <c r="A2741" t="inlineStr">
+        <is>
+          <t>f1975dda-1ea0-497d-a766-4a21bc82c68f</t>
+        </is>
+      </c>
+      <c r="B2741" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2741" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:18:34.387Z</t>
+        </is>
+      </c>
+      <c r="D2741" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2741" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2742">
+      <c r="A2742" t="inlineStr">
+        <is>
+          <t>babebee7-0ae0-4a16-8b7d-91d9d4310bcf</t>
+        </is>
+      </c>
+      <c r="B2742" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2742" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:32:21.793Z</t>
+        </is>
+      </c>
+      <c r="D2742" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2742" t="inlineStr">
+        <is>
+          <t>possible drug poss case</t>
+        </is>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" t="inlineStr">
+        <is>
+          <t>6714d3e6-64b8-4378-9db5-f7f90f16f298</t>
+        </is>
+      </c>
+      <c r="B2743" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2743" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:36:13.355Z</t>
+        </is>
+      </c>
+      <c r="D2743" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2743" t="inlineStr">
+        <is>
+          <t>Drug Intel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" t="inlineStr">
+        <is>
+          <t>8bc7d2dc-16a2-4823-8fcd-6da0f01fabf7</t>
+        </is>
+      </c>
+      <c r="B2744" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2744" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:44:12.395Z</t>
+        </is>
+      </c>
+      <c r="D2744" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2744" t="inlineStr">
+        <is>
+          <t>poss suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="inlineStr">
+        <is>
+          <t>606eacbb-002e-4bd9-97eb-f2fbcd550160</t>
+        </is>
+      </c>
+      <c r="B2745" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2745" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:46:29.562Z</t>
+        </is>
+      </c>
+      <c r="D2745" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2745" t="inlineStr">
+        <is>
+          <t>wire investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="inlineStr">
+        <is>
+          <t>acad20e6-9bbe-42b0-81d7-c51448f2c468</t>
+        </is>
+      </c>
+      <c r="B2746" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2746" t="inlineStr">
+        <is>
+          <t>2026-07-14T22:24:53.558Z</t>
+        </is>
+      </c>
+      <c r="D2746" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2746" t="inlineStr">
+        <is>
+          <t>poss wire theft</t>
+        </is>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="inlineStr">
+        <is>
+          <t>58b27841-c4e6-4287-9663-1bbc3b691f09</t>
+        </is>
+      </c>
+      <c r="B2747" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2747" t="inlineStr">
+        <is>
+          <t>2026-07-14T22:29:31.084Z</t>
+        </is>
+      </c>
+      <c r="D2747" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2747" t="inlineStr"/>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="inlineStr">
+        <is>
+          <t>52745e5f-9ae8-41b4-9dbb-cba563b493fd</t>
+        </is>
+      </c>
+      <c r="B2748" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2748" t="inlineStr">
+        <is>
+          <t>2026-07-14T22:36:58.998Z</t>
+        </is>
+      </c>
+      <c r="D2748" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2748" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="inlineStr">
+        <is>
+          <t>efa38980-931f-49b6-99f9-06a3123b3355</t>
+        </is>
+      </c>
+      <c r="B2749" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2749" t="inlineStr">
+        <is>
+          <t>2026-07-14T23:40:38.276Z</t>
+        </is>
+      </c>
+      <c r="D2749" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2749" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2749"/>
+  <dimension ref="A1:E2772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62541,6 +62541,521 @@
       </c>
       <c r="E2749" t="inlineStr"/>
     </row>
+    <row r="2750">
+      <c r="A2750" t="inlineStr">
+        <is>
+          <t>557194cb-57b0-4abd-a318-4b7d547413e0</t>
+        </is>
+      </c>
+      <c r="B2750" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2750" t="inlineStr">
+        <is>
+          <t>2026-07-15T00:00:14.289Z</t>
+        </is>
+      </c>
+      <c r="D2750" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2750" t="inlineStr"/>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="inlineStr">
+        <is>
+          <t>0ee5a65a-9a99-402c-bb77-9a1a27997f41</t>
+        </is>
+      </c>
+      <c r="B2751" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2751" t="inlineStr">
+        <is>
+          <t>2026-07-15T02:30:12.524Z</t>
+        </is>
+      </c>
+      <c r="D2751" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2751" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="inlineStr">
+        <is>
+          <t>f4277362-8de9-4e8a-8fcc-4fc48e8d3ae6</t>
+        </is>
+      </c>
+      <c r="B2752" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2752" t="inlineStr">
+        <is>
+          <t>2026-07-15T03:09:02.576Z</t>
+        </is>
+      </c>
+      <c r="D2752" t="n">
+        <v>564</v>
+      </c>
+      <c r="E2752" t="inlineStr"/>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="inlineStr">
+        <is>
+          <t>212d5c14-9d79-40b0-9db4-3e10551be3c0</t>
+        </is>
+      </c>
+      <c r="B2753" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2753" t="inlineStr">
+        <is>
+          <t>2026-07-15T03:18:11.086Z</t>
+        </is>
+      </c>
+      <c r="D2753" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2753" t="inlineStr"/>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="inlineStr">
+        <is>
+          <t>7b69470d-d8b8-4f47-b6ad-6e740b11c20c</t>
+        </is>
+      </c>
+      <c r="B2754" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2754" t="inlineStr">
+        <is>
+          <t>2026-07-15T03:18:49.166Z</t>
+        </is>
+      </c>
+      <c r="D2754" t="n">
+        <v>520</v>
+      </c>
+      <c r="E2754" t="inlineStr"/>
+    </row>
+    <row r="2755">
+      <c r="A2755" t="inlineStr">
+        <is>
+          <t>d3b4e37e-c9b3-4c08-ad15-72b559ebe072</t>
+        </is>
+      </c>
+      <c r="B2755" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2755" t="inlineStr">
+        <is>
+          <t>2026-07-15T05:50:21.537Z</t>
+        </is>
+      </c>
+      <c r="D2755" t="n">
+        <v>486</v>
+      </c>
+      <c r="E2755" t="inlineStr"/>
+    </row>
+    <row r="2756">
+      <c r="A2756" t="inlineStr">
+        <is>
+          <t>44635883-cb44-4317-8220-acb124c9ce6e</t>
+        </is>
+      </c>
+      <c r="B2756" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2756" t="inlineStr">
+        <is>
+          <t>2026-07-15T06:01:37.583Z</t>
+        </is>
+      </c>
+      <c r="D2756" t="n">
+        <v>486</v>
+      </c>
+      <c r="E2756" t="inlineStr"/>
+    </row>
+    <row r="2757">
+      <c r="A2757" t="inlineStr">
+        <is>
+          <t>062e2a63-bb3f-4f48-a6c0-b584410dfa7f</t>
+        </is>
+      </c>
+      <c r="B2757" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2757" t="inlineStr">
+        <is>
+          <t>2026-07-15T07:27:19.942Z</t>
+        </is>
+      </c>
+      <c r="D2757" t="n">
+        <v>486</v>
+      </c>
+      <c r="E2757" t="inlineStr"/>
+    </row>
+    <row r="2758">
+      <c r="A2758" t="inlineStr">
+        <is>
+          <t>6cdea9f3-e4b4-4daa-a701-1b19456edd71</t>
+        </is>
+      </c>
+      <c r="B2758" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2758" t="inlineStr">
+        <is>
+          <t>2026-07-15T09:41:26.392Z</t>
+        </is>
+      </c>
+      <c r="D2758" t="n">
+        <v>486</v>
+      </c>
+      <c r="E2758" t="inlineStr"/>
+    </row>
+    <row r="2759">
+      <c r="A2759" t="inlineStr">
+        <is>
+          <t>b0a7ad46-af5f-4264-946c-d80cf48736a9</t>
+        </is>
+      </c>
+      <c r="B2759" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2759" t="inlineStr">
+        <is>
+          <t>2026-07-15T10:57:31.628Z</t>
+        </is>
+      </c>
+      <c r="D2759" t="n">
+        <v>486</v>
+      </c>
+      <c r="E2759" t="inlineStr"/>
+    </row>
+    <row r="2760">
+      <c r="A2760" t="inlineStr">
+        <is>
+          <t>bbc33ebc-15c7-49ac-8155-5695652e977c</t>
+        </is>
+      </c>
+      <c r="B2760" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2760" t="inlineStr">
+        <is>
+          <t>2026-07-15T11:16:34.751Z</t>
+        </is>
+      </c>
+      <c r="D2760" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2760" t="inlineStr"/>
+    </row>
+    <row r="2761">
+      <c r="A2761" t="inlineStr">
+        <is>
+          <t>9c7f4ca5-3e71-45c0-a8dc-dc23dd6e1a26</t>
+        </is>
+      </c>
+      <c r="B2761" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2761" t="inlineStr">
+        <is>
+          <t>2026-07-15T16:00:28.043Z</t>
+        </is>
+      </c>
+      <c r="D2761" t="n">
+        <v>527</v>
+      </c>
+      <c r="E2761" t="inlineStr">
+        <is>
+          <t>wanted suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2762">
+      <c r="A2762" t="inlineStr">
+        <is>
+          <t>82649da5-03fe-4bc4-8c29-400c5ed21111</t>
+        </is>
+      </c>
+      <c r="B2762" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2762" t="inlineStr">
+        <is>
+          <t>2026-07-15T18:32:44.064Z</t>
+        </is>
+      </c>
+      <c r="D2762" t="n">
+        <v>563</v>
+      </c>
+      <c r="E2762" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2763">
+      <c r="A2763" t="inlineStr">
+        <is>
+          <t>d7784252-4991-4ff6-bae1-d920200db14d</t>
+        </is>
+      </c>
+      <c r="B2763" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2763" t="inlineStr">
+        <is>
+          <t>2026-07-15T18:34:28.307Z</t>
+        </is>
+      </c>
+      <c r="D2763" t="n">
+        <v>519</v>
+      </c>
+      <c r="E2763" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2764">
+      <c r="A2764" t="inlineStr">
+        <is>
+          <t>84af4830-448a-4607-9a6a-e227651770fa</t>
+        </is>
+      </c>
+      <c r="B2764" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2764" t="inlineStr">
+        <is>
+          <t>2026-07-15T21:00:22.502Z</t>
+        </is>
+      </c>
+      <c r="D2764" t="n">
+        <v>563</v>
+      </c>
+      <c r="E2764" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2765">
+      <c r="A2765" t="inlineStr">
+        <is>
+          <t>8fad28a7-5870-428b-909b-ab890dcabd9d</t>
+        </is>
+      </c>
+      <c r="B2765" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2765" t="inlineStr">
+        <is>
+          <t>2026-07-15T21:11:54.275Z</t>
+        </is>
+      </c>
+      <c r="D2765" t="n">
+        <v>563</v>
+      </c>
+      <c r="E2765" t="inlineStr">
+        <is>
+          <t>poss involvement in narc sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="2766">
+      <c r="A2766" t="inlineStr">
+        <is>
+          <t>8c975d77-4eae-41e2-98cd-dfd7bb17693b</t>
+        </is>
+      </c>
+      <c r="B2766" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2766" t="inlineStr">
+        <is>
+          <t>2026-07-15T21:22:33.174Z</t>
+        </is>
+      </c>
+      <c r="D2766" t="n">
+        <v>563</v>
+      </c>
+      <c r="E2766" t="inlineStr">
+        <is>
+          <t>poss of narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2767">
+      <c r="A2767" t="inlineStr">
+        <is>
+          <t>556107f7-40c7-4fc7-a087-2c36a36f39c4</t>
+        </is>
+      </c>
+      <c r="B2767" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2767" t="inlineStr">
+        <is>
+          <t>2026-07-15T21:25:11.729Z</t>
+        </is>
+      </c>
+      <c r="D2767" t="n">
+        <v>486</v>
+      </c>
+      <c r="E2767" t="inlineStr"/>
+    </row>
+    <row r="2768">
+      <c r="A2768" t="inlineStr">
+        <is>
+          <t>59b0d0ce-6aec-49d9-b511-b41fbf0f5519</t>
+        </is>
+      </c>
+      <c r="B2768" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2768" t="inlineStr">
+        <is>
+          <t>2026-07-15T21:32:37.928Z</t>
+        </is>
+      </c>
+      <c r="D2768" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2768" t="inlineStr"/>
+    </row>
+    <row r="2769">
+      <c r="A2769" t="inlineStr">
+        <is>
+          <t>0044cfe0-fbdc-423f-a63e-65de6917df54</t>
+        </is>
+      </c>
+      <c r="B2769" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2769" t="inlineStr">
+        <is>
+          <t>2026-07-15T21:42:15.040Z</t>
+        </is>
+      </c>
+      <c r="D2769" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2769" t="inlineStr"/>
+    </row>
+    <row r="2770">
+      <c r="A2770" t="inlineStr">
+        <is>
+          <t>89b5c917-037b-4f32-a1ae-e805f902c473</t>
+        </is>
+      </c>
+      <c r="B2770" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2770" t="inlineStr">
+        <is>
+          <t>2026-07-15T22:49:27.611Z</t>
+        </is>
+      </c>
+      <c r="D2770" t="n">
+        <v>519</v>
+      </c>
+      <c r="E2770" t="inlineStr"/>
+    </row>
+    <row r="2771">
+      <c r="A2771" t="inlineStr">
+        <is>
+          <t>58960b3e-2b35-4fd8-b4ab-4970fdceb929</t>
+        </is>
+      </c>
+      <c r="B2771" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2771" t="inlineStr">
+        <is>
+          <t>2026-07-15T23:01:44.624Z</t>
+        </is>
+      </c>
+      <c r="D2771" t="n">
+        <v>519</v>
+      </c>
+      <c r="E2771" t="inlineStr"/>
+    </row>
+    <row r="2772">
+      <c r="A2772" t="inlineStr">
+        <is>
+          <t>5ebc8682-69f3-426d-83a7-a5ccd029d845</t>
+        </is>
+      </c>
+      <c r="B2772" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2772" t="inlineStr">
+        <is>
+          <t>2026-07-15T23:55:49.704Z</t>
+        </is>
+      </c>
+      <c r="D2772" t="n">
+        <v>563</v>
+      </c>
+      <c r="E2772" t="inlineStr">
+        <is>
+          <t>ycso suspect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2772"/>
+  <dimension ref="A1:E2785"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63056,6 +63056,287 @@
         </is>
       </c>
     </row>
+    <row r="2773">
+      <c r="A2773" t="inlineStr">
+        <is>
+          <t>b9ce6e5a-bef5-42ac-ad36-51f3b1318aea</t>
+        </is>
+      </c>
+      <c r="B2773" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2773" t="inlineStr">
+        <is>
+          <t>2026-07-16T00:04:12.977Z</t>
+        </is>
+      </c>
+      <c r="D2773" t="n">
+        <v>519</v>
+      </c>
+      <c r="E2773" t="inlineStr"/>
+    </row>
+    <row r="2774">
+      <c r="A2774" t="inlineStr">
+        <is>
+          <t>3f0fe339-af20-4fea-802f-88982bc78503</t>
+        </is>
+      </c>
+      <c r="B2774" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2774" t="inlineStr">
+        <is>
+          <t>2026-07-16T02:16:47.877Z</t>
+        </is>
+      </c>
+      <c r="D2774" t="n">
+        <v>563</v>
+      </c>
+      <c r="E2774" t="inlineStr"/>
+    </row>
+    <row r="2775">
+      <c r="A2775" t="inlineStr">
+        <is>
+          <t>db17a726-b24c-4f9a-82aa-b3d71e37fcfb</t>
+        </is>
+      </c>
+      <c r="B2775" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2775" t="inlineStr">
+        <is>
+          <t>2026-07-16T02:53:20.910Z</t>
+        </is>
+      </c>
+      <c r="D2775" t="n">
+        <v>519</v>
+      </c>
+      <c r="E2775" t="inlineStr">
+        <is>
+          <t>Butte CO BOLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2776">
+      <c r="A2776" t="inlineStr">
+        <is>
+          <t>e6fa3248-14b8-4640-a95d-f4b9a2010c45</t>
+        </is>
+      </c>
+      <c r="B2776" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2776" t="inlineStr">
+        <is>
+          <t>2026-07-16T04:02:23.522Z</t>
+        </is>
+      </c>
+      <c r="D2776" t="n">
+        <v>519</v>
+      </c>
+      <c r="E2776" t="inlineStr"/>
+    </row>
+    <row r="2777">
+      <c r="A2777" t="inlineStr">
+        <is>
+          <t>dc783fb1-1415-4e79-b137-7084bec54ba6</t>
+        </is>
+      </c>
+      <c r="B2777" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2777" t="inlineStr">
+        <is>
+          <t>2026-07-16T12:46:01.382Z</t>
+        </is>
+      </c>
+      <c r="D2777" t="n">
+        <v>519</v>
+      </c>
+      <c r="E2777" t="inlineStr"/>
+    </row>
+    <row r="2778">
+      <c r="A2778" t="inlineStr">
+        <is>
+          <t>87d261df-527a-4da9-a9c2-fae5d8349133</t>
+        </is>
+      </c>
+      <c r="B2778" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2778" t="inlineStr">
+        <is>
+          <t>2026-07-16T16:42:35.623Z</t>
+        </is>
+      </c>
+      <c r="D2778" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2778" t="inlineStr"/>
+    </row>
+    <row r="2779">
+      <c r="A2779" t="inlineStr">
+        <is>
+          <t>901000d3-817f-4d0a-af8b-b30833b42b87</t>
+        </is>
+      </c>
+      <c r="B2779" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2779" t="inlineStr">
+        <is>
+          <t>2026-07-16T17:19:43.457Z</t>
+        </is>
+      </c>
+      <c r="D2779" t="n">
+        <v>519</v>
+      </c>
+      <c r="E2779" t="inlineStr"/>
+    </row>
+    <row r="2780">
+      <c r="A2780" t="inlineStr">
+        <is>
+          <t>63e5cd2a-edac-4967-aa80-d77c4f9b6946</t>
+        </is>
+      </c>
+      <c r="B2780" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2780" t="inlineStr">
+        <is>
+          <t>2026-07-16T19:19:38.918Z</t>
+        </is>
+      </c>
+      <c r="D2780" t="n">
+        <v>487</v>
+      </c>
+      <c r="E2780" t="inlineStr"/>
+    </row>
+    <row r="2781">
+      <c r="A2781" t="inlineStr">
+        <is>
+          <t>d3cc4a7a-57e1-40d7-bd25-52016efb7673</t>
+        </is>
+      </c>
+      <c r="B2781" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2781" t="inlineStr">
+        <is>
+          <t>2026-07-16T19:31:58.649Z</t>
+        </is>
+      </c>
+      <c r="D2781" t="n">
+        <v>519</v>
+      </c>
+      <c r="E2781" t="inlineStr"/>
+    </row>
+    <row r="2782">
+      <c r="A2782" t="inlineStr">
+        <is>
+          <t>badcb32d-9294-4604-98a0-3fc3bc7adfa3</t>
+        </is>
+      </c>
+      <c r="B2782" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2782" t="inlineStr">
+        <is>
+          <t>2026-07-16T21:07:28.853Z</t>
+        </is>
+      </c>
+      <c r="D2782" t="n">
+        <v>527</v>
+      </c>
+      <c r="E2782" t="inlineStr">
+        <is>
+          <t>suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2783">
+      <c r="A2783" t="inlineStr">
+        <is>
+          <t>b7d27862-3a45-476b-86ca-aad6c882b3ef</t>
+        </is>
+      </c>
+      <c r="B2783" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2783" t="inlineStr">
+        <is>
+          <t>2026-07-16T21:09:43.695Z</t>
+        </is>
+      </c>
+      <c r="D2783" t="n">
+        <v>519</v>
+      </c>
+      <c r="E2783" t="inlineStr"/>
+    </row>
+    <row r="2784">
+      <c r="A2784" t="inlineStr">
+        <is>
+          <t>b006b48b-a461-4497-9a60-2f73305ada5f</t>
+        </is>
+      </c>
+      <c r="B2784" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2784" t="inlineStr">
+        <is>
+          <t>2026-07-16T22:08:09.260Z</t>
+        </is>
+      </c>
+      <c r="D2784" t="n">
+        <v>519</v>
+      </c>
+      <c r="E2784" t="inlineStr"/>
+    </row>
+    <row r="2785">
+      <c r="A2785" t="inlineStr">
+        <is>
+          <t>9e6c6cfd-e69c-49d9-88b3-f7db42c86706</t>
+        </is>
+      </c>
+      <c r="B2785" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2785" t="inlineStr">
+        <is>
+          <t>2026-07-16T23:30:56.313Z</t>
+        </is>
+      </c>
+      <c r="D2785" t="n">
+        <v>519</v>
+      </c>
+      <c r="E2785" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2785"/>
+  <dimension ref="A1:E2799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63337,6 +63337,320 @@
       </c>
       <c r="E2785" t="inlineStr"/>
     </row>
+    <row r="2786">
+      <c r="A2786" t="inlineStr">
+        <is>
+          <t>06a6d960-dd4d-4ddd-80a6-f67b4f7de4b4</t>
+        </is>
+      </c>
+      <c r="B2786" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2786" t="inlineStr">
+        <is>
+          <t>2026-07-17T00:32:27.893Z</t>
+        </is>
+      </c>
+      <c r="D2786" t="n">
+        <v>519</v>
+      </c>
+      <c r="E2786" t="inlineStr"/>
+    </row>
+    <row r="2787">
+      <c r="A2787" t="inlineStr">
+        <is>
+          <t>e49f75af-df4b-463a-992f-68e7190b709d</t>
+        </is>
+      </c>
+      <c r="B2787" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2787" t="inlineStr">
+        <is>
+          <t>2026-07-17T06:11:44.566Z</t>
+        </is>
+      </c>
+      <c r="D2787" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2787" t="inlineStr"/>
+    </row>
+    <row r="2788">
+      <c r="A2788" t="inlineStr">
+        <is>
+          <t>e811353a-dfc7-433b-84a7-abe064ceb0b4</t>
+        </is>
+      </c>
+      <c r="B2788" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2788" t="inlineStr">
+        <is>
+          <t>2026-07-17T11:04:53.603Z</t>
+        </is>
+      </c>
+      <c r="D2788" t="n">
+        <v>563</v>
+      </c>
+      <c r="E2788" t="inlineStr"/>
+    </row>
+    <row r="2789">
+      <c r="A2789" t="inlineStr">
+        <is>
+          <t>e660c34f-c897-4cc4-b9ca-341244b2c30b</t>
+        </is>
+      </c>
+      <c r="B2789" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2789" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:47:20.731Z</t>
+        </is>
+      </c>
+      <c r="D2789" t="n">
+        <v>563</v>
+      </c>
+      <c r="E2789" t="inlineStr"/>
+    </row>
+    <row r="2790">
+      <c r="A2790" t="inlineStr">
+        <is>
+          <t>579fa153-5b4a-4997-afd5-1c51959f2915</t>
+        </is>
+      </c>
+      <c r="B2790" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2790" t="inlineStr">
+        <is>
+          <t>2026-07-17T16:15:36.078Z</t>
+        </is>
+      </c>
+      <c r="D2790" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2790" t="inlineStr"/>
+    </row>
+    <row r="2791">
+      <c r="A2791" t="inlineStr">
+        <is>
+          <t>f294b7c7-18c8-4c38-a282-cc5fa9735dc4</t>
+        </is>
+      </c>
+      <c r="B2791" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2791" t="inlineStr">
+        <is>
+          <t>2026-07-17T16:25:50.393Z</t>
+        </is>
+      </c>
+      <c r="D2791" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2791" t="inlineStr">
+        <is>
+          <t>drug sales transportation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2792">
+      <c r="A2792" t="inlineStr">
+        <is>
+          <t>f639df70-6ba1-4f61-95a4-a193add288ef</t>
+        </is>
+      </c>
+      <c r="B2792" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2792" t="inlineStr">
+        <is>
+          <t>2026-07-17T16:45:31.324Z</t>
+        </is>
+      </c>
+      <c r="D2792" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2792" t="inlineStr"/>
+    </row>
+    <row r="2793">
+      <c r="A2793" t="inlineStr">
+        <is>
+          <t>bd31c26a-9995-4502-8fd3-b9822256f558</t>
+        </is>
+      </c>
+      <c r="B2793" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2793" t="inlineStr">
+        <is>
+          <t>2026-07-17T17:03:59.055Z</t>
+        </is>
+      </c>
+      <c r="D2793" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2793" t="inlineStr"/>
+    </row>
+    <row r="2794">
+      <c r="A2794" t="inlineStr">
+        <is>
+          <t>87b29e22-3fb4-43c0-bdea-6f99bfa9b889</t>
+        </is>
+      </c>
+      <c r="B2794" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2794" t="inlineStr">
+        <is>
+          <t>2026-07-17T17:38:58.743Z</t>
+        </is>
+      </c>
+      <c r="D2794" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2794" t="inlineStr">
+        <is>
+          <t>drug sales transportation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2795">
+      <c r="A2795" t="inlineStr">
+        <is>
+          <t>b6c46323-a33e-4009-814b-bfa0cc466cdd</t>
+        </is>
+      </c>
+      <c r="B2795" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2795" t="inlineStr">
+        <is>
+          <t>2026-07-17T17:49:52.089Z</t>
+        </is>
+      </c>
+      <c r="D2795" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2795" t="inlineStr">
+        <is>
+          <t>transport narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2796">
+      <c r="A2796" t="inlineStr">
+        <is>
+          <t>db1f4b6e-ccfe-48e6-96bb-b2603a369824</t>
+        </is>
+      </c>
+      <c r="B2796" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2796" t="inlineStr">
+        <is>
+          <t>2026-07-17T19:01:00.355Z</t>
+        </is>
+      </c>
+      <c r="D2796" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2796" t="inlineStr"/>
+    </row>
+    <row r="2797">
+      <c r="A2797" t="inlineStr">
+        <is>
+          <t>b6f288b5-bb75-4e24-aa10-59ccd66fa63f</t>
+        </is>
+      </c>
+      <c r="B2797" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2797" t="inlineStr">
+        <is>
+          <t>2026-07-17T19:25:19.176Z</t>
+        </is>
+      </c>
+      <c r="D2797" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2797" t="inlineStr">
+        <is>
+          <t>211 pc possible suspect vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2798">
+      <c r="A2798" t="inlineStr">
+        <is>
+          <t>2f0f5ba5-5139-4af9-b309-65c53c643e2c</t>
+        </is>
+      </c>
+      <c r="B2798" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2798" t="inlineStr">
+        <is>
+          <t>2026-07-17T20:51:39.563Z</t>
+        </is>
+      </c>
+      <c r="D2798" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2798" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
+      </c>
+    </row>
+    <row r="2799">
+      <c r="A2799" t="inlineStr">
+        <is>
+          <t>03f7b75c-7ac3-4d03-8681-b2d62ad2e52d</t>
+        </is>
+      </c>
+      <c r="B2799" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2799" t="inlineStr">
+        <is>
+          <t>2026-07-17T21:27:04.349Z</t>
+        </is>
+      </c>
+      <c r="D2799" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2799" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2799"/>
+  <dimension ref="A1:E2809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63651,6 +63651,240 @@
       </c>
       <c r="E2799" t="inlineStr"/>
     </row>
+    <row r="2800">
+      <c r="A2800" t="inlineStr">
+        <is>
+          <t>145ab6be-2e0c-4935-ba62-ea946fec2668</t>
+        </is>
+      </c>
+      <c r="B2800" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2800" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:28:21.579Z</t>
+        </is>
+      </c>
+      <c r="D2800" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2800" t="inlineStr">
+        <is>
+          <t>law enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2801">
+      <c r="A2801" t="inlineStr">
+        <is>
+          <t>ae001870-09ae-42ec-87b2-77827f0cbeef</t>
+        </is>
+      </c>
+      <c r="B2801" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2801" t="inlineStr">
+        <is>
+          <t>2026-07-18T01:02:29.319Z</t>
+        </is>
+      </c>
+      <c r="D2801" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2801" t="inlineStr"/>
+    </row>
+    <row r="2802">
+      <c r="A2802" t="inlineStr">
+        <is>
+          <t>53cd9cb9-6c7e-4e2a-ab7a-c6daf10d0770</t>
+        </is>
+      </c>
+      <c r="B2802" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2802" t="inlineStr">
+        <is>
+          <t>2026-07-18T01:30:46.131Z</t>
+        </is>
+      </c>
+      <c r="D2802" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2802" t="inlineStr"/>
+    </row>
+    <row r="2803">
+      <c r="A2803" t="inlineStr">
+        <is>
+          <t>c186aeff-2946-4b6a-aaca-fc349bc96bb1</t>
+        </is>
+      </c>
+      <c r="B2803" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2803" t="inlineStr">
+        <is>
+          <t>2026-07-18T01:33:16.206Z</t>
+        </is>
+      </c>
+      <c r="D2803" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2803" t="inlineStr"/>
+    </row>
+    <row r="2804">
+      <c r="A2804" t="inlineStr">
+        <is>
+          <t>a7bfe6fa-76d1-4607-b72c-9ab0d46f6436</t>
+        </is>
+      </c>
+      <c r="B2804" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2804" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:55:16.565Z</t>
+        </is>
+      </c>
+      <c r="D2804" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2804" t="inlineStr">
+        <is>
+          <t>warrant</t>
+        </is>
+      </c>
+    </row>
+    <row r="2805">
+      <c r="A2805" t="inlineStr">
+        <is>
+          <t>cfc9e9d9-8a9c-4144-a12a-b94e2c66f1a5</t>
+        </is>
+      </c>
+      <c r="B2805" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2805" t="inlineStr">
+        <is>
+          <t>2026-07-18T03:34:54.657Z</t>
+        </is>
+      </c>
+      <c r="D2805" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2805" t="inlineStr">
+        <is>
+          <t>WARRANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2806">
+      <c r="A2806" t="inlineStr">
+        <is>
+          <t>985740c2-839e-4922-be16-51cf6001364d</t>
+        </is>
+      </c>
+      <c r="B2806" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2806" t="inlineStr">
+        <is>
+          <t>2026-07-18T04:52:44.959Z</t>
+        </is>
+      </c>
+      <c r="D2806" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2806" t="inlineStr">
+        <is>
+          <t>Sus loc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2807">
+      <c r="A2807" t="inlineStr">
+        <is>
+          <t>0f2eb0d0-fcfe-42b4-94dc-d6c1d8db12a0</t>
+        </is>
+      </c>
+      <c r="B2807" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2807" t="inlineStr">
+        <is>
+          <t>2026-07-18T09:14:51.446Z</t>
+        </is>
+      </c>
+      <c r="D2807" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2807" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2808">
+      <c r="A2808" t="inlineStr">
+        <is>
+          <t>d8b3964a-25e4-49b1-b434-0eeb8d060846</t>
+        </is>
+      </c>
+      <c r="B2808" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2808" t="inlineStr">
+        <is>
+          <t>2026-07-18T15:46:34.426Z</t>
+        </is>
+      </c>
+      <c r="D2808" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2808" t="inlineStr">
+        <is>
+          <t>Ycso suspect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2809">
+      <c r="A2809" t="inlineStr">
+        <is>
+          <t>6f8d5c54-c501-4459-8eb9-23fa3d4dc69a</t>
+        </is>
+      </c>
+      <c r="B2809" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2809" t="inlineStr">
+        <is>
+          <t>2026-07-18T15:48:51.500Z</t>
+        </is>
+      </c>
+      <c r="D2809" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2809" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2809"/>
+  <dimension ref="A1:E2813"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63885,6 +63885,98 @@
       </c>
       <c r="E2809" t="inlineStr"/>
     </row>
+    <row r="2810">
+      <c r="A2810" t="inlineStr">
+        <is>
+          <t>2150d9f1-859a-4f5e-9fbd-8e4a5e0cc172</t>
+        </is>
+      </c>
+      <c r="B2810" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2810" t="inlineStr">
+        <is>
+          <t>2026-07-19T12:55:42.140Z</t>
+        </is>
+      </c>
+      <c r="D2810" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2810" t="inlineStr"/>
+    </row>
+    <row r="2811">
+      <c r="A2811" t="inlineStr">
+        <is>
+          <t>5c3911bb-6166-450d-97a5-f1eb4843f58f</t>
+        </is>
+      </c>
+      <c r="B2811" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2811" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:20:43.105Z</t>
+        </is>
+      </c>
+      <c r="D2811" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2811" t="inlineStr"/>
+    </row>
+    <row r="2812">
+      <c r="A2812" t="inlineStr">
+        <is>
+          <t>d46c34df-914d-4271-8336-f6968f230ec8</t>
+        </is>
+      </c>
+      <c r="B2812" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2812" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:22:52.047Z</t>
+        </is>
+      </c>
+      <c r="D2812" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2812" t="inlineStr">
+        <is>
+          <t>CRIMINAL INVESTIGATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2813">
+      <c r="A2813" t="inlineStr">
+        <is>
+          <t>800114cb-5b4d-4d93-8a87-fd5ccd2077a6</t>
+        </is>
+      </c>
+      <c r="B2813" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2813" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:37:34.999Z</t>
+        </is>
+      </c>
+      <c r="D2813" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2813" t="inlineStr">
+        <is>
+          <t>Suspect vehicle.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2813"/>
+  <dimension ref="A1:E2826"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63977,6 +63977,295 @@
         </is>
       </c>
     </row>
+    <row r="2814">
+      <c r="A2814" t="inlineStr">
+        <is>
+          <t>01b706f1-b182-4d6c-bb51-c7d0b783250a</t>
+        </is>
+      </c>
+      <c r="B2814" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2814" t="inlineStr">
+        <is>
+          <t>2026-07-20T02:36:35.532Z</t>
+        </is>
+      </c>
+      <c r="D2814" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2814" t="inlineStr"/>
+    </row>
+    <row r="2815">
+      <c r="A2815" t="inlineStr">
+        <is>
+          <t>cedd5092-6f97-4400-8dd7-f3aa3ceff1b6</t>
+        </is>
+      </c>
+      <c r="B2815" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2815" t="inlineStr">
+        <is>
+          <t>2026-07-20T02:46:23.630Z</t>
+        </is>
+      </c>
+      <c r="D2815" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2815" t="inlineStr">
+        <is>
+          <t>Locate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2816">
+      <c r="A2816" t="inlineStr">
+        <is>
+          <t>8229d283-28b0-43ae-866a-613e464b14e3</t>
+        </is>
+      </c>
+      <c r="B2816" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2816" t="inlineStr">
+        <is>
+          <t>2026-07-20T03:01:34.713Z</t>
+        </is>
+      </c>
+      <c r="D2816" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2816" t="inlineStr">
+        <is>
+          <t>Locate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2817">
+      <c r="A2817" t="inlineStr">
+        <is>
+          <t>934f956d-8189-4c47-b54f-3565931e46a9</t>
+        </is>
+      </c>
+      <c r="B2817" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2817" t="inlineStr">
+        <is>
+          <t>2026-07-20T03:15:43.123Z</t>
+        </is>
+      </c>
+      <c r="D2817" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2817" t="inlineStr"/>
+    </row>
+    <row r="2818">
+      <c r="A2818" t="inlineStr">
+        <is>
+          <t>05af090d-04e0-474e-a931-d63701239fe7</t>
+        </is>
+      </c>
+      <c r="B2818" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2818" t="inlineStr">
+        <is>
+          <t>2026-07-20T03:49:13.587Z</t>
+        </is>
+      </c>
+      <c r="D2818" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2818" t="inlineStr"/>
+    </row>
+    <row r="2819">
+      <c r="A2819" t="inlineStr">
+        <is>
+          <t>97403c2b-c8ef-453d-9eb1-1bbbe6980fd4</t>
+        </is>
+      </c>
+      <c r="B2819" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2819" t="inlineStr">
+        <is>
+          <t>2026-07-20T04:55:31.879Z</t>
+        </is>
+      </c>
+      <c r="D2819" t="n">
+        <v>486</v>
+      </c>
+      <c r="E2819" t="inlineStr"/>
+    </row>
+    <row r="2820">
+      <c r="A2820" t="inlineStr">
+        <is>
+          <t>cf14cdf8-7f9d-409b-8df6-c036433f62ef</t>
+        </is>
+      </c>
+      <c r="B2820" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2820" t="inlineStr">
+        <is>
+          <t>2026-07-20T05:23:08.278Z</t>
+        </is>
+      </c>
+      <c r="D2820" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2820" t="inlineStr">
+        <is>
+          <t>Locate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2821">
+      <c r="A2821" t="inlineStr">
+        <is>
+          <t>353f877f-46be-402c-acec-2cca8dd7443d</t>
+        </is>
+      </c>
+      <c r="B2821" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2821" t="inlineStr">
+        <is>
+          <t>2026-07-20T07:18:01.716Z</t>
+        </is>
+      </c>
+      <c r="D2821" t="n">
+        <v>486</v>
+      </c>
+      <c r="E2821" t="inlineStr"/>
+    </row>
+    <row r="2822">
+      <c r="A2822" t="inlineStr">
+        <is>
+          <t>93cb0434-2486-443f-984d-c0bb4b1afd13</t>
+        </is>
+      </c>
+      <c r="B2822" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2822" t="inlineStr">
+        <is>
+          <t>2026-07-20T09:07:17.024Z</t>
+        </is>
+      </c>
+      <c r="D2822" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2822" t="inlineStr"/>
+    </row>
+    <row r="2823">
+      <c r="A2823" t="inlineStr">
+        <is>
+          <t>3c711c52-4f47-4ce3-a7d0-c5adeea5f8a9</t>
+        </is>
+      </c>
+      <c r="B2823" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2823" t="inlineStr">
+        <is>
+          <t>2026-07-20T10:05:39.256Z</t>
+        </is>
+      </c>
+      <c r="D2823" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2823" t="inlineStr"/>
+    </row>
+    <row r="2824">
+      <c r="A2824" t="inlineStr">
+        <is>
+          <t>03302487-9d96-4c67-814d-42efe802dc05</t>
+        </is>
+      </c>
+      <c r="B2824" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2824" t="inlineStr">
+        <is>
+          <t>2026-07-20T11:27:59.325Z</t>
+        </is>
+      </c>
+      <c r="D2824" t="n">
+        <v>486</v>
+      </c>
+      <c r="E2824" t="inlineStr"/>
+    </row>
+    <row r="2825">
+      <c r="A2825" t="inlineStr">
+        <is>
+          <t>f395ac5b-cfa3-407d-a502-839e39d7412f</t>
+        </is>
+      </c>
+      <c r="B2825" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2825" t="inlineStr">
+        <is>
+          <t>2026-07-20T11:35:43.858Z</t>
+        </is>
+      </c>
+      <c r="D2825" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2825" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+    </row>
+    <row r="2826">
+      <c r="A2826" t="inlineStr">
+        <is>
+          <t>f9660aee-7563-4fb9-9de5-6c8237eb9e8e</t>
+        </is>
+      </c>
+      <c r="B2826" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2826" t="inlineStr">
+        <is>
+          <t>2026-07-20T21:50:11.061Z</t>
+        </is>
+      </c>
+      <c r="D2826" t="n">
+        <v>526</v>
+      </c>
+      <c r="E2826" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2826"/>
+  <dimension ref="A1:E2841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64266,6 +64266,349 @@
       </c>
       <c r="E2826" t="inlineStr"/>
     </row>
+    <row r="2827">
+      <c r="A2827" t="inlineStr">
+        <is>
+          <t>798dbc50-280c-4141-841f-4ef3494c9071</t>
+        </is>
+      </c>
+      <c r="B2827" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2827" t="inlineStr">
+        <is>
+          <t>2026-07-21T04:26:28.286Z</t>
+        </is>
+      </c>
+      <c r="D2827" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2827" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+    </row>
+    <row r="2828">
+      <c r="A2828" t="inlineStr">
+        <is>
+          <t>5e18e865-7380-47dc-9476-b9f81f8054dc</t>
+        </is>
+      </c>
+      <c r="B2828" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2828" t="inlineStr">
+        <is>
+          <t>2026-07-21T04:30:20.718Z</t>
+        </is>
+      </c>
+      <c r="D2828" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2828" t="inlineStr"/>
+    </row>
+    <row r="2829">
+      <c r="A2829" t="inlineStr">
+        <is>
+          <t>76ef7d15-ed44-4359-ba64-86d961363b78</t>
+        </is>
+      </c>
+      <c r="B2829" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2829" t="inlineStr">
+        <is>
+          <t>2026-07-21T05:03:11.802Z</t>
+        </is>
+      </c>
+      <c r="D2829" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2829" t="inlineStr"/>
+    </row>
+    <row r="2830">
+      <c r="A2830" t="inlineStr">
+        <is>
+          <t>ab0f5dc7-d331-4106-b278-77b9c389b242</t>
+        </is>
+      </c>
+      <c r="B2830" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2830" t="inlineStr">
+        <is>
+          <t>2026-07-21T05:16:52.949Z</t>
+        </is>
+      </c>
+      <c r="D2830" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2830" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+    </row>
+    <row r="2831">
+      <c r="A2831" t="inlineStr">
+        <is>
+          <t>52dce6db-6c32-4178-9330-e8d29447c7dc</t>
+        </is>
+      </c>
+      <c r="B2831" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2831" t="inlineStr">
+        <is>
+          <t>2026-07-21T06:26:54.003Z</t>
+        </is>
+      </c>
+      <c r="D2831" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2831" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+    </row>
+    <row r="2832">
+      <c r="A2832" t="inlineStr">
+        <is>
+          <t>0a2e81f7-ca8e-4720-a35e-7aa73ace88e1</t>
+        </is>
+      </c>
+      <c r="B2832" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2832" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:31:57.338Z</t>
+        </is>
+      </c>
+      <c r="D2832" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2832" t="inlineStr">
+        <is>
+          <t>suspicious vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2833">
+      <c r="A2833" t="inlineStr">
+        <is>
+          <t>ea7a019d-7444-440a-ab42-1e6e54cdcb96</t>
+        </is>
+      </c>
+      <c r="B2833" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2833" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:33:36.297Z</t>
+        </is>
+      </c>
+      <c r="D2833" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2833" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+    </row>
+    <row r="2834">
+      <c r="A2834" t="inlineStr">
+        <is>
+          <t>6e2d1987-b6fd-44fe-bb13-b225b58841ab</t>
+        </is>
+      </c>
+      <c r="B2834" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2834" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:55:06.600Z</t>
+        </is>
+      </c>
+      <c r="D2834" t="n">
+        <v>486</v>
+      </c>
+      <c r="E2834" t="inlineStr"/>
+    </row>
+    <row r="2835">
+      <c r="A2835" t="inlineStr">
+        <is>
+          <t>b673c313-121e-4a3a-9d16-0161245c4302</t>
+        </is>
+      </c>
+      <c r="B2835" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2835" t="inlineStr">
+        <is>
+          <t>2026-07-21T10:06:54.285Z</t>
+        </is>
+      </c>
+      <c r="D2835" t="n">
+        <v>517</v>
+      </c>
+      <c r="E2835" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+    </row>
+    <row r="2836">
+      <c r="A2836" t="inlineStr">
+        <is>
+          <t>f93709e4-e7ef-4810-9662-7a6bc27853a6</t>
+        </is>
+      </c>
+      <c r="B2836" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2836" t="inlineStr">
+        <is>
+          <t>2026-07-21T14:43:13.339Z</t>
+        </is>
+      </c>
+      <c r="D2836" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2836" t="inlineStr"/>
+    </row>
+    <row r="2837">
+      <c r="A2837" t="inlineStr">
+        <is>
+          <t>1a53d4a0-bc5e-46f7-bc13-bfe72ca8bab4</t>
+        </is>
+      </c>
+      <c r="B2837" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2837" t="inlineStr">
+        <is>
+          <t>2026-07-21T20:04:57.412Z</t>
+        </is>
+      </c>
+      <c r="D2837" t="n">
+        <v>561</v>
+      </c>
+      <c r="E2837" t="inlineStr"/>
+    </row>
+    <row r="2838">
+      <c r="A2838" t="inlineStr">
+        <is>
+          <t>5072ca82-74e2-48dd-99c1-989890f24b1b</t>
+        </is>
+      </c>
+      <c r="B2838" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2838" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:05:57.125Z</t>
+        </is>
+      </c>
+      <c r="D2838" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2838" t="inlineStr"/>
+    </row>
+    <row r="2839">
+      <c r="A2839" t="inlineStr">
+        <is>
+          <t>04a3856b-3e2f-4de1-be4f-118ed11c37e5</t>
+        </is>
+      </c>
+      <c r="B2839" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2839" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:51:11.951Z</t>
+        </is>
+      </c>
+      <c r="D2839" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2839" t="inlineStr"/>
+    </row>
+    <row r="2840">
+      <c r="A2840" t="inlineStr">
+        <is>
+          <t>4f1096d4-9fdb-493f-b30e-7380a94f2077</t>
+        </is>
+      </c>
+      <c r="B2840" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2840" t="inlineStr">
+        <is>
+          <t>2026-07-21T22:15:58.125Z</t>
+        </is>
+      </c>
+      <c r="D2840" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2840" t="inlineStr"/>
+    </row>
+    <row r="2841">
+      <c r="A2841" t="inlineStr">
+        <is>
+          <t>aecdde89-28aa-4769-9bdb-0869107a2117</t>
+        </is>
+      </c>
+      <c r="B2841" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2841" t="inlineStr">
+        <is>
+          <t>2026-07-21T23:43:01.813Z</t>
+        </is>
+      </c>
+      <c r="D2841" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2841" t="inlineStr">
+        <is>
+          <t>trespass suspect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2841"/>
+  <dimension ref="A1:E2869"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64609,6 +64609,638 @@
         </is>
       </c>
     </row>
+    <row r="2842">
+      <c r="A2842" t="inlineStr">
+        <is>
+          <t>1a1a2fb5-1ba2-4d00-97e1-8b364b4e4747</t>
+        </is>
+      </c>
+      <c r="B2842" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2842" t="inlineStr">
+        <is>
+          <t>2026-07-22T01:55:16.726Z</t>
+        </is>
+      </c>
+      <c r="D2842" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2842" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+    </row>
+    <row r="2843">
+      <c r="A2843" t="inlineStr">
+        <is>
+          <t>9c22fa74-be40-46c7-8200-95c5b36cbf80</t>
+        </is>
+      </c>
+      <c r="B2843" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2843" t="inlineStr">
+        <is>
+          <t>2026-07-22T03:15:04.010Z</t>
+        </is>
+      </c>
+      <c r="D2843" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2843" t="inlineStr"/>
+    </row>
+    <row r="2844">
+      <c r="A2844" t="inlineStr">
+        <is>
+          <t>e26ff04d-a5d3-4761-8e72-1a6644b58724</t>
+        </is>
+      </c>
+      <c r="B2844" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2844" t="inlineStr">
+        <is>
+          <t>2026-07-22T04:06:00.578Z</t>
+        </is>
+      </c>
+      <c r="D2844" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2844" t="inlineStr">
+        <is>
+          <t>susp veh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2845">
+      <c r="A2845" t="inlineStr">
+        <is>
+          <t>0e5bef76-51c7-4af2-862d-5c4d7cb8162f</t>
+        </is>
+      </c>
+      <c r="B2845" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2845" t="inlineStr">
+        <is>
+          <t>2026-07-22T04:14:37.105Z</t>
+        </is>
+      </c>
+      <c r="D2845" t="n">
+        <v>485</v>
+      </c>
+      <c r="E2845" t="inlineStr"/>
+    </row>
+    <row r="2846">
+      <c r="A2846" t="inlineStr">
+        <is>
+          <t>5adad66b-928b-4988-905b-0355e50f1329</t>
+        </is>
+      </c>
+      <c r="B2846" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2846" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:02:36.982Z</t>
+        </is>
+      </c>
+      <c r="D2846" t="n">
+        <v>560</v>
+      </c>
+      <c r="E2846" t="inlineStr"/>
+    </row>
+    <row r="2847">
+      <c r="A2847" t="inlineStr">
+        <is>
+          <t>0582db45-8a0c-44e9-bf41-50c82a986f5a</t>
+        </is>
+      </c>
+      <c r="B2847" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2847" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:04:40.635Z</t>
+        </is>
+      </c>
+      <c r="D2847" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2847" t="inlineStr">
+        <is>
+          <t>susp veh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2848">
+      <c r="A2848" t="inlineStr">
+        <is>
+          <t>e87c3075-d8ca-4309-ab00-1cda82b570a3</t>
+        </is>
+      </c>
+      <c r="B2848" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2848" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:05:12.313Z</t>
+        </is>
+      </c>
+      <c r="D2848" t="n">
+        <v>485</v>
+      </c>
+      <c r="E2848" t="inlineStr"/>
+    </row>
+    <row r="2849">
+      <c r="A2849" t="inlineStr">
+        <is>
+          <t>33454718-da54-4a58-b0cb-bcb36f93a8ba</t>
+        </is>
+      </c>
+      <c r="B2849" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2849" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:06:04.450Z</t>
+        </is>
+      </c>
+      <c r="D2849" t="n">
+        <v>560</v>
+      </c>
+      <c r="E2849" t="inlineStr"/>
+    </row>
+    <row r="2850">
+      <c r="A2850" t="inlineStr">
+        <is>
+          <t>965381c2-1a0e-49d4-bcda-d1af70ebb77b</t>
+        </is>
+      </c>
+      <c r="B2850" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2850" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:10:55.240Z</t>
+        </is>
+      </c>
+      <c r="D2850" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2850" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+    </row>
+    <row r="2851">
+      <c r="A2851" t="inlineStr">
+        <is>
+          <t>0f8d201d-6d2b-4134-abd6-7c4669868a60</t>
+        </is>
+      </c>
+      <c r="B2851" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2851" t="inlineStr">
+        <is>
+          <t>2026-07-22T06:08:20.002Z</t>
+        </is>
+      </c>
+      <c r="D2851" t="n">
+        <v>485</v>
+      </c>
+      <c r="E2851" t="inlineStr"/>
+    </row>
+    <row r="2852">
+      <c r="A2852" t="inlineStr">
+        <is>
+          <t>87b2ae22-38c5-4019-87b8-cbf0ee34dee5</t>
+        </is>
+      </c>
+      <c r="B2852" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2852" t="inlineStr">
+        <is>
+          <t>2026-07-22T06:53:24.827Z</t>
+        </is>
+      </c>
+      <c r="D2852" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2852" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+    </row>
+    <row r="2853">
+      <c r="A2853" t="inlineStr">
+        <is>
+          <t>ca1fdd09-2584-4c89-b075-bc6d5ed6205c</t>
+        </is>
+      </c>
+      <c r="B2853" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2853" t="inlineStr">
+        <is>
+          <t>2026-07-22T07:05:03.616Z</t>
+        </is>
+      </c>
+      <c r="D2853" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2853" t="inlineStr"/>
+    </row>
+    <row r="2854">
+      <c r="A2854" t="inlineStr">
+        <is>
+          <t>44e54101-513e-432c-8335-b98623786035</t>
+        </is>
+      </c>
+      <c r="B2854" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2854" t="inlineStr">
+        <is>
+          <t>2026-07-22T08:01:58.209Z</t>
+        </is>
+      </c>
+      <c r="D2854" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2854" t="inlineStr"/>
+    </row>
+    <row r="2855">
+      <c r="A2855" t="inlineStr">
+        <is>
+          <t>5bde6d4f-4a4e-4ac8-89c1-ce9184beb820</t>
+        </is>
+      </c>
+      <c r="B2855" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2855" t="inlineStr">
+        <is>
+          <t>2026-07-22T08:10:22.571Z</t>
+        </is>
+      </c>
+      <c r="D2855" t="n">
+        <v>560</v>
+      </c>
+      <c r="E2855" t="inlineStr"/>
+    </row>
+    <row r="2856">
+      <c r="A2856" t="inlineStr">
+        <is>
+          <t>73c7007f-ed37-446d-ae9d-175725795a19</t>
+        </is>
+      </c>
+      <c r="B2856" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2856" t="inlineStr">
+        <is>
+          <t>2026-07-22T09:25:17.138Z</t>
+        </is>
+      </c>
+      <c r="D2856" t="n">
+        <v>485</v>
+      </c>
+      <c r="E2856" t="inlineStr"/>
+    </row>
+    <row r="2857">
+      <c r="A2857" t="inlineStr">
+        <is>
+          <t>46a2c185-f08e-42cb-93b9-d948617a2bf2</t>
+        </is>
+      </c>
+      <c r="B2857" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2857" t="inlineStr">
+        <is>
+          <t>2026-07-22T10:00:14.181Z</t>
+        </is>
+      </c>
+      <c r="D2857" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2857" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+    </row>
+    <row r="2858">
+      <c r="A2858" t="inlineStr">
+        <is>
+          <t>690f8568-a38d-410d-9982-34f056aa2ce0</t>
+        </is>
+      </c>
+      <c r="B2858" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2858" t="inlineStr">
+        <is>
+          <t>2026-07-22T10:04:52.634Z</t>
+        </is>
+      </c>
+      <c r="D2858" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2858" t="inlineStr"/>
+    </row>
+    <row r="2859">
+      <c r="A2859" t="inlineStr">
+        <is>
+          <t>0d93cbb8-4609-4418-9c87-81e92875c0a5</t>
+        </is>
+      </c>
+      <c r="B2859" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2859" t="inlineStr">
+        <is>
+          <t>2026-07-22T11:38:18.690Z</t>
+        </is>
+      </c>
+      <c r="D2859" t="n">
+        <v>485</v>
+      </c>
+      <c r="E2859" t="inlineStr"/>
+    </row>
+    <row r="2860">
+      <c r="A2860" t="inlineStr">
+        <is>
+          <t>7afb8bf7-883b-4fef-974f-cca1918a2417</t>
+        </is>
+      </c>
+      <c r="B2860" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2860" t="inlineStr">
+        <is>
+          <t>2026-07-22T15:50:56.765Z</t>
+        </is>
+      </c>
+      <c r="D2860" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2860" t="inlineStr"/>
+    </row>
+    <row r="2861">
+      <c r="A2861" t="inlineStr">
+        <is>
+          <t>0de969e5-61f4-4c51-b81b-0252d0ef6361</t>
+        </is>
+      </c>
+      <c r="B2861" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2861" t="inlineStr">
+        <is>
+          <t>2026-07-22T16:01:21.925Z</t>
+        </is>
+      </c>
+      <c r="D2861" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2861" t="inlineStr"/>
+    </row>
+    <row r="2862">
+      <c r="A2862" t="inlineStr">
+        <is>
+          <t>53186ea6-568b-4435-a1f6-56946f71060d</t>
+        </is>
+      </c>
+      <c r="B2862" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2862" t="inlineStr">
+        <is>
+          <t>2026-07-22T18:01:11.540Z</t>
+        </is>
+      </c>
+      <c r="D2862" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2862" t="inlineStr"/>
+    </row>
+    <row r="2863">
+      <c r="A2863" t="inlineStr">
+        <is>
+          <t>83259b64-c6c5-46c0-b89a-3a39b2207b07</t>
+        </is>
+      </c>
+      <c r="B2863" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2863" t="inlineStr">
+        <is>
+          <t>2026-07-22T18:39:14.506Z</t>
+        </is>
+      </c>
+      <c r="D2863" t="n">
+        <v>560</v>
+      </c>
+      <c r="E2863" t="inlineStr">
+        <is>
+          <t>Track veh-op</t>
+        </is>
+      </c>
+    </row>
+    <row r="2864">
+      <c r="A2864" t="inlineStr">
+        <is>
+          <t>77bd556e-8589-4a8a-b5e8-58f166c39219</t>
+        </is>
+      </c>
+      <c r="B2864" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2864" t="inlineStr">
+        <is>
+          <t>2026-07-22T19:23:56.662Z</t>
+        </is>
+      </c>
+      <c r="D2864" t="n">
+        <v>525</v>
+      </c>
+      <c r="E2864" t="inlineStr">
+        <is>
+          <t>Sex predator op</t>
+        </is>
+      </c>
+    </row>
+    <row r="2865">
+      <c r="A2865" t="inlineStr">
+        <is>
+          <t>35692ef0-97c3-42b0-9a1a-66da7184b454</t>
+        </is>
+      </c>
+      <c r="B2865" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2865" t="inlineStr">
+        <is>
+          <t>2026-07-22T19:36:14.260Z</t>
+        </is>
+      </c>
+      <c r="D2865" t="n">
+        <v>560</v>
+      </c>
+      <c r="E2865" t="inlineStr"/>
+    </row>
+    <row r="2866">
+      <c r="A2866" t="inlineStr">
+        <is>
+          <t>194ca86c-fa23-4502-8bbc-d10005e99253</t>
+        </is>
+      </c>
+      <c r="B2866" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2866" t="inlineStr">
+        <is>
+          <t>2026-07-22T20:33:08.021Z</t>
+        </is>
+      </c>
+      <c r="D2866" t="n">
+        <v>560</v>
+      </c>
+      <c r="E2866" t="inlineStr">
+        <is>
+          <t>Track veh-op</t>
+        </is>
+      </c>
+    </row>
+    <row r="2867">
+      <c r="A2867" t="inlineStr">
+        <is>
+          <t>fb8fb945-6aff-47e8-ab29-fea7b4904d6e</t>
+        </is>
+      </c>
+      <c r="B2867" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2867" t="inlineStr">
+        <is>
+          <t>2026-07-22T21:15:25.676Z</t>
+        </is>
+      </c>
+      <c r="D2867" t="n">
+        <v>560</v>
+      </c>
+      <c r="E2867" t="inlineStr">
+        <is>
+          <t>suspect id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2868">
+      <c r="A2868" t="inlineStr">
+        <is>
+          <t>e1a99486-4eb9-43e8-9d28-565f12ad903e</t>
+        </is>
+      </c>
+      <c r="B2868" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2868" t="inlineStr">
+        <is>
+          <t>2026-07-22T23:40:11.726Z</t>
+        </is>
+      </c>
+      <c r="D2868" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2868" t="inlineStr">
+        <is>
+          <t>Chat Op</t>
+        </is>
+      </c>
+    </row>
+    <row r="2869">
+      <c r="A2869" t="inlineStr">
+        <is>
+          <t>f09a6e42-8dde-4b83-aa7d-a12aedd906e1</t>
+        </is>
+      </c>
+      <c r="B2869" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2869" t="inlineStr">
+        <is>
+          <t>2026-07-22T23:52:42.223Z</t>
+        </is>
+      </c>
+      <c r="D2869" t="n">
+        <v>485</v>
+      </c>
+      <c r="E2869" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2869"/>
+  <dimension ref="A1:E2884"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65241,6 +65241,321 @@
       </c>
       <c r="E2869" t="inlineStr"/>
     </row>
+    <row r="2870">
+      <c r="A2870" t="inlineStr">
+        <is>
+          <t>9b905c42-873c-45b6-a8db-f7597a37c1e4</t>
+        </is>
+      </c>
+      <c r="B2870" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2870" t="inlineStr">
+        <is>
+          <t>2026-07-23T06:10:42.886Z</t>
+        </is>
+      </c>
+      <c r="D2870" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2870" t="inlineStr"/>
+    </row>
+    <row r="2871">
+      <c r="A2871" t="inlineStr">
+        <is>
+          <t>e46bee55-6cd8-4d83-8932-4c22df79883c</t>
+        </is>
+      </c>
+      <c r="B2871" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2871" t="inlineStr">
+        <is>
+          <t>2026-07-23T15:39:33.861Z</t>
+        </is>
+      </c>
+      <c r="D2871" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2871" t="inlineStr"/>
+    </row>
+    <row r="2872">
+      <c r="A2872" t="inlineStr">
+        <is>
+          <t>3e47f9a4-22df-4da6-9fc1-6f7f3da522f7</t>
+        </is>
+      </c>
+      <c r="B2872" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2872" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:27:24.550Z</t>
+        </is>
+      </c>
+      <c r="D2872" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2872" t="inlineStr"/>
+    </row>
+    <row r="2873">
+      <c r="A2873" t="inlineStr">
+        <is>
+          <t>65c666d7-484b-4975-aa2a-7e4a5eb78568</t>
+        </is>
+      </c>
+      <c r="B2873" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2873" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:48:03.200Z</t>
+        </is>
+      </c>
+      <c r="D2873" t="n">
+        <v>485</v>
+      </c>
+      <c r="E2873" t="inlineStr"/>
+    </row>
+    <row r="2874">
+      <c r="A2874" t="inlineStr">
+        <is>
+          <t>a4992136-1889-4a07-888f-d7ca7a377d76</t>
+        </is>
+      </c>
+      <c r="B2874" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2874" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:49:56.715Z</t>
+        </is>
+      </c>
+      <c r="D2874" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2874" t="inlineStr"/>
+    </row>
+    <row r="2875">
+      <c r="A2875" t="inlineStr">
+        <is>
+          <t>a24140d7-53b1-418e-aa73-2c3d8156bceb</t>
+        </is>
+      </c>
+      <c r="B2875" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2875" t="inlineStr">
+        <is>
+          <t>2026-07-23T17:02:55.396Z</t>
+        </is>
+      </c>
+      <c r="D2875" t="n">
+        <v>560</v>
+      </c>
+      <c r="E2875" t="inlineStr"/>
+    </row>
+    <row r="2876">
+      <c r="A2876" t="inlineStr">
+        <is>
+          <t>44827467-eeb9-456b-82de-082c41e8219b</t>
+        </is>
+      </c>
+      <c r="B2876" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2876" t="inlineStr">
+        <is>
+          <t>2026-07-23T17:11:23.204Z</t>
+        </is>
+      </c>
+      <c r="D2876" t="n">
+        <v>485</v>
+      </c>
+      <c r="E2876" t="inlineStr"/>
+    </row>
+    <row r="2877">
+      <c r="A2877" t="inlineStr">
+        <is>
+          <t>80f859c7-24bc-4481-913b-ec37355fba02</t>
+        </is>
+      </c>
+      <c r="B2877" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2877" t="inlineStr">
+        <is>
+          <t>2026-07-23T17:20:46.624Z</t>
+        </is>
+      </c>
+      <c r="D2877" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2877" t="inlineStr"/>
+    </row>
+    <row r="2878">
+      <c r="A2878" t="inlineStr">
+        <is>
+          <t>018568e1-527f-4be8-9b7c-76aa164ccc15</t>
+        </is>
+      </c>
+      <c r="B2878" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2878" t="inlineStr">
+        <is>
+          <t>2026-07-23T18:02:21.385Z</t>
+        </is>
+      </c>
+      <c r="D2878" t="n">
+        <v>560</v>
+      </c>
+      <c r="E2878" t="inlineStr"/>
+    </row>
+    <row r="2879">
+      <c r="A2879" t="inlineStr">
+        <is>
+          <t>859acd27-7d57-48e5-aa51-a9344605c8c8</t>
+        </is>
+      </c>
+      <c r="B2879" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2879" t="inlineStr">
+        <is>
+          <t>2026-07-23T19:28:37.981Z</t>
+        </is>
+      </c>
+      <c r="D2879" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2879" t="inlineStr"/>
+    </row>
+    <row r="2880">
+      <c r="A2880" t="inlineStr">
+        <is>
+          <t>97fbcb9f-1c94-4d0a-8521-d87f63d2a61c</t>
+        </is>
+      </c>
+      <c r="B2880" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2880" t="inlineStr">
+        <is>
+          <t>2026-07-23T19:28:45.962Z</t>
+        </is>
+      </c>
+      <c r="D2880" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2880" t="inlineStr"/>
+    </row>
+    <row r="2881">
+      <c r="A2881" t="inlineStr">
+        <is>
+          <t>1cdedc2b-3978-4604-904c-acf372bc4bc9</t>
+        </is>
+      </c>
+      <c r="B2881" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2881" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:38:39.782Z</t>
+        </is>
+      </c>
+      <c r="D2881" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2881" t="inlineStr"/>
+    </row>
+    <row r="2882">
+      <c r="A2882" t="inlineStr">
+        <is>
+          <t>7c9fa46f-6db6-4fe5-a9f0-18e67a4e3249</t>
+        </is>
+      </c>
+      <c r="B2882" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2882" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:43:47.202Z</t>
+        </is>
+      </c>
+      <c r="D2882" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2882" t="inlineStr"/>
+    </row>
+    <row r="2883">
+      <c r="A2883" t="inlineStr">
+        <is>
+          <t>e79c82bc-0638-44b3-a0c4-3e8753737c15</t>
+        </is>
+      </c>
+      <c r="B2883" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2883" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:44:53.360Z</t>
+        </is>
+      </c>
+      <c r="D2883" t="n">
+        <v>485</v>
+      </c>
+      <c r="E2883" t="inlineStr"/>
+    </row>
+    <row r="2884">
+      <c r="A2884" t="inlineStr">
+        <is>
+          <t>fab25da3-b6f1-4de9-b69a-cf3b8f78f060</t>
+        </is>
+      </c>
+      <c r="B2884" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2884" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:14:13.289Z</t>
+        </is>
+      </c>
+      <c r="D2884" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2884" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2884"/>
+  <dimension ref="A1:E2910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65556,6 +65556,588 @@
       </c>
       <c r="E2884" t="inlineStr"/>
     </row>
+    <row r="2885">
+      <c r="A2885" t="inlineStr">
+        <is>
+          <t>c775d9cb-8050-412f-b6d7-0d80e4731402</t>
+        </is>
+      </c>
+      <c r="B2885" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2885" t="inlineStr">
+        <is>
+          <t>2026-07-24T00:17:32.324Z</t>
+        </is>
+      </c>
+      <c r="D2885" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2885" t="inlineStr">
+        <is>
+          <t>Suspect location</t>
+        </is>
+      </c>
+    </row>
+    <row r="2886">
+      <c r="A2886" t="inlineStr">
+        <is>
+          <t>3fc1caaf-724c-4a65-bd2b-37410a10f15d</t>
+        </is>
+      </c>
+      <c r="B2886" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2886" t="inlineStr">
+        <is>
+          <t>2026-07-24T01:22:11.896Z</t>
+        </is>
+      </c>
+      <c r="D2886" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2886" t="inlineStr"/>
+    </row>
+    <row r="2887">
+      <c r="A2887" t="inlineStr">
+        <is>
+          <t>c7e0bf26-c74a-4081-af95-768f6b645dca</t>
+        </is>
+      </c>
+      <c r="B2887" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2887" t="inlineStr">
+        <is>
+          <t>2026-07-24T03:19:40.449Z</t>
+        </is>
+      </c>
+      <c r="D2887" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2887" t="inlineStr"/>
+    </row>
+    <row r="2888">
+      <c r="A2888" t="inlineStr">
+        <is>
+          <t>7885d499-55ab-490a-a049-b98c1136d37b</t>
+        </is>
+      </c>
+      <c r="B2888" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2888" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:22:27.585Z</t>
+        </is>
+      </c>
+      <c r="D2888" t="n">
+        <v>516</v>
+      </c>
+      <c r="E2888" t="inlineStr"/>
+    </row>
+    <row r="2889">
+      <c r="A2889" t="inlineStr">
+        <is>
+          <t>1b0f737c-5f4e-4909-be8c-d13f72c4b6f0</t>
+        </is>
+      </c>
+      <c r="B2889" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2889" t="inlineStr">
+        <is>
+          <t>2026-07-24T17:48:18.587Z</t>
+        </is>
+      </c>
+      <c r="D2889" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2889" t="inlineStr"/>
+    </row>
+    <row r="2890">
+      <c r="A2890" t="inlineStr">
+        <is>
+          <t>bd3ab362-1e3f-4393-bed4-59df0febbfe9</t>
+        </is>
+      </c>
+      <c r="B2890" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2890" t="inlineStr">
+        <is>
+          <t>2026-07-24T18:24:25.994Z</t>
+        </is>
+      </c>
+      <c r="D2890" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2890" t="inlineStr"/>
+    </row>
+    <row r="2891">
+      <c r="A2891" t="inlineStr">
+        <is>
+          <t>40b3e3ae-2d54-4dfe-9461-93e556a175b7</t>
+        </is>
+      </c>
+      <c r="B2891" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2891" t="inlineStr">
+        <is>
+          <t>2026-07-24T21:05:55.606Z</t>
+        </is>
+      </c>
+      <c r="D2891" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2891" t="inlineStr"/>
+    </row>
+    <row r="2892">
+      <c r="A2892" t="inlineStr">
+        <is>
+          <t>d67bd473-e235-44ae-b06e-366bda0670d8</t>
+        </is>
+      </c>
+      <c r="B2892" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2892" t="inlineStr">
+        <is>
+          <t>2026-07-24T21:47:05.111Z</t>
+        </is>
+      </c>
+      <c r="D2892" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2892" t="inlineStr">
+        <is>
+          <t>TRASH DUMPING SUSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2893">
+      <c r="A2893" t="inlineStr">
+        <is>
+          <t>d4aa33e6-003a-4293-b8f2-cbda763dbd20</t>
+        </is>
+      </c>
+      <c r="B2893" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2893" t="inlineStr">
+        <is>
+          <t>2026-07-24T21:47:45.476Z</t>
+        </is>
+      </c>
+      <c r="D2893" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2893" t="inlineStr"/>
+    </row>
+    <row r="2894">
+      <c r="A2894" t="inlineStr">
+        <is>
+          <t>372a3fa2-5c0b-465e-99b6-c26b43f5e129</t>
+        </is>
+      </c>
+      <c r="B2894" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2894" t="inlineStr">
+        <is>
+          <t>2026-07-24T21:50:19.123Z</t>
+        </is>
+      </c>
+      <c r="D2894" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2894" t="inlineStr">
+        <is>
+          <t>TRASH DUMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2895">
+      <c r="A2895" t="inlineStr">
+        <is>
+          <t>9233b1e3-b7c3-4283-bd77-b40860b52c86</t>
+        </is>
+      </c>
+      <c r="B2895" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2895" t="inlineStr">
+        <is>
+          <t>2026-07-24T22:07:49.978Z</t>
+        </is>
+      </c>
+      <c r="D2895" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2895" t="inlineStr"/>
+    </row>
+    <row r="2896">
+      <c r="A2896" t="inlineStr">
+        <is>
+          <t>6e8986be-65e8-4efd-91c2-be22d7776b56</t>
+        </is>
+      </c>
+      <c r="B2896" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2896" t="inlineStr">
+        <is>
+          <t>2026-07-24T22:15:44.991Z</t>
+        </is>
+      </c>
+      <c r="D2896" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2896" t="inlineStr"/>
+    </row>
+    <row r="2897">
+      <c r="A2897" t="inlineStr">
+        <is>
+          <t>fad23596-8117-4d1f-9db8-17e850e473e9</t>
+        </is>
+      </c>
+      <c r="B2897" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2897" t="inlineStr">
+        <is>
+          <t>2026-07-24T22:17:45.955Z</t>
+        </is>
+      </c>
+      <c r="D2897" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2897" t="inlineStr"/>
+    </row>
+    <row r="2898">
+      <c r="A2898" t="inlineStr">
+        <is>
+          <t>18cf9418-215d-44b9-99c0-c356cf34cb18</t>
+        </is>
+      </c>
+      <c r="B2898" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2898" t="inlineStr">
+        <is>
+          <t>2026-07-24T22:19:39.375Z</t>
+        </is>
+      </c>
+      <c r="D2898" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2898" t="inlineStr"/>
+    </row>
+    <row r="2899">
+      <c r="A2899" t="inlineStr">
+        <is>
+          <t>372f1875-682b-4b64-b2c0-14537a4b42c1</t>
+        </is>
+      </c>
+      <c r="B2899" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2899" t="inlineStr">
+        <is>
+          <t>2026-07-24T22:35:56.740Z</t>
+        </is>
+      </c>
+      <c r="D2899" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2899" t="inlineStr">
+        <is>
+          <t>sus</t>
+        </is>
+      </c>
+    </row>
+    <row r="2900">
+      <c r="A2900" t="inlineStr">
+        <is>
+          <t>8ecd5859-1c2f-4476-87ef-66de03e11101</t>
+        </is>
+      </c>
+      <c r="B2900" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2900" t="inlineStr">
+        <is>
+          <t>2026-07-24T22:47:37.417Z</t>
+        </is>
+      </c>
+      <c r="D2900" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2900" t="inlineStr">
+        <is>
+          <t>Missing juvenile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2901">
+      <c r="A2901" t="inlineStr">
+        <is>
+          <t>3ffcab10-7078-467a-90e7-3626018086ae</t>
+        </is>
+      </c>
+      <c r="B2901" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2901" t="inlineStr">
+        <is>
+          <t>2026-07-24T22:55:34.791Z</t>
+        </is>
+      </c>
+      <c r="D2901" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2901" t="inlineStr">
+        <is>
+          <t>law enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2902">
+      <c r="A2902" t="inlineStr">
+        <is>
+          <t>c2ee8077-89b8-4a28-b987-3c97892aa6d1</t>
+        </is>
+      </c>
+      <c r="B2902" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2902" t="inlineStr">
+        <is>
+          <t>2026-07-24T22:59:35.426Z</t>
+        </is>
+      </c>
+      <c r="D2902" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2902" t="inlineStr"/>
+    </row>
+    <row r="2903">
+      <c r="A2903" t="inlineStr">
+        <is>
+          <t>5826f045-4570-4284-9ffd-01b1bb180747</t>
+        </is>
+      </c>
+      <c r="B2903" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2903" t="inlineStr">
+        <is>
+          <t>2026-07-24T23:00:33.986Z</t>
+        </is>
+      </c>
+      <c r="D2903" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2903" t="inlineStr"/>
+    </row>
+    <row r="2904">
+      <c r="A2904" t="inlineStr">
+        <is>
+          <t>5a3ab6e6-8d61-41be-bd92-e2428bbe6e04</t>
+        </is>
+      </c>
+      <c r="B2904" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2904" t="inlineStr">
+        <is>
+          <t>2026-07-24T23:01:45.169Z</t>
+        </is>
+      </c>
+      <c r="D2904" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2904" t="inlineStr"/>
+    </row>
+    <row r="2905">
+      <c r="A2905" t="inlineStr">
+        <is>
+          <t>6d575550-d084-4511-bc4c-e40b5b77e426</t>
+        </is>
+      </c>
+      <c r="B2905" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2905" t="inlineStr">
+        <is>
+          <t>2026-07-24T23:02:20.631Z</t>
+        </is>
+      </c>
+      <c r="D2905" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2905" t="inlineStr">
+        <is>
+          <t>law enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2906">
+      <c r="A2906" t="inlineStr">
+        <is>
+          <t>6fcbf7c8-e9fe-41e5-a6fb-d2fc10e99df5</t>
+        </is>
+      </c>
+      <c r="B2906" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2906" t="inlineStr">
+        <is>
+          <t>2026-07-24T23:06:14.191Z</t>
+        </is>
+      </c>
+      <c r="D2906" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2906" t="inlineStr"/>
+    </row>
+    <row r="2907">
+      <c r="A2907" t="inlineStr">
+        <is>
+          <t>6a600dab-6381-42d9-9c5b-02b93df79411</t>
+        </is>
+      </c>
+      <c r="B2907" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2907" t="inlineStr">
+        <is>
+          <t>2026-07-24T23:14:06.670Z</t>
+        </is>
+      </c>
+      <c r="D2907" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2907" t="inlineStr"/>
+    </row>
+    <row r="2908">
+      <c r="A2908" t="inlineStr">
+        <is>
+          <t>04843170-3b6f-4e7c-9405-2dfa6dff4959</t>
+        </is>
+      </c>
+      <c r="B2908" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2908" t="inlineStr">
+        <is>
+          <t>2026-07-24T23:14:44.784Z</t>
+        </is>
+      </c>
+      <c r="D2908" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2908" t="inlineStr">
+        <is>
+          <t>Law enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2909">
+      <c r="A2909" t="inlineStr">
+        <is>
+          <t>87d36607-8393-4322-9338-c37e04b55924</t>
+        </is>
+      </c>
+      <c r="B2909" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2909" t="inlineStr">
+        <is>
+          <t>2026-07-24T23:14:51.514Z</t>
+        </is>
+      </c>
+      <c r="D2909" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2909" t="inlineStr"/>
+    </row>
+    <row r="2910">
+      <c r="A2910" t="inlineStr">
+        <is>
+          <t>4b97b013-7c6f-43a1-a8b3-51e1a2041efd</t>
+        </is>
+      </c>
+      <c r="B2910" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2910" t="inlineStr">
+        <is>
+          <t>2026-07-24T23:19:17.180Z</t>
+        </is>
+      </c>
+      <c r="D2910" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2910" t="inlineStr">
+        <is>
+          <t>Missing juvenile</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2910"/>
+  <dimension ref="A1:E2917"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66138,6 +66138,153 @@
         </is>
       </c>
     </row>
+    <row r="2911">
+      <c r="A2911" t="inlineStr">
+        <is>
+          <t>5fa22d5b-cd13-4af6-9c38-0e78a9ca31a4</t>
+        </is>
+      </c>
+      <c r="B2911" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2911" t="inlineStr">
+        <is>
+          <t>2026-07-25T00:25:17.253Z</t>
+        </is>
+      </c>
+      <c r="D2911" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2911" t="inlineStr"/>
+    </row>
+    <row r="2912">
+      <c r="A2912" t="inlineStr">
+        <is>
+          <t>21572a76-272b-4883-a560-9f82d801a51a</t>
+        </is>
+      </c>
+      <c r="B2912" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2912" t="inlineStr">
+        <is>
+          <t>2026-07-25T01:22:24.989Z</t>
+        </is>
+      </c>
+      <c r="D2912" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2912" t="inlineStr"/>
+    </row>
+    <row r="2913">
+      <c r="A2913" t="inlineStr">
+        <is>
+          <t>53d73cb7-ae94-469f-8723-47c56f78dc51</t>
+        </is>
+      </c>
+      <c r="B2913" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2913" t="inlineStr">
+        <is>
+          <t>2026-07-25T01:24:40.358Z</t>
+        </is>
+      </c>
+      <c r="D2913" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2913" t="inlineStr"/>
+    </row>
+    <row r="2914">
+      <c r="A2914" t="inlineStr">
+        <is>
+          <t>f87161c4-c722-48b8-a108-0ced6adb6f73</t>
+        </is>
+      </c>
+      <c r="B2914" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2914" t="inlineStr">
+        <is>
+          <t>2026-07-25T03:07:25.244Z</t>
+        </is>
+      </c>
+      <c r="D2914" t="n">
+        <v>484</v>
+      </c>
+      <c r="E2914" t="inlineStr"/>
+    </row>
+    <row r="2915">
+      <c r="A2915" t="inlineStr">
+        <is>
+          <t>4466f865-aef1-4353-b07a-8befb346a2fd</t>
+        </is>
+      </c>
+      <c r="B2915" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2915" t="inlineStr">
+        <is>
+          <t>2026-07-25T15:38:40.758Z</t>
+        </is>
+      </c>
+      <c r="D2915" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2915" t="inlineStr"/>
+    </row>
+    <row r="2916">
+      <c r="A2916" t="inlineStr">
+        <is>
+          <t>9102684c-9ce9-4dba-b7dc-02f7e3dae573</t>
+        </is>
+      </c>
+      <c r="B2916" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2916" t="inlineStr">
+        <is>
+          <t>2026-07-25T16:23:53.797Z</t>
+        </is>
+      </c>
+      <c r="D2916" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2916" t="inlineStr"/>
+    </row>
+    <row r="2917">
+      <c r="A2917" t="inlineStr">
+        <is>
+          <t>6a893337-3a08-452b-afd1-6f199c0243c6</t>
+        </is>
+      </c>
+      <c r="B2917" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2917" t="inlineStr">
+        <is>
+          <t>2026-07-25T20:49:39.591Z</t>
+        </is>
+      </c>
+      <c r="D2917" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2917" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2917"/>
+  <dimension ref="A1:E2931"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66285,6 +66285,304 @@
       </c>
       <c r="E2917" t="inlineStr"/>
     </row>
+    <row r="2918">
+      <c r="A2918" t="inlineStr">
+        <is>
+          <t>14ba879c-f506-41a3-be97-fa3daac4e229</t>
+        </is>
+      </c>
+      <c r="B2918" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2918" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:00:49.401Z</t>
+        </is>
+      </c>
+      <c r="D2918" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2918" t="inlineStr"/>
+    </row>
+    <row r="2919">
+      <c r="A2919" t="inlineStr">
+        <is>
+          <t>03986fd1-4915-482f-a67f-6f8abc0a3310</t>
+        </is>
+      </c>
+      <c r="B2919" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2919" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:01:35.679Z</t>
+        </is>
+      </c>
+      <c r="D2919" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2919" t="inlineStr"/>
+    </row>
+    <row r="2920">
+      <c r="A2920" t="inlineStr">
+        <is>
+          <t>a36b2920-650e-4643-ac3a-21bcc058851e</t>
+        </is>
+      </c>
+      <c r="B2920" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2920" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:59:33.987Z</t>
+        </is>
+      </c>
+      <c r="D2920" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2920" t="inlineStr"/>
+    </row>
+    <row r="2921">
+      <c r="A2921" t="inlineStr">
+        <is>
+          <t>734d8b23-dfc2-414c-9678-07ae65addc46</t>
+        </is>
+      </c>
+      <c r="B2921" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2921" t="inlineStr">
+        <is>
+          <t>2026-07-26T02:02:43.905Z</t>
+        </is>
+      </c>
+      <c r="D2921" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2921" t="inlineStr"/>
+    </row>
+    <row r="2922">
+      <c r="A2922" t="inlineStr">
+        <is>
+          <t>24bdf308-fcf5-49d2-9331-f29fb4026a84</t>
+        </is>
+      </c>
+      <c r="B2922" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2922" t="inlineStr">
+        <is>
+          <t>2026-07-26T02:34:29.594Z</t>
+        </is>
+      </c>
+      <c r="D2922" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2922" t="inlineStr"/>
+    </row>
+    <row r="2923">
+      <c r="A2923" t="inlineStr">
+        <is>
+          <t>f5f7b49c-15d4-473f-ad3c-3f41a376c71c</t>
+        </is>
+      </c>
+      <c r="B2923" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2923" t="inlineStr">
+        <is>
+          <t>2026-07-26T03:13:37.689Z</t>
+        </is>
+      </c>
+      <c r="D2923" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2923" t="inlineStr">
+        <is>
+          <t>Law Enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2924">
+      <c r="A2924" t="inlineStr">
+        <is>
+          <t>97cce8cd-2491-4ea1-b30a-e9c6ec00d13d</t>
+        </is>
+      </c>
+      <c r="B2924" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2924" t="inlineStr">
+        <is>
+          <t>2026-07-26T03:40:44.599Z</t>
+        </is>
+      </c>
+      <c r="D2924" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2924" t="inlineStr"/>
+    </row>
+    <row r="2925">
+      <c r="A2925" t="inlineStr">
+        <is>
+          <t>e53b82de-a791-42dc-a14c-d92899914b0c</t>
+        </is>
+      </c>
+      <c r="B2925" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2925" t="inlineStr">
+        <is>
+          <t>2026-07-26T04:10:12.796Z</t>
+        </is>
+      </c>
+      <c r="D2925" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2925" t="inlineStr"/>
+    </row>
+    <row r="2926">
+      <c r="A2926" t="inlineStr">
+        <is>
+          <t>dd2ba7f4-d9fe-4a02-94cb-812fff62c6ee</t>
+        </is>
+      </c>
+      <c r="B2926" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2926" t="inlineStr">
+        <is>
+          <t>2026-07-26T05:47:45.605Z</t>
+        </is>
+      </c>
+      <c r="D2926" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2926" t="inlineStr"/>
+    </row>
+    <row r="2927">
+      <c r="A2927" t="inlineStr">
+        <is>
+          <t>8311e49a-9a25-4f79-9a58-5793d1c2c171</t>
+        </is>
+      </c>
+      <c r="B2927" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2927" t="inlineStr">
+        <is>
+          <t>2026-07-26T06:50:40.462Z</t>
+        </is>
+      </c>
+      <c r="D2927" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2927" t="inlineStr"/>
+    </row>
+    <row r="2928">
+      <c r="A2928" t="inlineStr">
+        <is>
+          <t>58ba04ec-eb2f-453c-8a75-b33e3ee79cbb</t>
+        </is>
+      </c>
+      <c r="B2928" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2928" t="inlineStr">
+        <is>
+          <t>2026-07-26T07:44:31.329Z</t>
+        </is>
+      </c>
+      <c r="D2928" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2928" t="inlineStr"/>
+    </row>
+    <row r="2929">
+      <c r="A2929" t="inlineStr">
+        <is>
+          <t>436d4917-eff8-49d9-8af5-6b5e2a3b6ca5</t>
+        </is>
+      </c>
+      <c r="B2929" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2929" t="inlineStr">
+        <is>
+          <t>2026-07-26T11:20:50.019Z</t>
+        </is>
+      </c>
+      <c r="D2929" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2929" t="inlineStr"/>
+    </row>
+    <row r="2930">
+      <c r="A2930" t="inlineStr">
+        <is>
+          <t>d8fa7b0c-ca24-43dc-80fd-804d1440d515</t>
+        </is>
+      </c>
+      <c r="B2930" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2930" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:39:21.130Z</t>
+        </is>
+      </c>
+      <c r="D2930" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2930" t="inlineStr"/>
+    </row>
+    <row r="2931">
+      <c r="A2931" t="inlineStr">
+        <is>
+          <t>7ddbeaf8-9264-45ec-84a8-505950b1ba04</t>
+        </is>
+      </c>
+      <c r="B2931" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2931" t="inlineStr">
+        <is>
+          <t>2026-07-26T20:55:46.814Z</t>
+        </is>
+      </c>
+      <c r="D2931" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2931" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2947"/>
+  <dimension ref="A1:F2964"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69938,6 +69938,516 @@
         </is>
       </c>
     </row>
+    <row r="2948">
+      <c r="A2948" t="inlineStr">
+        <is>
+          <t>2af00018-766c-4560-820c-5b8b2eb3c327</t>
+        </is>
+      </c>
+      <c r="B2948" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2948" t="inlineStr">
+        <is>
+          <t>2026-07-28T03:47:42.851Z</t>
+        </is>
+      </c>
+      <c r="D2948" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2948" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2948" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="2949">
+      <c r="A2949" t="inlineStr">
+        <is>
+          <t>cd8a5e52-cbef-45cb-b18b-61706c503efd</t>
+        </is>
+      </c>
+      <c r="B2949" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2949" t="inlineStr">
+        <is>
+          <t>2026-07-28T06:56:13.900Z</t>
+        </is>
+      </c>
+      <c r="D2949" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2949" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2949" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="2950">
+      <c r="A2950" t="inlineStr">
+        <is>
+          <t>e28f1a25-2af9-4ea0-98a0-4b592b0ce09b</t>
+        </is>
+      </c>
+      <c r="B2950" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2950" t="inlineStr">
+        <is>
+          <t>2026-07-28T07:11:29.577Z</t>
+        </is>
+      </c>
+      <c r="D2950" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2950" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2950" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2951">
+      <c r="A2951" t="inlineStr">
+        <is>
+          <t>ae06d865-8462-4a78-9acb-21bbb4d649cc</t>
+        </is>
+      </c>
+      <c r="B2951" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2951" t="inlineStr">
+        <is>
+          <t>2026-07-28T09:29:35.401Z</t>
+        </is>
+      </c>
+      <c r="D2951" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2951" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2951" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2952">
+      <c r="A2952" t="inlineStr">
+        <is>
+          <t>a47ac4ca-1aec-4b4d-b85c-754181bf6e9b</t>
+        </is>
+      </c>
+      <c r="B2952" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2952" t="inlineStr">
+        <is>
+          <t>2026-07-28T12:46:44.377Z</t>
+        </is>
+      </c>
+      <c r="D2952" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2952" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2952" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="2953">
+      <c r="A2953" t="inlineStr">
+        <is>
+          <t>f4a76dbc-336c-41ba-9ed1-d3b424161be6</t>
+        </is>
+      </c>
+      <c r="B2953" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2953" t="inlineStr">
+        <is>
+          <t>2026-07-28T13:55:12.556Z</t>
+        </is>
+      </c>
+      <c r="D2953" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2953" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2953" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2954">
+      <c r="A2954" t="inlineStr">
+        <is>
+          <t>d8153e50-be08-47e4-b443-88955d399d7f</t>
+        </is>
+      </c>
+      <c r="B2954" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2954" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:02:48.119Z</t>
+        </is>
+      </c>
+      <c r="D2954" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2954" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2954" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2955">
+      <c r="A2955" t="inlineStr">
+        <is>
+          <t>60225941-be25-4807-87eb-ed0cdcd2e9cc</t>
+        </is>
+      </c>
+      <c r="B2955" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2955" t="inlineStr">
+        <is>
+          <t>2026-07-28T16:38:46.682Z</t>
+        </is>
+      </c>
+      <c r="D2955" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2955" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2955" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2956">
+      <c r="A2956" t="inlineStr">
+        <is>
+          <t>12f7cb06-e052-4ffb-9618-fe2a166b0a83</t>
+        </is>
+      </c>
+      <c r="B2956" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2956" t="inlineStr">
+        <is>
+          <t>2026-07-28T19:07:03.457Z</t>
+        </is>
+      </c>
+      <c r="D2956" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2956" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2956" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2957">
+      <c r="A2957" t="inlineStr">
+        <is>
+          <t>a8254823-bd98-4e1a-919b-135e5e55251c</t>
+        </is>
+      </c>
+      <c r="B2957" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2957" t="inlineStr">
+        <is>
+          <t>2026-07-28T19:35:02.789Z</t>
+        </is>
+      </c>
+      <c r="D2957" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2957" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2957" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2958">
+      <c r="A2958" t="inlineStr">
+        <is>
+          <t>7fdc0da6-1cb7-4ad9-8957-22cec70d2e91</t>
+        </is>
+      </c>
+      <c r="B2958" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2958" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:16:49.660Z</t>
+        </is>
+      </c>
+      <c r="D2958" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2958" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2958" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2959">
+      <c r="A2959" t="inlineStr">
+        <is>
+          <t>006155fb-f523-4d65-841b-2d7833b2d226</t>
+        </is>
+      </c>
+      <c r="B2959" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2959" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:22:23.136Z</t>
+        </is>
+      </c>
+      <c r="D2959" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2959" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2959" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="2960">
+      <c r="A2960" t="inlineStr">
+        <is>
+          <t>5d27b11d-1662-4857-83b3-5595fa945429</t>
+        </is>
+      </c>
+      <c r="B2960" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2960" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:33:31.921Z</t>
+        </is>
+      </c>
+      <c r="D2960" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2960" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2960" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2961">
+      <c r="A2961" t="inlineStr">
+        <is>
+          <t>feea4a35-e19f-471d-9020-d5c79ae9dc0b</t>
+        </is>
+      </c>
+      <c r="B2961" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2961" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:42:24.679Z</t>
+        </is>
+      </c>
+      <c r="D2961" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2961" t="inlineStr">
+        <is>
+          <t>Agency Assist</t>
+        </is>
+      </c>
+      <c r="F2961" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2962">
+      <c r="A2962" t="inlineStr">
+        <is>
+          <t>0f1da56d-c219-44bc-acd0-bd7dccd09ef1</t>
+        </is>
+      </c>
+      <c r="B2962" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2962" t="inlineStr">
+        <is>
+          <t>2026-07-28T21:24:01.858Z</t>
+        </is>
+      </c>
+      <c r="D2962" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2962" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2962" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2963">
+      <c r="A2963" t="inlineStr">
+        <is>
+          <t>927cc46b-c52e-4bb0-8ac6-da1bb173dea7</t>
+        </is>
+      </c>
+      <c r="B2963" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2963" t="inlineStr">
+        <is>
+          <t>2026-07-28T22:40:08.916Z</t>
+        </is>
+      </c>
+      <c r="D2963" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2963" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2963" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2964">
+      <c r="A2964" t="inlineStr">
+        <is>
+          <t>d8b8fab8-a4da-408a-89c3-fcac33ade80a</t>
+        </is>
+      </c>
+      <c r="B2964" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2964" t="inlineStr">
+        <is>
+          <t>2026-07-28T23:00:27.828Z</t>
+        </is>
+      </c>
+      <c r="D2964" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2964" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2964" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2964"/>
+  <dimension ref="A1:F2996"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70448,6 +70448,966 @@
         </is>
       </c>
     </row>
+    <row r="2965">
+      <c r="A2965" t="inlineStr">
+        <is>
+          <t>a59f1074-367f-4c5e-ab46-1dc42e511ba1</t>
+        </is>
+      </c>
+      <c r="B2965" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2965" t="inlineStr">
+        <is>
+          <t>2026-07-29T00:11:18.776Z</t>
+        </is>
+      </c>
+      <c r="D2965" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2965" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2965" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2966">
+      <c r="A2966" t="inlineStr">
+        <is>
+          <t>8d0cac96-a535-4e02-9f81-7f6804f9f531</t>
+        </is>
+      </c>
+      <c r="B2966" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2966" t="inlineStr">
+        <is>
+          <t>2026-07-29T00:24:15.404Z</t>
+        </is>
+      </c>
+      <c r="D2966" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2966" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F2966" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="2967">
+      <c r="A2967" t="inlineStr">
+        <is>
+          <t>e59444c9-1963-4102-815e-cc2c71555593</t>
+        </is>
+      </c>
+      <c r="B2967" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2967" t="inlineStr">
+        <is>
+          <t>2026-07-29T00:41:06.462Z</t>
+        </is>
+      </c>
+      <c r="D2967" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2967" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F2967" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2968">
+      <c r="A2968" t="inlineStr">
+        <is>
+          <t>de1e4e06-c7fc-450e-ad0d-42be94eb8e75</t>
+        </is>
+      </c>
+      <c r="B2968" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2968" t="inlineStr">
+        <is>
+          <t>2026-07-29T00:53:56.060Z</t>
+        </is>
+      </c>
+      <c r="D2968" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2968" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2968" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2969">
+      <c r="A2969" t="inlineStr">
+        <is>
+          <t>5313f9ac-ff82-4461-a0f4-d4c940661a2f</t>
+        </is>
+      </c>
+      <c r="B2969" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2969" t="inlineStr">
+        <is>
+          <t>2026-07-29T01:02:28.638Z</t>
+        </is>
+      </c>
+      <c r="D2969" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2969" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F2969" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2970">
+      <c r="A2970" t="inlineStr">
+        <is>
+          <t>c9978ca6-640a-47d5-b434-2988551de33a</t>
+        </is>
+      </c>
+      <c r="B2970" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2970" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:06:32.666Z</t>
+        </is>
+      </c>
+      <c r="D2970" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2970" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F2970" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2971">
+      <c r="A2971" t="inlineStr">
+        <is>
+          <t>b808e841-0b92-4d8d-a37f-9f703706ca1b</t>
+        </is>
+      </c>
+      <c r="B2971" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2971" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:06:32.952Z</t>
+        </is>
+      </c>
+      <c r="D2971" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2971" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F2971" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2972">
+      <c r="A2972" t="inlineStr">
+        <is>
+          <t>d88c8b46-144f-4119-960e-d0b226118216</t>
+        </is>
+      </c>
+      <c r="B2972" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2972" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:26:27.638Z</t>
+        </is>
+      </c>
+      <c r="D2972" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2972" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2972" t="inlineStr">
+        <is>
+          <t>Criminal Motor Vehicle Offense (incl. Road Rage/Reckless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2973">
+      <c r="A2973" t="inlineStr">
+        <is>
+          <t>3489dfad-a005-4c8b-aa07-957e4b4a9a2b</t>
+        </is>
+      </c>
+      <c r="B2973" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2973" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:42:03.011Z</t>
+        </is>
+      </c>
+      <c r="D2973" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2973" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2973" t="inlineStr">
+        <is>
+          <t>Criminal Motor Vehicle Offense (incl. Road Rage/Reckless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2974">
+      <c r="A2974" t="inlineStr">
+        <is>
+          <t>65bca2d5-2bad-45b7-a334-5bf1d458b14f</t>
+        </is>
+      </c>
+      <c r="B2974" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2974" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:53:27.224Z</t>
+        </is>
+      </c>
+      <c r="D2974" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2974" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2974" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2975">
+      <c r="A2975" t="inlineStr">
+        <is>
+          <t>532b109f-7844-45eb-9de2-1cc7aec5e9a5</t>
+        </is>
+      </c>
+      <c r="B2975" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2975" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:57:10.949Z</t>
+        </is>
+      </c>
+      <c r="D2975" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2975" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2975" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2976">
+      <c r="A2976" t="inlineStr">
+        <is>
+          <t>649e0b31-5236-4065-ae20-56c9f2f77439</t>
+        </is>
+      </c>
+      <c r="B2976" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2976" t="inlineStr">
+        <is>
+          <t>2026-07-29T03:00:26.973Z</t>
+        </is>
+      </c>
+      <c r="D2976" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2976" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2976" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2977">
+      <c r="A2977" t="inlineStr">
+        <is>
+          <t>04f2b6de-18e6-4cae-97d0-4dc72998aa6f</t>
+        </is>
+      </c>
+      <c r="B2977" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2977" t="inlineStr">
+        <is>
+          <t>2026-07-29T03:02:37.859Z</t>
+        </is>
+      </c>
+      <c r="D2977" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2977" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2977" t="inlineStr">
+        <is>
+          <t>Criminal Motor Vehicle Offense (incl. Road Rage/Reckless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2978">
+      <c r="A2978" t="inlineStr">
+        <is>
+          <t>a68d1e7e-2abc-4fca-8fd6-e31dee57d889</t>
+        </is>
+      </c>
+      <c r="B2978" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2978" t="inlineStr">
+        <is>
+          <t>2026-07-29T03:15:20.765Z</t>
+        </is>
+      </c>
+      <c r="D2978" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2978" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2978" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2979">
+      <c r="A2979" t="inlineStr">
+        <is>
+          <t>607e86e1-b343-4750-9b88-3c769741558e</t>
+        </is>
+      </c>
+      <c r="B2979" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2979" t="inlineStr">
+        <is>
+          <t>2026-07-29T04:00:53.011Z</t>
+        </is>
+      </c>
+      <c r="D2979" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2979" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2979" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2980">
+      <c r="A2980" t="inlineStr">
+        <is>
+          <t>3fd626be-c8e0-4021-a26b-ab16746e4da8</t>
+        </is>
+      </c>
+      <c r="B2980" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2980" t="inlineStr">
+        <is>
+          <t>2026-07-29T05:38:24.635Z</t>
+        </is>
+      </c>
+      <c r="D2980" t="n">
+        <v>515</v>
+      </c>
+      <c r="E2980" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2980" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2981">
+      <c r="A2981" t="inlineStr">
+        <is>
+          <t>a3b97af3-699c-4c29-99c7-72f1ed21e9ba</t>
+        </is>
+      </c>
+      <c r="B2981" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2981" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:27:19.732Z</t>
+        </is>
+      </c>
+      <c r="D2981" t="n">
+        <v>559</v>
+      </c>
+      <c r="E2981" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2981" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="2982">
+      <c r="A2982" t="inlineStr">
+        <is>
+          <t>1d8da858-94b8-43c0-912e-5f8d365871f2</t>
+        </is>
+      </c>
+      <c r="B2982" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2982" t="inlineStr">
+        <is>
+          <t>2026-07-29T08:39:54.590Z</t>
+        </is>
+      </c>
+      <c r="D2982" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2982" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2982" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="2983">
+      <c r="A2983" t="inlineStr">
+        <is>
+          <t>fe889fe4-055b-4cda-b1b4-fe7bfa0dd5fb</t>
+        </is>
+      </c>
+      <c r="B2983" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2983" t="inlineStr">
+        <is>
+          <t>2026-07-29T10:48:02.042Z</t>
+        </is>
+      </c>
+      <c r="D2983" t="n">
+        <v>524</v>
+      </c>
+      <c r="E2983" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2983" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="2984">
+      <c r="A2984" t="inlineStr">
+        <is>
+          <t>e28fe0be-f82f-4197-9e28-015eef8341db</t>
+        </is>
+      </c>
+      <c r="B2984" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2984" t="inlineStr">
+        <is>
+          <t>2026-07-29T12:29:16.251Z</t>
+        </is>
+      </c>
+      <c r="D2984" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2984" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2984" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2985">
+      <c r="A2985" t="inlineStr">
+        <is>
+          <t>1c68e407-2002-4820-8ab9-5f4a375308a6</t>
+        </is>
+      </c>
+      <c r="B2985" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2985" t="inlineStr">
+        <is>
+          <t>2026-07-29T14:23:56.322Z</t>
+        </is>
+      </c>
+      <c r="D2985" t="n">
+        <v>514</v>
+      </c>
+      <c r="E2985" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2985" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2986">
+      <c r="A2986" t="inlineStr">
+        <is>
+          <t>735bd706-28bf-44fc-ae09-d8fad9a00c71</t>
+        </is>
+      </c>
+      <c r="B2986" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2986" t="inlineStr">
+        <is>
+          <t>2026-07-29T16:02:48.537Z</t>
+        </is>
+      </c>
+      <c r="D2986" t="n">
+        <v>558</v>
+      </c>
+      <c r="E2986" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2986" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2987">
+      <c r="A2987" t="inlineStr">
+        <is>
+          <t>9850cb3c-a193-44bb-bcd3-77a4d0b558a2</t>
+        </is>
+      </c>
+      <c r="B2987" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2987" t="inlineStr">
+        <is>
+          <t>2026-07-29T16:04:12.761Z</t>
+        </is>
+      </c>
+      <c r="D2987" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2987" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2987" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2988">
+      <c r="A2988" t="inlineStr">
+        <is>
+          <t>4e6c0a21-e3c2-461d-9a38-d655f4656bbd</t>
+        </is>
+      </c>
+      <c r="B2988" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2988" t="inlineStr">
+        <is>
+          <t>2026-07-29T18:56:42.155Z</t>
+        </is>
+      </c>
+      <c r="D2988" t="n">
+        <v>558</v>
+      </c>
+      <c r="E2988" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2988" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2989">
+      <c r="A2989" t="inlineStr">
+        <is>
+          <t>7aabad8a-a7c1-4926-bcc7-10cc87653836</t>
+        </is>
+      </c>
+      <c r="B2989" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2989" t="inlineStr">
+        <is>
+          <t>2026-07-29T19:08:36.475Z</t>
+        </is>
+      </c>
+      <c r="D2989" t="n">
+        <v>523</v>
+      </c>
+      <c r="E2989" t="inlineStr">
+        <is>
+          <t>Agency Assist</t>
+        </is>
+      </c>
+      <c r="F2989" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2990">
+      <c r="A2990" t="inlineStr">
+        <is>
+          <t>a508bb7a-1ca5-4cb4-a1b6-76c829e8da08</t>
+        </is>
+      </c>
+      <c r="B2990" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2990" t="inlineStr">
+        <is>
+          <t>2026-07-29T19:32:56.400Z</t>
+        </is>
+      </c>
+      <c r="D2990" t="n">
+        <v>558</v>
+      </c>
+      <c r="E2990" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2990" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2991">
+      <c r="A2991" t="inlineStr">
+        <is>
+          <t>5f965f0b-860b-4c30-a2fe-8caad38ea56a</t>
+        </is>
+      </c>
+      <c r="B2991" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2991" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:12:41.591Z</t>
+        </is>
+      </c>
+      <c r="D2991" t="n">
+        <v>514</v>
+      </c>
+      <c r="E2991" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2991" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2992">
+      <c r="A2992" t="inlineStr">
+        <is>
+          <t>afb31d68-c45f-41ea-a222-463954d9a86c</t>
+        </is>
+      </c>
+      <c r="B2992" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2992" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:29:07.288Z</t>
+        </is>
+      </c>
+      <c r="D2992" t="n">
+        <v>558</v>
+      </c>
+      <c r="E2992" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2992" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2993">
+      <c r="A2993" t="inlineStr">
+        <is>
+          <t>dfc2c953-2965-4d90-aa92-4e3950fdc8ee</t>
+        </is>
+      </c>
+      <c r="B2993" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2993" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:58:52.003Z</t>
+        </is>
+      </c>
+      <c r="D2993" t="n">
+        <v>558</v>
+      </c>
+      <c r="E2993" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F2993" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="2994">
+      <c r="A2994" t="inlineStr">
+        <is>
+          <t>47bc2e47-0125-4652-86be-a67ccd0cd539</t>
+        </is>
+      </c>
+      <c r="B2994" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2994" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:15:19.400Z</t>
+        </is>
+      </c>
+      <c r="D2994" t="n">
+        <v>558</v>
+      </c>
+      <c r="E2994" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2994" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2995">
+      <c r="A2995" t="inlineStr">
+        <is>
+          <t>7b2f007e-5ff7-44e7-91d6-86fda4dbde5a</t>
+        </is>
+      </c>
+      <c r="B2995" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2995" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:55:21.863Z</t>
+        </is>
+      </c>
+      <c r="D2995" t="n">
+        <v>558</v>
+      </c>
+      <c r="E2995" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2995" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2996">
+      <c r="A2996" t="inlineStr">
+        <is>
+          <t>7678d119-8563-4e1d-90cf-7352cab019a3</t>
+        </is>
+      </c>
+      <c r="B2996" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2996" t="inlineStr">
+        <is>
+          <t>2026-07-29T23:31:47.668Z</t>
+        </is>
+      </c>
+      <c r="D2996" t="n">
+        <v>558</v>
+      </c>
+      <c r="E2996" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2996" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2996"/>
+  <dimension ref="A1:F3040"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71408,6 +71408,1326 @@
         </is>
       </c>
     </row>
+    <row r="2997">
+      <c r="A2997" t="inlineStr">
+        <is>
+          <t>132bf19c-19e5-4179-9f47-694c3b80bd36</t>
+        </is>
+      </c>
+      <c r="B2997" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2997" t="inlineStr">
+        <is>
+          <t>2026-07-30T00:00:26.235Z</t>
+        </is>
+      </c>
+      <c r="D2997" t="n">
+        <v>558</v>
+      </c>
+      <c r="E2997" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2997" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2998">
+      <c r="A2998" t="inlineStr">
+        <is>
+          <t>4cb29d47-69c9-4fcd-bb4d-c3781bce0ea7</t>
+        </is>
+      </c>
+      <c r="B2998" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2998" t="inlineStr">
+        <is>
+          <t>2026-07-30T00:01:21.144Z</t>
+        </is>
+      </c>
+      <c r="D2998" t="n">
+        <v>513</v>
+      </c>
+      <c r="E2998" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2998" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="2999">
+      <c r="A2999" t="inlineStr">
+        <is>
+          <t>e411bca1-74b6-434a-96a8-2b2d88aea32a</t>
+        </is>
+      </c>
+      <c r="B2999" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C2999" t="inlineStr">
+        <is>
+          <t>2026-07-30T00:03:21.891Z</t>
+        </is>
+      </c>
+      <c r="D2999" t="n">
+        <v>513</v>
+      </c>
+      <c r="E2999" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F2999" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3000">
+      <c r="A3000" t="inlineStr">
+        <is>
+          <t>db58d2e5-f67e-4b37-8710-d06a457c36a3</t>
+        </is>
+      </c>
+      <c r="B3000" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3000" t="inlineStr">
+        <is>
+          <t>2026-07-30T01:06:09.733Z</t>
+        </is>
+      </c>
+      <c r="D3000" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3000" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3000" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3001">
+      <c r="A3001" t="inlineStr">
+        <is>
+          <t>78404488-06b7-487c-82bd-a54822a68563</t>
+        </is>
+      </c>
+      <c r="B3001" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3001" t="inlineStr">
+        <is>
+          <t>2026-07-30T02:16:43.831Z</t>
+        </is>
+      </c>
+      <c r="D3001" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3001" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3001" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3002">
+      <c r="A3002" t="inlineStr">
+        <is>
+          <t>fff8cd5f-385c-4035-8511-88e36d42bbc7</t>
+        </is>
+      </c>
+      <c r="B3002" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3002" t="inlineStr">
+        <is>
+          <t>2026-07-30T03:07:37.438Z</t>
+        </is>
+      </c>
+      <c r="D3002" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3002" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3002" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3003">
+      <c r="A3003" t="inlineStr">
+        <is>
+          <t>c84b34c8-c479-4013-9f5c-65f71c5be4ef</t>
+        </is>
+      </c>
+      <c r="B3003" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3003" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:00:11.022Z</t>
+        </is>
+      </c>
+      <c r="D3003" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3003" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3003" t="inlineStr">
+        <is>
+          <t>Robbery</t>
+        </is>
+      </c>
+    </row>
+    <row r="3004">
+      <c r="A3004" t="inlineStr">
+        <is>
+          <t>41c5368b-e9f1-4484-8833-e1c3f9cae241</t>
+        </is>
+      </c>
+      <c r="B3004" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3004" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:02:18.455Z</t>
+        </is>
+      </c>
+      <c r="D3004" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3004" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3004" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3005">
+      <c r="A3005" t="inlineStr">
+        <is>
+          <t>83ef9f58-7929-4f32-8d83-e0a1ec31c51e</t>
+        </is>
+      </c>
+      <c r="B3005" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3005" t="inlineStr">
+        <is>
+          <t>2026-07-30T05:14:27.791Z</t>
+        </is>
+      </c>
+      <c r="D3005" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3005" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3005" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3006">
+      <c r="A3006" t="inlineStr">
+        <is>
+          <t>0434174f-0d0e-487f-9bc1-f9902359b928</t>
+        </is>
+      </c>
+      <c r="B3006" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3006" t="inlineStr">
+        <is>
+          <t>2026-07-30T05:16:43.850Z</t>
+        </is>
+      </c>
+      <c r="D3006" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3006" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3006" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3007">
+      <c r="A3007" t="inlineStr">
+        <is>
+          <t>25834da9-2a32-4292-aa1e-7804a353188a</t>
+        </is>
+      </c>
+      <c r="B3007" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3007" t="inlineStr">
+        <is>
+          <t>2026-07-30T06:45:38.429Z</t>
+        </is>
+      </c>
+      <c r="D3007" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3007" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3007" t="inlineStr">
+        <is>
+          <t>Robbery</t>
+        </is>
+      </c>
+    </row>
+    <row r="3008">
+      <c r="A3008" t="inlineStr">
+        <is>
+          <t>604c7e5d-45cc-484f-a6f4-8122ef70a617</t>
+        </is>
+      </c>
+      <c r="B3008" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3008" t="inlineStr">
+        <is>
+          <t>2026-07-30T10:43:19.837Z</t>
+        </is>
+      </c>
+      <c r="D3008" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3008" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3008" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3009">
+      <c r="A3009" t="inlineStr">
+        <is>
+          <t>e4a09287-bf7b-47e5-9fcf-54b0f36999c4</t>
+        </is>
+      </c>
+      <c r="B3009" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3009" t="inlineStr">
+        <is>
+          <t>2026-07-30T11:28:46.783Z</t>
+        </is>
+      </c>
+      <c r="D3009" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3009" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3009" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3010">
+      <c r="A3010" t="inlineStr">
+        <is>
+          <t>b14bfcac-ff85-4b11-ae33-8c5980d94762</t>
+        </is>
+      </c>
+      <c r="B3010" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3010" t="inlineStr">
+        <is>
+          <t>2026-07-30T12:13:14.757Z</t>
+        </is>
+      </c>
+      <c r="D3010" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3010" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3010" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3011">
+      <c r="A3011" t="inlineStr">
+        <is>
+          <t>82076cfd-fc02-4f3c-ba9d-07c26e5af6df</t>
+        </is>
+      </c>
+      <c r="B3011" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3011" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:02:13.749Z</t>
+        </is>
+      </c>
+      <c r="D3011" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3011" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3011" t="inlineStr">
+        <is>
+          <t>Juvenile Delinquency</t>
+        </is>
+      </c>
+    </row>
+    <row r="3012">
+      <c r="A3012" t="inlineStr">
+        <is>
+          <t>ba2bdbf8-a6e7-4b72-83c9-6075ae2fb5ab</t>
+        </is>
+      </c>
+      <c r="B3012" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3012" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:42:17.009Z</t>
+        </is>
+      </c>
+      <c r="D3012" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3012" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3012" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3013">
+      <c r="A3013" t="inlineStr">
+        <is>
+          <t>a1ea25ff-7620-4a16-9ff7-9bc69aa1a3e0</t>
+        </is>
+      </c>
+      <c r="B3013" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3013" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:50:14.395Z</t>
+        </is>
+      </c>
+      <c r="D3013" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3013" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3013" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3014">
+      <c r="A3014" t="inlineStr">
+        <is>
+          <t>d6eecfce-3056-4a60-877c-17e1ce05f074</t>
+        </is>
+      </c>
+      <c r="B3014" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3014" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:54:13.069Z</t>
+        </is>
+      </c>
+      <c r="D3014" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3014" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3014" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3015">
+      <c r="A3015" t="inlineStr">
+        <is>
+          <t>c9bb472a-13a8-4b58-ad4a-054ed3528ad3</t>
+        </is>
+      </c>
+      <c r="B3015" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3015" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:55:11.378Z</t>
+        </is>
+      </c>
+      <c r="D3015" t="n">
+        <v>482</v>
+      </c>
+      <c r="E3015" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3015" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3016">
+      <c r="A3016" t="inlineStr">
+        <is>
+          <t>b277a1d9-cc91-40d8-ad0a-b61c2ce257a8</t>
+        </is>
+      </c>
+      <c r="B3016" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3016" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:01:43.668Z</t>
+        </is>
+      </c>
+      <c r="D3016" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3016" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3016" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3017">
+      <c r="A3017" t="inlineStr">
+        <is>
+          <t>f97b3bbf-2661-4237-92f4-973aba67205c</t>
+        </is>
+      </c>
+      <c r="B3017" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3017" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:02:30.554Z</t>
+        </is>
+      </c>
+      <c r="D3017" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3017" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3017" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3018">
+      <c r="A3018" t="inlineStr">
+        <is>
+          <t>aa9cf27d-1a38-4bfc-8254-a9df45e2c66e</t>
+        </is>
+      </c>
+      <c r="B3018" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3018" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:02:53.946Z</t>
+        </is>
+      </c>
+      <c r="D3018" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3018" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3018" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3019">
+      <c r="A3019" t="inlineStr">
+        <is>
+          <t>db7c2b7f-9f1f-4132-8f89-f7c1ba517c02</t>
+        </is>
+      </c>
+      <c r="B3019" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3019" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:05:38.920Z</t>
+        </is>
+      </c>
+      <c r="D3019" t="n">
+        <v>482</v>
+      </c>
+      <c r="E3019" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3019" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3020">
+      <c r="A3020" t="inlineStr">
+        <is>
+          <t>4c8c900b-98b6-4d26-8dcb-1bd2e0608d96</t>
+        </is>
+      </c>
+      <c r="B3020" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3020" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:19:38.435Z</t>
+        </is>
+      </c>
+      <c r="D3020" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3020" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3020" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3021">
+      <c r="A3021" t="inlineStr">
+        <is>
+          <t>b951c9b9-4403-42fe-a234-30d95a9bd8b4</t>
+        </is>
+      </c>
+      <c r="B3021" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3021" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:01:34.421Z</t>
+        </is>
+      </c>
+      <c r="D3021" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3021" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3021" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3022">
+      <c r="A3022" t="inlineStr">
+        <is>
+          <t>8cd14440-17bd-47b2-b353-bd8ccdcdd295</t>
+        </is>
+      </c>
+      <c r="B3022" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3022" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:10:14.993Z</t>
+        </is>
+      </c>
+      <c r="D3022" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3022" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3022" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3023">
+      <c r="A3023" t="inlineStr">
+        <is>
+          <t>b98ee8dc-07bd-4b96-9c52-b28c7298d184</t>
+        </is>
+      </c>
+      <c r="B3023" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3023" t="inlineStr">
+        <is>
+          <t>2026-07-30T18:00:18.626Z</t>
+        </is>
+      </c>
+      <c r="D3023" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3023" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3023" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3024">
+      <c r="A3024" t="inlineStr">
+        <is>
+          <t>e7c30e02-00d9-4e00-be46-d4768e6f06b1</t>
+        </is>
+      </c>
+      <c r="B3024" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3024" t="inlineStr">
+        <is>
+          <t>2026-07-30T18:00:48.096Z</t>
+        </is>
+      </c>
+      <c r="D3024" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3024" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3024" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3025">
+      <c r="A3025" t="inlineStr">
+        <is>
+          <t>d3f6e4b2-fdea-4e47-9ed8-627dbf5493de</t>
+        </is>
+      </c>
+      <c r="B3025" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3025" t="inlineStr">
+        <is>
+          <t>2026-07-30T18:45:26.822Z</t>
+        </is>
+      </c>
+      <c r="D3025" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3025" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3025" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3026">
+      <c r="A3026" t="inlineStr">
+        <is>
+          <t>18b5221a-fa30-4cce-8f0f-26cd86209015</t>
+        </is>
+      </c>
+      <c r="B3026" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3026" t="inlineStr">
+        <is>
+          <t>2026-07-30T18:55:02.442Z</t>
+        </is>
+      </c>
+      <c r="D3026" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3026" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3026" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3027">
+      <c r="A3027" t="inlineStr">
+        <is>
+          <t>e8f4656f-edbf-4e1b-be87-341c9ace3bc8</t>
+        </is>
+      </c>
+      <c r="B3027" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3027" t="inlineStr">
+        <is>
+          <t>2026-07-30T19:32:26.388Z</t>
+        </is>
+      </c>
+      <c r="D3027" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3027" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3027" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3028">
+      <c r="A3028" t="inlineStr">
+        <is>
+          <t>ee3d9b11-3446-4ae1-9e53-2ef3e4bff7fe</t>
+        </is>
+      </c>
+      <c r="B3028" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3028" t="inlineStr">
+        <is>
+          <t>2026-07-30T19:59:54.753Z</t>
+        </is>
+      </c>
+      <c r="D3028" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3028" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3028" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3029">
+      <c r="A3029" t="inlineStr">
+        <is>
+          <t>bf119328-bc19-4b1e-9a68-4fa061adff44</t>
+        </is>
+      </c>
+      <c r="B3029" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3029" t="inlineStr">
+        <is>
+          <t>2026-07-30T20:04:05.190Z</t>
+        </is>
+      </c>
+      <c r="D3029" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3029" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3029" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3030">
+      <c r="A3030" t="inlineStr">
+        <is>
+          <t>0f53eebb-b3dd-4d0b-940b-983014a26733</t>
+        </is>
+      </c>
+      <c r="B3030" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3030" t="inlineStr">
+        <is>
+          <t>2026-07-30T21:10:02.982Z</t>
+        </is>
+      </c>
+      <c r="D3030" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3030" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3030" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3031">
+      <c r="A3031" t="inlineStr">
+        <is>
+          <t>df743b6c-630a-48a4-b18f-c434cafb6d2c</t>
+        </is>
+      </c>
+      <c r="B3031" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3031" t="inlineStr">
+        <is>
+          <t>2026-07-30T21:35:00.313Z</t>
+        </is>
+      </c>
+      <c r="D3031" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3031" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3031" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3032">
+      <c r="A3032" t="inlineStr">
+        <is>
+          <t>6d3520b9-6bb2-4c0d-85b9-821253913e82</t>
+        </is>
+      </c>
+      <c r="B3032" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3032" t="inlineStr">
+        <is>
+          <t>2026-07-30T21:35:17.618Z</t>
+        </is>
+      </c>
+      <c r="D3032" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3032" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3032" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3033">
+      <c r="A3033" t="inlineStr">
+        <is>
+          <t>005baeea-b488-4b0d-9fe2-407c4cad5e01</t>
+        </is>
+      </c>
+      <c r="B3033" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3033" t="inlineStr">
+        <is>
+          <t>2026-07-30T21:37:16.339Z</t>
+        </is>
+      </c>
+      <c r="D3033" t="n">
+        <v>482</v>
+      </c>
+      <c r="E3033" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3033" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3034">
+      <c r="A3034" t="inlineStr">
+        <is>
+          <t>ce33c072-9639-4596-9851-c8bb19aaaea0</t>
+        </is>
+      </c>
+      <c r="B3034" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3034" t="inlineStr">
+        <is>
+          <t>2026-07-30T21:37:21.111Z</t>
+        </is>
+      </c>
+      <c r="D3034" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3034" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3034" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3035">
+      <c r="A3035" t="inlineStr">
+        <is>
+          <t>f18cf789-3328-4527-ba99-a407da8af1ba</t>
+        </is>
+      </c>
+      <c r="B3035" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3035" t="inlineStr">
+        <is>
+          <t>2026-07-30T22:04:09.123Z</t>
+        </is>
+      </c>
+      <c r="D3035" t="n">
+        <v>482</v>
+      </c>
+      <c r="E3035" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3035" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3036">
+      <c r="A3036" t="inlineStr">
+        <is>
+          <t>6f5149be-10c0-42b9-a27e-2b0b9bd7dfdc</t>
+        </is>
+      </c>
+      <c r="B3036" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3036" t="inlineStr">
+        <is>
+          <t>2026-07-30T22:12:51.653Z</t>
+        </is>
+      </c>
+      <c r="D3036" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3036" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3036" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3037">
+      <c r="A3037" t="inlineStr">
+        <is>
+          <t>2c6768ef-b35c-4a45-9057-eb428795e69a</t>
+        </is>
+      </c>
+      <c r="B3037" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3037" t="inlineStr">
+        <is>
+          <t>2026-07-30T22:14:02.849Z</t>
+        </is>
+      </c>
+      <c r="D3037" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3037" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3037" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3038">
+      <c r="A3038" t="inlineStr">
+        <is>
+          <t>245f147d-9461-44cc-94bb-794699147459</t>
+        </is>
+      </c>
+      <c r="B3038" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3038" t="inlineStr">
+        <is>
+          <t>2026-07-30T23:00:53.874Z</t>
+        </is>
+      </c>
+      <c r="D3038" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3038" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3038" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3039">
+      <c r="A3039" t="inlineStr">
+        <is>
+          <t>29990e9b-fa88-4720-a252-73c665130c29</t>
+        </is>
+      </c>
+      <c r="B3039" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3039" t="inlineStr">
+        <is>
+          <t>2026-07-30T23:14:25.185Z</t>
+        </is>
+      </c>
+      <c r="D3039" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3039" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3039" t="inlineStr">
+        <is>
+          <t>Juvenile Delinquency</t>
+        </is>
+      </c>
+    </row>
+    <row r="3040">
+      <c r="A3040" t="inlineStr">
+        <is>
+          <t>173ae1cc-d9c0-4429-bd3d-95fde5b5ac3a</t>
+        </is>
+      </c>
+      <c r="B3040" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3040" t="inlineStr">
+        <is>
+          <t>2026-07-30T23:21:39.771Z</t>
+        </is>
+      </c>
+      <c r="D3040" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3040" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3040" t="inlineStr">
+        <is>
+          <t>Juvenile Delinquency</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3040"/>
+  <dimension ref="A1:F3057"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72728,6 +72728,516 @@
         </is>
       </c>
     </row>
+    <row r="3041">
+      <c r="A3041" t="inlineStr">
+        <is>
+          <t>b1fe0665-98fc-4591-b6fc-c8320a2dd06b</t>
+        </is>
+      </c>
+      <c r="B3041" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3041" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:01:58.697Z</t>
+        </is>
+      </c>
+      <c r="D3041" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3041" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3041" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3042">
+      <c r="A3042" t="inlineStr">
+        <is>
+          <t>d02d8e8a-28ae-4c76-8386-91a664273e20</t>
+        </is>
+      </c>
+      <c r="B3042" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3042" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:58:05.743Z</t>
+        </is>
+      </c>
+      <c r="D3042" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3042" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3042" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3043">
+      <c r="A3043" t="inlineStr">
+        <is>
+          <t>053d9886-65f6-4d31-98b3-65985121f01f</t>
+        </is>
+      </c>
+      <c r="B3043" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3043" t="inlineStr">
+        <is>
+          <t>2026-07-31T01:38:48.642Z</t>
+        </is>
+      </c>
+      <c r="D3043" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3043" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3043" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3044">
+      <c r="A3044" t="inlineStr">
+        <is>
+          <t>07567c65-21e1-4a30-8199-2f65c8bc47ca</t>
+        </is>
+      </c>
+      <c r="B3044" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3044" t="inlineStr">
+        <is>
+          <t>2026-07-31T05:22:13.600Z</t>
+        </is>
+      </c>
+      <c r="D3044" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3044" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3044" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3045">
+      <c r="A3045" t="inlineStr">
+        <is>
+          <t>c086ad14-9ef7-4227-96f2-d80247dedcc0</t>
+        </is>
+      </c>
+      <c r="B3045" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3045" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:17:13.837Z</t>
+        </is>
+      </c>
+      <c r="D3045" t="n">
+        <v>482</v>
+      </c>
+      <c r="E3045" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3045" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3046">
+      <c r="A3046" t="inlineStr">
+        <is>
+          <t>06266408-ff06-4bf5-b3b6-1b98c0cf30c7</t>
+        </is>
+      </c>
+      <c r="B3046" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3046" t="inlineStr">
+        <is>
+          <t>2026-07-31T14:11:04.407Z</t>
+        </is>
+      </c>
+      <c r="D3046" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3046" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3046" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3047">
+      <c r="A3047" t="inlineStr">
+        <is>
+          <t>ec5dda38-bbf1-4912-ad3b-e5e204b28bfb</t>
+        </is>
+      </c>
+      <c r="B3047" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3047" t="inlineStr">
+        <is>
+          <t>2026-07-31T14:43:43.860Z</t>
+        </is>
+      </c>
+      <c r="D3047" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3047" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3047" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3048">
+      <c r="A3048" t="inlineStr">
+        <is>
+          <t>e68b09be-1a94-4db9-8e28-88fb9f8cf61c</t>
+        </is>
+      </c>
+      <c r="B3048" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3048" t="inlineStr">
+        <is>
+          <t>2026-07-31T15:16:18.961Z</t>
+        </is>
+      </c>
+      <c r="D3048" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3048" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3048" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3049">
+      <c r="A3049" t="inlineStr">
+        <is>
+          <t>bd69b4e6-d450-4865-8b64-6aed65dabae3</t>
+        </is>
+      </c>
+      <c r="B3049" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3049" t="inlineStr">
+        <is>
+          <t>2026-07-31T15:59:43.796Z</t>
+        </is>
+      </c>
+      <c r="D3049" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3049" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3049" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3050">
+      <c r="A3050" t="inlineStr">
+        <is>
+          <t>ec9ef048-2376-4d44-b542-6fb43d1b7fec</t>
+        </is>
+      </c>
+      <c r="B3050" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3050" t="inlineStr">
+        <is>
+          <t>2026-07-31T16:00:42.591Z</t>
+        </is>
+      </c>
+      <c r="D3050" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3050" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3050" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3051">
+      <c r="A3051" t="inlineStr">
+        <is>
+          <t>230cfd65-5f3f-49e4-b988-e131d219bde6</t>
+        </is>
+      </c>
+      <c r="B3051" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3051" t="inlineStr">
+        <is>
+          <t>2026-07-31T17:15:29.320Z</t>
+        </is>
+      </c>
+      <c r="D3051" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3051" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3051" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3052">
+      <c r="A3052" t="inlineStr">
+        <is>
+          <t>2e204b9d-9a8b-420c-a5fa-fbe88a4f5f83</t>
+        </is>
+      </c>
+      <c r="B3052" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3052" t="inlineStr">
+        <is>
+          <t>2026-07-31T17:37:57.406Z</t>
+        </is>
+      </c>
+      <c r="D3052" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3052" t="inlineStr">
+        <is>
+          <t>Victim</t>
+        </is>
+      </c>
+      <c r="F3052" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3053">
+      <c r="A3053" t="inlineStr">
+        <is>
+          <t>da60b371-2d80-4a1f-8aab-4bb829bd2673</t>
+        </is>
+      </c>
+      <c r="B3053" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3053" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:11:57.666Z</t>
+        </is>
+      </c>
+      <c r="D3053" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3053" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3053" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3054">
+      <c r="A3054" t="inlineStr">
+        <is>
+          <t>7cce03e4-16d4-47b6-9c09-6e7037cae967</t>
+        </is>
+      </c>
+      <c r="B3054" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3054" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:38:47.844Z</t>
+        </is>
+      </c>
+      <c r="D3054" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3054" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3054" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3055">
+      <c r="A3055" t="inlineStr">
+        <is>
+          <t>0dbef11c-9be6-417b-a785-9047c5005c72</t>
+        </is>
+      </c>
+      <c r="B3055" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3055" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:41:06.595Z</t>
+        </is>
+      </c>
+      <c r="D3055" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3055" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3055" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3056">
+      <c r="A3056" t="inlineStr">
+        <is>
+          <t>d3c5b071-2f8a-4df8-8002-199903897bf2</t>
+        </is>
+      </c>
+      <c r="B3056" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3056" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:45:23.801Z</t>
+        </is>
+      </c>
+      <c r="D3056" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3056" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3056" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3057">
+      <c r="A3057" t="inlineStr">
+        <is>
+          <t>766cad1a-fbbd-4440-aede-537b5bb80f2d</t>
+        </is>
+      </c>
+      <c r="B3057" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3057" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:39:38.457Z</t>
+        </is>
+      </c>
+      <c r="D3057" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3057" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3057" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3057"/>
+  <dimension ref="A1:F3070"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73238,6 +73238,396 @@
         </is>
       </c>
     </row>
+    <row r="3058">
+      <c r="A3058" t="inlineStr">
+        <is>
+          <t>066fe056-75d8-4721-951c-ffa172a05132</t>
+        </is>
+      </c>
+      <c r="B3058" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3058" t="inlineStr">
+        <is>
+          <t>2026-08-01T00:26:30.576Z</t>
+        </is>
+      </c>
+      <c r="D3058" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3058" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3058" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3059">
+      <c r="A3059" t="inlineStr">
+        <is>
+          <t>5e08c47f-4779-4104-889b-8abc8966ce5f</t>
+        </is>
+      </c>
+      <c r="B3059" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3059" t="inlineStr">
+        <is>
+          <t>2026-08-01T01:23:28.374Z</t>
+        </is>
+      </c>
+      <c r="D3059" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3059" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3059" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3060">
+      <c r="A3060" t="inlineStr">
+        <is>
+          <t>91149505-b0bb-4bcf-ab65-8cbdf6602ff4</t>
+        </is>
+      </c>
+      <c r="B3060" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3060" t="inlineStr">
+        <is>
+          <t>2026-08-01T09:43:32.273Z</t>
+        </is>
+      </c>
+      <c r="D3060" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3060" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3060" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3061">
+      <c r="A3061" t="inlineStr">
+        <is>
+          <t>5854b689-5cf7-4c20-a74c-cb60c7622d75</t>
+        </is>
+      </c>
+      <c r="B3061" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3061" t="inlineStr">
+        <is>
+          <t>2026-08-01T18:40:49.634Z</t>
+        </is>
+      </c>
+      <c r="D3061" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3061" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3061" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3062">
+      <c r="A3062" t="inlineStr">
+        <is>
+          <t>4c919263-a8f1-4428-be05-56004c0b7a49</t>
+        </is>
+      </c>
+      <c r="B3062" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3062" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:48:10.627Z</t>
+        </is>
+      </c>
+      <c r="D3062" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3062" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3062" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3063">
+      <c r="A3063" t="inlineStr">
+        <is>
+          <t>e810c4e7-0c96-45e6-8ddc-2e86b87b0526</t>
+        </is>
+      </c>
+      <c r="B3063" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3063" t="inlineStr">
+        <is>
+          <t>2026-08-02T04:00:54.864Z</t>
+        </is>
+      </c>
+      <c r="D3063" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3063" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3063" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3064">
+      <c r="A3064" t="inlineStr">
+        <is>
+          <t>7aa8ab23-afaa-4833-9ee9-91db508ed1be</t>
+        </is>
+      </c>
+      <c r="B3064" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3064" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:08:07.970Z</t>
+        </is>
+      </c>
+      <c r="D3064" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3064" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3064" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3065">
+      <c r="A3065" t="inlineStr">
+        <is>
+          <t>256cbeaa-3388-4ad2-8bd3-b15cf0ab2225</t>
+        </is>
+      </c>
+      <c r="B3065" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3065" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:12:17.308Z</t>
+        </is>
+      </c>
+      <c r="D3065" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3065" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3065" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3066">
+      <c r="A3066" t="inlineStr">
+        <is>
+          <t>1557ce90-f3b2-4415-87c6-7c119d76f364</t>
+        </is>
+      </c>
+      <c r="B3066" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3066" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:16:23.452Z</t>
+        </is>
+      </c>
+      <c r="D3066" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3066" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3066" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3067">
+      <c r="A3067" t="inlineStr">
+        <is>
+          <t>2f7549ef-313f-4637-9d51-a8940720b786</t>
+        </is>
+      </c>
+      <c r="B3067" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3067" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:33.751Z</t>
+        </is>
+      </c>
+      <c r="D3067" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3067" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3067" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3068">
+      <c r="A3068" t="inlineStr">
+        <is>
+          <t>b5fd462f-1ec1-4203-967a-c19293c86136</t>
+        </is>
+      </c>
+      <c r="B3068" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3068" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:48:03.634Z</t>
+        </is>
+      </c>
+      <c r="D3068" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3068" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3068" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3069">
+      <c r="A3069" t="inlineStr">
+        <is>
+          <t>1b91a8dc-4efe-4568-a27e-0d25d95a0e6a</t>
+        </is>
+      </c>
+      <c r="B3069" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3069" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:59:57.815Z</t>
+        </is>
+      </c>
+      <c r="D3069" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3069" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3069" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3070">
+      <c r="A3070" t="inlineStr">
+        <is>
+          <t>3e7f28cf-47b4-4687-b147-81f857afbf0a</t>
+        </is>
+      </c>
+      <c r="B3070" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3070" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00:15.075Z</t>
+        </is>
+      </c>
+      <c r="D3070" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3070" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3070" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3070"/>
+  <dimension ref="A1:F3078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73628,6 +73628,246 @@
         </is>
       </c>
     </row>
+    <row r="3071">
+      <c r="A3071" t="inlineStr">
+        <is>
+          <t>0a9262d6-f8eb-48c8-865b-e293d4a441aa</t>
+        </is>
+      </c>
+      <c r="B3071" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3071" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:18:08.972Z</t>
+        </is>
+      </c>
+      <c r="D3071" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3071" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3071" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3072">
+      <c r="A3072" t="inlineStr">
+        <is>
+          <t>d4dc454b-febf-4f2d-94fe-db3fbf3fcc1f</t>
+        </is>
+      </c>
+      <c r="B3072" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3072" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:13:02.990Z</t>
+        </is>
+      </c>
+      <c r="D3072" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3072" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3072" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3073">
+      <c r="A3073" t="inlineStr">
+        <is>
+          <t>a2d3bbbd-09d2-4b7d-b3f4-35177eaa23a0</t>
+        </is>
+      </c>
+      <c r="B3073" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3073" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:03:09.031Z</t>
+        </is>
+      </c>
+      <c r="D3073" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3073" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3073" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3074">
+      <c r="A3074" t="inlineStr">
+        <is>
+          <t>bf62f7c8-4c85-4101-8932-51881ed473cd</t>
+        </is>
+      </c>
+      <c r="B3074" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3074" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:56:18.695Z</t>
+        </is>
+      </c>
+      <c r="D3074" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3074" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3074" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3075">
+      <c r="A3075" t="inlineStr">
+        <is>
+          <t>204779ad-53f7-4e05-838d-d3c8c788426b</t>
+        </is>
+      </c>
+      <c r="B3075" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3075" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:26:06.090Z</t>
+        </is>
+      </c>
+      <c r="D3075" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3075" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3075" t="inlineStr">
+        <is>
+          <t>Traffic Infraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3076">
+      <c r="A3076" t="inlineStr">
+        <is>
+          <t>a91f0ac2-c8df-4dbf-8221-ea169b162ac4</t>
+        </is>
+      </c>
+      <c r="B3076" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3076" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:21:21.281Z</t>
+        </is>
+      </c>
+      <c r="D3076" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3076" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3076" t="inlineStr">
+        <is>
+          <t>Financial Crime (Embezzlement/Fraud)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3077">
+      <c r="A3077" t="inlineStr">
+        <is>
+          <t>8d154fc9-3203-4016-8094-8312d370387c</t>
+        </is>
+      </c>
+      <c r="B3077" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3077" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:56:00.189Z</t>
+        </is>
+      </c>
+      <c r="D3077" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3077" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3077" t="inlineStr">
+        <is>
+          <t>Stolen Property Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3078">
+      <c r="A3078" t="inlineStr">
+        <is>
+          <t>4925c702-1d3f-4ab1-b222-bb40502526db</t>
+        </is>
+      </c>
+      <c r="B3078" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3078" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:23:44.044Z</t>
+        </is>
+      </c>
+      <c r="D3078" t="n">
+        <v>482</v>
+      </c>
+      <c r="E3078" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3078" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3078"/>
+  <dimension ref="A1:F3095"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73868,6 +73868,516 @@
         </is>
       </c>
     </row>
+    <row r="3079">
+      <c r="A3079" t="inlineStr">
+        <is>
+          <t>5afd40dc-7e25-4ca9-bdec-b7fca2b8272a</t>
+        </is>
+      </c>
+      <c r="B3079" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3079" t="inlineStr">
+        <is>
+          <t>2026-08-04T00:03:32.229Z</t>
+        </is>
+      </c>
+      <c r="D3079" t="n">
+        <v>482</v>
+      </c>
+      <c r="E3079" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3079" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3080">
+      <c r="A3080" t="inlineStr">
+        <is>
+          <t>91b96834-4eca-446e-8ce2-85977cf1a9ae</t>
+        </is>
+      </c>
+      <c r="B3080" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3080" t="inlineStr">
+        <is>
+          <t>2026-08-04T00:28:10.233Z</t>
+        </is>
+      </c>
+      <c r="D3080" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3080" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3080" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3081">
+      <c r="A3081" t="inlineStr">
+        <is>
+          <t>63ce1bf2-b93d-4e53-9b87-c52f32cc32d8</t>
+        </is>
+      </c>
+      <c r="B3081" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3081" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:54:53.019Z</t>
+        </is>
+      </c>
+      <c r="D3081" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3081" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3081" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3082">
+      <c r="A3082" t="inlineStr">
+        <is>
+          <t>89433546-4b71-4a73-8c62-defaec1c4252</t>
+        </is>
+      </c>
+      <c r="B3082" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3082" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:09:58.964Z</t>
+        </is>
+      </c>
+      <c r="D3082" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3082" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3082" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3083">
+      <c r="A3083" t="inlineStr">
+        <is>
+          <t>4d74630c-9d5c-45d9-8ba9-516e2d7dfe50</t>
+        </is>
+      </c>
+      <c r="B3083" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3083" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:19:13.539Z</t>
+        </is>
+      </c>
+      <c r="D3083" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3083" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3083" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3084">
+      <c r="A3084" t="inlineStr">
+        <is>
+          <t>c5b2b8cb-6859-49e0-81f1-958fbc7517cc</t>
+        </is>
+      </c>
+      <c r="B3084" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3084" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:14:02.787Z</t>
+        </is>
+      </c>
+      <c r="D3084" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3084" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3084" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3085">
+      <c r="A3085" t="inlineStr">
+        <is>
+          <t>178fd3cc-c0f0-4585-b37e-c0bfbf8b3eca</t>
+        </is>
+      </c>
+      <c r="B3085" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3085" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:08:14.110Z</t>
+        </is>
+      </c>
+      <c r="D3085" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3085" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3085" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3086">
+      <c r="A3086" t="inlineStr">
+        <is>
+          <t>510b5db9-4761-4dbc-8934-4139a8ed3fcc</t>
+        </is>
+      </c>
+      <c r="B3086" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3086" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:26:09.488Z</t>
+        </is>
+      </c>
+      <c r="D3086" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3086" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3086" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3087">
+      <c r="A3087" t="inlineStr">
+        <is>
+          <t>c17e425a-e3ac-4038-a53e-424dd5c78b71</t>
+        </is>
+      </c>
+      <c r="B3087" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3087" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:30:02.579Z</t>
+        </is>
+      </c>
+      <c r="D3087" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3087" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3087" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3088">
+      <c r="A3088" t="inlineStr">
+        <is>
+          <t>606c91e2-be09-4ead-962a-d9cc3969f7f1</t>
+        </is>
+      </c>
+      <c r="B3088" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3088" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:30:50.233Z</t>
+        </is>
+      </c>
+      <c r="D3088" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3088" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3088" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3089">
+      <c r="A3089" t="inlineStr">
+        <is>
+          <t>10119074-6538-47ee-b720-055734a00f72</t>
+        </is>
+      </c>
+      <c r="B3089" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3089" t="inlineStr">
+        <is>
+          <t>2026-08-04T19:55:46.539Z</t>
+        </is>
+      </c>
+      <c r="D3089" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3089" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3089" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3090">
+      <c r="A3090" t="inlineStr">
+        <is>
+          <t>d6e3c5cd-1177-4fe6-b70a-be2f4076f8ea</t>
+        </is>
+      </c>
+      <c r="B3090" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3090" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:38:42.946Z</t>
+        </is>
+      </c>
+      <c r="D3090" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3090" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3090" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3091">
+      <c r="A3091" t="inlineStr">
+        <is>
+          <t>792edeff-e773-4187-87cc-b08615fd2160</t>
+        </is>
+      </c>
+      <c r="B3091" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3091" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:43:23.069Z</t>
+        </is>
+      </c>
+      <c r="D3091" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3091" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3091" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3092">
+      <c r="A3092" t="inlineStr">
+        <is>
+          <t>5f85d65a-66cf-4b06-b858-f19ae03ea4f5</t>
+        </is>
+      </c>
+      <c r="B3092" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3092" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:18:39.937Z</t>
+        </is>
+      </c>
+      <c r="D3092" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3092" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3092" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3093">
+      <c r="A3093" t="inlineStr">
+        <is>
+          <t>7b1225dd-1c43-4926-a2f8-5e3d2d6ca141</t>
+        </is>
+      </c>
+      <c r="B3093" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3093" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:43:49.571Z</t>
+        </is>
+      </c>
+      <c r="D3093" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3093" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3093" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3094">
+      <c r="A3094" t="inlineStr">
+        <is>
+          <t>e7fc6e66-fd07-47e9-9aa7-162092ba62d5</t>
+        </is>
+      </c>
+      <c r="B3094" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3094" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:17:08.901Z</t>
+        </is>
+      </c>
+      <c r="D3094" t="n">
+        <v>482</v>
+      </c>
+      <c r="E3094" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3094" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3095">
+      <c r="A3095" t="inlineStr">
+        <is>
+          <t>9ededcc5-adc6-466c-8f52-3d21bebe64e6</t>
+        </is>
+      </c>
+      <c r="B3095" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3095" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:19:47.835Z</t>
+        </is>
+      </c>
+      <c r="D3095" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3095" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3095" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3095"/>
+  <dimension ref="A1:F3108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74378,6 +74378,396 @@
         </is>
       </c>
     </row>
+    <row r="3096">
+      <c r="A3096" t="inlineStr">
+        <is>
+          <t>59836bec-54ec-4f56-b370-b2f083dc5440</t>
+        </is>
+      </c>
+      <c r="B3096" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3096" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:32:04.534Z</t>
+        </is>
+      </c>
+      <c r="D3096" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3096" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3096" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3097">
+      <c r="A3097" t="inlineStr">
+        <is>
+          <t>d5dc4489-a4b4-4cca-9c98-293139bf993a</t>
+        </is>
+      </c>
+      <c r="B3097" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3097" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:56:44.366Z</t>
+        </is>
+      </c>
+      <c r="D3097" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3097" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3097" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3098">
+      <c r="A3098" t="inlineStr">
+        <is>
+          <t>180a9ae5-049d-42df-b29f-1b5ec4d535a6</t>
+        </is>
+      </c>
+      <c r="B3098" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3098" t="inlineStr">
+        <is>
+          <t>2026-08-05T05:13:50.476Z</t>
+        </is>
+      </c>
+      <c r="D3098" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3098" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3098" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3099">
+      <c r="A3099" t="inlineStr">
+        <is>
+          <t>ed503c2f-a3db-467f-ba79-38ae61ff5d2d</t>
+        </is>
+      </c>
+      <c r="B3099" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3099" t="inlineStr">
+        <is>
+          <t>2026-08-05T05:29:02.625Z</t>
+        </is>
+      </c>
+      <c r="D3099" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3099" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3099" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3100">
+      <c r="A3100" t="inlineStr">
+        <is>
+          <t>2fdb5244-d85c-4786-a15a-c23110f9920a</t>
+        </is>
+      </c>
+      <c r="B3100" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3100" t="inlineStr">
+        <is>
+          <t>2026-08-05T06:43:18.749Z</t>
+        </is>
+      </c>
+      <c r="D3100" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3100" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3100" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3101">
+      <c r="A3101" t="inlineStr">
+        <is>
+          <t>34a562f2-1fe1-4955-bf0a-0bd434ca5255</t>
+        </is>
+      </c>
+      <c r="B3101" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3101" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:18:16.934Z</t>
+        </is>
+      </c>
+      <c r="D3101" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3101" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3101" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3102">
+      <c r="A3102" t="inlineStr">
+        <is>
+          <t>7e6706d1-314a-4326-8f71-628aca210649</t>
+        </is>
+      </c>
+      <c r="B3102" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3102" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:41:55.643Z</t>
+        </is>
+      </c>
+      <c r="D3102" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3102" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3102" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3103">
+      <c r="A3103" t="inlineStr">
+        <is>
+          <t>85d5e111-152b-419b-b24b-89e8babddb98</t>
+        </is>
+      </c>
+      <c r="B3103" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3103" t="inlineStr">
+        <is>
+          <t>2026-08-05T15:47:24.725Z</t>
+        </is>
+      </c>
+      <c r="D3103" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3103" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3103" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3104">
+      <c r="A3104" t="inlineStr">
+        <is>
+          <t>463a0455-d925-440c-9656-3cd3ccbbe264</t>
+        </is>
+      </c>
+      <c r="B3104" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3104" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:24:08.938Z</t>
+        </is>
+      </c>
+      <c r="D3104" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3104" t="inlineStr">
+        <is>
+          <t>Agency Assist</t>
+        </is>
+      </c>
+      <c r="F3104" t="inlineStr">
+        <is>
+          <t>City Planning/Traffic Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3105">
+      <c r="A3105" t="inlineStr">
+        <is>
+          <t>182413e0-356f-4a50-b6de-564d2dddb83c</t>
+        </is>
+      </c>
+      <c r="B3105" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3105" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:16:21.214Z</t>
+        </is>
+      </c>
+      <c r="D3105" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3105" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3105" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3106">
+      <c r="A3106" t="inlineStr">
+        <is>
+          <t>72c009fb-a290-4971-826e-ea1fd1c987db</t>
+        </is>
+      </c>
+      <c r="B3106" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3106" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:34:04.730Z</t>
+        </is>
+      </c>
+      <c r="D3106" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3106" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3106" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3107">
+      <c r="A3107" t="inlineStr">
+        <is>
+          <t>a1f7af55-8cdf-449e-bcef-44f44df2697c</t>
+        </is>
+      </c>
+      <c r="B3107" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3107" t="inlineStr">
+        <is>
+          <t>2026-08-05T23:14:12.541Z</t>
+        </is>
+      </c>
+      <c r="D3107" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3107" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3107" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3108">
+      <c r="A3108" t="inlineStr">
+        <is>
+          <t>15d9ec43-daa1-422d-b033-ed678d53663b</t>
+        </is>
+      </c>
+      <c r="B3108" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3108" t="inlineStr">
+        <is>
+          <t>2026-08-05T23:34:04.538Z</t>
+        </is>
+      </c>
+      <c r="D3108" t="n">
+        <v>558</v>
+      </c>
+      <c r="E3108" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3108" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3108"/>
+  <dimension ref="A1:F3110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74768,6 +74768,66 @@
         </is>
       </c>
     </row>
+    <row r="3109">
+      <c r="A3109" t="inlineStr">
+        <is>
+          <t>d9f5dce8-e4b5-4110-8c55-f6e8ed5cef3b</t>
+        </is>
+      </c>
+      <c r="B3109" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3109" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:13:54.909Z</t>
+        </is>
+      </c>
+      <c r="D3109" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3109" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3109" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3110">
+      <c r="A3110" t="inlineStr">
+        <is>
+          <t>fbe14c51-207d-4f79-a8b0-75d72d5a15af</t>
+        </is>
+      </c>
+      <c r="B3110" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3110" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:41:43.723Z</t>
+        </is>
+      </c>
+      <c r="D3110" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3110" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3110" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3110"/>
+  <dimension ref="A1:F3119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74828,6 +74828,276 @@
         </is>
       </c>
     </row>
+    <row r="3111">
+      <c r="A3111" t="inlineStr">
+        <is>
+          <t>c9e00508-c7e4-464c-8f07-58dbe95a3f52</t>
+        </is>
+      </c>
+      <c r="B3111" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3111" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:02:41.440Z</t>
+        </is>
+      </c>
+      <c r="D3111" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3111" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3111" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3112">
+      <c r="A3112" t="inlineStr">
+        <is>
+          <t>50511d95-dd3a-421f-99e6-ba151228c1c1</t>
+        </is>
+      </c>
+      <c r="B3112" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3112" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:43:31.136Z</t>
+        </is>
+      </c>
+      <c r="D3112" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3112" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3112" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3113">
+      <c r="A3113" t="inlineStr">
+        <is>
+          <t>0b36ccde-91cd-4397-95f4-1419c73f263b</t>
+        </is>
+      </c>
+      <c r="B3113" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3113" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:44:21.015Z</t>
+        </is>
+      </c>
+      <c r="D3113" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3113" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3113" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3114">
+      <c r="A3114" t="inlineStr">
+        <is>
+          <t>983956c3-436d-4413-af2d-38bd8a3bc2c8</t>
+        </is>
+      </c>
+      <c r="B3114" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3114" t="inlineStr">
+        <is>
+          <t>2026-08-07T16:41:31.434Z</t>
+        </is>
+      </c>
+      <c r="D3114" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3114" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3114" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3115">
+      <c r="A3115" t="inlineStr">
+        <is>
+          <t>145cadfb-2044-4a7b-9590-c2dcc6328200</t>
+        </is>
+      </c>
+      <c r="B3115" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3115" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:02:48.900Z</t>
+        </is>
+      </c>
+      <c r="D3115" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3115" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3115" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3116">
+      <c r="A3116" t="inlineStr">
+        <is>
+          <t>e27b392a-b4ac-4c4a-bce3-7ed026056322</t>
+        </is>
+      </c>
+      <c r="B3116" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3116" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:11:11.163Z</t>
+        </is>
+      </c>
+      <c r="D3116" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3116" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3116" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3117">
+      <c r="A3117" t="inlineStr">
+        <is>
+          <t>16b016da-35e9-4845-8198-f78360e185cb</t>
+        </is>
+      </c>
+      <c r="B3117" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3117" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:23:55.789Z</t>
+        </is>
+      </c>
+      <c r="D3117" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3117" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3117" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3118">
+      <c r="A3118" t="inlineStr">
+        <is>
+          <t>c1583d43-ee9c-4f6e-b26e-123dbd63ecc2</t>
+        </is>
+      </c>
+      <c r="B3118" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3118" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:24:15.793Z</t>
+        </is>
+      </c>
+      <c r="D3118" t="n">
+        <v>482</v>
+      </c>
+      <c r="E3118" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3118" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3119">
+      <c r="A3119" t="inlineStr">
+        <is>
+          <t>17c5a39a-d6eb-47f8-bd7f-8eeda30a6d4e</t>
+        </is>
+      </c>
+      <c r="B3119" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3119" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:32:06.602Z</t>
+        </is>
+      </c>
+      <c r="D3119" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3119" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3119" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3119"/>
+  <dimension ref="A1:F3122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75098,6 +75098,96 @@
         </is>
       </c>
     </row>
+    <row r="3120">
+      <c r="A3120" t="inlineStr">
+        <is>
+          <t>ae777f3f-8bcd-4fb1-b3a8-3a5adae92501</t>
+        </is>
+      </c>
+      <c r="B3120" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3120" t="inlineStr">
+        <is>
+          <t>2026-08-08T13:42:52.344Z</t>
+        </is>
+      </c>
+      <c r="D3120" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3120" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3120" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3121">
+      <c r="A3121" t="inlineStr">
+        <is>
+          <t>9f6d9b86-3f3b-4976-b403-09111c884059</t>
+        </is>
+      </c>
+      <c r="B3121" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3121" t="inlineStr">
+        <is>
+          <t>2026-08-08T19:39:24.599Z</t>
+        </is>
+      </c>
+      <c r="D3121" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3121" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3121" t="inlineStr">
+        <is>
+          <t>Welfare Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="3122">
+      <c r="A3122" t="inlineStr">
+        <is>
+          <t>441c4012-8afb-482b-8f61-a3b73847f3ad</t>
+        </is>
+      </c>
+      <c r="B3122" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3122" t="inlineStr">
+        <is>
+          <t>2026-08-08T23:47:48.333Z</t>
+        </is>
+      </c>
+      <c r="D3122" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3122" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3122" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3122"/>
+  <dimension ref="A1:F3124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75188,6 +75188,66 @@
         </is>
       </c>
     </row>
+    <row r="3123">
+      <c r="A3123" t="inlineStr">
+        <is>
+          <t>9af06951-1550-434a-97fd-2f7e6ecaeb3d</t>
+        </is>
+      </c>
+      <c r="B3123" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3123" t="inlineStr">
+        <is>
+          <t>2026-08-09T00:01:54.112Z</t>
+        </is>
+      </c>
+      <c r="D3123" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3123" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3123" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3124">
+      <c r="A3124" t="inlineStr">
+        <is>
+          <t>8b14784e-110c-4506-93bd-25081c79d5b3</t>
+        </is>
+      </c>
+      <c r="B3124" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3124" t="inlineStr">
+        <is>
+          <t>2026-08-09T16:26:02.956Z</t>
+        </is>
+      </c>
+      <c r="D3124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3124" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3124" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3124"/>
+  <dimension ref="A1:F3127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75248,6 +75248,96 @@
         </is>
       </c>
     </row>
+    <row r="3125">
+      <c r="A3125" t="inlineStr">
+        <is>
+          <t>8c3ce08d-bd97-471e-9222-d714191bcbf6</t>
+        </is>
+      </c>
+      <c r="B3125" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3125" t="inlineStr">
+        <is>
+          <t>2026-08-10T06:31:24.666Z</t>
+        </is>
+      </c>
+      <c r="D3125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3125" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3125" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3126">
+      <c r="A3126" t="inlineStr">
+        <is>
+          <t>31a7eb71-6299-40e8-8927-e2f321ab5c7f</t>
+        </is>
+      </c>
+      <c r="B3126" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3126" t="inlineStr">
+        <is>
+          <t>2026-08-10T14:34:56.662Z</t>
+        </is>
+      </c>
+      <c r="D3126" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3126" t="inlineStr">
+        <is>
+          <t>Agency Assist</t>
+        </is>
+      </c>
+      <c r="F3126" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3127">
+      <c r="A3127" t="inlineStr">
+        <is>
+          <t>4290b6a7-dd43-4b8c-9e52-88c4618f6b9d</t>
+        </is>
+      </c>
+      <c r="B3127" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3127" t="inlineStr">
+        <is>
+          <t>2026-08-10T22:14:42.980Z</t>
+        </is>
+      </c>
+      <c r="D3127" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3127" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3127" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3127"/>
+  <dimension ref="A1:F3133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75338,6 +75338,186 @@
         </is>
       </c>
     </row>
+    <row r="3128">
+      <c r="A3128" t="inlineStr">
+        <is>
+          <t>b1375660-9a06-4987-b50f-23bf9d81a716</t>
+        </is>
+      </c>
+      <c r="B3128" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3128" t="inlineStr">
+        <is>
+          <t>2026-08-11T03:52:20.133Z</t>
+        </is>
+      </c>
+      <c r="D3128" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3128" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3128" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3129">
+      <c r="A3129" t="inlineStr">
+        <is>
+          <t>f986ec3f-196a-4b76-b2ac-3b8254b7845f</t>
+        </is>
+      </c>
+      <c r="B3129" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3129" t="inlineStr">
+        <is>
+          <t>2026-08-11T11:10:53.625Z</t>
+        </is>
+      </c>
+      <c r="D3129" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3129" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3129" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3130">
+      <c r="A3130" t="inlineStr">
+        <is>
+          <t>ea1d50f0-4a8e-4921-8e85-43afd4818dc8</t>
+        </is>
+      </c>
+      <c r="B3130" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3130" t="inlineStr">
+        <is>
+          <t>2026-08-11T14:49:02.456Z</t>
+        </is>
+      </c>
+      <c r="D3130" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3130" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3130" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3131">
+      <c r="A3131" t="inlineStr">
+        <is>
+          <t>85b2f4aa-6946-473a-a34a-421ecde37aa8</t>
+        </is>
+      </c>
+      <c r="B3131" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3131" t="inlineStr">
+        <is>
+          <t>2026-08-11T15:41:47.481Z</t>
+        </is>
+      </c>
+      <c r="D3131" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3131" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3131" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3132">
+      <c r="A3132" t="inlineStr">
+        <is>
+          <t>df2f5f8d-79c4-4f37-84e9-1ba4ddc5c83b</t>
+        </is>
+      </c>
+      <c r="B3132" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3132" t="inlineStr">
+        <is>
+          <t>2026-08-11T18:41:51.488Z</t>
+        </is>
+      </c>
+      <c r="D3132" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3132" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3132" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3133">
+      <c r="A3133" t="inlineStr">
+        <is>
+          <t>c488f397-79c3-4df8-a8ab-d18f0a3f48c4</t>
+        </is>
+      </c>
+      <c r="B3133" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3133" t="inlineStr">
+        <is>
+          <t>2026-08-11T22:29:12.297Z</t>
+        </is>
+      </c>
+      <c r="D3133" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3133" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3133" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3133"/>
+  <dimension ref="A1:F3149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75518,6 +75518,486 @@
         </is>
       </c>
     </row>
+    <row r="3134">
+      <c r="A3134" t="inlineStr">
+        <is>
+          <t>8f7bb7b7-b72e-462f-8999-cab86a70f2d6</t>
+        </is>
+      </c>
+      <c r="B3134" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3134" t="inlineStr">
+        <is>
+          <t>2026-08-12T04:33:26.176Z</t>
+        </is>
+      </c>
+      <c r="D3134" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3134" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3134" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3135">
+      <c r="A3135" t="inlineStr">
+        <is>
+          <t>a46a70de-3119-4622-b5b2-a1e9e29f4ccb</t>
+        </is>
+      </c>
+      <c r="B3135" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3135" t="inlineStr">
+        <is>
+          <t>2026-08-12T04:42:03.547Z</t>
+        </is>
+      </c>
+      <c r="D3135" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3135" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3135" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3136">
+      <c r="A3136" t="inlineStr">
+        <is>
+          <t>b54dffb7-7228-417f-a3e3-000b41dd4438</t>
+        </is>
+      </c>
+      <c r="B3136" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3136" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:12:57.083Z</t>
+        </is>
+      </c>
+      <c r="D3136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3136" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3136" t="inlineStr">
+        <is>
+          <t>Financial Crime (Embezzlement/Fraud)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3137">
+      <c r="A3137" t="inlineStr">
+        <is>
+          <t>caf48846-7560-4f02-9c1a-7b404e831ecc</t>
+        </is>
+      </c>
+      <c r="B3137" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3137" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:14:54.245Z</t>
+        </is>
+      </c>
+      <c r="D3137" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3137" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3137" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3138">
+      <c r="A3138" t="inlineStr">
+        <is>
+          <t>db8df627-eb11-4830-b6c4-1debe5de2ba4</t>
+        </is>
+      </c>
+      <c r="B3138" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3138" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:31:45.226Z</t>
+        </is>
+      </c>
+      <c r="D3138" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3138" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3138" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3139">
+      <c r="A3139" t="inlineStr">
+        <is>
+          <t>44fe9e21-b042-423d-9600-8efa4ef6eca0</t>
+        </is>
+      </c>
+      <c r="B3139" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3139" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:49:49.013Z</t>
+        </is>
+      </c>
+      <c r="D3139" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3139" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3139" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3140">
+      <c r="A3140" t="inlineStr">
+        <is>
+          <t>229fc9ea-bed7-4e95-95e1-aeba4b82f67f</t>
+        </is>
+      </c>
+      <c r="B3140" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3140" t="inlineStr">
+        <is>
+          <t>2026-08-12T06:01:33.431Z</t>
+        </is>
+      </c>
+      <c r="D3140" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3140" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3140" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3141">
+      <c r="A3141" t="inlineStr">
+        <is>
+          <t>fc9349f7-7740-4a3f-bb6d-67e4f4be0df6</t>
+        </is>
+      </c>
+      <c r="B3141" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3141" t="inlineStr">
+        <is>
+          <t>2026-08-12T06:03:09.139Z</t>
+        </is>
+      </c>
+      <c r="D3141" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3141" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3141" t="inlineStr">
+        <is>
+          <t>Financial Crime (Embezzlement/Fraud)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3142">
+      <c r="A3142" t="inlineStr">
+        <is>
+          <t>f9e00bae-bc74-4f75-a7d8-f03b496951e3</t>
+        </is>
+      </c>
+      <c r="B3142" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3142" t="inlineStr">
+        <is>
+          <t>2026-08-12T06:06:41.207Z</t>
+        </is>
+      </c>
+      <c r="D3142" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3142" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3142" t="inlineStr">
+        <is>
+          <t>Financial Crime (Embezzlement/Fraud)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3143">
+      <c r="A3143" t="inlineStr">
+        <is>
+          <t>cd1b8a74-30bf-43c2-8e94-e42d31e6cf41</t>
+        </is>
+      </c>
+      <c r="B3143" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3143" t="inlineStr">
+        <is>
+          <t>2026-08-12T07:46:02.651Z</t>
+        </is>
+      </c>
+      <c r="D3143" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3143" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3143" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3144">
+      <c r="A3144" t="inlineStr">
+        <is>
+          <t>ebc2ecdb-7646-46b0-9c23-7547a0f5e397</t>
+        </is>
+      </c>
+      <c r="B3144" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3144" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:28:08.461Z</t>
+        </is>
+      </c>
+      <c r="D3144" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3144" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3144" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3145">
+      <c r="A3145" t="inlineStr">
+        <is>
+          <t>2c437d6f-71a4-4df3-ae04-724ef43e4f98</t>
+        </is>
+      </c>
+      <c r="B3145" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3145" t="inlineStr">
+        <is>
+          <t>2026-08-12T10:41:24.122Z</t>
+        </is>
+      </c>
+      <c r="D3145" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3145" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3145" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3146">
+      <c r="A3146" t="inlineStr">
+        <is>
+          <t>e44cf8e1-b579-46ad-ab5b-fae748c22304</t>
+        </is>
+      </c>
+      <c r="B3146" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3146" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:02:48.110Z</t>
+        </is>
+      </c>
+      <c r="D3146" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3146" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3146" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3147">
+      <c r="A3147" t="inlineStr">
+        <is>
+          <t>a79baeb7-5098-43ae-94e6-adae01a2a333</t>
+        </is>
+      </c>
+      <c r="B3147" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3147" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:04:00.031Z</t>
+        </is>
+      </c>
+      <c r="D3147" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3147" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3147" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3148">
+      <c r="A3148" t="inlineStr">
+        <is>
+          <t>2088d2c6-0c76-4ef0-b86e-e56b9e6d2013</t>
+        </is>
+      </c>
+      <c r="B3148" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3148" t="inlineStr">
+        <is>
+          <t>2026-08-12T20:41:33.136Z</t>
+        </is>
+      </c>
+      <c r="D3148" t="n">
+        <v>482</v>
+      </c>
+      <c r="E3148" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3148" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3149">
+      <c r="A3149" t="inlineStr">
+        <is>
+          <t>8db071a1-b965-473c-ab51-8d5392b26978</t>
+        </is>
+      </c>
+      <c r="B3149" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3149" t="inlineStr">
+        <is>
+          <t>2026-08-12T22:09:16.430Z</t>
+        </is>
+      </c>
+      <c r="D3149" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3149" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3149" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3149"/>
+  <dimension ref="A1:F3154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75998,6 +75998,156 @@
         </is>
       </c>
     </row>
+    <row r="3150">
+      <c r="A3150" t="inlineStr">
+        <is>
+          <t>60795948-43e3-4e3e-844a-faaf80a7cc40</t>
+        </is>
+      </c>
+      <c r="B3150" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3150" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:30:26.712Z</t>
+        </is>
+      </c>
+      <c r="D3150" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3150" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3150" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3151">
+      <c r="A3151" t="inlineStr">
+        <is>
+          <t>d2f2c3bb-06ed-4b72-ba1d-1360ee72e072</t>
+        </is>
+      </c>
+      <c r="B3151" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3151" t="inlineStr">
+        <is>
+          <t>2026-08-13T04:42:20.505Z</t>
+        </is>
+      </c>
+      <c r="D3151" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3151" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3151" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3152">
+      <c r="A3152" t="inlineStr">
+        <is>
+          <t>5ade60e6-7b68-42eb-8942-fa302b197c90</t>
+        </is>
+      </c>
+      <c r="B3152" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3152" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:20:12.214Z</t>
+        </is>
+      </c>
+      <c r="D3152" t="n">
+        <v>523</v>
+      </c>
+      <c r="E3152" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3152" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3153">
+      <c r="A3153" t="inlineStr">
+        <is>
+          <t>cc597cdf-aeaf-470b-a962-de38c2292d9b</t>
+        </is>
+      </c>
+      <c r="B3153" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3153" t="inlineStr">
+        <is>
+          <t>2026-08-13T19:26:49.004Z</t>
+        </is>
+      </c>
+      <c r="D3153" t="n">
+        <v>557</v>
+      </c>
+      <c r="E3153" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3153" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3154">
+      <c r="A3154" t="inlineStr">
+        <is>
+          <t>a2acde2f-c850-4832-994a-61fc4382cee5</t>
+        </is>
+      </c>
+      <c r="B3154" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3154" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:03:46.636Z</t>
+        </is>
+      </c>
+      <c r="D3154" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3154" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3154" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3154"/>
+  <dimension ref="A1:F3158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76148,6 +76148,126 @@
         </is>
       </c>
     </row>
+    <row r="3155">
+      <c r="A3155" t="inlineStr">
+        <is>
+          <t>f267e772-155d-475b-836b-0ea7c33e4142</t>
+        </is>
+      </c>
+      <c r="B3155" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3155" t="inlineStr">
+        <is>
+          <t>2026-08-14T14:42:33.080Z</t>
+        </is>
+      </c>
+      <c r="D3155" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3155" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3155" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3156">
+      <c r="A3156" t="inlineStr">
+        <is>
+          <t>11028d48-b033-4998-8883-4d778a69f99b</t>
+        </is>
+      </c>
+      <c r="B3156" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3156" t="inlineStr">
+        <is>
+          <t>2026-08-14T15:59:52.488Z</t>
+        </is>
+      </c>
+      <c r="D3156" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3156" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3156" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3157">
+      <c r="A3157" t="inlineStr">
+        <is>
+          <t>a73d1ebf-f451-4878-9f15-7324e23bf68e</t>
+        </is>
+      </c>
+      <c r="B3157" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3157" t="inlineStr">
+        <is>
+          <t>2026-08-14T17:50:55.680Z</t>
+        </is>
+      </c>
+      <c r="D3157" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3157" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3157" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3158">
+      <c r="A3158" t="inlineStr">
+        <is>
+          <t>47cc099b-bbbb-47fa-a37d-1b5545b59bb8</t>
+        </is>
+      </c>
+      <c r="B3158" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3158" t="inlineStr">
+        <is>
+          <t>2026-08-14T21:52:34.213Z</t>
+        </is>
+      </c>
+      <c r="D3158" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3158" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3158" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3158"/>
+  <dimension ref="A1:F3166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76268,6 +76268,246 @@
         </is>
       </c>
     </row>
+    <row r="3159">
+      <c r="A3159" t="inlineStr">
+        <is>
+          <t>ed542169-2081-4a4e-b65f-d8767f45d175</t>
+        </is>
+      </c>
+      <c r="B3159" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3159" t="inlineStr">
+        <is>
+          <t>2026-08-15T02:57:21.315Z</t>
+        </is>
+      </c>
+      <c r="D3159" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3159" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3159" t="inlineStr">
+        <is>
+          <t>Stolen Property Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3160">
+      <c r="A3160" t="inlineStr">
+        <is>
+          <t>6a70e52d-f648-425a-ae76-e2fe698f22fc</t>
+        </is>
+      </c>
+      <c r="B3160" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3160" t="inlineStr">
+        <is>
+          <t>2026-08-15T03:10:31.770Z</t>
+        </is>
+      </c>
+      <c r="D3160" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3160" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3160" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3161">
+      <c r="A3161" t="inlineStr">
+        <is>
+          <t>ce1cce6c-9584-47bf-866d-5c645def31a7</t>
+        </is>
+      </c>
+      <c r="B3161" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3161" t="inlineStr">
+        <is>
+          <t>2026-08-15T03:11:51.106Z</t>
+        </is>
+      </c>
+      <c r="D3161" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3161" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3161" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3162">
+      <c r="A3162" t="inlineStr">
+        <is>
+          <t>9da9a6de-328b-4349-a4eb-15d3b7835dbd</t>
+        </is>
+      </c>
+      <c r="B3162" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3162" t="inlineStr">
+        <is>
+          <t>2026-08-15T10:14:48.769Z</t>
+        </is>
+      </c>
+      <c r="D3162" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3162" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3162" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3163">
+      <c r="A3163" t="inlineStr">
+        <is>
+          <t>ff2b8e58-c77a-42c3-bba0-0a6f06471951</t>
+        </is>
+      </c>
+      <c r="B3163" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3163" t="inlineStr">
+        <is>
+          <t>2026-08-15T11:50:35.893Z</t>
+        </is>
+      </c>
+      <c r="D3163" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3163" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3163" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3164">
+      <c r="A3164" t="inlineStr">
+        <is>
+          <t>95d7ed84-7d26-44a3-b757-3d7aa2a67465</t>
+        </is>
+      </c>
+      <c r="B3164" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3164" t="inlineStr">
+        <is>
+          <t>2026-08-15T12:00:13.883Z</t>
+        </is>
+      </c>
+      <c r="D3164" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3164" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3164" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3165">
+      <c r="A3165" t="inlineStr">
+        <is>
+          <t>818a715b-b8c1-4c4a-825c-267376adefbd</t>
+        </is>
+      </c>
+      <c r="B3165" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3165" t="inlineStr">
+        <is>
+          <t>2026-08-15T15:26:18.290Z</t>
+        </is>
+      </c>
+      <c r="D3165" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3165" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3165" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3166">
+      <c r="A3166" t="inlineStr">
+        <is>
+          <t>1ed62135-04fb-4f47-8e76-32b5ba01f540</t>
+        </is>
+      </c>
+      <c r="B3166" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3166" t="inlineStr">
+        <is>
+          <t>2026-08-15T15:51:25.947Z</t>
+        </is>
+      </c>
+      <c r="D3166" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3166" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3166" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3166"/>
+  <dimension ref="A1:F3191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76508,6 +76508,756 @@
         </is>
       </c>
     </row>
+    <row r="3167">
+      <c r="A3167" t="inlineStr">
+        <is>
+          <t>310f4651-0b04-4831-848d-035dc4ceefa5</t>
+        </is>
+      </c>
+      <c r="B3167" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3167" t="inlineStr">
+        <is>
+          <t>2026-08-16T00:21:47.365Z</t>
+        </is>
+      </c>
+      <c r="D3167" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3167" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3167" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3168">
+      <c r="A3168" t="inlineStr">
+        <is>
+          <t>c8015bba-4cc0-432d-bf5d-55aa2621831d</t>
+        </is>
+      </c>
+      <c r="B3168" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3168" t="inlineStr">
+        <is>
+          <t>2026-08-16T00:48:27.666Z</t>
+        </is>
+      </c>
+      <c r="D3168" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3168" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3168" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3169">
+      <c r="A3169" t="inlineStr">
+        <is>
+          <t>57edd282-af79-48c9-8cac-de5d308a79b8</t>
+        </is>
+      </c>
+      <c r="B3169" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3169" t="inlineStr">
+        <is>
+          <t>2026-08-16T02:40:47.025Z</t>
+        </is>
+      </c>
+      <c r="D3169" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3169" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3169" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3170">
+      <c r="A3170" t="inlineStr">
+        <is>
+          <t>6bfb4c8f-f208-4f1d-a033-fd0cb934e9d0</t>
+        </is>
+      </c>
+      <c r="B3170" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3170" t="inlineStr">
+        <is>
+          <t>2026-08-16T05:07:09.410Z</t>
+        </is>
+      </c>
+      <c r="D3170" t="n">
+        <v>553</v>
+      </c>
+      <c r="E3170" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3170" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3171">
+      <c r="A3171" t="inlineStr">
+        <is>
+          <t>3ce09e97-121d-4c58-b7c7-f609bc58b677</t>
+        </is>
+      </c>
+      <c r="B3171" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3171" t="inlineStr">
+        <is>
+          <t>2026-08-16T07:34:59.083Z</t>
+        </is>
+      </c>
+      <c r="D3171" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3171" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3171" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3172">
+      <c r="A3172" t="inlineStr">
+        <is>
+          <t>86ed69c2-667a-4548-acb1-7e3c7ba64ddd</t>
+        </is>
+      </c>
+      <c r="B3172" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3172" t="inlineStr">
+        <is>
+          <t>2026-08-17T04:53:05.697Z</t>
+        </is>
+      </c>
+      <c r="D3172" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3172" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3172" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3173">
+      <c r="A3173" t="inlineStr">
+        <is>
+          <t>ae8de006-1b31-495a-9c1a-6def4b1491c7</t>
+        </is>
+      </c>
+      <c r="B3173" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3173" t="inlineStr">
+        <is>
+          <t>2026-08-17T06:15:54.516Z</t>
+        </is>
+      </c>
+      <c r="D3173" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3173" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3173" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3174">
+      <c r="A3174" t="inlineStr">
+        <is>
+          <t>f6dc14f3-7c01-47b8-9617-de1bc675956c</t>
+        </is>
+      </c>
+      <c r="B3174" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3174" t="inlineStr">
+        <is>
+          <t>2026-08-17T07:24:27.351Z</t>
+        </is>
+      </c>
+      <c r="D3174" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3174" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3174" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3175">
+      <c r="A3175" t="inlineStr">
+        <is>
+          <t>cba5d091-50e2-49f3-92c0-57a673cbc68c</t>
+        </is>
+      </c>
+      <c r="B3175" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3175" t="inlineStr">
+        <is>
+          <t>2026-08-17T08:58:56.436Z</t>
+        </is>
+      </c>
+      <c r="D3175" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3175" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3175" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3176">
+      <c r="A3176" t="inlineStr">
+        <is>
+          <t>e7f51a7c-bd81-4527-bce8-6db8b78739e9</t>
+        </is>
+      </c>
+      <c r="B3176" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3176" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:04:46.728Z</t>
+        </is>
+      </c>
+      <c r="D3176" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3176" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3176" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3177">
+      <c r="A3177" t="inlineStr">
+        <is>
+          <t>f5fdc984-c00e-49e1-a800-6bbc09b2c498</t>
+        </is>
+      </c>
+      <c r="B3177" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3177" t="inlineStr">
+        <is>
+          <t>2026-08-17T10:20:43.269Z</t>
+        </is>
+      </c>
+      <c r="D3177" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3177" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3177" t="inlineStr">
+        <is>
+          <t>Traffic Infraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3178">
+      <c r="A3178" t="inlineStr">
+        <is>
+          <t>a5185e30-a8e4-42f8-8b31-a0512368f091</t>
+        </is>
+      </c>
+      <c r="B3178" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3178" t="inlineStr">
+        <is>
+          <t>2026-08-17T11:51:07.041Z</t>
+        </is>
+      </c>
+      <c r="D3178" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3178" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3178" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3179">
+      <c r="A3179" t="inlineStr">
+        <is>
+          <t>97d1d449-9fc7-4931-adfe-6cd323417c00</t>
+        </is>
+      </c>
+      <c r="B3179" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3179" t="inlineStr">
+        <is>
+          <t>2026-08-17T15:12:56.024Z</t>
+        </is>
+      </c>
+      <c r="D3179" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3179" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3179" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3180">
+      <c r="A3180" t="inlineStr">
+        <is>
+          <t>574b254e-77db-4cc3-ae27-92e6837eeb1f</t>
+        </is>
+      </c>
+      <c r="B3180" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3180" t="inlineStr">
+        <is>
+          <t>2026-08-17T15:58:44.885Z</t>
+        </is>
+      </c>
+      <c r="D3180" t="n">
+        <v>481</v>
+      </c>
+      <c r="E3180" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3180" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3181">
+      <c r="A3181" t="inlineStr">
+        <is>
+          <t>76b35bd0-3d36-4fae-9157-af8a0a9ae5ab</t>
+        </is>
+      </c>
+      <c r="B3181" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3181" t="inlineStr">
+        <is>
+          <t>2026-08-17T16:58:24.525Z</t>
+        </is>
+      </c>
+      <c r="D3181" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3181" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3181" t="inlineStr">
+        <is>
+          <t>Financial Crime (Embezzlement/Fraud)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3182">
+      <c r="A3182" t="inlineStr">
+        <is>
+          <t>31090930-6474-48ab-9cde-7ef1317f6fc6</t>
+        </is>
+      </c>
+      <c r="B3182" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3182" t="inlineStr">
+        <is>
+          <t>2026-08-17T18:05:17.018Z</t>
+        </is>
+      </c>
+      <c r="D3182" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3182" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3182" t="inlineStr">
+        <is>
+          <t>Terrorism/Terroristic Threats</t>
+        </is>
+      </c>
+    </row>
+    <row r="3183">
+      <c r="A3183" t="inlineStr">
+        <is>
+          <t>36f7c35f-9e2e-43af-aee6-5c3dcb704e09</t>
+        </is>
+      </c>
+      <c r="B3183" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3183" t="inlineStr">
+        <is>
+          <t>2026-08-17T18:54:11.646Z</t>
+        </is>
+      </c>
+      <c r="D3183" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3183" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3183" t="inlineStr">
+        <is>
+          <t>Trespass</t>
+        </is>
+      </c>
+    </row>
+    <row r="3184">
+      <c r="A3184" t="inlineStr">
+        <is>
+          <t>c43036c3-f439-4c37-8a60-b2041ba47cb1</t>
+        </is>
+      </c>
+      <c r="B3184" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3184" t="inlineStr">
+        <is>
+          <t>2026-08-17T19:02:59.089Z</t>
+        </is>
+      </c>
+      <c r="D3184" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3184" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3184" t="inlineStr">
+        <is>
+          <t>Trespass</t>
+        </is>
+      </c>
+    </row>
+    <row r="3185">
+      <c r="A3185" t="inlineStr">
+        <is>
+          <t>23ec169a-05d2-446c-bd47-591a5f081f67</t>
+        </is>
+      </c>
+      <c r="B3185" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3185" t="inlineStr">
+        <is>
+          <t>2026-08-17T19:44:14.330Z</t>
+        </is>
+      </c>
+      <c r="D3185" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3185" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3185" t="inlineStr">
+        <is>
+          <t>Terrorism/Terroristic Threats</t>
+        </is>
+      </c>
+    </row>
+    <row r="3186">
+      <c r="A3186" t="inlineStr">
+        <is>
+          <t>5b13dce8-fb08-43d1-bced-4d8bc45628b8</t>
+        </is>
+      </c>
+      <c r="B3186" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3186" t="inlineStr">
+        <is>
+          <t>2026-08-17T20:26:52.365Z</t>
+        </is>
+      </c>
+      <c r="D3186" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3186" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3186" t="inlineStr">
+        <is>
+          <t>Terrorism/Terroristic Threats</t>
+        </is>
+      </c>
+    </row>
+    <row r="3187">
+      <c r="A3187" t="inlineStr">
+        <is>
+          <t>5c29bb85-5c0f-4a38-a8b4-f184e112c533</t>
+        </is>
+      </c>
+      <c r="B3187" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3187" t="inlineStr">
+        <is>
+          <t>2026-08-17T20:48:53.617Z</t>
+        </is>
+      </c>
+      <c r="D3187" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3187" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3187" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3188">
+      <c r="A3188" t="inlineStr">
+        <is>
+          <t>330e75fa-32c3-4f68-a058-d2a48b99730e</t>
+        </is>
+      </c>
+      <c r="B3188" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3188" t="inlineStr">
+        <is>
+          <t>2026-08-17T21:52:26.719Z</t>
+        </is>
+      </c>
+      <c r="D3188" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3188" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3188" t="inlineStr">
+        <is>
+          <t>Terrorism/Terroristic Threats</t>
+        </is>
+      </c>
+    </row>
+    <row r="3189">
+      <c r="A3189" t="inlineStr">
+        <is>
+          <t>8a7aeb41-eeed-45d0-9c48-c19df7c1e050</t>
+        </is>
+      </c>
+      <c r="B3189" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3189" t="inlineStr">
+        <is>
+          <t>2026-08-17T21:56:36.354Z</t>
+        </is>
+      </c>
+      <c r="D3189" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3189" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3189" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3190">
+      <c r="A3190" t="inlineStr">
+        <is>
+          <t>0e88efd4-19a8-4e76-a3f1-ee81ca575cd7</t>
+        </is>
+      </c>
+      <c r="B3190" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3190" t="inlineStr">
+        <is>
+          <t>2026-08-17T22:00:05.643Z</t>
+        </is>
+      </c>
+      <c r="D3190" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3190" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3190" t="inlineStr">
+        <is>
+          <t>Terrorism/Terroristic Threats</t>
+        </is>
+      </c>
+    </row>
+    <row r="3191">
+      <c r="A3191" t="inlineStr">
+        <is>
+          <t>663af48c-3a70-416d-9611-62ee6824b9b9</t>
+        </is>
+      </c>
+      <c r="B3191" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3191" t="inlineStr">
+        <is>
+          <t>2026-08-17T22:05:26.854Z</t>
+        </is>
+      </c>
+      <c r="D3191" t="n">
+        <v>481</v>
+      </c>
+      <c r="E3191" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3191" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3191"/>
+  <dimension ref="A1:F3212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77258,6 +77258,636 @@
         </is>
       </c>
     </row>
+    <row r="3192">
+      <c r="A3192" t="inlineStr">
+        <is>
+          <t>c843eeae-c8db-4575-8841-b8241016797b</t>
+        </is>
+      </c>
+      <c r="B3192" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3192" t="inlineStr">
+        <is>
+          <t>2026-08-18T00:55:59.809Z</t>
+        </is>
+      </c>
+      <c r="D3192" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3192" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3192" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3193">
+      <c r="A3193" t="inlineStr">
+        <is>
+          <t>0af01e50-a36d-4b11-9a17-5dcb576335de</t>
+        </is>
+      </c>
+      <c r="B3193" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3193" t="inlineStr">
+        <is>
+          <t>2026-08-18T03:31:49.315Z</t>
+        </is>
+      </c>
+      <c r="D3193" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3193" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3193" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3194">
+      <c r="A3194" t="inlineStr">
+        <is>
+          <t>d9fe702e-2c46-4fc5-a5ba-c5d7fd114c1b</t>
+        </is>
+      </c>
+      <c r="B3194" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3194" t="inlineStr">
+        <is>
+          <t>2026-08-18T03:54:49.455Z</t>
+        </is>
+      </c>
+      <c r="D3194" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3194" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3194" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3195">
+      <c r="A3195" t="inlineStr">
+        <is>
+          <t>e5b18e97-ac2d-4498-9224-092ea45ad409</t>
+        </is>
+      </c>
+      <c r="B3195" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3195" t="inlineStr">
+        <is>
+          <t>2026-08-18T04:14:43.016Z</t>
+        </is>
+      </c>
+      <c r="D3195" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3195" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3195" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3196">
+      <c r="A3196" t="inlineStr">
+        <is>
+          <t>385d7bf3-8b9a-4cc0-aa16-4758332ed76e</t>
+        </is>
+      </c>
+      <c r="B3196" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3196" t="inlineStr">
+        <is>
+          <t>2026-08-18T05:16:43.592Z</t>
+        </is>
+      </c>
+      <c r="D3196" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3196" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3196" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3197">
+      <c r="A3197" t="inlineStr">
+        <is>
+          <t>02e164e3-ecbf-4543-87a2-6c68dcdf062a</t>
+        </is>
+      </c>
+      <c r="B3197" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3197" t="inlineStr">
+        <is>
+          <t>2026-08-18T06:15:18.879Z</t>
+        </is>
+      </c>
+      <c r="D3197" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3197" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3197" t="inlineStr">
+        <is>
+          <t>Financial Crime (Embezzlement/Fraud)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3198">
+      <c r="A3198" t="inlineStr">
+        <is>
+          <t>0398fea4-e321-482f-8c93-3c529a939779</t>
+        </is>
+      </c>
+      <c r="B3198" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3198" t="inlineStr">
+        <is>
+          <t>2026-08-18T06:45:19.847Z</t>
+        </is>
+      </c>
+      <c r="D3198" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3198" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3198" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3199">
+      <c r="A3199" t="inlineStr">
+        <is>
+          <t>a882e779-0340-40d3-b583-84d0613de6dd</t>
+        </is>
+      </c>
+      <c r="B3199" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3199" t="inlineStr">
+        <is>
+          <t>2026-08-18T06:57:49.187Z</t>
+        </is>
+      </c>
+      <c r="D3199" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3199" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3199" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3200">
+      <c r="A3200" t="inlineStr">
+        <is>
+          <t>e6955d55-811a-450e-9cbe-0ea062568c45</t>
+        </is>
+      </c>
+      <c r="B3200" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3200" t="inlineStr">
+        <is>
+          <t>2026-08-18T07:19:34.544Z</t>
+        </is>
+      </c>
+      <c r="D3200" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3200" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3200" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3201">
+      <c r="A3201" t="inlineStr">
+        <is>
+          <t>1e58011c-7cf8-4ab2-bd3e-956805935e10</t>
+        </is>
+      </c>
+      <c r="B3201" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3201" t="inlineStr">
+        <is>
+          <t>2026-08-18T08:06:07.285Z</t>
+        </is>
+      </c>
+      <c r="D3201" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3201" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3201" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3202">
+      <c r="A3202" t="inlineStr">
+        <is>
+          <t>5de4d19b-ac75-48b0-8e0e-9ae988786d5a</t>
+        </is>
+      </c>
+      <c r="B3202" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3202" t="inlineStr">
+        <is>
+          <t>2026-08-18T09:23:57.481Z</t>
+        </is>
+      </c>
+      <c r="D3202" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3202" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3202" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3203">
+      <c r="A3203" t="inlineStr">
+        <is>
+          <t>a88e4bd8-467e-4d82-82e0-a0f49bc8383f</t>
+        </is>
+      </c>
+      <c r="B3203" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3203" t="inlineStr">
+        <is>
+          <t>2026-08-18T10:06:11.609Z</t>
+        </is>
+      </c>
+      <c r="D3203" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3203" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3203" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3204">
+      <c r="A3204" t="inlineStr">
+        <is>
+          <t>314bb5b3-fb23-46e9-ba75-95b64a259800</t>
+        </is>
+      </c>
+      <c r="B3204" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3204" t="inlineStr">
+        <is>
+          <t>2026-08-18T11:49:59.083Z</t>
+        </is>
+      </c>
+      <c r="D3204" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3204" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3204" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3205">
+      <c r="A3205" t="inlineStr">
+        <is>
+          <t>f8a5ddaa-b907-4ac4-8498-d1e357dad349</t>
+        </is>
+      </c>
+      <c r="B3205" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3205" t="inlineStr">
+        <is>
+          <t>2026-08-18T14:36:53.684Z</t>
+        </is>
+      </c>
+      <c r="D3205" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3205" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3205" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3206">
+      <c r="A3206" t="inlineStr">
+        <is>
+          <t>0d42a746-10be-4298-a552-3f7dea9901ca</t>
+        </is>
+      </c>
+      <c r="B3206" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3206" t="inlineStr">
+        <is>
+          <t>2026-08-18T15:24:59.352Z</t>
+        </is>
+      </c>
+      <c r="D3206" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3206" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3206" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3207">
+      <c r="A3207" t="inlineStr">
+        <is>
+          <t>1c355ad8-388e-460c-a33c-8d5b5095aee8</t>
+        </is>
+      </c>
+      <c r="B3207" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3207" t="inlineStr">
+        <is>
+          <t>2026-08-18T19:58:23.644Z</t>
+        </is>
+      </c>
+      <c r="D3207" t="n">
+        <v>556</v>
+      </c>
+      <c r="E3207" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3207" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3208">
+      <c r="A3208" t="inlineStr">
+        <is>
+          <t>784faa9f-a640-4dab-8be7-3d79d15b19d4</t>
+        </is>
+      </c>
+      <c r="B3208" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3208" t="inlineStr">
+        <is>
+          <t>2026-08-18T20:00:11.857Z</t>
+        </is>
+      </c>
+      <c r="D3208" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3208" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3208" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3209">
+      <c r="A3209" t="inlineStr">
+        <is>
+          <t>11c59a43-636b-42ac-93c3-0eca3a23dba5</t>
+        </is>
+      </c>
+      <c r="B3209" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3209" t="inlineStr">
+        <is>
+          <t>2026-08-18T22:12:17.417Z</t>
+        </is>
+      </c>
+      <c r="D3209" t="n">
+        <v>511</v>
+      </c>
+      <c r="E3209" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3209" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3210">
+      <c r="A3210" t="inlineStr">
+        <is>
+          <t>b05d49db-b405-4a9c-9535-633200b1786a</t>
+        </is>
+      </c>
+      <c r="B3210" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3210" t="inlineStr">
+        <is>
+          <t>2026-08-18T22:12:43.228Z</t>
+        </is>
+      </c>
+      <c r="D3210" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3210" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3210" t="inlineStr">
+        <is>
+          <t>Stalking</t>
+        </is>
+      </c>
+    </row>
+    <row r="3211">
+      <c r="A3211" t="inlineStr">
+        <is>
+          <t>c230ef0b-e9c4-4725-b955-696b445638c9</t>
+        </is>
+      </c>
+      <c r="B3211" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3211" t="inlineStr">
+        <is>
+          <t>2026-08-18T23:01:52.646Z</t>
+        </is>
+      </c>
+      <c r="D3211" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3211" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3211" t="inlineStr">
+        <is>
+          <t>Stalking</t>
+        </is>
+      </c>
+    </row>
+    <row r="3212">
+      <c r="A3212" t="inlineStr">
+        <is>
+          <t>8cebebe2-84c4-497e-bac5-6294fa99325c</t>
+        </is>
+      </c>
+      <c r="B3212" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3212" t="inlineStr">
+        <is>
+          <t>2026-08-18T23:22:29.702Z</t>
+        </is>
+      </c>
+      <c r="D3212" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3212" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3212" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3212"/>
+  <dimension ref="A1:F3241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77888,6 +77888,876 @@
         </is>
       </c>
     </row>
+    <row r="3213">
+      <c r="A3213" t="inlineStr">
+        <is>
+          <t>2d15048d-02bf-4201-9fad-93e7300885ad</t>
+        </is>
+      </c>
+      <c r="B3213" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3213" t="inlineStr">
+        <is>
+          <t>2026-08-19T00:25:04.428Z</t>
+        </is>
+      </c>
+      <c r="D3213" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3213" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3213" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3214">
+      <c r="A3214" t="inlineStr">
+        <is>
+          <t>2bd5f0a7-e40d-479c-8de9-ad4764514152</t>
+        </is>
+      </c>
+      <c r="B3214" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3214" t="inlineStr">
+        <is>
+          <t>2026-08-19T00:26:04.718Z</t>
+        </is>
+      </c>
+      <c r="D3214" t="n">
+        <v>552</v>
+      </c>
+      <c r="E3214" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3214" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct/Disturbance</t>
+        </is>
+      </c>
+    </row>
+    <row r="3215">
+      <c r="A3215" t="inlineStr">
+        <is>
+          <t>0936cd4f-7c5d-4dfb-83f1-3aeff788f6f2</t>
+        </is>
+      </c>
+      <c r="B3215" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3215" t="inlineStr">
+        <is>
+          <t>2026-08-19T00:37:29.657Z</t>
+        </is>
+      </c>
+      <c r="D3215" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3215" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3215" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3216">
+      <c r="A3216" t="inlineStr">
+        <is>
+          <t>ba1168fa-f03f-4851-8322-8e64777e4833</t>
+        </is>
+      </c>
+      <c r="B3216" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3216" t="inlineStr">
+        <is>
+          <t>2026-08-19T02:04:08.539Z</t>
+        </is>
+      </c>
+      <c r="D3216" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3216" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3216" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3217">
+      <c r="A3217" t="inlineStr">
+        <is>
+          <t>dedb253e-a67d-47c4-ab0a-d80b4581d220</t>
+        </is>
+      </c>
+      <c r="B3217" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3217" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:35:43.552Z</t>
+        </is>
+      </c>
+      <c r="D3217" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3217" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3217" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3218">
+      <c r="A3218" t="inlineStr">
+        <is>
+          <t>f2d1bd1c-1520-4d36-a2f9-038d69776185</t>
+        </is>
+      </c>
+      <c r="B3218" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3218" t="inlineStr">
+        <is>
+          <t>2026-08-19T04:58:28.095Z</t>
+        </is>
+      </c>
+      <c r="D3218" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3218" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3218" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3219">
+      <c r="A3219" t="inlineStr">
+        <is>
+          <t>9ed91970-3795-4ddd-a557-3566fab0b191</t>
+        </is>
+      </c>
+      <c r="B3219" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3219" t="inlineStr">
+        <is>
+          <t>2026-08-19T05:00:44.683Z</t>
+        </is>
+      </c>
+      <c r="D3219" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3219" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3219" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3220">
+      <c r="A3220" t="inlineStr">
+        <is>
+          <t>57097283-2754-4914-a71a-51aeee56dda3</t>
+        </is>
+      </c>
+      <c r="B3220" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3220" t="inlineStr">
+        <is>
+          <t>2026-08-19T06:33:23.838Z</t>
+        </is>
+      </c>
+      <c r="D3220" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3220" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3220" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3221">
+      <c r="A3221" t="inlineStr">
+        <is>
+          <t>ae5d0710-ef0c-44bd-82bd-0b369764c2da</t>
+        </is>
+      </c>
+      <c r="B3221" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3221" t="inlineStr">
+        <is>
+          <t>2026-08-19T06:42:17.214Z</t>
+        </is>
+      </c>
+      <c r="D3221" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3221" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3221" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3222">
+      <c r="A3222" t="inlineStr">
+        <is>
+          <t>e8fe75a9-50cf-4cf9-bf18-0a53872476e1</t>
+        </is>
+      </c>
+      <c r="B3222" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3222" t="inlineStr">
+        <is>
+          <t>2026-08-19T07:15:10.047Z</t>
+        </is>
+      </c>
+      <c r="D3222" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3222" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3222" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3223">
+      <c r="A3223" t="inlineStr">
+        <is>
+          <t>953a0443-1091-48b9-aced-3ab0be29da55</t>
+        </is>
+      </c>
+      <c r="B3223" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3223" t="inlineStr">
+        <is>
+          <t>2026-08-19T07:39:12.364Z</t>
+        </is>
+      </c>
+      <c r="D3223" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3223" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3223" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3224">
+      <c r="A3224" t="inlineStr">
+        <is>
+          <t>1dad946f-e07a-4ad7-ac78-17d0d453174a</t>
+        </is>
+      </c>
+      <c r="B3224" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3224" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:07:44.611Z</t>
+        </is>
+      </c>
+      <c r="D3224" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3224" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3224" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3225">
+      <c r="A3225" t="inlineStr">
+        <is>
+          <t>494e702f-605e-45c5-80d6-47cac290c79e</t>
+        </is>
+      </c>
+      <c r="B3225" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3225" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:12:47.062Z</t>
+        </is>
+      </c>
+      <c r="D3225" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3225" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3225" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3226">
+      <c r="A3226" t="inlineStr">
+        <is>
+          <t>42156133-1cd9-4e51-85f3-e2d0277000bb</t>
+        </is>
+      </c>
+      <c r="B3226" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3226" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:23:12.982Z</t>
+        </is>
+      </c>
+      <c r="D3226" t="n">
+        <v>511</v>
+      </c>
+      <c r="E3226" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3226" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3227">
+      <c r="A3227" t="inlineStr">
+        <is>
+          <t>2170c5d0-8942-4481-8d42-d8bfc7e94f79</t>
+        </is>
+      </c>
+      <c r="B3227" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3227" t="inlineStr">
+        <is>
+          <t>2026-08-19T12:02:30.215Z</t>
+        </is>
+      </c>
+      <c r="D3227" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3227" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3227" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3228">
+      <c r="A3228" t="inlineStr">
+        <is>
+          <t>dd8b85c0-d170-4bb7-bfbd-10fa15e6565f</t>
+        </is>
+      </c>
+      <c r="B3228" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3228" t="inlineStr">
+        <is>
+          <t>2026-08-19T12:20:29.739Z</t>
+        </is>
+      </c>
+      <c r="D3228" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3228" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3228" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3229">
+      <c r="A3229" t="inlineStr">
+        <is>
+          <t>93632b43-d5c6-4b1d-9a27-38d5d90e1e06</t>
+        </is>
+      </c>
+      <c r="B3229" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3229" t="inlineStr">
+        <is>
+          <t>2026-08-19T12:49:16.027Z</t>
+        </is>
+      </c>
+      <c r="D3229" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3229" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3229" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3230">
+      <c r="A3230" t="inlineStr">
+        <is>
+          <t>03a4ce24-b93e-4a75-b99b-0a8695fc271f</t>
+        </is>
+      </c>
+      <c r="B3230" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3230" t="inlineStr">
+        <is>
+          <t>2026-08-19T15:32:09.533Z</t>
+        </is>
+      </c>
+      <c r="D3230" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3230" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3230" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3231">
+      <c r="A3231" t="inlineStr">
+        <is>
+          <t>ccddbb7f-7130-42bf-bf98-d3b214ae0cf8</t>
+        </is>
+      </c>
+      <c r="B3231" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3231" t="inlineStr">
+        <is>
+          <t>2026-08-19T15:47:17.617Z</t>
+        </is>
+      </c>
+      <c r="D3231" t="n">
+        <v>511</v>
+      </c>
+      <c r="E3231" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3231" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3232">
+      <c r="A3232" t="inlineStr">
+        <is>
+          <t>06f3f9b2-91de-4b8a-9d91-278d018ea399</t>
+        </is>
+      </c>
+      <c r="B3232" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3232" t="inlineStr">
+        <is>
+          <t>2026-08-19T15:56:42.268Z</t>
+        </is>
+      </c>
+      <c r="D3232" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3232" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3232" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3233">
+      <c r="A3233" t="inlineStr">
+        <is>
+          <t>277c41a4-9319-49f4-9952-fa02a2396881</t>
+        </is>
+      </c>
+      <c r="B3233" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3233" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:06:12.593Z</t>
+        </is>
+      </c>
+      <c r="D3233" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3233" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3233" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3234">
+      <c r="A3234" t="inlineStr">
+        <is>
+          <t>d3166ff2-c46a-4079-aa69-b0570cb423b0</t>
+        </is>
+      </c>
+      <c r="B3234" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3234" t="inlineStr">
+        <is>
+          <t>2026-08-19T17:48:32.179Z</t>
+        </is>
+      </c>
+      <c r="D3234" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3234" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3234" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3235">
+      <c r="A3235" t="inlineStr">
+        <is>
+          <t>50dbd24a-cb22-4840-bea0-3bc0bf4a5b86</t>
+        </is>
+      </c>
+      <c r="B3235" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3235" t="inlineStr">
+        <is>
+          <t>2026-08-19T17:59:18.381Z</t>
+        </is>
+      </c>
+      <c r="D3235" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3235" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3235" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3236">
+      <c r="A3236" t="inlineStr">
+        <is>
+          <t>528b02cb-5fc9-4f1f-9806-791073a51fc0</t>
+        </is>
+      </c>
+      <c r="B3236" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3236" t="inlineStr">
+        <is>
+          <t>2026-08-19T18:11:23.635Z</t>
+        </is>
+      </c>
+      <c r="D3236" t="n">
+        <v>511</v>
+      </c>
+      <c r="E3236" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3236" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3237">
+      <c r="A3237" t="inlineStr">
+        <is>
+          <t>c3e5182f-3bda-4f94-b390-45b931a87c3e</t>
+        </is>
+      </c>
+      <c r="B3237" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3237" t="inlineStr">
+        <is>
+          <t>2026-08-19T18:37:01.839Z</t>
+        </is>
+      </c>
+      <c r="D3237" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3237" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3237" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3238">
+      <c r="A3238" t="inlineStr">
+        <is>
+          <t>ca6f208b-7a46-4211-bfb9-d1fd2bee282e</t>
+        </is>
+      </c>
+      <c r="B3238" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3238" t="inlineStr">
+        <is>
+          <t>2026-08-19T18:58:11.932Z</t>
+        </is>
+      </c>
+      <c r="D3238" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3238" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3238" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3239">
+      <c r="A3239" t="inlineStr">
+        <is>
+          <t>ba9bc372-98e3-4668-be90-d1ada110d6d5</t>
+        </is>
+      </c>
+      <c r="B3239" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3239" t="inlineStr">
+        <is>
+          <t>2026-08-19T19:05:59.626Z</t>
+        </is>
+      </c>
+      <c r="D3239" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3239" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3239" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3240">
+      <c r="A3240" t="inlineStr">
+        <is>
+          <t>7ef14b3b-e6d2-4aa7-bba2-61578fccb931</t>
+        </is>
+      </c>
+      <c r="B3240" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3240" t="inlineStr">
+        <is>
+          <t>2026-08-19T19:56:20.907Z</t>
+        </is>
+      </c>
+      <c r="D3240" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3240" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3240" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3241">
+      <c r="A3241" t="inlineStr">
+        <is>
+          <t>04f1bbd3-3494-45d8-94fb-5d206fabae70</t>
+        </is>
+      </c>
+      <c r="B3241" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3241" t="inlineStr">
+        <is>
+          <t>2026-08-19T23:55:54.859Z</t>
+        </is>
+      </c>
+      <c r="D3241" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3241" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3241" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3241"/>
+  <dimension ref="A1:F3258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78758,6 +78758,516 @@
         </is>
       </c>
     </row>
+    <row r="3242">
+      <c r="A3242" t="inlineStr">
+        <is>
+          <t>dcc66bf9-2181-4a3a-970b-8eed13c3be15</t>
+        </is>
+      </c>
+      <c r="B3242" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3242" t="inlineStr">
+        <is>
+          <t>2026-08-20T00:38:07.622Z</t>
+        </is>
+      </c>
+      <c r="D3242" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3242" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3242" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3243">
+      <c r="A3243" t="inlineStr">
+        <is>
+          <t>2d605ff3-7b4c-45e4-a6cb-7a0aba81b614</t>
+        </is>
+      </c>
+      <c r="B3243" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3243" t="inlineStr">
+        <is>
+          <t>2026-08-20T01:11:27.538Z</t>
+        </is>
+      </c>
+      <c r="D3243" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3243" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3243" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3244">
+      <c r="A3244" t="inlineStr">
+        <is>
+          <t>ba5caf96-377b-44f2-a5bf-994682f4d9b0</t>
+        </is>
+      </c>
+      <c r="B3244" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3244" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:31:29.337Z</t>
+        </is>
+      </c>
+      <c r="D3244" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3244" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3244" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence (DUI/DWI/OWI/OVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3245">
+      <c r="A3245" t="inlineStr">
+        <is>
+          <t>f80a7835-6260-49b7-8702-34c4ae0abcc8</t>
+        </is>
+      </c>
+      <c r="B3245" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3245" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:32:03.548Z</t>
+        </is>
+      </c>
+      <c r="D3245" t="n">
+        <v>778</v>
+      </c>
+      <c r="E3245" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3245" t="inlineStr">
+        <is>
+          <t>Obstructing the Police (Fleeing/Eluding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3246">
+      <c r="A3246" t="inlineStr">
+        <is>
+          <t>03cdaedf-1019-4e6c-877e-718bf7515e23</t>
+        </is>
+      </c>
+      <c r="B3246" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3246" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:32:24.411Z</t>
+        </is>
+      </c>
+      <c r="D3246" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3246" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3246" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence (DUI/DWI/OWI/OVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3247">
+      <c r="A3247" t="inlineStr">
+        <is>
+          <t>8e53116c-0dc9-437f-9a20-78c06f76478f</t>
+        </is>
+      </c>
+      <c r="B3247" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3247" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:32:56.481Z</t>
+        </is>
+      </c>
+      <c r="D3247" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3247" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3247" t="inlineStr">
+        <is>
+          <t>Obstructing Justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="3248">
+      <c r="A3248" t="inlineStr">
+        <is>
+          <t>728f1c3c-19ee-4976-bcaf-5e6905dc6ffe</t>
+        </is>
+      </c>
+      <c r="B3248" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3248" t="inlineStr">
+        <is>
+          <t>2026-08-20T05:48:40.466Z</t>
+        </is>
+      </c>
+      <c r="D3248" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3248" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3248" t="inlineStr">
+        <is>
+          <t>Obstructing the Police (Fleeing/Eluding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3249">
+      <c r="A3249" t="inlineStr">
+        <is>
+          <t>098b820b-dab0-4f4c-96c2-6d61e9fd5fb8</t>
+        </is>
+      </c>
+      <c r="B3249" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3249" t="inlineStr">
+        <is>
+          <t>2026-08-20T06:03:57.987Z</t>
+        </is>
+      </c>
+      <c r="D3249" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3249" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3249" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence (DUI/DWI/OWI/OVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3250">
+      <c r="A3250" t="inlineStr">
+        <is>
+          <t>51541fee-df5d-401f-946d-3c655bccdcde</t>
+        </is>
+      </c>
+      <c r="B3250" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3250" t="inlineStr">
+        <is>
+          <t>2026-08-20T06:04:25.008Z</t>
+        </is>
+      </c>
+      <c r="D3250" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3250" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3250" t="inlineStr">
+        <is>
+          <t>Obstructing Justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="3251">
+      <c r="A3251" t="inlineStr">
+        <is>
+          <t>cd97bb77-6290-4448-9ff8-98014ec9b94b</t>
+        </is>
+      </c>
+      <c r="B3251" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3251" t="inlineStr">
+        <is>
+          <t>2026-08-20T06:04:42.695Z</t>
+        </is>
+      </c>
+      <c r="D3251" t="n">
+        <v>778</v>
+      </c>
+      <c r="E3251" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3251" t="inlineStr">
+        <is>
+          <t>Obstructing the Police (Fleeing/Eluding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3252">
+      <c r="A3252" t="inlineStr">
+        <is>
+          <t>9b01b397-2ad4-48af-a53a-2ccb9cdfc02a</t>
+        </is>
+      </c>
+      <c r="B3252" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3252" t="inlineStr">
+        <is>
+          <t>2026-08-20T06:10:52.770Z</t>
+        </is>
+      </c>
+      <c r="D3252" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3252" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3252" t="inlineStr">
+        <is>
+          <t>Obstructing the Police (Fleeing/Eluding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3253">
+      <c r="A3253" t="inlineStr">
+        <is>
+          <t>c2e0dd05-d29a-4859-9f4e-860343c0b211</t>
+        </is>
+      </c>
+      <c r="B3253" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3253" t="inlineStr">
+        <is>
+          <t>2026-08-20T07:03:58.097Z</t>
+        </is>
+      </c>
+      <c r="D3253" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3253" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3253" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence (DUI/DWI/OWI/OVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3254">
+      <c r="A3254" t="inlineStr">
+        <is>
+          <t>66010ee7-c4a4-4f47-bff5-aea3b97dc503</t>
+        </is>
+      </c>
+      <c r="B3254" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3254" t="inlineStr">
+        <is>
+          <t>2026-08-20T07:43:38.417Z</t>
+        </is>
+      </c>
+      <c r="D3254" t="n">
+        <v>778</v>
+      </c>
+      <c r="E3254" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3254" t="inlineStr">
+        <is>
+          <t>Obstructing Justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="3255">
+      <c r="A3255" t="inlineStr">
+        <is>
+          <t>63999c16-4d13-466c-8440-dd5316e87544</t>
+        </is>
+      </c>
+      <c r="B3255" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3255" t="inlineStr">
+        <is>
+          <t>2026-08-20T08:22:50.754Z</t>
+        </is>
+      </c>
+      <c r="D3255" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3255" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3255" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence (DUI/DWI/OWI/OVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3256">
+      <c r="A3256" t="inlineStr">
+        <is>
+          <t>9b76eb82-b742-406b-826d-cb0674b9daf0</t>
+        </is>
+      </c>
+      <c r="B3256" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3256" t="inlineStr">
+        <is>
+          <t>2026-08-20T09:13:02.302Z</t>
+        </is>
+      </c>
+      <c r="D3256" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3256" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3256" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence (DUI/DWI/OWI/OVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3257">
+      <c r="A3257" t="inlineStr">
+        <is>
+          <t>65378128-0b60-4cc2-a159-89c06c4775a7</t>
+        </is>
+      </c>
+      <c r="B3257" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3257" t="inlineStr">
+        <is>
+          <t>2026-08-20T13:37:57.980Z</t>
+        </is>
+      </c>
+      <c r="D3257" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3257" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3257" t="inlineStr">
+        <is>
+          <t>Obstructing the Police (Fleeing/Eluding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3258">
+      <c r="A3258" t="inlineStr">
+        <is>
+          <t>558c1ea7-c57c-4622-8ff6-1e22c39a033f</t>
+        </is>
+      </c>
+      <c r="B3258" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3258" t="inlineStr">
+        <is>
+          <t>2026-08-20T13:56:38.488Z</t>
+        </is>
+      </c>
+      <c r="D3258" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3258" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3258" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence (DUI/DWI/OWI/OVI)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3258"/>
+  <dimension ref="A1:F3264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79268,6 +79268,186 @@
         </is>
       </c>
     </row>
+    <row r="3259">
+      <c r="A3259" t="inlineStr">
+        <is>
+          <t>b31a0bdb-5098-4cde-8b93-c5017600b7ce</t>
+        </is>
+      </c>
+      <c r="B3259" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3259" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:58:45.176Z</t>
+        </is>
+      </c>
+      <c r="D3259" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3259" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3259" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3260">
+      <c r="A3260" t="inlineStr">
+        <is>
+          <t>7d54b274-c5d8-4bb3-8a7e-4a7362c0457a</t>
+        </is>
+      </c>
+      <c r="B3260" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3260" t="inlineStr">
+        <is>
+          <t>2026-08-21T07:35:25.098Z</t>
+        </is>
+      </c>
+      <c r="D3260" t="n">
+        <v>511</v>
+      </c>
+      <c r="E3260" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3260" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3261">
+      <c r="A3261" t="inlineStr">
+        <is>
+          <t>29858e12-90f2-4ce3-ad6f-31d18f6826d2</t>
+        </is>
+      </c>
+      <c r="B3261" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3261" t="inlineStr">
+        <is>
+          <t>2026-08-21T08:05:06.235Z</t>
+        </is>
+      </c>
+      <c r="D3261" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3261" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3261" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3262">
+      <c r="A3262" t="inlineStr">
+        <is>
+          <t>8e53fd8e-c567-427c-8b2e-55704f896d41</t>
+        </is>
+      </c>
+      <c r="B3262" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3262" t="inlineStr">
+        <is>
+          <t>2026-08-21T18:08:58.019Z</t>
+        </is>
+      </c>
+      <c r="D3262" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3262" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3262" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3263">
+      <c r="A3263" t="inlineStr">
+        <is>
+          <t>e66a2967-47bf-48c7-9e2b-97e65043f2b0</t>
+        </is>
+      </c>
+      <c r="B3263" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3263" t="inlineStr">
+        <is>
+          <t>2026-08-21T19:07:40.170Z</t>
+        </is>
+      </c>
+      <c r="D3263" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3263" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3263" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3264">
+      <c r="A3264" t="inlineStr">
+        <is>
+          <t>5c5b1c36-98ab-4ca5-850b-f8443225321b</t>
+        </is>
+      </c>
+      <c r="B3264" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3264" t="inlineStr">
+        <is>
+          <t>2026-08-21T22:25:45.563Z</t>
+        </is>
+      </c>
+      <c r="D3264" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3264" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3264" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3264"/>
+  <dimension ref="A1:F3273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79448,6 +79448,276 @@
         </is>
       </c>
     </row>
+    <row r="3265">
+      <c r="A3265" t="inlineStr">
+        <is>
+          <t>5b39cc29-3906-487c-9643-650912a3d4c6</t>
+        </is>
+      </c>
+      <c r="B3265" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3265" t="inlineStr">
+        <is>
+          <t>2026-08-22T02:50:40.382Z</t>
+        </is>
+      </c>
+      <c r="D3265" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3265" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3265" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3266">
+      <c r="A3266" t="inlineStr">
+        <is>
+          <t>bc28a865-50c1-40c9-b028-73adb5009100</t>
+        </is>
+      </c>
+      <c r="B3266" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3266" t="inlineStr">
+        <is>
+          <t>2026-08-22T04:46:01.934Z</t>
+        </is>
+      </c>
+      <c r="D3266" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3266" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3266" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence (DUI/DWI/OWI/OVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3267">
+      <c r="A3267" t="inlineStr">
+        <is>
+          <t>5f72f6c8-b73b-4508-a38b-0af17a0e55f5</t>
+        </is>
+      </c>
+      <c r="B3267" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3267" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:09:29.988Z</t>
+        </is>
+      </c>
+      <c r="D3267" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3267" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3267" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3268">
+      <c r="A3268" t="inlineStr">
+        <is>
+          <t>cb097c32-da0e-4575-9863-564f4758cf7c</t>
+        </is>
+      </c>
+      <c r="B3268" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3268" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:12:58.059Z</t>
+        </is>
+      </c>
+      <c r="D3268" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3268" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3268" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence (DUI/DWI/OWI/OVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3269">
+      <c r="A3269" t="inlineStr">
+        <is>
+          <t>a5a00e55-005b-4ffd-ab87-d1c11498c8cc</t>
+        </is>
+      </c>
+      <c r="B3269" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3269" t="inlineStr">
+        <is>
+          <t>2026-08-22T07:59:47.288Z</t>
+        </is>
+      </c>
+      <c r="D3269" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3269" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3269" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3270">
+      <c r="A3270" t="inlineStr">
+        <is>
+          <t>e7f8be68-d132-4a17-abed-0ddd695aa5c3</t>
+        </is>
+      </c>
+      <c r="B3270" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3270" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:00:08.411Z</t>
+        </is>
+      </c>
+      <c r="D3270" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3270" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3270" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3271">
+      <c r="A3271" t="inlineStr">
+        <is>
+          <t>33903d2c-b19e-4301-a52a-e075ebf7bceb</t>
+        </is>
+      </c>
+      <c r="B3271" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3271" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:03:05.945Z</t>
+        </is>
+      </c>
+      <c r="D3271" t="n">
+        <v>779</v>
+      </c>
+      <c r="E3271" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3271" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3272">
+      <c r="A3272" t="inlineStr">
+        <is>
+          <t>49b69120-1b71-413e-aa55-8cc15caa8c87</t>
+        </is>
+      </c>
+      <c r="B3272" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3272" t="inlineStr">
+        <is>
+          <t>2026-08-22T13:35:17.689Z</t>
+        </is>
+      </c>
+      <c r="D3272" t="n">
+        <v>779</v>
+      </c>
+      <c r="E3272" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3272" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence (DUI/DWI/OWI/OVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3273">
+      <c r="A3273" t="inlineStr">
+        <is>
+          <t>7aebd0cb-f3f6-45db-9959-6402ab50608f</t>
+        </is>
+      </c>
+      <c r="B3273" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3273" t="inlineStr">
+        <is>
+          <t>2026-08-22T15:00:18.245Z</t>
+        </is>
+      </c>
+      <c r="D3273" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3273" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3273" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3273"/>
+  <dimension ref="A1:F3284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79718,6 +79718,336 @@
         </is>
       </c>
     </row>
+    <row r="3274">
+      <c r="A3274" t="inlineStr">
+        <is>
+          <t>4b3e10ae-bce1-4e92-b0d8-a6b9a1834d3e</t>
+        </is>
+      </c>
+      <c r="B3274" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3274" t="inlineStr">
+        <is>
+          <t>2026-08-23T02:44:02.876Z</t>
+        </is>
+      </c>
+      <c r="D3274" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3274" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3274" t="inlineStr">
+        <is>
+          <t>Kidnapping/Abduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3275">
+      <c r="A3275" t="inlineStr">
+        <is>
+          <t>7c55b350-e5cd-4546-8514-417512799ada</t>
+        </is>
+      </c>
+      <c r="B3275" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3275" t="inlineStr">
+        <is>
+          <t>2026-08-23T02:47:15.644Z</t>
+        </is>
+      </c>
+      <c r="D3275" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3275" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3275" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3276">
+      <c r="A3276" t="inlineStr">
+        <is>
+          <t>8be72dd2-e996-45ad-8573-840ddd403c80</t>
+        </is>
+      </c>
+      <c r="B3276" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3276" t="inlineStr">
+        <is>
+          <t>2026-08-23T02:49:55.033Z</t>
+        </is>
+      </c>
+      <c r="D3276" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3276" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3276" t="inlineStr">
+        <is>
+          <t>Kidnapping/Abduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3277">
+      <c r="A3277" t="inlineStr">
+        <is>
+          <t>30108819-657a-4ff4-a0a9-514d75bf9a00</t>
+        </is>
+      </c>
+      <c r="B3277" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3277" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:06:52.000Z</t>
+        </is>
+      </c>
+      <c r="D3277" t="n">
+        <v>779</v>
+      </c>
+      <c r="E3277" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3277" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3278">
+      <c r="A3278" t="inlineStr">
+        <is>
+          <t>9cfe4399-e72a-4148-8f6d-663e6928c678</t>
+        </is>
+      </c>
+      <c r="B3278" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3278" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:07:55.253Z</t>
+        </is>
+      </c>
+      <c r="D3278" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3278" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3278" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3279">
+      <c r="A3279" t="inlineStr">
+        <is>
+          <t>d3c0c212-c2a3-477c-ba89-80f2ee3452b7</t>
+        </is>
+      </c>
+      <c r="B3279" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3279" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:10:41.752Z</t>
+        </is>
+      </c>
+      <c r="D3279" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3279" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3279" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3280">
+      <c r="A3280" t="inlineStr">
+        <is>
+          <t>493aeb64-f508-45e0-8024-640fee5ef1cb</t>
+        </is>
+      </c>
+      <c r="B3280" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3280" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:10:55.842Z</t>
+        </is>
+      </c>
+      <c r="D3280" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3280" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3280" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3281">
+      <c r="A3281" t="inlineStr">
+        <is>
+          <t>d3f343cd-3f65-473a-b3cb-c65d4bf3242a</t>
+        </is>
+      </c>
+      <c r="B3281" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3281" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:12:58.596Z</t>
+        </is>
+      </c>
+      <c r="D3281" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3281" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3281" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3282">
+      <c r="A3282" t="inlineStr">
+        <is>
+          <t>6cd12d6f-8dec-4bf5-ae99-5ef64cbf099a</t>
+        </is>
+      </c>
+      <c r="B3282" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3282" t="inlineStr">
+        <is>
+          <t>2026-08-23T05:09:58.003Z</t>
+        </is>
+      </c>
+      <c r="D3282" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3282" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3282" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3283">
+      <c r="A3283" t="inlineStr">
+        <is>
+          <t>67e6651b-feae-4685-a085-e52ff1dbb93c</t>
+        </is>
+      </c>
+      <c r="B3283" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3283" t="inlineStr">
+        <is>
+          <t>2026-08-23T11:38:21.943Z</t>
+        </is>
+      </c>
+      <c r="D3283" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3283" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3283" t="inlineStr">
+        <is>
+          <t>Obstructing the Police (Fleeing/Eluding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3284">
+      <c r="A3284" t="inlineStr">
+        <is>
+          <t>a8e35dc7-1ddd-4ff1-a615-a36f8f3102b4</t>
+        </is>
+      </c>
+      <c r="B3284" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3284" t="inlineStr">
+        <is>
+          <t>2026-08-23T17:11:27.813Z</t>
+        </is>
+      </c>
+      <c r="D3284" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3284" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3284" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3284"/>
+  <dimension ref="A1:F3297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80048,6 +80048,396 @@
         </is>
       </c>
     </row>
+    <row r="3285">
+      <c r="A3285" t="inlineStr">
+        <is>
+          <t>c8d66749-b0ee-49d3-aa6d-3ecf8718aa25</t>
+        </is>
+      </c>
+      <c r="B3285" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3285" t="inlineStr">
+        <is>
+          <t>2026-08-24T04:43:14.296Z</t>
+        </is>
+      </c>
+      <c r="D3285" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3285" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3285" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3286">
+      <c r="A3286" t="inlineStr">
+        <is>
+          <t>96738d64-f3e5-4431-9b7d-c45e9ca7dd3f</t>
+        </is>
+      </c>
+      <c r="B3286" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3286" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:02:36.709Z</t>
+        </is>
+      </c>
+      <c r="D3286" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3286" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3286" t="inlineStr">
+        <is>
+          <t>Welfare Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="3287">
+      <c r="A3287" t="inlineStr">
+        <is>
+          <t>5af3606c-9503-46fe-abb2-e9c396326178</t>
+        </is>
+      </c>
+      <c r="B3287" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3287" t="inlineStr">
+        <is>
+          <t>2026-08-24T06:18:58.933Z</t>
+        </is>
+      </c>
+      <c r="D3287" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3287" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3287" t="inlineStr">
+        <is>
+          <t>Welfare Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="3288">
+      <c r="A3288" t="inlineStr">
+        <is>
+          <t>e9929473-8c50-456d-8368-50dbc19a16f0</t>
+        </is>
+      </c>
+      <c r="B3288" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3288" t="inlineStr">
+        <is>
+          <t>2026-08-24T08:21:43.211Z</t>
+        </is>
+      </c>
+      <c r="D3288" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3288" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3288" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3289">
+      <c r="A3289" t="inlineStr">
+        <is>
+          <t>286c90e5-a6f8-4d2a-a058-f27ff625cb57</t>
+        </is>
+      </c>
+      <c r="B3289" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3289" t="inlineStr">
+        <is>
+          <t>2026-08-24T11:47:09.523Z</t>
+        </is>
+      </c>
+      <c r="D3289" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3289" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3289" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3290">
+      <c r="A3290" t="inlineStr">
+        <is>
+          <t>5e93b6ee-57e2-46a8-bc3b-394395d6fe3e</t>
+        </is>
+      </c>
+      <c r="B3290" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3290" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:45:44.198Z</t>
+        </is>
+      </c>
+      <c r="D3290" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3290" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3290" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3291">
+      <c r="A3291" t="inlineStr">
+        <is>
+          <t>7eccf04c-92ea-41df-9758-9ffa4f26fa64</t>
+        </is>
+      </c>
+      <c r="B3291" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3291" t="inlineStr">
+        <is>
+          <t>2026-08-24T14:27:44.196Z</t>
+        </is>
+      </c>
+      <c r="D3291" t="n">
+        <v>522</v>
+      </c>
+      <c r="E3291" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3291" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3292">
+      <c r="A3292" t="inlineStr">
+        <is>
+          <t>acd6e8a4-1826-4ab5-a376-ee4d67d72f51</t>
+        </is>
+      </c>
+      <c r="B3292" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3292" t="inlineStr">
+        <is>
+          <t>2026-08-24T15:24:22.168Z</t>
+        </is>
+      </c>
+      <c r="D3292" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3292" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3292" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3293">
+      <c r="A3293" t="inlineStr">
+        <is>
+          <t>51a58264-ea83-4637-91be-bc5be9d40a4b</t>
+        </is>
+      </c>
+      <c r="B3293" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3293" t="inlineStr">
+        <is>
+          <t>2026-08-24T18:31:06.572Z</t>
+        </is>
+      </c>
+      <c r="D3293" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3293" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3293" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3294">
+      <c r="A3294" t="inlineStr">
+        <is>
+          <t>3c24fb6e-41b1-470d-af53-fdc3226a62be</t>
+        </is>
+      </c>
+      <c r="B3294" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3294" t="inlineStr">
+        <is>
+          <t>2026-08-24T18:38:29.285Z</t>
+        </is>
+      </c>
+      <c r="D3294" t="n">
+        <v>555</v>
+      </c>
+      <c r="E3294" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3294" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3295">
+      <c r="A3295" t="inlineStr">
+        <is>
+          <t>71841374-8c7c-4327-89ca-b369246d39cd</t>
+        </is>
+      </c>
+      <c r="B3295" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3295" t="inlineStr">
+        <is>
+          <t>2026-08-24T20:44:05.728Z</t>
+        </is>
+      </c>
+      <c r="D3295" t="n">
+        <v>511</v>
+      </c>
+      <c r="E3295" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3295" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3296">
+      <c r="A3296" t="inlineStr">
+        <is>
+          <t>38a64c83-0b71-49e3-bdaa-3ce5cef457eb</t>
+        </is>
+      </c>
+      <c r="B3296" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3296" t="inlineStr">
+        <is>
+          <t>2026-08-24T22:30:50.042Z</t>
+        </is>
+      </c>
+      <c r="D3296" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3296" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3296" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3297">
+      <c r="A3297" t="inlineStr">
+        <is>
+          <t>d0bdd7b9-6b5c-4dd7-af84-29b6c6e92c40</t>
+        </is>
+      </c>
+      <c r="B3297" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3297" t="inlineStr">
+        <is>
+          <t>2026-08-24T22:46:55.158Z</t>
+        </is>
+      </c>
+      <c r="D3297" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3297" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3297" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3297"/>
+  <dimension ref="A1:F3344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80438,6 +80438,1416 @@
         </is>
       </c>
     </row>
+    <row r="3298">
+      <c r="A3298" t="inlineStr">
+        <is>
+          <t>56f3366a-ee5c-4293-b351-7c5598567b45</t>
+        </is>
+      </c>
+      <c r="B3298" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3298" t="inlineStr">
+        <is>
+          <t>2026-08-25T00:04:39.168Z</t>
+        </is>
+      </c>
+      <c r="D3298" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3298" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3298" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3299">
+      <c r="A3299" t="inlineStr">
+        <is>
+          <t>d24e89c0-c6fc-4f6a-90ea-87ff09f991c2</t>
+        </is>
+      </c>
+      <c r="B3299" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3299" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:13:01.622Z</t>
+        </is>
+      </c>
+      <c r="D3299" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3299" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3299" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3300">
+      <c r="A3300" t="inlineStr">
+        <is>
+          <t>eed05d46-b6bb-4e8d-a25a-6b474fb0e96a</t>
+        </is>
+      </c>
+      <c r="B3300" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3300" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:58:26.660Z</t>
+        </is>
+      </c>
+      <c r="D3300" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3300" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3300" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3301">
+      <c r="A3301" t="inlineStr">
+        <is>
+          <t>460abd90-661e-4b90-9fb9-4e14c3ba14c1</t>
+        </is>
+      </c>
+      <c r="B3301" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3301" t="inlineStr">
+        <is>
+          <t>2026-08-25T03:20:35.624Z</t>
+        </is>
+      </c>
+      <c r="D3301" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3301" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3301" t="inlineStr">
+        <is>
+          <t>Welfare Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="3302">
+      <c r="A3302" t="inlineStr">
+        <is>
+          <t>7af3c79f-014a-4a0d-8751-3ab48bf5c01c</t>
+        </is>
+      </c>
+      <c r="B3302" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3302" t="inlineStr">
+        <is>
+          <t>2026-08-25T03:20:40.027Z</t>
+        </is>
+      </c>
+      <c r="D3302" t="n">
+        <v>521</v>
+      </c>
+      <c r="E3302" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3302" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3303">
+      <c r="A3303" t="inlineStr">
+        <is>
+          <t>47762a95-bef3-4034-8b4b-e1404443dd09</t>
+        </is>
+      </c>
+      <c r="B3303" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3303" t="inlineStr">
+        <is>
+          <t>2026-08-25T03:21:23.174Z</t>
+        </is>
+      </c>
+      <c r="D3303" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3303" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3303" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3304">
+      <c r="A3304" t="inlineStr">
+        <is>
+          <t>9a555a64-e3a6-4d44-b9df-5405cc507bea</t>
+        </is>
+      </c>
+      <c r="B3304" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3304" t="inlineStr">
+        <is>
+          <t>2026-08-25T03:40:37.570Z</t>
+        </is>
+      </c>
+      <c r="D3304" t="n">
+        <v>510</v>
+      </c>
+      <c r="E3304" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3304" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3305">
+      <c r="A3305" t="inlineStr">
+        <is>
+          <t>5fa28a2b-431c-40ed-8c08-eeb0a7dc85a2</t>
+        </is>
+      </c>
+      <c r="B3305" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3305" t="inlineStr">
+        <is>
+          <t>2026-08-25T03:54:52.220Z</t>
+        </is>
+      </c>
+      <c r="D3305" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3305" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3305" t="inlineStr">
+        <is>
+          <t>Welfare Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="3306">
+      <c r="A3306" t="inlineStr">
+        <is>
+          <t>7e07b4ed-c541-4bc2-a2db-ad3977536078</t>
+        </is>
+      </c>
+      <c r="B3306" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3306" t="inlineStr">
+        <is>
+          <t>2026-08-25T04:17:42.038Z</t>
+        </is>
+      </c>
+      <c r="D3306" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3306" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3306" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3307">
+      <c r="A3307" t="inlineStr">
+        <is>
+          <t>68213c4b-316e-4509-9299-7cd12c9d01de</t>
+        </is>
+      </c>
+      <c r="B3307" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3307" t="inlineStr">
+        <is>
+          <t>2026-08-25T05:00:42.464Z</t>
+        </is>
+      </c>
+      <c r="D3307" t="n">
+        <v>521</v>
+      </c>
+      <c r="E3307" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3307" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3308">
+      <c r="A3308" t="inlineStr">
+        <is>
+          <t>995d5e9a-5deb-4858-87d7-6367887a3465</t>
+        </is>
+      </c>
+      <c r="B3308" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3308" t="inlineStr">
+        <is>
+          <t>2026-08-25T05:57:27.881Z</t>
+        </is>
+      </c>
+      <c r="D3308" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3308" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3308" t="inlineStr">
+        <is>
+          <t>Hit and Run/Car Accident</t>
+        </is>
+      </c>
+    </row>
+    <row r="3309">
+      <c r="A3309" t="inlineStr">
+        <is>
+          <t>1695247f-0cca-4268-9264-21dcf3df9770</t>
+        </is>
+      </c>
+      <c r="B3309" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3309" t="inlineStr">
+        <is>
+          <t>2026-08-25T06:22:55.347Z</t>
+        </is>
+      </c>
+      <c r="D3309" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3309" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3309" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3310">
+      <c r="A3310" t="inlineStr">
+        <is>
+          <t>26850794-025f-4e3d-a683-6484536f7516</t>
+        </is>
+      </c>
+      <c r="B3310" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3310" t="inlineStr">
+        <is>
+          <t>2026-08-25T06:30:29.634Z</t>
+        </is>
+      </c>
+      <c r="D3310" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3310" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3310" t="inlineStr">
+        <is>
+          <t>Hit and Run/Car Accident</t>
+        </is>
+      </c>
+    </row>
+    <row r="3311">
+      <c r="A3311" t="inlineStr">
+        <is>
+          <t>12c7c21c-d37c-490c-8230-3773675d8f9c</t>
+        </is>
+      </c>
+      <c r="B3311" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3311" t="inlineStr">
+        <is>
+          <t>2026-08-25T06:38:18.050Z</t>
+        </is>
+      </c>
+      <c r="D3311" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3311" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3311" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3312">
+      <c r="A3312" t="inlineStr">
+        <is>
+          <t>903f2a9e-6582-4da7-98cc-e0784c67f432</t>
+        </is>
+      </c>
+      <c r="B3312" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3312" t="inlineStr">
+        <is>
+          <t>2026-08-25T06:38:45.046Z</t>
+        </is>
+      </c>
+      <c r="D3312" t="n">
+        <v>521</v>
+      </c>
+      <c r="E3312" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3312" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3313">
+      <c r="A3313" t="inlineStr">
+        <is>
+          <t>da9ed62d-ae62-442f-ab6c-600b7d0b3e07</t>
+        </is>
+      </c>
+      <c r="B3313" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3313" t="inlineStr">
+        <is>
+          <t>2026-08-25T06:45:56.057Z</t>
+        </is>
+      </c>
+      <c r="D3313" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3313" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3313" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3314">
+      <c r="A3314" t="inlineStr">
+        <is>
+          <t>315c50e6-c9d3-41d5-bce1-09c01d7be7bb</t>
+        </is>
+      </c>
+      <c r="B3314" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3314" t="inlineStr">
+        <is>
+          <t>2026-08-25T07:18:39.501Z</t>
+        </is>
+      </c>
+      <c r="D3314" t="n">
+        <v>521</v>
+      </c>
+      <c r="E3314" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3314" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3315">
+      <c r="A3315" t="inlineStr">
+        <is>
+          <t>9b52cec3-40ca-4c3e-9e82-5502ec045789</t>
+        </is>
+      </c>
+      <c r="B3315" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3315" t="inlineStr">
+        <is>
+          <t>2026-08-25T07:28:59.432Z</t>
+        </is>
+      </c>
+      <c r="D3315" t="n">
+        <v>521</v>
+      </c>
+      <c r="E3315" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3315" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3316">
+      <c r="A3316" t="inlineStr">
+        <is>
+          <t>0473e10c-b423-46e0-a894-43f0ccde7a55</t>
+        </is>
+      </c>
+      <c r="B3316" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3316" t="inlineStr">
+        <is>
+          <t>2026-08-25T07:29:06.925Z</t>
+        </is>
+      </c>
+      <c r="D3316" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3316" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3316" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3317">
+      <c r="A3317" t="inlineStr">
+        <is>
+          <t>e8b4564f-3701-4519-968a-6f96c2a5b9aa</t>
+        </is>
+      </c>
+      <c r="B3317" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3317" t="inlineStr">
+        <is>
+          <t>2026-08-25T08:00:00.759Z</t>
+        </is>
+      </c>
+      <c r="D3317" t="n">
+        <v>521</v>
+      </c>
+      <c r="E3317" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3317" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3318">
+      <c r="A3318" t="inlineStr">
+        <is>
+          <t>8fc87f93-04f4-48cd-a476-2a5d0e6e13fb</t>
+        </is>
+      </c>
+      <c r="B3318" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3318" t="inlineStr">
+        <is>
+          <t>2026-08-25T08:00:07.993Z</t>
+        </is>
+      </c>
+      <c r="D3318" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3318" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3318" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3319">
+      <c r="A3319" t="inlineStr">
+        <is>
+          <t>301e3827-815c-4b17-b233-0d5dd1d3a3fe</t>
+        </is>
+      </c>
+      <c r="B3319" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3319" t="inlineStr">
+        <is>
+          <t>2026-08-25T08:04:16.101Z</t>
+        </is>
+      </c>
+      <c r="D3319" t="n">
+        <v>521</v>
+      </c>
+      <c r="E3319" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3319" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3320">
+      <c r="A3320" t="inlineStr">
+        <is>
+          <t>b9ce313c-1d45-4894-aa4f-d370e0b9b85b</t>
+        </is>
+      </c>
+      <c r="B3320" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3320" t="inlineStr">
+        <is>
+          <t>2026-08-25T09:15:29.449Z</t>
+        </is>
+      </c>
+      <c r="D3320" t="n">
+        <v>521</v>
+      </c>
+      <c r="E3320" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3320" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3321">
+      <c r="A3321" t="inlineStr">
+        <is>
+          <t>d608b13c-ecd4-45a6-96e4-7f89c9e7ee04</t>
+        </is>
+      </c>
+      <c r="B3321" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3321" t="inlineStr">
+        <is>
+          <t>2026-08-25T09:35:12.415Z</t>
+        </is>
+      </c>
+      <c r="D3321" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3321" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3321" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3322">
+      <c r="A3322" t="inlineStr">
+        <is>
+          <t>221c00a9-880b-4c4a-addb-ec08f2e7d1b1</t>
+        </is>
+      </c>
+      <c r="B3322" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3322" t="inlineStr">
+        <is>
+          <t>2026-08-25T15:19:04.065Z</t>
+        </is>
+      </c>
+      <c r="D3322" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3322" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3322" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3323">
+      <c r="A3323" t="inlineStr">
+        <is>
+          <t>1ce61be9-b569-4312-a06b-b08c16716885</t>
+        </is>
+      </c>
+      <c r="B3323" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3323" t="inlineStr">
+        <is>
+          <t>2026-08-25T15:38:48.120Z</t>
+        </is>
+      </c>
+      <c r="D3323" t="n">
+        <v>521</v>
+      </c>
+      <c r="E3323" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3323" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3324">
+      <c r="A3324" t="inlineStr">
+        <is>
+          <t>da1e9787-e415-485c-8c34-cb6af37b7ba8</t>
+        </is>
+      </c>
+      <c r="B3324" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3324" t="inlineStr">
+        <is>
+          <t>2026-08-25T16:05:56.950Z</t>
+        </is>
+      </c>
+      <c r="D3324" t="n">
+        <v>510</v>
+      </c>
+      <c r="E3324" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3324" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3325">
+      <c r="A3325" t="inlineStr">
+        <is>
+          <t>1653169a-9dc6-4658-965d-ce0868a8d450</t>
+        </is>
+      </c>
+      <c r="B3325" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3325" t="inlineStr">
+        <is>
+          <t>2026-08-25T16:32:06.834Z</t>
+        </is>
+      </c>
+      <c r="D3325" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3325" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3325" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3326">
+      <c r="A3326" t="inlineStr">
+        <is>
+          <t>c67fe473-1347-421c-9c6c-1cc73ba31d2a</t>
+        </is>
+      </c>
+      <c r="B3326" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3326" t="inlineStr">
+        <is>
+          <t>2026-08-25T17:34:09.318Z</t>
+        </is>
+      </c>
+      <c r="D3326" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3326" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3326" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3327">
+      <c r="A3327" t="inlineStr">
+        <is>
+          <t>db025af3-6194-4ca5-8c0f-e766419b3a38</t>
+        </is>
+      </c>
+      <c r="B3327" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3327" t="inlineStr">
+        <is>
+          <t>2026-08-25T18:05:48.148Z</t>
+        </is>
+      </c>
+      <c r="D3327" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3327" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3327" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3328">
+      <c r="A3328" t="inlineStr">
+        <is>
+          <t>3b79b4bf-576e-4d11-8149-658c54a3e0af</t>
+        </is>
+      </c>
+      <c r="B3328" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3328" t="inlineStr">
+        <is>
+          <t>2026-08-25T18:08:50.474Z</t>
+        </is>
+      </c>
+      <c r="D3328" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3328" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3328" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3329">
+      <c r="A3329" t="inlineStr">
+        <is>
+          <t>754d0c08-a750-49f6-9b6b-8d4882724c22</t>
+        </is>
+      </c>
+      <c r="B3329" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3329" t="inlineStr">
+        <is>
+          <t>2026-08-25T18:21:15.252Z</t>
+        </is>
+      </c>
+      <c r="D3329" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3329" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3329" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3330">
+      <c r="A3330" t="inlineStr">
+        <is>
+          <t>a149c957-2a8a-465b-8383-d8264c943c53</t>
+        </is>
+      </c>
+      <c r="B3330" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3330" t="inlineStr">
+        <is>
+          <t>2026-08-25T18:25:59.755Z</t>
+        </is>
+      </c>
+      <c r="D3330" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3330" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3330" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3331">
+      <c r="A3331" t="inlineStr">
+        <is>
+          <t>b535e646-e931-42e0-97c4-5518fbc10c6e</t>
+        </is>
+      </c>
+      <c r="B3331" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3331" t="inlineStr">
+        <is>
+          <t>2026-08-25T18:29:05.193Z</t>
+        </is>
+      </c>
+      <c r="D3331" t="n">
+        <v>510</v>
+      </c>
+      <c r="E3331" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3331" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3332">
+      <c r="A3332" t="inlineStr">
+        <is>
+          <t>747fdb4d-aa40-4899-88b2-654ec901c46c</t>
+        </is>
+      </c>
+      <c r="B3332" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3332" t="inlineStr">
+        <is>
+          <t>2026-08-25T18:30:38.700Z</t>
+        </is>
+      </c>
+      <c r="D3332" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3332" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3332" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3333">
+      <c r="A3333" t="inlineStr">
+        <is>
+          <t>cadd0da1-fa8b-413a-8342-d30521ff06c7</t>
+        </is>
+      </c>
+      <c r="B3333" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3333" t="inlineStr">
+        <is>
+          <t>2026-08-25T18:38:46.682Z</t>
+        </is>
+      </c>
+      <c r="D3333" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3333" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3333" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3334">
+      <c r="A3334" t="inlineStr">
+        <is>
+          <t>4acf8ec9-0ec9-438f-942b-34d60566918b</t>
+        </is>
+      </c>
+      <c r="B3334" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3334" t="inlineStr">
+        <is>
+          <t>2026-08-25T18:45:49.115Z</t>
+        </is>
+      </c>
+      <c r="D3334" t="n">
+        <v>510</v>
+      </c>
+      <c r="E3334" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3334" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3335">
+      <c r="A3335" t="inlineStr">
+        <is>
+          <t>6dcbd741-cd64-41e0-a4ce-3a170367cd93</t>
+        </is>
+      </c>
+      <c r="B3335" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3335" t="inlineStr">
+        <is>
+          <t>2026-08-25T19:55:24.438Z</t>
+        </is>
+      </c>
+      <c r="D3335" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3335" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3335" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3336">
+      <c r="A3336" t="inlineStr">
+        <is>
+          <t>ae3786c8-6e06-404b-955f-370ca4159d3b</t>
+        </is>
+      </c>
+      <c r="B3336" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3336" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:25:06.203Z</t>
+        </is>
+      </c>
+      <c r="D3336" t="n">
+        <v>510</v>
+      </c>
+      <c r="E3336" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3336" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3337">
+      <c r="A3337" t="inlineStr">
+        <is>
+          <t>73b66f17-99b7-43db-a55c-a2b52820337c</t>
+        </is>
+      </c>
+      <c r="B3337" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3337" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:32:41.999Z</t>
+        </is>
+      </c>
+      <c r="D3337" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3337" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3337" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3338">
+      <c r="A3338" t="inlineStr">
+        <is>
+          <t>62a8bdf7-eca8-4cc8-bf31-43bffc08efae</t>
+        </is>
+      </c>
+      <c r="B3338" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3338" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:45:14.147Z</t>
+        </is>
+      </c>
+      <c r="D3338" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3338" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3338" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3339">
+      <c r="A3339" t="inlineStr">
+        <is>
+          <t>2708d92c-bd17-48d2-b03e-30e533acff6f</t>
+        </is>
+      </c>
+      <c r="B3339" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3339" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:54:52.189Z</t>
+        </is>
+      </c>
+      <c r="D3339" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3339" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3339" t="inlineStr">
+        <is>
+          <t>Traffic Infraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3340">
+      <c r="A3340" t="inlineStr">
+        <is>
+          <t>6e10957d-6233-4bb3-b353-6f8470bdad17</t>
+        </is>
+      </c>
+      <c r="B3340" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3340" t="inlineStr">
+        <is>
+          <t>2026-08-25T21:01:12.795Z</t>
+        </is>
+      </c>
+      <c r="D3340" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3340" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3340" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3341">
+      <c r="A3341" t="inlineStr">
+        <is>
+          <t>676e99be-0e18-4769-9e95-1aa4981024b6</t>
+        </is>
+      </c>
+      <c r="B3341" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3341" t="inlineStr">
+        <is>
+          <t>2026-08-25T21:10:53.178Z</t>
+        </is>
+      </c>
+      <c r="D3341" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3341" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3341" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3342">
+      <c r="A3342" t="inlineStr">
+        <is>
+          <t>30234c6c-94c9-4d33-833f-5963374bf2e4</t>
+        </is>
+      </c>
+      <c r="B3342" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3342" t="inlineStr">
+        <is>
+          <t>2026-08-25T22:04:53.218Z</t>
+        </is>
+      </c>
+      <c r="D3342" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3342" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3342" t="inlineStr">
+        <is>
+          <t>Stalking</t>
+        </is>
+      </c>
+    </row>
+    <row r="3343">
+      <c r="A3343" t="inlineStr">
+        <is>
+          <t>4ee17581-7148-4abb-a450-2c0ff462dc39</t>
+        </is>
+      </c>
+      <c r="B3343" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3343" t="inlineStr">
+        <is>
+          <t>2026-08-25T22:34:09.269Z</t>
+        </is>
+      </c>
+      <c r="D3343" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3343" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3343" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3344">
+      <c r="A3344" t="inlineStr">
+        <is>
+          <t>729e850c-9d8c-4e6c-92ab-ee56668c18f1</t>
+        </is>
+      </c>
+      <c r="B3344" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3344" t="inlineStr">
+        <is>
+          <t>2026-08-25T22:56:56.011Z</t>
+        </is>
+      </c>
+      <c r="D3344" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3344" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3344" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3344"/>
+  <dimension ref="A1:F3360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81848,6 +81848,486 @@
         </is>
       </c>
     </row>
+    <row r="3345">
+      <c r="A3345" t="inlineStr">
+        <is>
+          <t>9f85d0b3-ee70-431a-9b41-46ae8401f312</t>
+        </is>
+      </c>
+      <c r="B3345" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3345" t="inlineStr">
+        <is>
+          <t>2026-08-26T01:34:29.441Z</t>
+        </is>
+      </c>
+      <c r="D3345" t="n">
+        <v>510</v>
+      </c>
+      <c r="E3345" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3345" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3346">
+      <c r="A3346" t="inlineStr">
+        <is>
+          <t>ceeb30b3-4dcf-4b1d-96db-79a1b8a0941d</t>
+        </is>
+      </c>
+      <c r="B3346" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3346" t="inlineStr">
+        <is>
+          <t>2026-08-26T04:53:08.108Z</t>
+        </is>
+      </c>
+      <c r="D3346" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3346" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3346" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3347">
+      <c r="A3347" t="inlineStr">
+        <is>
+          <t>043bbd8a-e25a-4d6c-813d-b98b7d085173</t>
+        </is>
+      </c>
+      <c r="B3347" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3347" t="inlineStr">
+        <is>
+          <t>2026-08-26T05:00:37.692Z</t>
+        </is>
+      </c>
+      <c r="D3347" t="n">
+        <v>779</v>
+      </c>
+      <c r="E3347" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3347" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3348">
+      <c r="A3348" t="inlineStr">
+        <is>
+          <t>7bb797fd-6874-4838-9124-d2fab5f40157</t>
+        </is>
+      </c>
+      <c r="B3348" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3348" t="inlineStr">
+        <is>
+          <t>2026-08-26T05:06:30.768Z</t>
+        </is>
+      </c>
+      <c r="D3348" t="n">
+        <v>521</v>
+      </c>
+      <c r="E3348" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3348" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3349">
+      <c r="A3349" t="inlineStr">
+        <is>
+          <t>614ac52c-489a-4316-a1e5-ca8f0eaf681d</t>
+        </is>
+      </c>
+      <c r="B3349" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3349" t="inlineStr">
+        <is>
+          <t>2026-08-26T06:46:54.210Z</t>
+        </is>
+      </c>
+      <c r="D3349" t="n">
+        <v>521</v>
+      </c>
+      <c r="E3349" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3349" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3350">
+      <c r="A3350" t="inlineStr">
+        <is>
+          <t>b3cbb959-7d5f-4b0c-880c-76aee48cf58d</t>
+        </is>
+      </c>
+      <c r="B3350" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3350" t="inlineStr">
+        <is>
+          <t>2026-08-26T07:27:04.164Z</t>
+        </is>
+      </c>
+      <c r="D3350" t="n">
+        <v>521</v>
+      </c>
+      <c r="E3350" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3350" t="inlineStr">
+        <is>
+          <t>Threats/Harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3351">
+      <c r="A3351" t="inlineStr">
+        <is>
+          <t>22d1a815-3b38-4ef0-9398-53470b5873c5</t>
+        </is>
+      </c>
+      <c r="B3351" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3351" t="inlineStr">
+        <is>
+          <t>2026-08-26T12:31:45.477Z</t>
+        </is>
+      </c>
+      <c r="D3351" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3351" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3351" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3352">
+      <c r="A3352" t="inlineStr">
+        <is>
+          <t>fc49b09d-5214-4d6a-9b52-bf3dd74378c3</t>
+        </is>
+      </c>
+      <c r="B3352" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3352" t="inlineStr">
+        <is>
+          <t>2026-08-26T15:13:26.876Z</t>
+        </is>
+      </c>
+      <c r="D3352" t="n">
+        <v>510</v>
+      </c>
+      <c r="E3352" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3352" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3353">
+      <c r="A3353" t="inlineStr">
+        <is>
+          <t>d7592571-401e-48bf-b21f-3f501a2b206d</t>
+        </is>
+      </c>
+      <c r="B3353" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3353" t="inlineStr">
+        <is>
+          <t>2026-08-26T17:58:51.808Z</t>
+        </is>
+      </c>
+      <c r="D3353" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3353" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3353" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3354">
+      <c r="A3354" t="inlineStr">
+        <is>
+          <t>cc518aca-85ca-4066-9882-ba0d7d1f4c94</t>
+        </is>
+      </c>
+      <c r="B3354" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3354" t="inlineStr">
+        <is>
+          <t>2026-08-26T18:02:09.069Z</t>
+        </is>
+      </c>
+      <c r="D3354" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3354" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3354" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3355">
+      <c r="A3355" t="inlineStr">
+        <is>
+          <t>21f76273-1f20-436d-841d-53ff2efefdc9</t>
+        </is>
+      </c>
+      <c r="B3355" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3355" t="inlineStr">
+        <is>
+          <t>2026-08-26T18:03:23.741Z</t>
+        </is>
+      </c>
+      <c r="D3355" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3355" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3355" t="inlineStr">
+        <is>
+          <t>Trespass</t>
+        </is>
+      </c>
+    </row>
+    <row r="3356">
+      <c r="A3356" t="inlineStr">
+        <is>
+          <t>0d150232-d8be-4fa9-916b-ee6960ac5748</t>
+        </is>
+      </c>
+      <c r="B3356" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3356" t="inlineStr">
+        <is>
+          <t>2026-08-26T19:19:15.620Z</t>
+        </is>
+      </c>
+      <c r="D3356" t="n">
+        <v>510</v>
+      </c>
+      <c r="E3356" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3356" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3357">
+      <c r="A3357" t="inlineStr">
+        <is>
+          <t>90e1c1ba-abb6-404f-8f72-4559d4914501</t>
+        </is>
+      </c>
+      <c r="B3357" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3357" t="inlineStr">
+        <is>
+          <t>2026-08-26T19:34:16.165Z</t>
+        </is>
+      </c>
+      <c r="D3357" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3357" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3357" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3358">
+      <c r="A3358" t="inlineStr">
+        <is>
+          <t>cc17f68e-ed86-43f3-9d0a-f8cfbfba1395</t>
+        </is>
+      </c>
+      <c r="B3358" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3358" t="inlineStr">
+        <is>
+          <t>2026-08-26T21:14:21.671Z</t>
+        </is>
+      </c>
+      <c r="D3358" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3358" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3358" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3359">
+      <c r="A3359" t="inlineStr">
+        <is>
+          <t>eaabfb95-d5ad-4e37-b9ca-80fe295c76b1</t>
+        </is>
+      </c>
+      <c r="B3359" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3359" t="inlineStr">
+        <is>
+          <t>2026-08-26T22:09:28.417Z</t>
+        </is>
+      </c>
+      <c r="D3359" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3359" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3359" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3360">
+      <c r="A3360" t="inlineStr">
+        <is>
+          <t>01b98adf-182b-448a-b272-6126b60b7db3</t>
+        </is>
+      </c>
+      <c r="B3360" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3360" t="inlineStr">
+        <is>
+          <t>2026-08-26T22:50:52.629Z</t>
+        </is>
+      </c>
+      <c r="D3360" t="n">
+        <v>510</v>
+      </c>
+      <c r="E3360" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3360" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3360"/>
+  <dimension ref="A1:F3366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82328,6 +82328,186 @@
         </is>
       </c>
     </row>
+    <row r="3361">
+      <c r="A3361" t="inlineStr">
+        <is>
+          <t>dbd51a68-8207-48b1-af30-96c66badc9e9</t>
+        </is>
+      </c>
+      <c r="B3361" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3361" t="inlineStr">
+        <is>
+          <t>2026-08-27T00:03:56.735Z</t>
+        </is>
+      </c>
+      <c r="D3361" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3361" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3361" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3362">
+      <c r="A3362" t="inlineStr">
+        <is>
+          <t>8e0529b4-1ee3-4704-a996-c20583a9e402</t>
+        </is>
+      </c>
+      <c r="B3362" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3362" t="inlineStr">
+        <is>
+          <t>2026-08-27T01:11:22.382Z</t>
+        </is>
+      </c>
+      <c r="D3362" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3362" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3362" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3363">
+      <c r="A3363" t="inlineStr">
+        <is>
+          <t>3ebe58c7-17fa-4ecf-ac53-7cbef4aaf308</t>
+        </is>
+      </c>
+      <c r="B3363" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3363" t="inlineStr">
+        <is>
+          <t>2026-08-27T07:53:33.771Z</t>
+        </is>
+      </c>
+      <c r="D3363" t="n">
+        <v>521</v>
+      </c>
+      <c r="E3363" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3363" t="inlineStr">
+        <is>
+          <t>Hit and Run/Car Accident</t>
+        </is>
+      </c>
+    </row>
+    <row r="3364">
+      <c r="A3364" t="inlineStr">
+        <is>
+          <t>133de411-29e0-46e6-b889-1c43811e7409</t>
+        </is>
+      </c>
+      <c r="B3364" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3364" t="inlineStr">
+        <is>
+          <t>2026-08-27T13:22:57.500Z</t>
+        </is>
+      </c>
+      <c r="D3364" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3364" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3364" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3365">
+      <c r="A3365" t="inlineStr">
+        <is>
+          <t>efd7603c-8379-4fe4-956d-435d4a393aa6</t>
+        </is>
+      </c>
+      <c r="B3365" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3365" t="inlineStr">
+        <is>
+          <t>2026-08-27T19:04:27.219Z</t>
+        </is>
+      </c>
+      <c r="D3365" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3365" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3365" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3366">
+      <c r="A3366" t="inlineStr">
+        <is>
+          <t>d2df235a-eb6d-4407-b6da-8c758f3c828d</t>
+        </is>
+      </c>
+      <c r="B3366" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3366" t="inlineStr">
+        <is>
+          <t>2026-08-27T20:39:54.262Z</t>
+        </is>
+      </c>
+      <c r="D3366" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3366" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3366" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3366"/>
+  <dimension ref="A1:F3369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82508,6 +82508,96 @@
         </is>
       </c>
     </row>
+    <row r="3367">
+      <c r="A3367" t="inlineStr">
+        <is>
+          <t>7ee11ad6-e785-40ad-91bf-3325b90a9cd5</t>
+        </is>
+      </c>
+      <c r="B3367" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3367" t="inlineStr">
+        <is>
+          <t>2026-08-28T16:40:23.924Z</t>
+        </is>
+      </c>
+      <c r="D3367" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3367" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3367" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3368">
+      <c r="A3368" t="inlineStr">
+        <is>
+          <t>22dbe101-e4fc-43e5-a47f-9c8ce0f6b5d7</t>
+        </is>
+      </c>
+      <c r="B3368" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3368" t="inlineStr">
+        <is>
+          <t>2026-08-28T17:37:22.035Z</t>
+        </is>
+      </c>
+      <c r="D3368" t="n">
+        <v>554</v>
+      </c>
+      <c r="E3368" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3368" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3369">
+      <c r="A3369" t="inlineStr">
+        <is>
+          <t>ea1005ea-da02-4b6c-8e8c-87c264169327</t>
+        </is>
+      </c>
+      <c r="B3369" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3369" t="inlineStr">
+        <is>
+          <t>2026-08-28T23:27:58.105Z</t>
+        </is>
+      </c>
+      <c r="D3369" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3369" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3369" t="inlineStr">
+        <is>
+          <t>Child Abuse/Neglect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3369"/>
+  <dimension ref="A1:F3371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82598,6 +82598,66 @@
         </is>
       </c>
     </row>
+    <row r="3370">
+      <c r="A3370" t="inlineStr">
+        <is>
+          <t>af9d0d5c-1ad0-41df-a21f-cec896658969</t>
+        </is>
+      </c>
+      <c r="B3370" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3370" t="inlineStr">
+        <is>
+          <t>2026-08-29T20:49:58.809Z</t>
+        </is>
+      </c>
+      <c r="D3370" t="n">
+        <v>553</v>
+      </c>
+      <c r="E3370" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3370" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3371">
+      <c r="A3371" t="inlineStr">
+        <is>
+          <t>0166391d-ab84-4afd-a67a-2711dcc30408</t>
+        </is>
+      </c>
+      <c r="B3371" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3371" t="inlineStr">
+        <is>
+          <t>2026-08-29T22:02:46.985Z</t>
+        </is>
+      </c>
+      <c r="D3371" t="n">
+        <v>553</v>
+      </c>
+      <c r="E3371" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3371" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3371"/>
+  <dimension ref="A1:F3377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82658,6 +82658,186 @@
         </is>
       </c>
     </row>
+    <row r="3372">
+      <c r="A3372" t="inlineStr">
+        <is>
+          <t>49c602ed-2056-4720-a13b-7ddd847a3416</t>
+        </is>
+      </c>
+      <c r="B3372" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3372" t="inlineStr">
+        <is>
+          <t>2026-08-30T00:07:36.657Z</t>
+        </is>
+      </c>
+      <c r="D3372" t="n">
+        <v>553</v>
+      </c>
+      <c r="E3372" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3372" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3373">
+      <c r="A3373" t="inlineStr">
+        <is>
+          <t>576e1085-11e6-4123-859c-5b135fe84b76</t>
+        </is>
+      </c>
+      <c r="B3373" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3373" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:13:23.181Z</t>
+        </is>
+      </c>
+      <c r="D3373" t="n">
+        <v>553</v>
+      </c>
+      <c r="E3373" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3373" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3374">
+      <c r="A3374" t="inlineStr">
+        <is>
+          <t>8c1e19b1-8221-4da4-9e40-ad973022cccf</t>
+        </is>
+      </c>
+      <c r="B3374" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3374" t="inlineStr">
+        <is>
+          <t>2026-08-30T03:29:15.545Z</t>
+        </is>
+      </c>
+      <c r="D3374" t="n">
+        <v>553</v>
+      </c>
+      <c r="E3374" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3374" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3375">
+      <c r="A3375" t="inlineStr">
+        <is>
+          <t>bada4d52-06df-4572-a11c-e519a7a69a0a</t>
+        </is>
+      </c>
+      <c r="B3375" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3375" t="inlineStr">
+        <is>
+          <t>2026-08-30T03:58:56.906Z</t>
+        </is>
+      </c>
+      <c r="D3375" t="n">
+        <v>553</v>
+      </c>
+      <c r="E3375" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3375" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3376">
+      <c r="A3376" t="inlineStr">
+        <is>
+          <t>48e80a92-5c1f-4a40-8bb4-89364e015665</t>
+        </is>
+      </c>
+      <c r="B3376" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3376" t="inlineStr">
+        <is>
+          <t>2026-08-30T05:42:11.164Z</t>
+        </is>
+      </c>
+      <c r="D3376" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3376" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3376" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3377">
+      <c r="A3377" t="inlineStr">
+        <is>
+          <t>dda73cc8-e844-4509-8af2-f9e1519dae6b</t>
+        </is>
+      </c>
+      <c r="B3377" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3377" t="inlineStr">
+        <is>
+          <t>2026-08-30T23:40:46.709Z</t>
+        </is>
+      </c>
+      <c r="D3377" t="n">
+        <v>553</v>
+      </c>
+      <c r="E3377" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3377" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3377"/>
+  <dimension ref="A1:F3387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82838,6 +82838,306 @@
         </is>
       </c>
     </row>
+    <row r="3378">
+      <c r="A3378" t="inlineStr">
+        <is>
+          <t>f4f0b57b-3fcf-4962-9b30-421bb04dc654</t>
+        </is>
+      </c>
+      <c r="B3378" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3378" t="inlineStr">
+        <is>
+          <t>2026-08-31T05:28:07.233Z</t>
+        </is>
+      </c>
+      <c r="D3378" t="n">
+        <v>553</v>
+      </c>
+      <c r="E3378" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3378" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3379">
+      <c r="A3379" t="inlineStr">
+        <is>
+          <t>1d08467a-f290-4773-8f72-f0444dfe1c05</t>
+        </is>
+      </c>
+      <c r="B3379" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3379" t="inlineStr">
+        <is>
+          <t>2026-08-31T06:07:15.239Z</t>
+        </is>
+      </c>
+      <c r="D3379" t="n">
+        <v>510</v>
+      </c>
+      <c r="E3379" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3379" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3380">
+      <c r="A3380" t="inlineStr">
+        <is>
+          <t>4cbb1113-a94a-43e2-a3fb-c47c178170fb</t>
+        </is>
+      </c>
+      <c r="B3380" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3380" t="inlineStr">
+        <is>
+          <t>2026-08-31T07:07:28.943Z</t>
+        </is>
+      </c>
+      <c r="D3380" t="n">
+        <v>510</v>
+      </c>
+      <c r="E3380" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3380" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3381">
+      <c r="A3381" t="inlineStr">
+        <is>
+          <t>74a264c9-9cc5-4963-b36e-cad47d518996</t>
+        </is>
+      </c>
+      <c r="B3381" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3381" t="inlineStr">
+        <is>
+          <t>2026-08-31T07:25:24.327Z</t>
+        </is>
+      </c>
+      <c r="D3381" t="n">
+        <v>520</v>
+      </c>
+      <c r="E3381" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3381" t="inlineStr">
+        <is>
+          <t>Criminal Motor Vehicle Offense (incl. Road Rage/Reckless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3382">
+      <c r="A3382" t="inlineStr">
+        <is>
+          <t>66f19475-e206-4d62-9e18-2f24725ee334</t>
+        </is>
+      </c>
+      <c r="B3382" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3382" t="inlineStr">
+        <is>
+          <t>2026-08-31T08:53:28.749Z</t>
+        </is>
+      </c>
+      <c r="D3382" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3382" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3382" t="inlineStr">
+        <is>
+          <t>Criminal Motor Vehicle Offense (incl. Road Rage/Reckless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3383">
+      <c r="A3383" t="inlineStr">
+        <is>
+          <t>bfa8fa6c-f04a-417e-b614-6c71141396bc</t>
+        </is>
+      </c>
+      <c r="B3383" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3383" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:06:38.686Z</t>
+        </is>
+      </c>
+      <c r="D3383" t="n">
+        <v>553</v>
+      </c>
+      <c r="E3383" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3383" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3384">
+      <c r="A3384" t="inlineStr">
+        <is>
+          <t>ccbcd19d-b6a7-4f85-b828-97be28113811</t>
+        </is>
+      </c>
+      <c r="B3384" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3384" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:10:33.783Z</t>
+        </is>
+      </c>
+      <c r="D3384" t="n">
+        <v>553</v>
+      </c>
+      <c r="E3384" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3384" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3385">
+      <c r="A3385" t="inlineStr">
+        <is>
+          <t>e1b67cf8-6da9-4526-8e84-f41335b301a6</t>
+        </is>
+      </c>
+      <c r="B3385" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3385" t="inlineStr">
+        <is>
+          <t>2026-08-31T20:44:01.674Z</t>
+        </is>
+      </c>
+      <c r="D3385" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3385" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3385" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3386">
+      <c r="A3386" t="inlineStr">
+        <is>
+          <t>165a5ff9-e2a1-4e0e-a5c3-7cd060adbc75</t>
+        </is>
+      </c>
+      <c r="B3386" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3386" t="inlineStr">
+        <is>
+          <t>2026-08-31T20:47:38.477Z</t>
+        </is>
+      </c>
+      <c r="D3386" t="n">
+        <v>553</v>
+      </c>
+      <c r="E3386" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3386" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3387">
+      <c r="A3387" t="inlineStr">
+        <is>
+          <t>defb23c9-a5f3-411f-8134-03d7b0797f84</t>
+        </is>
+      </c>
+      <c r="B3387" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3387" t="inlineStr">
+        <is>
+          <t>2026-08-31T21:22:41.731Z</t>
+        </is>
+      </c>
+      <c r="D3387" t="n">
+        <v>553</v>
+      </c>
+      <c r="E3387" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3387" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3387"/>
+  <dimension ref="A1:F3394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83138,6 +83138,216 @@
         </is>
       </c>
     </row>
+    <row r="3388">
+      <c r="A3388" t="inlineStr">
+        <is>
+          <t>05daa658-35a4-4351-93cd-244821d74e9e</t>
+        </is>
+      </c>
+      <c r="B3388" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3388" t="inlineStr">
+        <is>
+          <t>2026-09-01T05:10:11.682Z</t>
+        </is>
+      </c>
+      <c r="D3388" t="n">
+        <v>520</v>
+      </c>
+      <c r="E3388" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3388" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3389">
+      <c r="A3389" t="inlineStr">
+        <is>
+          <t>4c9c51d3-e282-43cc-88bd-27b2fa39b685</t>
+        </is>
+      </c>
+      <c r="B3389" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3389" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:09:36.481Z</t>
+        </is>
+      </c>
+      <c r="D3389" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3389" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3389" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3390">
+      <c r="A3390" t="inlineStr">
+        <is>
+          <t>c5280136-2779-4fc3-aa64-7b71aa2444da</t>
+        </is>
+      </c>
+      <c r="B3390" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3390" t="inlineStr">
+        <is>
+          <t>2026-09-01T10:35:01.755Z</t>
+        </is>
+      </c>
+      <c r="D3390" t="n">
+        <v>510</v>
+      </c>
+      <c r="E3390" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3390" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3391">
+      <c r="A3391" t="inlineStr">
+        <is>
+          <t>1e220779-bcec-415e-98c7-c60c97f446aa</t>
+        </is>
+      </c>
+      <c r="B3391" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3391" t="inlineStr">
+        <is>
+          <t>2026-09-01T13:28:40.192Z</t>
+        </is>
+      </c>
+      <c r="D3391" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3391" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3391" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3392">
+      <c r="A3392" t="inlineStr">
+        <is>
+          <t>851137ad-b9cb-4959-a9fd-0fe8fd1b7c06</t>
+        </is>
+      </c>
+      <c r="B3392" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3392" t="inlineStr">
+        <is>
+          <t>2026-09-01T16:42:34.778Z</t>
+        </is>
+      </c>
+      <c r="D3392" t="n">
+        <v>550</v>
+      </c>
+      <c r="E3392" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3392" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3393">
+      <c r="A3393" t="inlineStr">
+        <is>
+          <t>081ef503-a3e1-4948-85ad-533e3b24802c</t>
+        </is>
+      </c>
+      <c r="B3393" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3393" t="inlineStr">
+        <is>
+          <t>2026-09-01T17:10:01.731Z</t>
+        </is>
+      </c>
+      <c r="D3393" t="n">
+        <v>550</v>
+      </c>
+      <c r="E3393" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3393" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3394">
+      <c r="A3394" t="inlineStr">
+        <is>
+          <t>bbed8aca-8beb-45a5-8536-b3d874b1df1f</t>
+        </is>
+      </c>
+      <c r="B3394" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3394" t="inlineStr">
+        <is>
+          <t>2026-09-01T20:18:21.669Z</t>
+        </is>
+      </c>
+      <c r="D3394" t="n">
+        <v>548</v>
+      </c>
+      <c r="E3394" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3394" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3394"/>
+  <dimension ref="A1:F3416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83348,6 +83348,666 @@
         </is>
       </c>
     </row>
+    <row r="3395">
+      <c r="A3395" t="inlineStr">
+        <is>
+          <t>35c2b759-473a-462a-9ef1-f0c798d4336c</t>
+        </is>
+      </c>
+      <c r="B3395" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3395" t="inlineStr">
+        <is>
+          <t>2026-09-02T01:23:47.349Z</t>
+        </is>
+      </c>
+      <c r="D3395" t="n">
+        <v>547</v>
+      </c>
+      <c r="E3395" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3395" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3396">
+      <c r="A3396" t="inlineStr">
+        <is>
+          <t>7bb0ef3c-3790-485c-963f-578065703a1b</t>
+        </is>
+      </c>
+      <c r="B3396" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3396" t="inlineStr">
+        <is>
+          <t>2026-09-02T06:54:08.571Z</t>
+        </is>
+      </c>
+      <c r="D3396" t="n">
+        <v>547</v>
+      </c>
+      <c r="E3396" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3396" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3397">
+      <c r="A3397" t="inlineStr">
+        <is>
+          <t>ddc572be-06ef-4eda-951f-6fd2de8e1a03</t>
+        </is>
+      </c>
+      <c r="B3397" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3397" t="inlineStr">
+        <is>
+          <t>2026-09-02T07:02:59.268Z</t>
+        </is>
+      </c>
+      <c r="D3397" t="n">
+        <v>547</v>
+      </c>
+      <c r="E3397" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3397" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3398">
+      <c r="A3398" t="inlineStr">
+        <is>
+          <t>9c4612b1-f508-459c-8fd5-a9a2a6d0a41f</t>
+        </is>
+      </c>
+      <c r="B3398" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3398" t="inlineStr">
+        <is>
+          <t>2026-09-02T08:13:14.857Z</t>
+        </is>
+      </c>
+      <c r="D3398" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3398" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3398" t="inlineStr">
+        <is>
+          <t>Traffic Infraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3399">
+      <c r="A3399" t="inlineStr">
+        <is>
+          <t>f0943fe5-f5d2-4266-bcef-4997d9b7e07b</t>
+        </is>
+      </c>
+      <c r="B3399" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3399" t="inlineStr">
+        <is>
+          <t>2026-09-02T09:55:30.818Z</t>
+        </is>
+      </c>
+      <c r="D3399" t="n">
+        <v>515</v>
+      </c>
+      <c r="E3399" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3399" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3400">
+      <c r="A3400" t="inlineStr">
+        <is>
+          <t>dc2e3762-ae08-4101-8e23-15a48abf546f</t>
+        </is>
+      </c>
+      <c r="B3400" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3400" t="inlineStr">
+        <is>
+          <t>2026-09-02T10:52:22.328Z</t>
+        </is>
+      </c>
+      <c r="D3400" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3400" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3400" t="inlineStr">
+        <is>
+          <t>Criminal Motor Vehicle Offense (incl. Road Rage/Reckless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3401">
+      <c r="A3401" t="inlineStr">
+        <is>
+          <t>29a13b11-d0f4-4f88-9a29-dce8d79f4660</t>
+        </is>
+      </c>
+      <c r="B3401" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3401" t="inlineStr">
+        <is>
+          <t>2026-09-02T11:11:52.087Z</t>
+        </is>
+      </c>
+      <c r="D3401" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3401" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3401" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3402">
+      <c r="A3402" t="inlineStr">
+        <is>
+          <t>714c219c-06ef-47e8-9c1f-2c165cefb75b</t>
+        </is>
+      </c>
+      <c r="B3402" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3402" t="inlineStr">
+        <is>
+          <t>2026-09-02T11:57:20.555Z</t>
+        </is>
+      </c>
+      <c r="D3402" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3402" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3402" t="inlineStr">
+        <is>
+          <t>Criminal Motor Vehicle Offense (incl. Road Rage/Reckless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3403">
+      <c r="A3403" t="inlineStr">
+        <is>
+          <t>9048997b-6097-4db4-a70c-37b5c925b934</t>
+        </is>
+      </c>
+      <c r="B3403" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3403" t="inlineStr">
+        <is>
+          <t>2026-09-02T12:05:51.662Z</t>
+        </is>
+      </c>
+      <c r="D3403" t="n">
+        <v>547</v>
+      </c>
+      <c r="E3403" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3403" t="inlineStr">
+        <is>
+          <t>Criminal Motor Vehicle Offense (incl. Road Rage/Reckless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3404">
+      <c r="A3404" t="inlineStr">
+        <is>
+          <t>3e879e6c-035e-4f4e-a689-e76db899a07f</t>
+        </is>
+      </c>
+      <c r="B3404" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3404" t="inlineStr">
+        <is>
+          <t>2026-09-02T13:46:16.610Z</t>
+        </is>
+      </c>
+      <c r="D3404" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3404" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3404" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3405">
+      <c r="A3405" t="inlineStr">
+        <is>
+          <t>7b23ae38-408a-4d51-a2ca-7857fa41decd</t>
+        </is>
+      </c>
+      <c r="B3405" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3405" t="inlineStr">
+        <is>
+          <t>2026-09-02T15:18:10.024Z</t>
+        </is>
+      </c>
+      <c r="D3405" t="n">
+        <v>504</v>
+      </c>
+      <c r="E3405" t="inlineStr">
+        <is>
+          <t>Agency Assist</t>
+        </is>
+      </c>
+      <c r="F3405" t="inlineStr">
+        <is>
+          <t>Traffic Infraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3406">
+      <c r="A3406" t="inlineStr">
+        <is>
+          <t>2c4412c7-40cb-446e-a3d4-2f488ecb80a1</t>
+        </is>
+      </c>
+      <c r="B3406" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3406" t="inlineStr">
+        <is>
+          <t>2026-09-02T16:22:07.904Z</t>
+        </is>
+      </c>
+      <c r="D3406" t="n">
+        <v>504</v>
+      </c>
+      <c r="E3406" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3406" t="inlineStr">
+        <is>
+          <t>Criminal Motor Vehicle Offense (incl. Road Rage/Reckless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3407">
+      <c r="A3407" t="inlineStr">
+        <is>
+          <t>a5242a3a-0a44-413a-b14b-e85d914ebe46</t>
+        </is>
+      </c>
+      <c r="B3407" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3407" t="inlineStr">
+        <is>
+          <t>2026-09-03T14:27:41.961Z</t>
+        </is>
+      </c>
+      <c r="D3407" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3407" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3407" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3408">
+      <c r="A3408" t="inlineStr">
+        <is>
+          <t>c0b9d677-7848-4604-9a59-a827676d7047</t>
+        </is>
+      </c>
+      <c r="B3408" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3408" t="inlineStr">
+        <is>
+          <t>2026-09-03T14:40:21.743Z</t>
+        </is>
+      </c>
+      <c r="D3408" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3408" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3408" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3409">
+      <c r="A3409" t="inlineStr">
+        <is>
+          <t>e105177c-2aea-426b-a59f-93fd8a7946af</t>
+        </is>
+      </c>
+      <c r="B3409" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3409" t="inlineStr">
+        <is>
+          <t>2026-09-03T17:05:00.015Z</t>
+        </is>
+      </c>
+      <c r="D3409" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3409" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3409" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3410">
+      <c r="A3410" t="inlineStr">
+        <is>
+          <t>ad8bfcc4-c364-452d-af34-7cb52ef30552</t>
+        </is>
+      </c>
+      <c r="B3410" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3410" t="inlineStr">
+        <is>
+          <t>2026-09-03T18:19:09.427Z</t>
+        </is>
+      </c>
+      <c r="D3410" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3410" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3410" t="inlineStr">
+        <is>
+          <t>Stolen Property Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3411">
+      <c r="A3411" t="inlineStr">
+        <is>
+          <t>3fea29d7-49c1-4a4d-8a3c-f1b99f932658</t>
+        </is>
+      </c>
+      <c r="B3411" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3411" t="inlineStr">
+        <is>
+          <t>2026-09-03T18:58:23.599Z</t>
+        </is>
+      </c>
+      <c r="D3411" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3411" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3411" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3412">
+      <c r="A3412" t="inlineStr">
+        <is>
+          <t>cb3f6666-34c5-45ec-aa16-4e83c68dfa6d</t>
+        </is>
+      </c>
+      <c r="B3412" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3412" t="inlineStr">
+        <is>
+          <t>2026-09-03T19:02:58.274Z</t>
+        </is>
+      </c>
+      <c r="D3412" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3412" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3412" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3413">
+      <c r="A3413" t="inlineStr">
+        <is>
+          <t>c57b28e5-c3b9-4069-a799-fdd463f1185e</t>
+        </is>
+      </c>
+      <c r="B3413" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3413" t="inlineStr">
+        <is>
+          <t>2026-09-03T20:31:13.498Z</t>
+        </is>
+      </c>
+      <c r="D3413" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3413" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3413" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3414">
+      <c r="A3414" t="inlineStr">
+        <is>
+          <t>05a1bb37-6c33-4c38-b05c-59a4e21f5c7b</t>
+        </is>
+      </c>
+      <c r="B3414" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3414" t="inlineStr">
+        <is>
+          <t>2026-09-03T20:41:30.502Z</t>
+        </is>
+      </c>
+      <c r="D3414" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3414" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3414" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3415">
+      <c r="A3415" t="inlineStr">
+        <is>
+          <t>13821701-cfd0-439a-8c00-fd84c9fb9372</t>
+        </is>
+      </c>
+      <c r="B3415" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3415" t="inlineStr">
+        <is>
+          <t>2026-09-03T23:18:51.088Z</t>
+        </is>
+      </c>
+      <c r="D3415" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3415" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3415" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3416">
+      <c r="A3416" t="inlineStr">
+        <is>
+          <t>428d493a-6e74-491a-a88a-010f0b8f529c</t>
+        </is>
+      </c>
+      <c r="B3416" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3416" t="inlineStr">
+        <is>
+          <t>2026-09-03T23:59:00.800Z</t>
+        </is>
+      </c>
+      <c r="D3416" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3416" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3416" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3416"/>
+  <dimension ref="A1:F3431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84008,6 +84008,456 @@
         </is>
       </c>
     </row>
+    <row r="3417">
+      <c r="A3417" t="inlineStr">
+        <is>
+          <t>dc178d57-a508-4276-bdb6-425cdafd266d</t>
+        </is>
+      </c>
+      <c r="B3417" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3417" t="inlineStr">
+        <is>
+          <t>2026-09-04T00:00:00.393Z</t>
+        </is>
+      </c>
+      <c r="D3417" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3417" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3417" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3418">
+      <c r="A3418" t="inlineStr">
+        <is>
+          <t>c6a56287-5bcd-4546-ba91-ff78ce75d08e</t>
+        </is>
+      </c>
+      <c r="B3418" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3418" t="inlineStr">
+        <is>
+          <t>2026-09-04T00:32:56.381Z</t>
+        </is>
+      </c>
+      <c r="D3418" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3418" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3418" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3419">
+      <c r="A3419" t="inlineStr">
+        <is>
+          <t>2b0c40bc-872a-4579-aeae-3158f7b5ca91</t>
+        </is>
+      </c>
+      <c r="B3419" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3419" t="inlineStr">
+        <is>
+          <t>2026-09-04T01:18:49.117Z</t>
+        </is>
+      </c>
+      <c r="D3419" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3419" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3419" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3420">
+      <c r="A3420" t="inlineStr">
+        <is>
+          <t>d9b91b72-8f11-4bb2-b15a-29071167a1a1</t>
+        </is>
+      </c>
+      <c r="B3420" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3420" t="inlineStr">
+        <is>
+          <t>2026-09-04T02:26:03.285Z</t>
+        </is>
+      </c>
+      <c r="D3420" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3420" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3420" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3421">
+      <c r="A3421" t="inlineStr">
+        <is>
+          <t>225685dd-4c4a-4919-928b-25a088a63e8d</t>
+        </is>
+      </c>
+      <c r="B3421" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3421" t="inlineStr">
+        <is>
+          <t>2026-09-04T03:38:21.833Z</t>
+        </is>
+      </c>
+      <c r="D3421" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3421" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3421" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3422">
+      <c r="A3422" t="inlineStr">
+        <is>
+          <t>b020e39e-f0ee-4be1-bf67-6e7067e6eeaf</t>
+        </is>
+      </c>
+      <c r="B3422" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3422" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:21:06.104Z</t>
+        </is>
+      </c>
+      <c r="D3422" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3422" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3422" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3423">
+      <c r="A3423" t="inlineStr">
+        <is>
+          <t>d00c4fc8-15db-438e-bcc9-6a0c5019cfba</t>
+        </is>
+      </c>
+      <c r="B3423" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3423" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:24:36.574Z</t>
+        </is>
+      </c>
+      <c r="D3423" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3423" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3423" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3424">
+      <c r="A3424" t="inlineStr">
+        <is>
+          <t>adcba31c-1078-407e-b7b6-dd0c86c3f76b</t>
+        </is>
+      </c>
+      <c r="B3424" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3424" t="inlineStr">
+        <is>
+          <t>2026-09-04T06:04:09.048Z</t>
+        </is>
+      </c>
+      <c r="D3424" t="n">
+        <v>546</v>
+      </c>
+      <c r="E3424" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3424" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3425">
+      <c r="A3425" t="inlineStr">
+        <is>
+          <t>59e82cb9-09bd-4fd2-b28f-3c7b2effb6d5</t>
+        </is>
+      </c>
+      <c r="B3425" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3425" t="inlineStr">
+        <is>
+          <t>2026-09-04T15:53:00.304Z</t>
+        </is>
+      </c>
+      <c r="D3425" t="n">
+        <v>502</v>
+      </c>
+      <c r="E3425" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3425" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3426">
+      <c r="A3426" t="inlineStr">
+        <is>
+          <t>8b4e4800-aee9-4caf-817e-a7fe92285b22</t>
+        </is>
+      </c>
+      <c r="B3426" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3426" t="inlineStr">
+        <is>
+          <t>2026-09-04T16:10:11.535Z</t>
+        </is>
+      </c>
+      <c r="D3426" t="n">
+        <v>502</v>
+      </c>
+      <c r="E3426" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3426" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3427">
+      <c r="A3427" t="inlineStr">
+        <is>
+          <t>d8595b7c-9380-41e4-8d45-389b65aaac8a</t>
+        </is>
+      </c>
+      <c r="B3427" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3427" t="inlineStr">
+        <is>
+          <t>2026-09-04T16:24:54.505Z</t>
+        </is>
+      </c>
+      <c r="D3427" t="n">
+        <v>515</v>
+      </c>
+      <c r="E3427" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3427" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3428">
+      <c r="A3428" t="inlineStr">
+        <is>
+          <t>618484dd-ad67-4345-8662-d94d977971c7</t>
+        </is>
+      </c>
+      <c r="B3428" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3428" t="inlineStr">
+        <is>
+          <t>2026-09-04T18:24:57.059Z</t>
+        </is>
+      </c>
+      <c r="D3428" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3428" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3428" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3429">
+      <c r="A3429" t="inlineStr">
+        <is>
+          <t>7265dc01-5be6-4842-b045-268808b10c85</t>
+        </is>
+      </c>
+      <c r="B3429" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3429" t="inlineStr">
+        <is>
+          <t>2026-09-04T19:00:28.235Z</t>
+        </is>
+      </c>
+      <c r="D3429" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3429" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3429" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3430">
+      <c r="A3430" t="inlineStr">
+        <is>
+          <t>eee4b712-2994-4557-9c7c-e26564b0dfe1</t>
+        </is>
+      </c>
+      <c r="B3430" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3430" t="inlineStr">
+        <is>
+          <t>2026-09-04T20:04:38.350Z</t>
+        </is>
+      </c>
+      <c r="D3430" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3430" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3430" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3431">
+      <c r="A3431" t="inlineStr">
+        <is>
+          <t>4c567cdc-cca4-47fe-aff2-6c0d8b9fa0a3</t>
+        </is>
+      </c>
+      <c r="B3431" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3431" t="inlineStr">
+        <is>
+          <t>2026-09-04T21:11:04.602Z</t>
+        </is>
+      </c>
+      <c r="D3431" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3431" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3431" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3431"/>
+  <dimension ref="A1:F3435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84458,6 +84458,126 @@
         </is>
       </c>
     </row>
+    <row r="3432">
+      <c r="A3432" t="inlineStr">
+        <is>
+          <t>f8e416ce-1f36-4324-8c21-f51880d9a372</t>
+        </is>
+      </c>
+      <c r="B3432" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3432" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:06:26.334Z</t>
+        </is>
+      </c>
+      <c r="D3432" t="n">
+        <v>502</v>
+      </c>
+      <c r="E3432" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3432" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3433">
+      <c r="A3433" t="inlineStr">
+        <is>
+          <t>887100f2-0761-4c63-b802-e857f40c5ebd</t>
+        </is>
+      </c>
+      <c r="B3433" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3433" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:14:47.216Z</t>
+        </is>
+      </c>
+      <c r="D3433" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3433" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3433" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3434">
+      <c r="A3434" t="inlineStr">
+        <is>
+          <t>61c04b2b-3d60-4daa-b9b5-48d43665337a</t>
+        </is>
+      </c>
+      <c r="B3434" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3434" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:18:56.870Z</t>
+        </is>
+      </c>
+      <c r="D3434" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3434" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3434" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3435">
+      <c r="A3435" t="inlineStr">
+        <is>
+          <t>425cc15e-9811-46a0-921b-3a0d639485bf</t>
+        </is>
+      </c>
+      <c r="B3435" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3435" t="inlineStr">
+        <is>
+          <t>2026-09-05T18:53:40.989Z</t>
+        </is>
+      </c>
+      <c r="D3435" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3435" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3435" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3435"/>
+  <dimension ref="A1:F3438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84578,6 +84578,96 @@
         </is>
       </c>
     </row>
+    <row r="3436">
+      <c r="A3436" t="inlineStr">
+        <is>
+          <t>3dd36242-7c56-47b9-9946-1b14e853b7c0</t>
+        </is>
+      </c>
+      <c r="B3436" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3436" t="inlineStr">
+        <is>
+          <t>2026-09-06T00:17:59.968Z</t>
+        </is>
+      </c>
+      <c r="D3436" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3436" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3436" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3437">
+      <c r="A3437" t="inlineStr">
+        <is>
+          <t>06687257-37e9-4171-a477-f252c491b6eb</t>
+        </is>
+      </c>
+      <c r="B3437" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3437" t="inlineStr">
+        <is>
+          <t>2026-09-06T02:45:01.605Z</t>
+        </is>
+      </c>
+      <c r="D3437" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3437" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3437" t="inlineStr">
+        <is>
+          <t>Arson</t>
+        </is>
+      </c>
+    </row>
+    <row r="3438">
+      <c r="A3438" t="inlineStr">
+        <is>
+          <t>7c516056-f3f9-4933-8efa-79c8a9b09335</t>
+        </is>
+      </c>
+      <c r="B3438" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3438" t="inlineStr">
+        <is>
+          <t>2026-09-06T08:27:35.782Z</t>
+        </is>
+      </c>
+      <c r="D3438" t="n">
+        <v>515</v>
+      </c>
+      <c r="E3438" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3438" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3438"/>
+  <dimension ref="A1:F3456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84668,6 +84668,546 @@
         </is>
       </c>
     </row>
+    <row r="3439">
+      <c r="A3439" t="inlineStr">
+        <is>
+          <t>083bcbec-5b70-4bba-93f6-7f44ca5c06e8</t>
+        </is>
+      </c>
+      <c r="B3439" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3439" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:56:37.704Z</t>
+        </is>
+      </c>
+      <c r="D3439" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3439" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3439" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3440">
+      <c r="A3440" t="inlineStr">
+        <is>
+          <t>1f8b3c72-96f6-437b-8541-51b24c829a3d</t>
+        </is>
+      </c>
+      <c r="B3440" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3440" t="inlineStr">
+        <is>
+          <t>2026-09-07T04:24:34.129Z</t>
+        </is>
+      </c>
+      <c r="D3440" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3440" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3440" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3441">
+      <c r="A3441" t="inlineStr">
+        <is>
+          <t>37504846-a14d-4880-9395-ed767bed8169</t>
+        </is>
+      </c>
+      <c r="B3441" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3441" t="inlineStr">
+        <is>
+          <t>2026-09-07T04:41:57.008Z</t>
+        </is>
+      </c>
+      <c r="D3441" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3441" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3441" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3442">
+      <c r="A3442" t="inlineStr">
+        <is>
+          <t>eff84a53-34f5-4b5b-bca1-f2576bae76bf</t>
+        </is>
+      </c>
+      <c r="B3442" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3442" t="inlineStr">
+        <is>
+          <t>2026-09-07T05:07:49.305Z</t>
+        </is>
+      </c>
+      <c r="D3442" t="n">
+        <v>515</v>
+      </c>
+      <c r="E3442" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3442" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3443">
+      <c r="A3443" t="inlineStr">
+        <is>
+          <t>a61385ba-d891-4970-bc80-64094e57f0b0</t>
+        </is>
+      </c>
+      <c r="B3443" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3443" t="inlineStr">
+        <is>
+          <t>2026-09-07T07:09:06.168Z</t>
+        </is>
+      </c>
+      <c r="D3443" t="n">
+        <v>515</v>
+      </c>
+      <c r="E3443" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3443" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3444">
+      <c r="A3444" t="inlineStr">
+        <is>
+          <t>3e01f68c-a072-45e7-b58b-6ee4a0c562fc</t>
+        </is>
+      </c>
+      <c r="B3444" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3444" t="inlineStr">
+        <is>
+          <t>2026-09-07T07:32:39.578Z</t>
+        </is>
+      </c>
+      <c r="D3444" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3444" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3444" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3445">
+      <c r="A3445" t="inlineStr">
+        <is>
+          <t>cd9dc89d-c666-4200-952a-d6d7ad33e94b</t>
+        </is>
+      </c>
+      <c r="B3445" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3445" t="inlineStr">
+        <is>
+          <t>2026-09-07T08:02:54.639Z</t>
+        </is>
+      </c>
+      <c r="D3445" t="n">
+        <v>515</v>
+      </c>
+      <c r="E3445" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3445" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3446">
+      <c r="A3446" t="inlineStr">
+        <is>
+          <t>1328ad7c-2385-47b8-b4af-b4115c8617d1</t>
+        </is>
+      </c>
+      <c r="B3446" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3446" t="inlineStr">
+        <is>
+          <t>2026-09-07T08:36:22.903Z</t>
+        </is>
+      </c>
+      <c r="D3446" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3446" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3446" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3447">
+      <c r="A3447" t="inlineStr">
+        <is>
+          <t>c60fda60-52c1-4c51-a6b9-c65b3e3a11de</t>
+        </is>
+      </c>
+      <c r="B3447" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3447" t="inlineStr">
+        <is>
+          <t>2026-09-07T09:04:20.194Z</t>
+        </is>
+      </c>
+      <c r="D3447" t="n">
+        <v>502</v>
+      </c>
+      <c r="E3447" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3447" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3448">
+      <c r="A3448" t="inlineStr">
+        <is>
+          <t>3ba2537f-8428-42a9-855e-fad0ea6e12e7</t>
+        </is>
+      </c>
+      <c r="B3448" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3448" t="inlineStr">
+        <is>
+          <t>2026-09-07T09:05:32.277Z</t>
+        </is>
+      </c>
+      <c r="D3448" t="n">
+        <v>515</v>
+      </c>
+      <c r="E3448" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3448" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3449">
+      <c r="A3449" t="inlineStr">
+        <is>
+          <t>99dacedd-ebd2-48b4-9742-c15a4abe45a3</t>
+        </is>
+      </c>
+      <c r="B3449" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3449" t="inlineStr">
+        <is>
+          <t>2026-09-07T09:13:03.486Z</t>
+        </is>
+      </c>
+      <c r="D3449" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3449" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3449" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3450">
+      <c r="A3450" t="inlineStr">
+        <is>
+          <t>3a89468c-10ad-4f6b-bef8-88b6bf76112b</t>
+        </is>
+      </c>
+      <c r="B3450" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3450" t="inlineStr">
+        <is>
+          <t>2026-09-07T10:23:38.784Z</t>
+        </is>
+      </c>
+      <c r="D3450" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3450" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3450" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3451">
+      <c r="A3451" t="inlineStr">
+        <is>
+          <t>d7895092-ff12-4af0-a45a-12e9156995c5</t>
+        </is>
+      </c>
+      <c r="B3451" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3451" t="inlineStr">
+        <is>
+          <t>2026-09-07T10:58:02.547Z</t>
+        </is>
+      </c>
+      <c r="D3451" t="n">
+        <v>515</v>
+      </c>
+      <c r="E3451" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3451" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3452">
+      <c r="A3452" t="inlineStr">
+        <is>
+          <t>c79b3da9-5332-4792-95b4-3f47bde04f43</t>
+        </is>
+      </c>
+      <c r="B3452" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3452" t="inlineStr">
+        <is>
+          <t>2026-09-07T11:36:04.203Z</t>
+        </is>
+      </c>
+      <c r="D3452" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3452" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3452" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3453">
+      <c r="A3453" t="inlineStr">
+        <is>
+          <t>bd53c7f5-4ed1-4daa-bb0e-59de7675e041</t>
+        </is>
+      </c>
+      <c r="B3453" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3453" t="inlineStr">
+        <is>
+          <t>2026-09-07T11:46:17.544Z</t>
+        </is>
+      </c>
+      <c r="D3453" t="n">
+        <v>502</v>
+      </c>
+      <c r="E3453" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3453" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3454">
+      <c r="A3454" t="inlineStr">
+        <is>
+          <t>b62f200f-0e05-4564-abf0-d21d7243bdf8</t>
+        </is>
+      </c>
+      <c r="B3454" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3454" t="inlineStr">
+        <is>
+          <t>2026-09-07T13:09:30.119Z</t>
+        </is>
+      </c>
+      <c r="D3454" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3454" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3454" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3455">
+      <c r="A3455" t="inlineStr">
+        <is>
+          <t>7d39ecf7-a44a-4096-b960-332b0197eb4b</t>
+        </is>
+      </c>
+      <c r="B3455" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3455" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:43:24.349Z</t>
+        </is>
+      </c>
+      <c r="D3455" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3455" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3455" t="inlineStr">
+        <is>
+          <t>Criminal Motor Vehicle Offense (incl. Road Rage/Reckless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3456">
+      <c r="A3456" t="inlineStr">
+        <is>
+          <t>a7bd31a8-e78e-4a98-a8d3-66694213935a</t>
+        </is>
+      </c>
+      <c r="B3456" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3456" t="inlineStr">
+        <is>
+          <t>2026-09-07T17:35:44.246Z</t>
+        </is>
+      </c>
+      <c r="D3456" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3456" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3456" t="inlineStr">
+        <is>
+          <t>Child Abuse/Neglect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3456"/>
+  <dimension ref="A1:F3482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85208,6 +85208,786 @@
         </is>
       </c>
     </row>
+    <row r="3457">
+      <c r="A3457" t="inlineStr">
+        <is>
+          <t>df12be47-8abc-4b8c-ac95-b96369d5f8d5</t>
+        </is>
+      </c>
+      <c r="B3457" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3457" t="inlineStr">
+        <is>
+          <t>2026-09-08T02:27:34.229Z</t>
+        </is>
+      </c>
+      <c r="D3457" t="n">
+        <v>502</v>
+      </c>
+      <c r="E3457" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3457" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3458">
+      <c r="A3458" t="inlineStr">
+        <is>
+          <t>97540f4a-8d08-4a14-89aa-37b590dabf81</t>
+        </is>
+      </c>
+      <c r="B3458" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3458" t="inlineStr">
+        <is>
+          <t>2026-09-08T03:25:40.489Z</t>
+        </is>
+      </c>
+      <c r="D3458" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3458" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3458" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3459">
+      <c r="A3459" t="inlineStr">
+        <is>
+          <t>4763cd7a-d4a6-43fa-a30c-8c183cc36ae8</t>
+        </is>
+      </c>
+      <c r="B3459" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3459" t="inlineStr">
+        <is>
+          <t>2026-09-08T03:50:44.196Z</t>
+        </is>
+      </c>
+      <c r="D3459" t="n">
+        <v>515</v>
+      </c>
+      <c r="E3459" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3459" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3460">
+      <c r="A3460" t="inlineStr">
+        <is>
+          <t>7019bc69-82c9-4335-a8e7-0cad838f161e</t>
+        </is>
+      </c>
+      <c r="B3460" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3460" t="inlineStr">
+        <is>
+          <t>2026-09-08T04:05:52.927Z</t>
+        </is>
+      </c>
+      <c r="D3460" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3460" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3460" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3461">
+      <c r="A3461" t="inlineStr">
+        <is>
+          <t>a625bf2d-accf-4da1-9a68-6c422c4e49d0</t>
+        </is>
+      </c>
+      <c r="B3461" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3461" t="inlineStr">
+        <is>
+          <t>2026-09-08T04:43:29.370Z</t>
+        </is>
+      </c>
+      <c r="D3461" t="n">
+        <v>515</v>
+      </c>
+      <c r="E3461" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3461" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3462">
+      <c r="A3462" t="inlineStr">
+        <is>
+          <t>fde9f2a3-589a-47c2-81b7-34464b19d4ef</t>
+        </is>
+      </c>
+      <c r="B3462" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3462" t="inlineStr">
+        <is>
+          <t>2026-09-08T05:18:11.096Z</t>
+        </is>
+      </c>
+      <c r="D3462" t="n">
+        <v>515</v>
+      </c>
+      <c r="E3462" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3462" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3463">
+      <c r="A3463" t="inlineStr">
+        <is>
+          <t>e1d51d82-643e-44dd-8d4e-2a6376ec017d</t>
+        </is>
+      </c>
+      <c r="B3463" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3463" t="inlineStr">
+        <is>
+          <t>2026-09-08T05:21:46.732Z</t>
+        </is>
+      </c>
+      <c r="D3463" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3463" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3463" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3464">
+      <c r="A3464" t="inlineStr">
+        <is>
+          <t>4b956915-9a5a-443c-95b4-dab81269a406</t>
+        </is>
+      </c>
+      <c r="B3464" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3464" t="inlineStr">
+        <is>
+          <t>2026-09-08T05:44:34.990Z</t>
+        </is>
+      </c>
+      <c r="D3464" t="n">
+        <v>502</v>
+      </c>
+      <c r="E3464" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3464" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3465">
+      <c r="A3465" t="inlineStr">
+        <is>
+          <t>7f22bf9e-8277-4519-9277-26c8e79ad87b</t>
+        </is>
+      </c>
+      <c r="B3465" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3465" t="inlineStr">
+        <is>
+          <t>2026-09-08T06:06:04.423Z</t>
+        </is>
+      </c>
+      <c r="D3465" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3465" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3465" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3466">
+      <c r="A3466" t="inlineStr">
+        <is>
+          <t>a2dfc06a-74fd-4e83-8e95-d020a98ec94b</t>
+        </is>
+      </c>
+      <c r="B3466" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3466" t="inlineStr">
+        <is>
+          <t>2026-09-08T07:02:19.246Z</t>
+        </is>
+      </c>
+      <c r="D3466" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3466" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3466" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3467">
+      <c r="A3467" t="inlineStr">
+        <is>
+          <t>39fceb8b-cd02-42d4-aac8-b84add1a223b</t>
+        </is>
+      </c>
+      <c r="B3467" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3467" t="inlineStr">
+        <is>
+          <t>2026-09-08T07:10:04.951Z</t>
+        </is>
+      </c>
+      <c r="D3467" t="n">
+        <v>502</v>
+      </c>
+      <c r="E3467" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3467" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3468">
+      <c r="A3468" t="inlineStr">
+        <is>
+          <t>c49c4ed7-4684-48dc-9f00-885d8d1b5629</t>
+        </is>
+      </c>
+      <c r="B3468" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3468" t="inlineStr">
+        <is>
+          <t>2026-09-08T08:07:00.887Z</t>
+        </is>
+      </c>
+      <c r="D3468" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3468" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3468" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3469">
+      <c r="A3469" t="inlineStr">
+        <is>
+          <t>8523e38a-d4a8-469b-9bff-b2c05ba090fe</t>
+        </is>
+      </c>
+      <c r="B3469" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3469" t="inlineStr">
+        <is>
+          <t>2026-09-08T09:20:41.086Z</t>
+        </is>
+      </c>
+      <c r="D3469" t="n">
+        <v>502</v>
+      </c>
+      <c r="E3469" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3469" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3470">
+      <c r="A3470" t="inlineStr">
+        <is>
+          <t>6459b501-09ca-42ef-af18-913e67a1f72f</t>
+        </is>
+      </c>
+      <c r="B3470" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3470" t="inlineStr">
+        <is>
+          <t>2026-09-08T09:46:23.283Z</t>
+        </is>
+      </c>
+      <c r="D3470" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3470" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3470" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3471">
+      <c r="A3471" t="inlineStr">
+        <is>
+          <t>1828b69d-a295-43d0-9851-81d275ceb8a4</t>
+        </is>
+      </c>
+      <c r="B3471" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3471" t="inlineStr">
+        <is>
+          <t>2026-09-08T11:00:14.999Z</t>
+        </is>
+      </c>
+      <c r="D3471" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3471" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3471" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3472">
+      <c r="A3472" t="inlineStr">
+        <is>
+          <t>0b428333-164f-4941-8d2a-710de3e8993b</t>
+        </is>
+      </c>
+      <c r="B3472" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3472" t="inlineStr">
+        <is>
+          <t>2026-09-08T12:32:45.951Z</t>
+        </is>
+      </c>
+      <c r="D3472" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3472" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3472" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3473">
+      <c r="A3473" t="inlineStr">
+        <is>
+          <t>acfef04b-6221-4f9b-a53d-623946b60ff9</t>
+        </is>
+      </c>
+      <c r="B3473" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3473" t="inlineStr">
+        <is>
+          <t>2026-09-08T16:32:47.314Z</t>
+        </is>
+      </c>
+      <c r="D3473" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3473" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3473" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3474">
+      <c r="A3474" t="inlineStr">
+        <is>
+          <t>e21b0af5-619e-4717-8f52-e619e1105588</t>
+        </is>
+      </c>
+      <c r="B3474" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3474" t="inlineStr">
+        <is>
+          <t>2026-09-08T16:39:57.158Z</t>
+        </is>
+      </c>
+      <c r="D3474" t="n">
+        <v>545</v>
+      </c>
+      <c r="E3474" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3474" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3475">
+      <c r="A3475" t="inlineStr">
+        <is>
+          <t>8b780ac9-86c7-4aa3-a0c6-32050325d175</t>
+        </is>
+      </c>
+      <c r="B3475" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3475" t="inlineStr">
+        <is>
+          <t>2026-09-08T20:54:04.629Z</t>
+        </is>
+      </c>
+      <c r="D3475" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3475" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3475" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3476">
+      <c r="A3476" t="inlineStr">
+        <is>
+          <t>777b9117-8349-4dc6-8b31-129a800622a7</t>
+        </is>
+      </c>
+      <c r="B3476" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3476" t="inlineStr">
+        <is>
+          <t>2026-09-08T20:59:23.009Z</t>
+        </is>
+      </c>
+      <c r="D3476" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3476" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3476" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3477">
+      <c r="A3477" t="inlineStr">
+        <is>
+          <t>40e01f73-5a8d-4f95-90b2-3333539ed9e7</t>
+        </is>
+      </c>
+      <c r="B3477" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3477" t="inlineStr">
+        <is>
+          <t>2026-09-08T21:26:20.167Z</t>
+        </is>
+      </c>
+      <c r="D3477" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3477" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3477" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3478">
+      <c r="A3478" t="inlineStr">
+        <is>
+          <t>2e458851-3ffe-444b-8dfe-d92b97924020</t>
+        </is>
+      </c>
+      <c r="B3478" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3478" t="inlineStr">
+        <is>
+          <t>2026-09-08T21:31:03.902Z</t>
+        </is>
+      </c>
+      <c r="D3478" t="n">
+        <v>544</v>
+      </c>
+      <c r="E3478" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3478" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3479">
+      <c r="A3479" t="inlineStr">
+        <is>
+          <t>730ab9a4-7b64-4e4c-9a7f-c0cda64da042</t>
+        </is>
+      </c>
+      <c r="B3479" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3479" t="inlineStr">
+        <is>
+          <t>2026-09-08T21:53:29.753Z</t>
+        </is>
+      </c>
+      <c r="D3479" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3479" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3479" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3480">
+      <c r="A3480" t="inlineStr">
+        <is>
+          <t>b4d875c1-514f-40f2-8727-f37eaf2b6d5e</t>
+        </is>
+      </c>
+      <c r="B3480" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3480" t="inlineStr">
+        <is>
+          <t>2026-09-08T22:03:25.390Z</t>
+        </is>
+      </c>
+      <c r="D3480" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3480" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3480" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3481">
+      <c r="A3481" t="inlineStr">
+        <is>
+          <t>ca28d381-690e-4883-a037-3440c1d9386d</t>
+        </is>
+      </c>
+      <c r="B3481" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3481" t="inlineStr">
+        <is>
+          <t>2026-09-08T23:52:00.844Z</t>
+        </is>
+      </c>
+      <c r="D3481" t="n">
+        <v>544</v>
+      </c>
+      <c r="E3481" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3481" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3482">
+      <c r="A3482" t="inlineStr">
+        <is>
+          <t>a2693a3c-a352-4d83-a07a-faddb134ba7a</t>
+        </is>
+      </c>
+      <c r="B3482" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3482" t="inlineStr">
+        <is>
+          <t>2026-09-08T23:57:32.553Z</t>
+        </is>
+      </c>
+      <c r="D3482" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3482" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3482" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3482"/>
+  <dimension ref="A1:F3504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85988,6 +85988,666 @@
         </is>
       </c>
     </row>
+    <row r="3483">
+      <c r="A3483" t="inlineStr">
+        <is>
+          <t>0eb34001-8587-488e-99a4-81127d8b1c60</t>
+        </is>
+      </c>
+      <c r="B3483" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3483" t="inlineStr">
+        <is>
+          <t>2026-09-09T00:34:06.987Z</t>
+        </is>
+      </c>
+      <c r="D3483" t="n">
+        <v>544</v>
+      </c>
+      <c r="E3483" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3483" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3484">
+      <c r="A3484" t="inlineStr">
+        <is>
+          <t>79508e94-6aea-431e-8ce3-818332108d71</t>
+        </is>
+      </c>
+      <c r="B3484" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3484" t="inlineStr">
+        <is>
+          <t>2026-09-09T00:41:01.319Z</t>
+        </is>
+      </c>
+      <c r="D3484" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3484" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3484" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3485">
+      <c r="A3485" t="inlineStr">
+        <is>
+          <t>7701f480-5ee0-45f2-82b6-009af77f814b</t>
+        </is>
+      </c>
+      <c r="B3485" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3485" t="inlineStr">
+        <is>
+          <t>2026-09-09T03:19:24.602Z</t>
+        </is>
+      </c>
+      <c r="D3485" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3485" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3485" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3486">
+      <c r="A3486" t="inlineStr">
+        <is>
+          <t>0428a57b-0655-4e9d-aadd-e04845266ea7</t>
+        </is>
+      </c>
+      <c r="B3486" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3486" t="inlineStr">
+        <is>
+          <t>2026-09-09T04:06:33.845Z</t>
+        </is>
+      </c>
+      <c r="D3486" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3486" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3486" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3487">
+      <c r="A3487" t="inlineStr">
+        <is>
+          <t>26f041ac-294e-4781-aa38-ed8e844364ef</t>
+        </is>
+      </c>
+      <c r="B3487" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3487" t="inlineStr">
+        <is>
+          <t>2026-09-09T05:33:37.581Z</t>
+        </is>
+      </c>
+      <c r="D3487" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3487" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3487" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3488">
+      <c r="A3488" t="inlineStr">
+        <is>
+          <t>abab1f5c-3c26-46ba-8e07-a4e611fcc526</t>
+        </is>
+      </c>
+      <c r="B3488" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3488" t="inlineStr">
+        <is>
+          <t>2026-09-09T07:32:13.808Z</t>
+        </is>
+      </c>
+      <c r="D3488" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3488" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3488" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3489">
+      <c r="A3489" t="inlineStr">
+        <is>
+          <t>79ba1781-0191-4953-be63-1a61426b0b63</t>
+        </is>
+      </c>
+      <c r="B3489" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3489" t="inlineStr">
+        <is>
+          <t>2026-09-09T13:46:12.355Z</t>
+        </is>
+      </c>
+      <c r="D3489" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3489" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3489" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3490">
+      <c r="A3490" t="inlineStr">
+        <is>
+          <t>d8d30508-c3e3-4648-a980-95c51e556590</t>
+        </is>
+      </c>
+      <c r="B3490" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3490" t="inlineStr">
+        <is>
+          <t>2026-09-09T14:46:07.393Z</t>
+        </is>
+      </c>
+      <c r="D3490" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3490" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3490" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3491">
+      <c r="A3491" t="inlineStr">
+        <is>
+          <t>efbf8cb1-cd78-49d9-ae72-a54103918a59</t>
+        </is>
+      </c>
+      <c r="B3491" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3491" t="inlineStr">
+        <is>
+          <t>2026-09-09T15:40:21.630Z</t>
+        </is>
+      </c>
+      <c r="D3491" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3491" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3491" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3492">
+      <c r="A3492" t="inlineStr">
+        <is>
+          <t>6ace6e23-ef72-4075-af3c-ae786163524d</t>
+        </is>
+      </c>
+      <c r="B3492" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3492" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:48:42.833Z</t>
+        </is>
+      </c>
+      <c r="D3492" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3492" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3492" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3493">
+      <c r="A3493" t="inlineStr">
+        <is>
+          <t>5145fab3-2539-47c6-b332-8670ff45737f</t>
+        </is>
+      </c>
+      <c r="B3493" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3493" t="inlineStr">
+        <is>
+          <t>2026-09-09T16:58:34.824Z</t>
+        </is>
+      </c>
+      <c r="D3493" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3493" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3493" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3494">
+      <c r="A3494" t="inlineStr">
+        <is>
+          <t>49509813-a710-42fa-bb93-6608ad0b4ef2</t>
+        </is>
+      </c>
+      <c r="B3494" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3494" t="inlineStr">
+        <is>
+          <t>2026-09-09T17:15:00.518Z</t>
+        </is>
+      </c>
+      <c r="D3494" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3494" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3494" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3495">
+      <c r="A3495" t="inlineStr">
+        <is>
+          <t>9cefac5b-9069-44ff-ae60-79c9823206b0</t>
+        </is>
+      </c>
+      <c r="B3495" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3495" t="inlineStr">
+        <is>
+          <t>2026-09-09T17:27:35.014Z</t>
+        </is>
+      </c>
+      <c r="D3495" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3495" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3495" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3496">
+      <c r="A3496" t="inlineStr">
+        <is>
+          <t>9b7c2a2a-cd4c-4d21-8f14-aa11652d3cb9</t>
+        </is>
+      </c>
+      <c r="B3496" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3496" t="inlineStr">
+        <is>
+          <t>2026-09-09T18:14:55.007Z</t>
+        </is>
+      </c>
+      <c r="D3496" t="n">
+        <v>544</v>
+      </c>
+      <c r="E3496" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3496" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3497">
+      <c r="A3497" t="inlineStr">
+        <is>
+          <t>2d1a2ce4-98a5-49d5-89a4-ab16748c3c8d</t>
+        </is>
+      </c>
+      <c r="B3497" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3497" t="inlineStr">
+        <is>
+          <t>2026-09-09T18:20:01.908Z</t>
+        </is>
+      </c>
+      <c r="D3497" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3497" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3497" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3498">
+      <c r="A3498" t="inlineStr">
+        <is>
+          <t>920ee4dd-c631-407d-8333-0610a36b4add</t>
+        </is>
+      </c>
+      <c r="B3498" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3498" t="inlineStr">
+        <is>
+          <t>2026-09-09T18:24:10.386Z</t>
+        </is>
+      </c>
+      <c r="D3498" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3498" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3498" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3499">
+      <c r="A3499" t="inlineStr">
+        <is>
+          <t>3a7bbbef-123f-4be5-acea-1d1dfc4c99a5</t>
+        </is>
+      </c>
+      <c r="B3499" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3499" t="inlineStr">
+        <is>
+          <t>2026-09-09T19:02:28.385Z</t>
+        </is>
+      </c>
+      <c r="D3499" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3499" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3499" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3500">
+      <c r="A3500" t="inlineStr">
+        <is>
+          <t>6d1bb727-e381-467a-beb1-d468f3d843c0</t>
+        </is>
+      </c>
+      <c r="B3500" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3500" t="inlineStr">
+        <is>
+          <t>2026-09-09T19:07:25.637Z</t>
+        </is>
+      </c>
+      <c r="D3500" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3500" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3500" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3501">
+      <c r="A3501" t="inlineStr">
+        <is>
+          <t>dacda8bd-e998-47a3-858c-fd80099d3bf4</t>
+        </is>
+      </c>
+      <c r="B3501" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3501" t="inlineStr">
+        <is>
+          <t>2026-09-09T19:16:42.866Z</t>
+        </is>
+      </c>
+      <c r="D3501" t="n">
+        <v>544</v>
+      </c>
+      <c r="E3501" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3501" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3502">
+      <c r="A3502" t="inlineStr">
+        <is>
+          <t>1e517e38-15a4-40f7-a944-0bbf1f8d9d2b</t>
+        </is>
+      </c>
+      <c r="B3502" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3502" t="inlineStr">
+        <is>
+          <t>2026-09-09T20:13:17.660Z</t>
+        </is>
+      </c>
+      <c r="D3502" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3502" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3502" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3503">
+      <c r="A3503" t="inlineStr">
+        <is>
+          <t>2584da4f-ed50-4f09-bbad-25f9319cf20a</t>
+        </is>
+      </c>
+      <c r="B3503" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3503" t="inlineStr">
+        <is>
+          <t>2026-09-09T22:32:59.242Z</t>
+        </is>
+      </c>
+      <c r="D3503" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3503" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3503" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3504">
+      <c r="A3504" t="inlineStr">
+        <is>
+          <t>beebbe5b-f257-4b55-83e0-8358f3cf4b56</t>
+        </is>
+      </c>
+      <c r="B3504" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3504" t="inlineStr">
+        <is>
+          <t>2026-09-09T23:25:24.160Z</t>
+        </is>
+      </c>
+      <c r="D3504" t="n">
+        <v>501</v>
+      </c>
+      <c r="E3504" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3504" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3504"/>
+  <dimension ref="A1:F3511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86648,6 +86648,216 @@
         </is>
       </c>
     </row>
+    <row r="3505">
+      <c r="A3505" t="inlineStr">
+        <is>
+          <t>67b5f9f1-aad3-4511-828b-8277aaa7de62</t>
+        </is>
+      </c>
+      <c r="B3505" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3505" t="inlineStr">
+        <is>
+          <t>2026-09-10T04:22:57.009Z</t>
+        </is>
+      </c>
+      <c r="D3505" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3505" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3505" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3506">
+      <c r="A3506" t="inlineStr">
+        <is>
+          <t>f9ec40f7-cdce-470c-9560-f612f96fd8d9</t>
+        </is>
+      </c>
+      <c r="B3506" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3506" t="inlineStr">
+        <is>
+          <t>2026-09-10T15:09:51.406Z</t>
+        </is>
+      </c>
+      <c r="D3506" t="n">
+        <v>544</v>
+      </c>
+      <c r="E3506" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3506" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3507">
+      <c r="A3507" t="inlineStr">
+        <is>
+          <t>aa4cc57d-ab96-4c20-835a-e3b1dc92975a</t>
+        </is>
+      </c>
+      <c r="B3507" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3507" t="inlineStr">
+        <is>
+          <t>2026-09-10T15:49:17.453Z</t>
+        </is>
+      </c>
+      <c r="D3507" t="n">
+        <v>514</v>
+      </c>
+      <c r="E3507" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3507" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3508">
+      <c r="A3508" t="inlineStr">
+        <is>
+          <t>3a336fdb-221a-40ba-83ae-79523b12b81b</t>
+        </is>
+      </c>
+      <c r="B3508" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3508" t="inlineStr">
+        <is>
+          <t>2026-09-10T16:03:26.769Z</t>
+        </is>
+      </c>
+      <c r="D3508" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3508" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3508" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3509">
+      <c r="A3509" t="inlineStr">
+        <is>
+          <t>a2e28aea-cab1-440c-a41b-1bc3ced221c3</t>
+        </is>
+      </c>
+      <c r="B3509" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3509" t="inlineStr">
+        <is>
+          <t>2026-09-10T21:25:22.605Z</t>
+        </is>
+      </c>
+      <c r="D3509" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3509" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3509" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3510">
+      <c r="A3510" t="inlineStr">
+        <is>
+          <t>e87ae517-13aa-4305-a232-d358b2c1b461</t>
+        </is>
+      </c>
+      <c r="B3510" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3510" t="inlineStr">
+        <is>
+          <t>2026-09-10T22:51:45.467Z</t>
+        </is>
+      </c>
+      <c r="D3510" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3510" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3510" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3511">
+      <c r="A3511" t="inlineStr">
+        <is>
+          <t>f1034de5-aa68-448d-b263-6ef7e940969d</t>
+        </is>
+      </c>
+      <c r="B3511" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3511" t="inlineStr">
+        <is>
+          <t>2026-09-10T23:05:48.458Z</t>
+        </is>
+      </c>
+      <c r="D3511" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3511" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3511" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3511"/>
+  <dimension ref="A1:F3524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86858,6 +86858,396 @@
         </is>
       </c>
     </row>
+    <row r="3512">
+      <c r="A3512" t="inlineStr">
+        <is>
+          <t>70ee28ca-3dd1-4030-bd66-53aa03962f3a</t>
+        </is>
+      </c>
+      <c r="B3512" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3512" t="inlineStr">
+        <is>
+          <t>2026-09-11T05:35:40.842Z</t>
+        </is>
+      </c>
+      <c r="D3512" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3512" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3512" t="inlineStr">
+        <is>
+          <t>Traffic Infraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3513">
+      <c r="A3513" t="inlineStr">
+        <is>
+          <t>c96c49c3-cbcc-4b31-9ba9-f011d7c69c5c</t>
+        </is>
+      </c>
+      <c r="B3513" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3513" t="inlineStr">
+        <is>
+          <t>2026-09-11T05:59:23.377Z</t>
+        </is>
+      </c>
+      <c r="D3513" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3513" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3513" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3514">
+      <c r="A3514" t="inlineStr">
+        <is>
+          <t>9de3101f-edd3-4bc5-89d0-c493ae2eac29</t>
+        </is>
+      </c>
+      <c r="B3514" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3514" t="inlineStr">
+        <is>
+          <t>2026-09-11T06:00:55.375Z</t>
+        </is>
+      </c>
+      <c r="D3514" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3514" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3514" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3515">
+      <c r="A3515" t="inlineStr">
+        <is>
+          <t>1a146ffc-07bf-42a6-9370-339cc8d22038</t>
+        </is>
+      </c>
+      <c r="B3515" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3515" t="inlineStr">
+        <is>
+          <t>2026-09-11T14:23:44.639Z</t>
+        </is>
+      </c>
+      <c r="D3515" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3515" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3515" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3516">
+      <c r="A3516" t="inlineStr">
+        <is>
+          <t>cd56cc2c-04ad-439c-ad9a-9b087270577d</t>
+        </is>
+      </c>
+      <c r="B3516" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3516" t="inlineStr">
+        <is>
+          <t>2026-09-11T16:38:49.935Z</t>
+        </is>
+      </c>
+      <c r="D3516" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3516" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3516" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3517">
+      <c r="A3517" t="inlineStr">
+        <is>
+          <t>ba4f05e4-bc7c-401b-9ac7-1294e41eeea4</t>
+        </is>
+      </c>
+      <c r="B3517" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3517" t="inlineStr">
+        <is>
+          <t>2026-09-11T19:07:56.696Z</t>
+        </is>
+      </c>
+      <c r="D3517" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3517" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3517" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3518">
+      <c r="A3518" t="inlineStr">
+        <is>
+          <t>afd987d9-339b-43f9-9f40-5c065774ed07</t>
+        </is>
+      </c>
+      <c r="B3518" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3518" t="inlineStr">
+        <is>
+          <t>2026-09-11T19:18:40.323Z</t>
+        </is>
+      </c>
+      <c r="D3518" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3518" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3518" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3519">
+      <c r="A3519" t="inlineStr">
+        <is>
+          <t>c621323b-07b1-4f36-a038-5fa03c6f3300</t>
+        </is>
+      </c>
+      <c r="B3519" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3519" t="inlineStr">
+        <is>
+          <t>2026-09-11T20:19:44.535Z</t>
+        </is>
+      </c>
+      <c r="D3519" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3519" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3519" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3520">
+      <c r="A3520" t="inlineStr">
+        <is>
+          <t>e75827c3-09a9-4da6-8f31-5bb48864c4b1</t>
+        </is>
+      </c>
+      <c r="B3520" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3520" t="inlineStr">
+        <is>
+          <t>2026-09-11T20:34:25.072Z</t>
+        </is>
+      </c>
+      <c r="D3520" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3520" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3520" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3521">
+      <c r="A3521" t="inlineStr">
+        <is>
+          <t>9a203d80-3238-4c36-8bbb-21bfe11c32f5</t>
+        </is>
+      </c>
+      <c r="B3521" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3521" t="inlineStr">
+        <is>
+          <t>2026-09-11T21:57:30.318Z</t>
+        </is>
+      </c>
+      <c r="D3521" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3521" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3521" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3522">
+      <c r="A3522" t="inlineStr">
+        <is>
+          <t>6428b3e1-6ba9-4985-8778-91b13a7a7c01</t>
+        </is>
+      </c>
+      <c r="B3522" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3522" t="inlineStr">
+        <is>
+          <t>2026-09-11T22:02:33.045Z</t>
+        </is>
+      </c>
+      <c r="D3522" t="n">
+        <v>500</v>
+      </c>
+      <c r="E3522" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3522" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3523">
+      <c r="A3523" t="inlineStr">
+        <is>
+          <t>b9c74120-8568-447c-9990-3b4b339b14b0</t>
+        </is>
+      </c>
+      <c r="B3523" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3523" t="inlineStr">
+        <is>
+          <t>2026-09-11T22:23:19.514Z</t>
+        </is>
+      </c>
+      <c r="D3523" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3523" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3523" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3524">
+      <c r="A3524" t="inlineStr">
+        <is>
+          <t>95ae4a0b-98c3-4d92-8a4c-4f108fa6276c</t>
+        </is>
+      </c>
+      <c r="B3524" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3524" t="inlineStr">
+        <is>
+          <t>2026-09-11T23:42:55.432Z</t>
+        </is>
+      </c>
+      <c r="D3524" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3524" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3524" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
